--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="Re3ac7168c1514a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="R9b02cd81242b4146"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="R575ce20036944503"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="Ra398a99c23ba48ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -164,6 +164,9 @@
     <x:t xml:space="preserve">震碎斬</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">{"m":12,"mPer":0.5}</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">斬擊會向前飛出 {m} 米距離，命中路徑上的敵人</x:t>
   </x:si>
   <x:si>
@@ -341,19 +344,13 @@
     <x:t xml:space="preserve">血毒刃</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">{"dotPct":25,"dotPctPer":3,"dotSec":4,"dotGap":0.5}</x:t>
+    <x:t xml:space="preserve">{"dotPct":25,"dotPctPer":3,"dotSec":6,"dotGap":0.5}</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">敵人流血的同時也會中毒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的毒屬性傷害，持續 {dotSec} 秒</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">毒霧感染</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">{"chance":10,"chancePer":1}</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">血毒刃的毒在每次作用時，有 {chance}% 機率傳染給附近的 1 個敵人</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">死亡屍爆</x:t>
@@ -590,7 +587,7 @@
     </x:font>
     <x:font>
       <x:sz val="9"/>
-      <x:name val="新細明體"/>
+      <x:name val="細明體"/>
     </x:font>
   </x:fonts>
   <x:fills count="33">
@@ -642,12 +639,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.59999"/>
+        <x:fgColor theme="4" tint="0.79995"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4" tint="0.59996"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -662,12 +659,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.59999"/>
+        <x:fgColor theme="5" tint="0.79995"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="5" tint="0.59996"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -682,12 +679,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.59999"/>
+        <x:fgColor theme="6" tint="0.79995"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="6" tint="0.59996"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -702,12 +699,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.59999"/>
+        <x:fgColor theme="7" tint="0.79995"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="7" tint="0.59996"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -722,12 +719,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.59999"/>
+        <x:fgColor theme="8" tint="0.79995"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="8" tint="0.59996"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -742,12 +739,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.79998"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.59999"/>
+        <x:fgColor theme="9" tint="0.79995"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="9" tint="0.59996"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -765,7 +762,7 @@
     </x:border>
     <x:border>
       <x:bottom style="thick">
-        <x:color theme="4" tint="0.49998"/>
+        <x:color theme="4" tint="0.49995"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -971,8 +968,11 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1218,6 +1218,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="16.5"/>
   <x:cols>
+    <x:col min="8" max="8" width="33.5" customWidth="1"/>
     <x:col min="10" max="10" width="12.625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1698,8 +1699,8 @@
       <x:c r="G14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H14" t="str">
-        <x:v>{"m":12,"mPer":0.5}</x:v>
+      <x:c r="H14" t="s">
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I14">
         <x:v>3000000</x:v>
@@ -1708,7 +1709,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K14" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1731,10 +1732,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G15" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H15" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I15">
         <x:v>5000000</x:v>
@@ -1743,18 +1744,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K15" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D16">
         <x:v>4</x:v>
@@ -1766,10 +1767,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H16" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I16">
         <x:v>100000</x:v>
@@ -1778,18 +1779,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K16" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D17">
         <x:v>4</x:v>
@@ -1801,10 +1802,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G17" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H17" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I17">
         <x:v>200000</x:v>
@@ -1813,18 +1814,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K17" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D18">
         <x:v>4</x:v>
@@ -1836,10 +1837,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G18" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H18" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I18">
         <x:v>400000</x:v>
@@ -1848,18 +1849,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K18" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D19">
         <x:v>4</x:v>
@@ -1871,7 +1872,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="G19" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H19" t="s">
         <x:v>23</x:v>
@@ -1883,18 +1884,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K19" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D20">
         <x:v>4</x:v>
@@ -1906,10 +1907,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G20" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H20" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I20">
         <x:v>1500000</x:v>
@@ -1918,18 +1919,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K20" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D21">
         <x:v>4</x:v>
@@ -1941,10 +1942,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H21" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I21">
         <x:v>3000000</x:v>
@@ -1953,18 +1954,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K21" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D22">
         <x:v>4</x:v>
@@ -1976,10 +1977,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G22" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H22" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I22">
         <x:v>5000000</x:v>
@@ -1988,18 +1989,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K22" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D23">
         <x:v>6</x:v>
@@ -2011,10 +2012,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H23" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="I23">
         <x:v>100000</x:v>
@@ -2023,18 +2024,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K23" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D24">
         <x:v>6</x:v>
@@ -2046,10 +2047,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G24" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H24" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I24">
         <x:v>200000</x:v>
@@ -2058,18 +2059,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K24" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D25">
         <x:v>6</x:v>
@@ -2081,10 +2082,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G25" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H25" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="I25">
         <x:v>400000</x:v>
@@ -2098,13 +2099,13 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D26">
         <x:v>6</x:v>
@@ -2119,7 +2120,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H26" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I26">
         <x:v>800000</x:v>
@@ -2128,18 +2129,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K26" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D27">
         <x:v>6</x:v>
@@ -2151,10 +2152,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G27" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H27" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I27">
         <x:v>1500000</x:v>
@@ -2163,18 +2164,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K27" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D28">
         <x:v>6</x:v>
@@ -2186,10 +2187,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G28" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H28" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I28">
         <x:v>3000000</x:v>
@@ -2198,18 +2199,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K28" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D29">
         <x:v>6</x:v>
@@ -2221,10 +2222,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G29" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H29" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I29">
         <x:v>5000000</x:v>
@@ -2233,18 +2234,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K29" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D30">
         <x:v>8</x:v>
@@ -2256,10 +2257,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H30" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I30">
         <x:v>100000</x:v>
@@ -2268,18 +2269,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K30" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D31">
         <x:v>8</x:v>
@@ -2291,10 +2292,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G31" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H31" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="I31">
         <x:v>200000</x:v>
@@ -2303,18 +2304,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K31" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D32">
         <x:v>8</x:v>
@@ -2326,10 +2327,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G32" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="H32" t="s">
         <x:v>107</x:v>
+      </x:c>
+      <x:c r="H32" s="1" t="s">
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I32">
         <x:v>400000</x:v>
@@ -2338,18 +2339,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K32" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D33">
         <x:v>8</x:v>
@@ -2361,10 +2362,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="G33" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H33" t="s">
         <x:v>110</x:v>
+      </x:c>
+      <x:c r="H33" s="1" t="s">
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I33">
         <x:v>800000</x:v>
@@ -2373,18 +2374,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K33" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D34">
         <x:v>8</x:v>
@@ -2396,10 +2397,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G34" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H34" t="s">
         <x:v>113</x:v>
+      </x:c>
+      <x:c r="H34" s="1" t="str">
+        <x:v>{"chance":30,"chancePer":2,"count":1}</x:v>
       </x:c>
       <x:c r="I34">
         <x:v>1500000</x:v>
@@ -2407,19 +2408,19 @@
       <x:c r="J34">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="K34" t="s">
-        <x:v>114</x:v>
+      <x:c r="K34" s="1" t="str">
+        <x:v>血毒刃的毒在每次作用時，有 {chance}% 機率傳染給附近的 {count} 個敵人</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D35">
         <x:v>8</x:v>
@@ -2431,10 +2432,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G35" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H35" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="H35" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="I35">
         <x:v>3000000</x:v>
@@ -2443,18 +2444,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K35" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D36">
         <x:v>8</x:v>
@@ -2466,10 +2467,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G36" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H36" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="H36" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="I36">
         <x:v>5000000</x:v>
@@ -2478,18 +2479,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K36" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B37" t="s">
+      <x:c r="C37" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C37" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="D37">
         <x:v>10</x:v>
@@ -2501,10 +2502,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G37" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H37" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I37">
         <x:v>100000</x:v>
@@ -2513,18 +2514,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K37" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B38" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B38" t="s">
+      <x:c r="C38" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C38" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="D38">
         <x:v>10</x:v>
@@ -2536,10 +2537,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G38" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H38" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I38">
         <x:v>200000</x:v>
@@ -2548,18 +2549,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K38" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B39" t="s">
+      <x:c r="C39" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C39" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="D39">
         <x:v>10</x:v>
@@ -2571,10 +2572,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G39" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H39" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="H39" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="I39">
         <x:v>400000</x:v>
@@ -2583,18 +2584,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K39" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B40" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B40" t="s">
+      <x:c r="C40" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C40" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="D40">
         <x:v>10</x:v>
@@ -2606,10 +2607,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="G40" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H40" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="H40" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="I40">
         <x:v>800000</x:v>
@@ -2618,18 +2619,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K40" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B41" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B41" t="s">
+      <x:c r="C41" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C41" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="D41">
         <x:v>10</x:v>
@@ -2641,10 +2642,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G41" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H41" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="H41" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="I41">
         <x:v>1500000</x:v>
@@ -2653,18 +2654,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K41" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B42" t="s">
+      <x:c r="C42" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C42" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="D42">
         <x:v>10</x:v>
@@ -2676,10 +2677,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G42" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H42" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="H42" t="s">
-        <x:v>138</x:v>
       </x:c>
       <x:c r="I42">
         <x:v>3000000</x:v>
@@ -2688,18 +2689,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K42" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B43" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B43" t="s">
+      <x:c r="C43" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C43" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="D43">
         <x:v>10</x:v>
@@ -2711,10 +2712,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G43" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H43" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="H43" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="I43">
         <x:v>5000000</x:v>
@@ -2723,7 +2724,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="K43" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2742,12 +2743,12 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2757,22 +2758,22 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2782,42 +2783,42 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2827,7 +2828,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -2544,7 +2544,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":0.5,"addPer":0.1,"kill":0.1}</t>
+          <t xml:space="preserve">{"add":0.5,"addPer":0.1,"kill":0.1,"killMax":5}</t>
         </is>
       </c>
       <c r="I54">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間基礎連擊數 +{add}，且每擊殺 1 個敵人再 +{kill}（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">狂怒期間基礎連擊數 +{add}，且每擊殺 1 個敵人再 +{kill}（累計上限 +{killMax}；不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":0.5,"pct":1,"pctPer":0.1}</t>
+          <t xml:space="preserve">{"sec":0.5,"pct":1,"pctPer":0.1,"maxSec":20}</t>
         </is>
       </c>
       <c r="I57">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間每擊殺 1 個敵人，持續時間延長 {sec} 秒；且生命值每減少 1%，傷害額外 +{pct}%（乘算，無限疊加）</t>
+          <t xml:space="preserve">狂怒期間每擊殺 1 個敵人，持續時間延長 {sec} 秒（累計上限 {maxSec} 秒）；且生命值每減少 1%，傷害額外 +{pct}%（乘算，無限疊加）</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">同時朝前後兩個方向各使出 {times} 次迴旋斬，且物理傷害額外 +{pct}%</t>
+          <t xml:space="preserve">同時朝前後左右四個方向各使出 {times} 次迴旋斬，且物理傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1433E7F6-32F5-4FA3-818E-BC37EE380E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA30700-1182-4F24-9F2D-21CD4D927F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,9 +68,6 @@
     <t>🗡️</t>
   </si>
   <si>
-    <t>{"pct":300,"pctPer":30,"count":2}</t>
-  </si>
-  <si>
     <t>對前方敵人造成 {count} 次 {pct}% 物理傷害</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
   </si>
   <si>
     <t>傷害強化</t>
-  </si>
-  <si>
-    <t>{"pct":30,"pctPer":10}</t>
   </si>
   <si>
     <t>進一步強化突刺傷害，額外 +{pct}% 物理傷害（與第 1 階累加）</t>
@@ -652,6 +646,14 @@
   </si>
   <si>
     <t>{"m":5,"mPer":0.5}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pct":150,"pctPer":15,"count":2}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pct":20,"pctPer":3}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1679,7 +1681,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -1694,7 +1696,7 @@
         <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>208</v>
       </c>
       <c r="J2">
         <v>100000</v>
@@ -1703,7 +1705,7 @@
         <v>1.5</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -1717,7 +1719,7 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -1729,10 +1731,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
       </c>
       <c r="J3">
         <v>200000</v>
@@ -1741,7 +1743,7 @@
         <v>1.5</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -1755,7 +1757,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -1767,10 +1769,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="J4">
         <v>400000</v>
@@ -1779,7 +1781,7 @@
         <v>1.5</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -1793,7 +1795,7 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1805,10 +1807,10 @@
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J5">
         <v>800000</v>
@@ -1817,7 +1819,7 @@
         <v>1.5</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -1831,7 +1833,7 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1843,10 +1845,10 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J6">
         <v>1500000</v>
@@ -1855,7 +1857,7 @@
         <v>1.5</v>
       </c>
       <c r="L6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -1869,7 +1871,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1881,10 +1883,10 @@
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J7">
         <v>3000000</v>
@@ -1893,7 +1895,7 @@
         <v>1.5</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -1907,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1919,10 +1921,10 @@
         <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J8">
         <v>5000000</v>
@@ -1931,18 +1933,18 @@
         <v>1.5</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
         <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1954,10 +1956,10 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" t="s">
         <v>35</v>
-      </c>
-      <c r="I9" t="s">
-        <v>37</v>
       </c>
       <c r="J9">
         <v>100000</v>
@@ -1966,18 +1968,18 @@
         <v>1.5</v>
       </c>
       <c r="L9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
         <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -1989,10 +1991,10 @@
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J10">
         <v>200000</v>
@@ -2001,18 +2003,18 @@
         <v>1.5</v>
       </c>
       <c r="L10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
         <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -2024,10 +2026,10 @@
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J11">
         <v>400000</v>
@@ -2036,18 +2038,18 @@
         <v>1.5</v>
       </c>
       <c r="L11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
         <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -2059,10 +2061,10 @@
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J12">
         <v>800000</v>
@@ -2071,18 +2073,18 @@
         <v>1.5</v>
       </c>
       <c r="L12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -2094,10 +2096,10 @@
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J13">
         <v>1500000</v>
@@ -2106,18 +2108,18 @@
         <v>1.5</v>
       </c>
       <c r="L13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
         <v>34</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
       </c>
       <c r="E14">
         <v>8</v>
@@ -2129,10 +2131,10 @@
         <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J14">
         <v>3000000</v>
@@ -2141,18 +2143,18 @@
         <v>1.5</v>
       </c>
       <c r="L14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
       </c>
       <c r="E15">
         <v>8</v>
@@ -2164,10 +2166,10 @@
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J15">
         <v>5000000</v>
@@ -2176,18 +2178,18 @@
         <v>1.5</v>
       </c>
       <c r="L15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" t="s">
         <v>56</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>58</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -2199,10 +2201,10 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" t="s">
         <v>57</v>
-      </c>
-      <c r="I16" t="s">
-        <v>59</v>
       </c>
       <c r="J16">
         <v>100000</v>
@@ -2211,18 +2213,18 @@
         <v>1.5</v>
       </c>
       <c r="L16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" t="s">
         <v>56</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>58</v>
       </c>
       <c r="E17">
         <v>4</v>
@@ -2234,10 +2236,10 @@
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J17">
         <v>200000</v>
@@ -2246,18 +2248,18 @@
         <v>1.5</v>
       </c>
       <c r="L17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
         <v>56</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -2269,10 +2271,10 @@
         <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J18">
         <v>400000</v>
@@ -2281,18 +2283,18 @@
         <v>1.5</v>
       </c>
       <c r="L18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
         <v>56</v>
-      </c>
-      <c r="B19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -2304,10 +2306,10 @@
         <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J19">
         <v>800000</v>
@@ -2316,18 +2318,18 @@
         <v>1.5</v>
       </c>
       <c r="L19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
         <v>56</v>
-      </c>
-      <c r="B20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
       </c>
       <c r="E20">
         <v>4</v>
@@ -2339,10 +2341,10 @@
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J20">
         <v>1500000</v>
@@ -2351,18 +2353,18 @@
         <v>1.5</v>
       </c>
       <c r="L20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="s">
         <v>56</v>
-      </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
       </c>
       <c r="E21">
         <v>4</v>
@@ -2374,10 +2376,10 @@
         <v>6</v>
       </c>
       <c r="H21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J21">
         <v>3000000</v>
@@ -2386,18 +2388,18 @@
         <v>1.5</v>
       </c>
       <c r="L21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" t="s">
         <v>56</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
       </c>
       <c r="E22">
         <v>4</v>
@@ -2409,10 +2411,10 @@
         <v>7</v>
       </c>
       <c r="H22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J22">
         <v>5000000</v>
@@ -2421,18 +2423,18 @@
         <v>1.5</v>
       </c>
       <c r="L22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
         <v>79</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>81</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -2444,10 +2446,10 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
+        <v>78</v>
+      </c>
+      <c r="I23" t="s">
         <v>80</v>
-      </c>
-      <c r="I23" t="s">
-        <v>82</v>
       </c>
       <c r="J23">
         <v>100000</v>
@@ -2456,18 +2458,18 @@
         <v>1.5</v>
       </c>
       <c r="L23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
         <v>79</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>81</v>
       </c>
       <c r="E24">
         <v>6</v>
@@ -2479,10 +2481,10 @@
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J24">
         <v>200000</v>
@@ -2491,18 +2493,18 @@
         <v>1.5</v>
       </c>
       <c r="L24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
         <v>79</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -2514,10 +2516,10 @@
         <v>3</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J25">
         <v>400000</v>
@@ -2526,18 +2528,18 @@
         <v>1.5</v>
       </c>
       <c r="L25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
         <v>79</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>81</v>
       </c>
       <c r="E26">
         <v>6</v>
@@ -2549,10 +2551,10 @@
         <v>4</v>
       </c>
       <c r="H26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J26">
         <v>800000</v>
@@ -2561,18 +2563,18 @@
         <v>1.5</v>
       </c>
       <c r="L26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
         <v>79</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
       </c>
       <c r="E27">
         <v>6</v>
@@ -2584,10 +2586,10 @@
         <v>5</v>
       </c>
       <c r="H27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J27">
         <v>1500000</v>
@@ -2596,18 +2598,18 @@
         <v>1.5</v>
       </c>
       <c r="L27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" t="s">
         <v>79</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -2619,10 +2621,10 @@
         <v>6</v>
       </c>
       <c r="H28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J28">
         <v>3000000</v>
@@ -2631,18 +2633,18 @@
         <v>1.5</v>
       </c>
       <c r="L28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
         <v>79</v>
-      </c>
-      <c r="B29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" t="s">
-        <v>81</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -2654,10 +2656,10 @@
         <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J29">
         <v>5000000</v>
@@ -2666,18 +2668,18 @@
         <v>1.5</v>
       </c>
       <c r="L29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" t="s">
         <v>100</v>
-      </c>
-      <c r="B30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>102</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -2689,10 +2691,10 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
+        <v>99</v>
+      </c>
+      <c r="I30" t="s">
         <v>101</v>
-      </c>
-      <c r="I30" t="s">
-        <v>103</v>
       </c>
       <c r="J30">
         <v>100000</v>
@@ -2701,18 +2703,18 @@
         <v>1.5</v>
       </c>
       <c r="L30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" t="s">
         <v>100</v>
-      </c>
-      <c r="B31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" t="s">
-        <v>102</v>
       </c>
       <c r="E31">
         <v>8</v>
@@ -2724,10 +2726,10 @@
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I31" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J31">
         <v>200000</v>
@@ -2736,18 +2738,18 @@
         <v>1.5</v>
       </c>
       <c r="L31" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" t="s">
         <v>100</v>
-      </c>
-      <c r="B32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" t="s">
-        <v>102</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -2759,10 +2761,10 @@
         <v>3</v>
       </c>
       <c r="H32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J32">
         <v>400000</v>
@@ -2771,18 +2773,18 @@
         <v>1.5</v>
       </c>
       <c r="L32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" t="s">
         <v>100</v>
-      </c>
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" t="s">
-        <v>102</v>
       </c>
       <c r="E33">
         <v>8</v>
@@ -2794,10 +2796,10 @@
         <v>4</v>
       </c>
       <c r="H33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J33">
         <v>800000</v>
@@ -2806,18 +2808,18 @@
         <v>1.5</v>
       </c>
       <c r="L33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" t="s">
         <v>100</v>
-      </c>
-      <c r="B34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
       </c>
       <c r="E34">
         <v>8</v>
@@ -2829,10 +2831,10 @@
         <v>5</v>
       </c>
       <c r="H34" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I34" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J34">
         <v>1500000</v>
@@ -2841,18 +2843,18 @@
         <v>1.5</v>
       </c>
       <c r="L34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" t="s">
         <v>100</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
       </c>
       <c r="E35">
         <v>8</v>
@@ -2864,10 +2866,10 @@
         <v>6</v>
       </c>
       <c r="H35" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I35" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J35">
         <v>3000000</v>
@@ -2876,18 +2878,18 @@
         <v>1.5</v>
       </c>
       <c r="L35" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" t="s">
         <v>100</v>
-      </c>
-      <c r="B36" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" t="s">
-        <v>102</v>
       </c>
       <c r="E36">
         <v>8</v>
@@ -2899,10 +2901,10 @@
         <v>7</v>
       </c>
       <c r="H36" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J36">
         <v>5000000</v>
@@ -2911,18 +2913,18 @@
         <v>1.5</v>
       </c>
       <c r="L36" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" t="s">
         <v>123</v>
-      </c>
-      <c r="B37" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" t="s">
-        <v>125</v>
       </c>
       <c r="E37">
         <v>10</v>
@@ -2934,10 +2936,10 @@
         <v>1</v>
       </c>
       <c r="H37" t="s">
+        <v>122</v>
+      </c>
+      <c r="I37" t="s">
         <v>124</v>
-      </c>
-      <c r="I37" t="s">
-        <v>126</v>
       </c>
       <c r="J37">
         <v>100000</v>
@@ -2946,18 +2948,18 @@
         <v>1.5</v>
       </c>
       <c r="L37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" t="s">
         <v>123</v>
-      </c>
-      <c r="B38" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" t="s">
-        <v>125</v>
       </c>
       <c r="E38">
         <v>10</v>
@@ -2969,10 +2971,10 @@
         <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I38" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J38">
         <v>200000</v>
@@ -2981,18 +2983,18 @@
         <v>1.5</v>
       </c>
       <c r="L38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" t="s">
         <v>123</v>
-      </c>
-      <c r="B39" t="s">
-        <v>124</v>
-      </c>
-      <c r="C39" t="s">
-        <v>125</v>
       </c>
       <c r="E39">
         <v>10</v>
@@ -3004,10 +3006,10 @@
         <v>3</v>
       </c>
       <c r="H39" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I39" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J39">
         <v>400000</v>
@@ -3016,18 +3018,18 @@
         <v>1.5</v>
       </c>
       <c r="L39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s">
+        <v>122</v>
+      </c>
+      <c r="C40" t="s">
         <v>123</v>
-      </c>
-      <c r="B40" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" t="s">
-        <v>125</v>
       </c>
       <c r="E40">
         <v>10</v>
@@ -3039,10 +3041,10 @@
         <v>4</v>
       </c>
       <c r="H40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J40">
         <v>800000</v>
@@ -3051,18 +3053,18 @@
         <v>1.5</v>
       </c>
       <c r="L40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" t="s">
         <v>123</v>
-      </c>
-      <c r="B41" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41" t="s">
-        <v>125</v>
       </c>
       <c r="E41">
         <v>10</v>
@@ -3074,10 +3076,10 @@
         <v>5</v>
       </c>
       <c r="H41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I41" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J41">
         <v>1500000</v>
@@ -3086,18 +3088,18 @@
         <v>1.5</v>
       </c>
       <c r="L41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" t="s">
         <v>123</v>
-      </c>
-      <c r="B42" t="s">
-        <v>124</v>
-      </c>
-      <c r="C42" t="s">
-        <v>125</v>
       </c>
       <c r="E42">
         <v>10</v>
@@ -3109,10 +3111,10 @@
         <v>6</v>
       </c>
       <c r="H42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I42" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J42">
         <v>3000000</v>
@@ -3121,18 +3123,18 @@
         <v>1.5</v>
       </c>
       <c r="L42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" t="s">
         <v>123</v>
-      </c>
-      <c r="B43" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" t="s">
-        <v>125</v>
       </c>
       <c r="E43">
         <v>10</v>
@@ -3144,10 +3146,10 @@
         <v>7</v>
       </c>
       <c r="H43" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I43" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J43">
         <v>5000000</v>
@@ -3156,18 +3158,18 @@
         <v>1.5</v>
       </c>
       <c r="L43" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" t="s">
         <v>145</v>
-      </c>
-      <c r="B44" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" t="s">
-        <v>147</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3179,10 +3181,10 @@
         <v>1</v>
       </c>
       <c r="H44" t="s">
+        <v>144</v>
+      </c>
+      <c r="I44" t="s">
         <v>146</v>
-      </c>
-      <c r="I44" t="s">
-        <v>148</v>
       </c>
       <c r="J44">
         <v>100000</v>
@@ -3191,18 +3193,18 @@
         <v>1.5</v>
       </c>
       <c r="L44" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>143</v>
+      </c>
+      <c r="B45" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" t="s">
         <v>145</v>
-      </c>
-      <c r="B45" t="s">
-        <v>146</v>
-      </c>
-      <c r="C45" t="s">
-        <v>147</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3214,10 +3216,10 @@
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I45" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J45">
         <v>200000</v>
@@ -3226,18 +3228,18 @@
         <v>1.5</v>
       </c>
       <c r="L45" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>143</v>
+      </c>
+      <c r="B46" t="s">
+        <v>144</v>
+      </c>
+      <c r="C46" t="s">
         <v>145</v>
-      </c>
-      <c r="B46" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" t="s">
-        <v>147</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3249,10 +3251,10 @@
         <v>3</v>
       </c>
       <c r="H46" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I46" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J46">
         <v>400000</v>
@@ -3261,18 +3263,18 @@
         <v>1.5</v>
       </c>
       <c r="L46" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" t="s">
         <v>145</v>
-      </c>
-      <c r="B47" t="s">
-        <v>146</v>
-      </c>
-      <c r="C47" t="s">
-        <v>147</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3284,10 +3286,10 @@
         <v>4</v>
       </c>
       <c r="H47" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I47" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J47">
         <v>800000</v>
@@ -3296,18 +3298,18 @@
         <v>1.5</v>
       </c>
       <c r="L47" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>143</v>
+      </c>
+      <c r="B48" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" t="s">
         <v>145</v>
-      </c>
-      <c r="B48" t="s">
-        <v>146</v>
-      </c>
-      <c r="C48" t="s">
-        <v>147</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3319,10 +3321,10 @@
         <v>5</v>
       </c>
       <c r="H48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I48" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J48">
         <v>1500000</v>
@@ -3331,18 +3333,18 @@
         <v>1.5</v>
       </c>
       <c r="L48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>143</v>
+      </c>
+      <c r="B49" t="s">
+        <v>144</v>
+      </c>
+      <c r="C49" t="s">
         <v>145</v>
-      </c>
-      <c r="B49" t="s">
-        <v>146</v>
-      </c>
-      <c r="C49" t="s">
-        <v>147</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3354,10 +3356,10 @@
         <v>6</v>
       </c>
       <c r="H49" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I49" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J49">
         <v>3000000</v>
@@ -3366,18 +3368,18 @@
         <v>1.5</v>
       </c>
       <c r="L49" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>143</v>
+      </c>
+      <c r="B50" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" t="s">
         <v>145</v>
-      </c>
-      <c r="B50" t="s">
-        <v>146</v>
-      </c>
-      <c r="C50" t="s">
-        <v>147</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3389,10 +3391,10 @@
         <v>7</v>
       </c>
       <c r="H50" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I50" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J50">
         <v>5000000</v>
@@ -3401,18 +3403,18 @@
         <v>1.5</v>
       </c>
       <c r="L50" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" t="s">
         <v>168</v>
-      </c>
-      <c r="B51" t="s">
-        <v>169</v>
-      </c>
-      <c r="C51" t="s">
-        <v>170</v>
       </c>
       <c r="E51">
         <v>60</v>
@@ -3424,10 +3426,10 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
+        <v>167</v>
+      </c>
+      <c r="I51" t="s">
         <v>169</v>
-      </c>
-      <c r="I51" t="s">
-        <v>171</v>
       </c>
       <c r="J51">
         <v>100000</v>
@@ -3436,18 +3438,18 @@
         <v>1.5</v>
       </c>
       <c r="L51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" t="s">
         <v>168</v>
-      </c>
-      <c r="B52" t="s">
-        <v>169</v>
-      </c>
-      <c r="C52" t="s">
-        <v>170</v>
       </c>
       <c r="E52">
         <v>60</v>
@@ -3459,10 +3461,10 @@
         <v>2</v>
       </c>
       <c r="H52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I52" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J52">
         <v>200000</v>
@@ -3471,18 +3473,18 @@
         <v>1.5</v>
       </c>
       <c r="L52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" t="s">
         <v>168</v>
-      </c>
-      <c r="B53" t="s">
-        <v>169</v>
-      </c>
-      <c r="C53" t="s">
-        <v>170</v>
       </c>
       <c r="E53">
         <v>60</v>
@@ -3494,10 +3496,10 @@
         <v>3</v>
       </c>
       <c r="H53" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I53" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J53">
         <v>400000</v>
@@ -3506,18 +3508,18 @@
         <v>1.5</v>
       </c>
       <c r="L53" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" t="s">
         <v>168</v>
-      </c>
-      <c r="B54" t="s">
-        <v>169</v>
-      </c>
-      <c r="C54" t="s">
-        <v>170</v>
       </c>
       <c r="E54">
         <v>60</v>
@@ -3529,10 +3531,10 @@
         <v>4</v>
       </c>
       <c r="H54" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I54" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J54">
         <v>800000</v>
@@ -3541,18 +3543,18 @@
         <v>1.5</v>
       </c>
       <c r="L54" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>166</v>
+      </c>
+      <c r="B55" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" t="s">
         <v>168</v>
-      </c>
-      <c r="B55" t="s">
-        <v>169</v>
-      </c>
-      <c r="C55" t="s">
-        <v>170</v>
       </c>
       <c r="E55">
         <v>60</v>
@@ -3564,10 +3566,10 @@
         <v>5</v>
       </c>
       <c r="H55" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I55" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J55">
         <v>1500000</v>
@@ -3576,18 +3578,18 @@
         <v>1.5</v>
       </c>
       <c r="L55" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" t="s">
         <v>168</v>
-      </c>
-      <c r="B56" t="s">
-        <v>169</v>
-      </c>
-      <c r="C56" t="s">
-        <v>170</v>
       </c>
       <c r="E56">
         <v>60</v>
@@ -3599,10 +3601,10 @@
         <v>6</v>
       </c>
       <c r="H56" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I56" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J56">
         <v>3000000</v>
@@ -3611,18 +3613,18 @@
         <v>1.5</v>
       </c>
       <c r="L56" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" t="s">
+        <v>167</v>
+      </c>
+      <c r="C57" t="s">
         <v>168</v>
-      </c>
-      <c r="B57" t="s">
-        <v>169</v>
-      </c>
-      <c r="C57" t="s">
-        <v>170</v>
       </c>
       <c r="E57">
         <v>60</v>
@@ -3634,10 +3636,10 @@
         <v>7</v>
       </c>
       <c r="H57" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I57" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J57">
         <v>5000000</v>
@@ -3646,7 +3648,7 @@
         <v>1.5</v>
       </c>
       <c r="L57" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -3667,12 +3669,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
@@ -3682,12 +3684,12 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
@@ -3697,22 +3699,22 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
@@ -3722,52 +3724,52 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
@@ -3777,7 +3779,7 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20992853-24D2-4EDB-BD32-02358E8F51C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46927382-DAF8-4E9E-B161-A652B74A9B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -651,10 +651,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{"chance":20,"chancePer":2,"pct":40,"pctPer":4,"m":80,"count":1}</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>暴風亂舞</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -676,6 +672,10 @@
   </si>
   <si>
     <t>{"pct":50,"pctPer":5,"times":3,"timesPer":0}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"chance":20,"chancePer":2,"pct":40,"pctPer":4,"m":20,"count":1}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1876,7 +1876,7 @@
         <v>41</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J10">
         <v>200000</v>
@@ -1911,7 +1911,7 @@
         <v>21</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J11">
         <v>400000</v>
@@ -2051,7 +2051,7 @@
         <v>53</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J15">
         <v>5000000</v>
@@ -2786,7 +2786,7 @@
         <v>113</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J36">
         <v>5000000</v>
@@ -3028,7 +3028,7 @@
         <v>7</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I43" t="s">
         <v>134</v>
@@ -3206,7 +3206,7 @@
         <v>150</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J48">
         <v>1500000</v>
@@ -3276,7 +3276,7 @@
         <v>155</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J50">
         <v>5000000</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -3548,6 +3548,440 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="G72">
+        <v>26</v>
+      </c>
+      <c r="H72">
+        <v>50</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":120,"pctPer":12,"count":2,"sec":4,"m":8,"rps":1,"castM":8}</t>
+        </is>
+      </c>
+      <c r="L72">
+        <v>100000</v>
+      </c>
+      <c r="M72">
+        <v>1.5</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">召喚 {count} 團火狩環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 火屬性傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="G73">
+        <v>26</v>
+      </c>
+      <c r="H73">
+        <v>50</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">強化火狩</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+        </is>
+      </c>
+      <c r="L73">
+        <v>200000</v>
+      </c>
+      <c r="M73">
+        <v>1.5</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩的體積與環繞範圍同步擴大 {pct}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="G74">
+        <v>26</v>
+      </c>
+      <c r="H74">
+        <v>50</v>
+      </c>
+      <c r="I74">
+        <v>3</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伴生火狩</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"m":1}</t>
+        </is>
+      </c>
+      <c r="L74">
+        <v>400000</v>
+      </c>
+      <c r="M74">
+        <v>1.5</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩命中時有 {chance}% 機率在其後方 {m} 米處伴生一團火狩（每團只能伴生一次，伴生出的不再伴生）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="G75">
+        <v>26</v>
+      </c>
+      <c r="H75">
+        <v>50</v>
+      </c>
+      <c r="I75">
+        <v>4</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三重火狩</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":3,"pct":150,"pctPer":15,"sec":4}</t>
+        </is>
+      </c>
+      <c r="L75">
+        <v>800000</v>
+      </c>
+      <c r="M75">
+        <v>1.5</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改為召喚 {count} 團火狩，每團造成 {pct}% 火屬性傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="G76">
+        <v>26</v>
+      </c>
+      <c r="H76">
+        <v>50</v>
+      </c>
+      <c r="I76">
+        <v>5</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">極速火狩</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
+        </is>
+      </c>
+      <c r="L76">
+        <v>1500000</v>
+      </c>
+      <c r="M76">
+        <v>1.5</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩的旋轉速度 +{pct}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="G77">
+        <v>26</v>
+      </c>
+      <c r="H77">
+        <v>50</v>
+      </c>
+      <c r="I77">
+        <v>6</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">再生</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"sec":0.4,"secPer":0.04}</t>
+        </is>
+      </c>
+      <c r="L77">
+        <v>3000000</v>
+      </c>
+      <c r="M77">
+        <v>1.5</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩每擊殺 1 個敵人，全部火狩的持續時間延長 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="G78">
+        <v>26</v>
+      </c>
+      <c r="H78">
+        <v>50</v>
+      </c>
+      <c r="I78">
+        <v>7</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狩神之舞</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rings":2,"pct":200,"pctPer":20,"sec":6,"m":6}</t>
+        </is>
+      </c>
+      <c r="L78">
+        <v>5000000</v>
+      </c>
+      <c r="M78">
+        <v>1.5</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改為一次施放 {rings} 道火狩（外圈距內圈 {m} 米、兩道旋轉方向相反），每團造成 {pct}% 火屬性傷害、出現時自帶伴生，持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3620,160 +4054,174 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">傷害類型 / 傷害屬性</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環繞型技能（火狩）以此欄描述單一環繞體的體積（例如 3*3），半徑取長寬較大者的一半；</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">傷害類型：phys＝物理（吃物攻與物穿）、magic＝魔法（吃魔攻與魔穿）；留白＝phys；</t>
+          <t xml:space="preserve">傷害類型 / 傷害屬性</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">傷害屬性：fire/ice/lightning/poison/light/dark/earth，本體傷害整段歸屬該屬性（吃元素抗性與屬性傷害提升）；留白＝無屬性；</t>
+          <t xml:space="preserve">傷害類型：phys＝物理（吃物攻與物穿）、magic＝魔法（吃魔攻與魔穿）；留白＝phys；</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t xml:space="preserve">傷害屬性：fire/ice/lightning/poison/light/dark/earth，本體傷害整段歸屬該屬性（吃元素抗性與屬性傷害提升）；留白＝無屬性；</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t xml:space="preserve">兩欄都只需填在階數=1 那一列（整個群組共用）；</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冷卻時間 / 施法消耗</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">冷卻時間 / 施法消耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">整個群組共用（同群組是同一個技能）；只需填在階數=1 那一列，其餘列僅供對照；</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果參數(JSON)</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">各階的數值參數。命名慣例：&lt;鍵&gt;＝Lv.1 基準值、&lt;鍵&gt;Per＝每級增量，值＝基準＋增量×(等級-1)；</t>
+          <t xml:space="preserve">效果參數(JSON)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">常用鍵：pct＝傷害/效果百分比、chance＝機率%、add＝追加次數/目標數（小數部分以機率觸發）、</t>
+          <t xml:space="preserve">各階的數值參數。命名慣例：&lt;鍵&gt;＝Lv.1 基準值、&lt;鍵&gt;Per＝每級增量，值＝基準＋增量×(等級-1)；</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　count＝目標/次數、m＝距離（米，近戰攻擊距離=5米換算）、sec＝秒數、deg＝角度、</t>
+          <t xml:space="preserve">常用鍵：pct＝傷害/效果百分比、chance＝機率%、add＝追加次數/目標數（小數部分以機率觸發）、</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　dotPct＝每跳傷害%（占技能傷害）、dotSec＝持續秒數、dotGap＝作用間隔秒、</t>
+          <t xml:space="preserve">　　　　count＝目標/次數、m＝距離（米，近戰攻擊距離=5米換算）、sec＝秒數、deg＝角度、</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　gapPct＝間隔縮短%、times＝連擊次數、max＝連鎖上限/疊層上限、cr/cd＝爆擊率/爆擊傷害%、hits＝段數、</t>
+          <t xml:space="preserve">　　　　dotPct＝每跳傷害%（占技能傷害）、dotSec＝持續秒數、dotGap＝作用間隔秒、</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　mult＝倍率%（反擊·招架：格擋減傷值×此倍率）、def＝防禦降低%（破甲）、</t>
+          <t xml:space="preserve">　　　　gapPct＝間隔縮短%、times＝連擊次數、max＝連鎖上限/疊層上限、cr/cd＝爆擊率/爆擊傷害%、hits＝段數、</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　self＝自身損血%（血飲術反噬，占最大生命）、kill＝每擊殺追加量（狂化連殺連擊數）、</t>
+          <t xml:space="preserve">　　　　mult＝倍率%（反擊·招架：格擋減傷值×此倍率）、def＝防禦降低%（破甲）、</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　castM＝施法距離（米，決定這個技能站多遠可以開始施放；留白＝近戰 5 米，</t>
+          <t xml:space="preserve">　　　　self＝自身損血%（血飲術反噬，占最大生命）、kill＝每擊殺追加量（狂化連殺連擊數）、</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　高階可覆寫低階，例如殞石術把射程由 30 改成 20）、</t>
+          <t xml:space="preserve">　　　　castM＝施法距離（米，決定這個技能站多遠可以開始施放；留白＝近戰 5 米，</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　len/wid＝矩形場域的長與寬（米，火牆）、respawn＝場域消失後可再召喚的次數；</t>
+          <t xml:space="preserve">　　　　　　　　高階可覆寫低階，例如殞石術把射程由 30 改成 20）、</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">注意：鍵名是程式接線，不能自創或改名；只調數字即可；</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+          <t xml:space="preserve">　　　　len/wid＝矩形場域的長與寬（米，火牆）、respawn＝場域消失後可再召喚的次數；</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　rps＝每秒旋轉圈數、rings＝環繞場域的道數（火狩第 2 道在更外圈且反向旋轉）；</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t xml:space="preserve">注意：鍵名是程式接線，不能自創或改名；只調數字即可；</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t xml:space="preserve">升級金幣基數 / 升級金幣倍率</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">升到下一級費用＝基數 × 倍率^目前等級（取整）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t xml:space="preserve">升到下一級費用＝基數 × 倍率^目前等級（取整）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t xml:space="preserve">效果說明模板</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t xml:space="preserve">遊戲內顯示的說明文字；{鍵} 會代入目前等級的計算值（鍵名同「效果參數(JSON)」）。</t>
         </is>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB7FDA2-19D9-45C5-81C9-AB4874C944E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F32E80-032C-470D-B732-2625A498B716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -798,9 +798,6 @@
     <t>三重火狩</t>
   </si>
   <si>
-    <t>{"count":3,"pct":150,"pctPer":15,"sec":4}</t>
-  </si>
-  <si>
     <t>極速火狩</t>
   </si>
   <si>
@@ -822,9 +819,6 @@
     <t>狩神之舞</t>
   </si>
   <si>
-    <t>{"rings":2,"pct":200,"pctPer":20,"sec":6,"m":6}</t>
-  </si>
-  <si>
     <t>用途：技能群組唯一識別碼（裝載欄鍵為 sg:&lt;群組ID&gt;、存檔等級以此為鍵）；</t>
   </si>
   <si>
@@ -916,9 +910,6 @@
   </si>
   <si>
     <t>遊戲內顯示的說明文字；{鍵} 會代入目前等級的計算值（鍵名同「效果參數(JSON)」）。</t>
-  </si>
-  <si>
-    <t>{"pct":120,"pctPer":12,"count":2,"sec":4,"m":8,"rps":0.455,"castM":8}</t>
   </si>
   <si>
     <t>{"count":3,"hits":8,"pct":100,"pctPer":10,"len":18,"wid":6,"respawn":1}</t>
@@ -962,6 +953,18 @@
   </si>
   <si>
     <t>{"pct":300,"pctPer":30,"count":3,"m":15,"castM":20}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pct":100,"pctPer":10,"count":2,"sec":4,"m":8,"rps":0.455,"castM":8}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"count":3,"pct":120,"pctPer":12,"sec":4}</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rings":2,"pct":150,"pctPer":15,"sec":6,"m":6}</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -4037,7 +4040,7 @@
         <v>1.5</v>
       </c>
       <c r="O58" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -4081,7 +4084,7 @@
         <v>1.5</v>
       </c>
       <c r="O59" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -4257,7 +4260,7 @@
         <v>1.5</v>
       </c>
       <c r="O63" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -4292,7 +4295,7 @@
         <v>227</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M64">
         <v>5000000</v>
@@ -4301,7 +4304,7 @@
         <v>1.5</v>
       </c>
       <c r="O64" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -4345,7 +4348,7 @@
         <v>1.5</v>
       </c>
       <c r="O65" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
@@ -4377,7 +4380,7 @@
         <v>29</v>
       </c>
       <c r="K66" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="L66" t="s">
         <v>122</v>
@@ -4433,7 +4436,7 @@
         <v>1.5</v>
       </c>
       <c r="O67" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
@@ -4477,7 +4480,7 @@
         <v>1.5</v>
       </c>
       <c r="O68" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
@@ -4600,7 +4603,7 @@
         <v>242</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="M71">
         <v>5000000</v>
@@ -4609,7 +4612,7 @@
         <v>1.5</v>
       </c>
       <c r="O71" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
@@ -4646,8 +4649,8 @@
       <c r="K72" t="s">
         <v>244</v>
       </c>
-      <c r="L72" t="s">
-        <v>294</v>
+      <c r="L72" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="M72">
         <v>100000</v>
@@ -4656,7 +4659,7 @@
         <v>1.5</v>
       </c>
       <c r="O72" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
@@ -4787,8 +4790,8 @@
       <c r="K75" t="s">
         <v>253</v>
       </c>
-      <c r="L75" t="s">
-        <v>254</v>
+      <c r="L75" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="M75">
         <v>800000</v>
@@ -4797,7 +4800,7 @@
         <v>1.5</v>
       </c>
       <c r="O75" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
@@ -4832,10 +4835,10 @@
         <v>83</v>
       </c>
       <c r="K76" t="s">
+        <v>254</v>
+      </c>
+      <c r="L76" t="s">
         <v>255</v>
-      </c>
-      <c r="L76" t="s">
-        <v>256</v>
       </c>
       <c r="M76">
         <v>1500000</v>
@@ -4844,7 +4847,7 @@
         <v>1.5</v>
       </c>
       <c r="O76" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
@@ -4879,10 +4882,10 @@
         <v>87</v>
       </c>
       <c r="K77" t="s">
+        <v>257</v>
+      </c>
+      <c r="L77" t="s">
         <v>258</v>
-      </c>
-      <c r="L77" t="s">
-        <v>259</v>
       </c>
       <c r="M77">
         <v>3000000</v>
@@ -4891,7 +4894,7 @@
         <v>1.5</v>
       </c>
       <c r="O77" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
@@ -4926,10 +4929,10 @@
         <v>109</v>
       </c>
       <c r="K78" t="s">
-        <v>261</v>
-      </c>
-      <c r="L78" t="s">
-        <v>262</v>
+        <v>260</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="M78">
         <v>5000000</v>
@@ -4938,7 +4941,7 @@
         <v>1.5</v>
       </c>
       <c r="O78" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -4960,12 +4963,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -4975,12 +4978,12 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -4990,47 +4993,47 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -5040,62 +5043,62 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -5105,27 +5108,27 @@
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
@@ -5135,7 +5138,7 @@
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5709,6 +5709,1343 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連鎖閃電</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚡</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G100">
+        <v>18</v>
+      </c>
+      <c r="H100">
+        <v>40</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|300</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連鎖閃電</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":4,"m":30,"castM":30}</t>
+        </is>
+      </c>
+      <c r="M100">
+        <v>100000</v>
+      </c>
+      <c r="N100">
+        <v>1.5</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">丟出一道閃電鏈（射程 {castM} 米），在最多 {count} 個目標間彈射（每段彈射範圍 {m} 米），每擊造成 {pct}% 雷電傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連鎖閃電</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚡</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G101">
+        <v>18</v>
+      </c>
+      <c r="H101">
+        <v>40</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|350</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">強化閃電</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
+        </is>
+      </c>
+      <c r="M101">
+        <v>200000</v>
+      </c>
+      <c r="N101">
+        <v>1.5</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">強化閃電威力，閃電鏈傷害進一步 +{pct}% 雷電傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連鎖閃電</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚡</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G102">
+        <v>18</v>
+      </c>
+      <c r="H102">
+        <v>40</v>
+      </c>
+      <c r="I102">
+        <v>3</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|400</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷鳴術</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M102">
+        <v>400000</v>
+      </c>
+      <c r="N102">
+        <v>1.5</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被閃電鏈擊中的敵人額外再受到 {add} 次雷電傷害（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連鎖閃電</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚡</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G103">
+        <v>18</v>
+      </c>
+      <c r="H103">
+        <v>40</v>
+      </c>
+      <c r="I103">
+        <v>4</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|450</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">強化連鎖</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
+        </is>
+      </c>
+      <c r="M103">
+        <v>800000</v>
+      </c>
+      <c r="N103">
+        <v>1.5</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">閃電鏈的彈射數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連鎖閃電</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚡</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G104">
+        <v>18</v>
+      </c>
+      <c r="H104">
+        <v>40</v>
+      </c>
+      <c r="I104">
+        <v>5</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|500</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電殛擴散</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5,"count":1,"m":6}</t>
+        </is>
+      </c>
+      <c r="M104">
+        <v>1500000</v>
+      </c>
+      <c r="N104">
+        <v>1.5</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">閃電鏈每次彈射時，額外對 {m} 米內的 {count} 個敵人造成閃電鏈 {pct}% 的雷電傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連鎖閃電</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚡</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G105">
+        <v>18</v>
+      </c>
+      <c r="H105">
+        <v>40</v>
+      </c>
+      <c r="I105">
+        <v>6</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|550</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷幻身</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
+        </is>
+      </c>
+      <c r="M105">
+        <v>3000000</v>
+      </c>
+      <c r="N105">
+        <v>1.5</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">閃電鏈傷害額外 +{pct}% 雷電傷害；沒有其它彈射目標時可用自身當中繼點繼續彈射（彈到自身不消耗彈射數）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連鎖閃電</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚡</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G106">
+        <v>18</v>
+      </c>
+      <c r="H106">
+        <v>40</v>
+      </c>
+      <c r="I106">
+        <v>7</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|600</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷電暴風</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":3,"add":1,"addPer":0.1,"pct":100,"pctPer":10}</t>
+        </is>
+      </c>
+      <c r="M106">
+        <v>5000000</v>
+      </c>
+      <c r="N106">
+        <v>1.5</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同時發射 {count} 道閃電鏈，彈射數額外 +{add} 次，且閃電傷害額外 +{pct}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷術</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌩️</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G107">
+        <v>14</v>
+      </c>
+      <c r="H107">
+        <v>40</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|350</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷術</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"count":2,"gap":0.2,"castM":30}</t>
+        </is>
+      </c>
+      <c r="M107">
+        <v>100000</v>
+      </c>
+      <c r="N107">
+        <v>1.5</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對 {castM} 米內的 {count} 個目標降下落雷（每道間隔 {gap} 秒），每道造成 {pct}% 雷電傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷術</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌩️</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G108">
+        <v>14</v>
+      </c>
+      <c r="H108">
+        <v>40</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|400</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷連鎖</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M108">
+        <v>200000</v>
+      </c>
+      <c r="N108">
+        <v>1.5</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊目標額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷術</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌩️</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G109">
+        <v>14</v>
+      </c>
+      <c r="H109">
+        <v>40</v>
+      </c>
+      <c r="I109">
+        <v>3</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|450</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雙重落雷</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M109">
+        <v>400000</v>
+      </c>
+      <c r="N109">
+        <v>1.5</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對每個目標的攻擊次數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷術</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌩️</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G110">
+        <v>14</v>
+      </c>
+      <c r="H110">
+        <v>40</v>
+      </c>
+      <c r="I110">
+        <v>4</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|500</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">閃電增幅</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
+        </is>
+      </c>
+      <c r="M110">
+        <v>800000</v>
+      </c>
+      <c r="N110">
+        <v>1.5</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進一步強化落雷傷害，額外 +{pct}% 雷電傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷術</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌩️</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G111">
+        <v>14</v>
+      </c>
+      <c r="H111">
+        <v>40</v>
+      </c>
+      <c r="I111">
+        <v>5</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|550</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷電脈衝</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"sec":1.5,"secPer":0.15,"count":2,"m":6}</t>
+        </is>
+      </c>
+      <c r="M111">
+        <v>1500000</v>
+      </c>
+      <c r="N111">
+        <v>1.5</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷落地時產生衝擊波，震暈目標本身與 {m} 米內共 {count} 個敵人 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷術</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌩️</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G112">
+        <v>14</v>
+      </c>
+      <c r="H112">
+        <v>40</v>
+      </c>
+      <c r="I112">
+        <v>6</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|600</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迅雷重生</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"max":5}</t>
+        </is>
+      </c>
+      <c r="M112">
+        <v>3000000</v>
+      </c>
+      <c r="N112">
+        <v>1.5</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每道落雷結束後有 {chance}% 機率再產生 1 道落雷（同一次施放最多再生 {max} 道）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷術</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌩️</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G113">
+        <v>14</v>
+      </c>
+      <c r="H113">
+        <v>40</v>
+      </c>
+      <c r="I113">
+        <v>7</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|650</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">殛道落雷</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"mult":2,"pct":30,"pctPer":3}</t>
+        </is>
+      </c>
+      <c r="M113">
+        <v>5000000</v>
+      </c>
+      <c r="N113">
+        <v>1.5</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷的攻擊次數與目標數量 ×{mult}，且暈眩中的敵人受到落雷傷害額外 +{pct}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G114">
+        <v>20</v>
+      </c>
+      <c r="H114">
+        <v>40</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|400</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"gap":0.35,"sec":2,"m":3,"speed":6,"castM":30}</t>
+        </is>
+      </c>
+      <c r="M114">
+        <v>100000</v>
+      </c>
+      <c r="N114">
+        <v>1.5</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G115">
+        <v>20</v>
+      </c>
+      <c r="H115">
+        <v>40</v>
+      </c>
+      <c r="I115">
+        <v>2</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|450</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">擴增雷球</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+        </is>
+      </c>
+      <c r="M115">
+        <v>200000</v>
+      </c>
+      <c r="N115">
+        <v>1.5</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球的體積擴大 {pct}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G116">
+        <v>20</v>
+      </c>
+      <c r="H116">
+        <v>40</v>
+      </c>
+      <c r="I116">
+        <v>3</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|500</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多重雷球</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M116">
+        <v>400000</v>
+      </c>
+      <c r="N116">
+        <v>1.5</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球數量額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G117">
+        <v>20</v>
+      </c>
+      <c r="H117">
+        <v>40</v>
+      </c>
+      <c r="I117">
+        <v>4</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|550</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環體電球</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":2,"pct":100,"pctPer":10,"sec":6,"m":8,"rps":0.7}</t>
+        </is>
+      </c>
+      <c r="M117">
+        <v>800000</v>
+      </c>
+      <c r="N117">
+        <v>1.5</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外召喚 {count} 個電球環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G118">
+        <v>20</v>
+      </c>
+      <c r="H118">
+        <v>40</v>
+      </c>
+      <c r="I118">
+        <v>5</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|600</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">強化雷球</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+        </is>
+      </c>
+      <c r="M118">
+        <v>1500000</v>
+      </c>
+      <c r="N118">
+        <v>1.5</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所有雷球與電球的雷電傷害額外 +{pct}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G119">
+        <v>20</v>
+      </c>
+      <c r="H119">
+        <v>40</v>
+      </c>
+      <c r="I119">
+        <v>6</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|650</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伴生雷球</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"sec":2}</t>
+        </is>
+      </c>
+      <c r="M119">
+        <v>3000000</v>
+      </c>
+      <c r="N119">
+        <v>1.5</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環體電球命中時有 {chance}% 機率在該處生成一個靜止雷球，持續 {sec} 秒（每次作用只判定一次機率）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="G120">
+        <v>20</v>
+      </c>
+      <c r="H120">
+        <v>40</v>
+      </c>
+      <c r="I120">
+        <v>7</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|700</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷殞天落</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":2,"pct":300,"pctPer":30,"m":15,"sec":3}</t>
+        </is>
+      </c>
+      <c r="M120">
+        <v>5000000</v>
+      </c>
+      <c r="N120">
+        <v>1.5</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外召喚 {count} 個巨大雷球從天而降，各對 {m} 米內的敵人造成 {pct}% 雷電傷害，並以衝擊波擊暈 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="Rf5a5b5dd81e64d87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="R5f335da67a524c03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="Rff54f1164d5c489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="Rd4cac0cf47654aa9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9456,10 +9456,8 @@
           <x:t xml:space="preserve">虛空斬</x:t>
         </x:is>
       </x:c>
-      <x:c r="L155" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">{"pct":400,"pctPer":40,"count":2,"sec":6,"m":6,"growM":2,"bodyM":6,"rps":1}</x:t>
-        </x:is>
+      <x:c r="L155" t="str">
+        <x:v>{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</x:v>
       </x:c>
       <x:c r="M155">
         <x:v>5000000</x:v>
@@ -9467,10 +9465,8 @@
       <x:c r="N155">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="O155" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、每秒繞行 {rps} 圈（第 2 道反向），對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</x:t>
-        </x:is>
+      <x:c r="O155" t="str">
+        <x:v>額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</x:v>
       </x:c>
     </x:row>
     <x:row r="156">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="R544c40cbc5bb4851"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="R90ea295067cb446e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="R57f51da49ea74d15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="R87fdb8391e454d75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -870,10 +870,8 @@
           <x:t xml:space="preserve">迴旋斬</x:t>
         </x:is>
       </x:c>
-      <x:c r="L12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">{"pct":200,"pctPer":20,"count":6}</x:t>
-        </x:is>
+      <x:c r="L12" t="str">
+        <x:v>{"pct":200,"pctPer":20}</x:v>
       </x:c>
       <x:c r="M12">
         <x:v>100000</x:v>
@@ -881,10 +879,8 @@
       <x:c r="N12">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="O12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">對前方 {count} 個敵人造成 1 次 {pct}% 物理傷害</x:t>
-        </x:is>
+      <x:c r="O12" t="str">
+        <x:v>對範圍內的所有敵人造成 1 次 {pct}% 物理傷害</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -922,10 +918,8 @@
           <x:t xml:space="preserve">強化斬</x:t>
         </x:is>
       </x:c>
-      <x:c r="L13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">{"add":1,"addPer":0.25}</x:t>
-        </x:is>
+      <x:c r="L13" t="str">
+        <x:v>{"range":15,"rangePer":1.5}</x:v>
       </x:c>
       <x:c r="M13">
         <x:v>200000</x:v>
@@ -933,10 +927,8 @@
       <x:c r="N13">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="O13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">斬擊的敵人數量額外 +{add} 個（不足 1 個的部分以機率觸發）</x:t>
-        </x:is>
+      <x:c r="O13" t="str">
+        <x:v>斬擊範圍擴大 {range}%（每級 +1.5% 範圍）</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1177,10 +1169,8 @@
           <x:t xml:space="preserve">0|250</x:t>
         </x:is>
       </x:c>
-      <x:c r="K18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">迴身雙連斬</x:t>
-        </x:is>
+      <x:c r="K18" t="str">
+        <x:v>迴身四方斬</x:v>
       </x:c>
       <x:c r="L18" t="inlineStr">
         <x:is>
@@ -1193,10 +1183,8 @@
       <x:c r="N18">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="O18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">同時朝前後左右四個方向各使出 {times} 次迴旋斬，且物理傷害額外 +{pct}%</x:t>
-        </x:is>
+      <x:c r="O18" t="str">
+        <x:v>同時朝前後左右四個方向各使出 {times} 次斬擊，且傷害額外 +{pct}%（每級 +5% 傷害；與原有傷害乘法計算）</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1227,10 +1215,8 @@
       <x:c r="N19">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="O19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">【迴身雙連斬】的攻擊次數 +{times} 次，且物理傷害再額外 +{pct}%</x:t>
-        </x:is>
+      <x:c r="O19" t="str">
+        <x:v>【迴身四方斬】的攻擊次數 +{times} 次，且物理傷害再額外 +{pct}%</x:v>
       </x:c>
       <x:c r="P19" t="inlineStr">
         <x:is>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -2419,156 +2419,117 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">dualdance</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雙刀亂舞</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚔️</t>
-        </is>
-      </c>
-      <c r="G49">
-        <v>10</v>
+          <t xml:space="preserve">bloodblade</t>
+        </is>
       </c>
       <c r="H49">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="I49">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|250</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙刀亂舞</t>
+          <t xml:space="preserve">殺神領域</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":300,"pctPer":25,"count":2}</t>
+          <t xml:space="preserve">{"pct":2,"pctPer":0.2,"healPct":2,"healPctPer":0.2,"m":24,"dur":6,"maxStacks":100}</t>
         </is>
       </c>
       <c r="M49">
-        <v>100000</v>
+        <v>10000000</v>
       </c>
       <c r="N49">
         <v>1.5</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve">對附近 {count} 個敵人各造成 1 次 {pct}% 物理傷害（只有 1 個敵人時全部打向同一目標）</t>
+          <t xml:space="preserve">永久展開 {m} 米的殺神領域：領域內的敵人死亡時堆疊【殺神】，每層使你造成的傷害 +{pct}%，同時回復 {healPct}% 最大生命；最多 {maxStacks} 層，持續 {dur} 秒</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slayerDomain</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">dualdance</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雙刀亂舞</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚔️</t>
-        </is>
-      </c>
-      <c r="G50">
-        <v>10</v>
+          <t xml:space="preserve">bloodblade</t>
+        </is>
       </c>
       <c r="H50">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I50">
-        <v>2</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|300</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">疾風亂舞</t>
+          <t xml:space="preserve">萬毒血霧</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"m":24,"gap":0.5,"dur":6,"maxStacks":10}</t>
         </is>
       </c>
       <c r="M50">
-        <v>200000</v>
+        <v>10000000</v>
       </c>
       <c r="N50">
         <v>1.5</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外攻擊附近 {add} 個敵人（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">永久展開 {m} 米的萬毒領域：領域內的敵人每 {gap} 秒受到 {pct}% 中毒傷害，該中毒持續 {dur} 秒且可堆疊至 {maxStacks} 層</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">venomDomain</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">dualdance</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">雙刀亂舞</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚔️</t>
-        </is>
-      </c>
-      <c r="G51">
+          <t xml:space="preserve">bloodblade</t>
+        </is>
+      </c>
+      <c r="H51">
+        <v>300</v>
+      </c>
+      <c r="I51">
         <v>10</v>
       </c>
-      <c r="H51">
-        <v>60</v>
-      </c>
-      <c r="I51">
-        <v>3</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|350</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化雙刀</t>
+          <t xml:space="preserve">崩解</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":6}</t>
         </is>
       </c>
       <c r="M51">
-        <v>400000</v>
+        <v>10000000</v>
       </c>
       <c r="N51">
         <v>1.5</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化雙刀傷害，額外 +{pct}% 物理傷害</t>
+          <t xml:space="preserve">中毒與流血不再有持續時間，塗上的當下就結算完整傷害；結算後爆炸，對周圍 {m} 米內的敵人造成該效果 {pct}% 的傷害</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">disintegrate</t>
         </is>
       </c>
     </row>
@@ -2592,35 +2553,35 @@
         <v>10</v>
       </c>
       <c r="H52">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="I52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|400</t>
+          <t xml:space="preserve">0|250</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂暴之舞</t>
+          <t xml:space="preserve">雙刀亂舞</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"cr":100,"crPer":10,"add":1,"addPer":0.1,"sec":6}</t>
+          <t xml:space="preserve">{"pct":300,"pctPer":25,"count":2}</t>
         </is>
       </c>
       <c r="M52">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="N52">
         <v>1.5</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">讓你的暴擊率 +{cr}%、連擊數 +{add}，持續 {sec} 秒</t>
+          <t xml:space="preserve">對附近 {count} 個敵人各造成 1 次 {pct}% 物理傷害（只有 1 個敵人時全部打向同一目標）</t>
         </is>
       </c>
     </row>
@@ -2644,35 +2605,35 @@
         <v>10</v>
       </c>
       <c r="H53">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|450</t>
+          <t xml:space="preserve">0|300</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">鐵血之舞</t>
+          <t xml:space="preserve">疾風亂舞</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":3.5,"pctPer":0.35,"sec":3,"gap":0.35,"m":5}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
         </is>
       </c>
       <c r="M53">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="N53">
         <v>1.5</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放雙刀亂舞時使你以及附近 {m} 米內的所有敵人流血：每 {gap} 秒造成最大生命值 {pct}% 傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">額外攻擊附近 {add} 個敵人（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
     </row>
@@ -2696,35 +2657,35 @@
         <v>10</v>
       </c>
       <c r="H54">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|500</t>
+          <t xml:space="preserve">0|350</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血狂化</t>
+          <t xml:space="preserve">強化雙刀</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":0.25,"pctPer":0.025,"sec":6}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":5}</t>
         </is>
       </c>
       <c r="M54">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="N54">
         <v>1.5</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放雙刀亂舞後 {sec} 秒內，生命值或護盾每減少 1%，獲得 {pct}% 技能傷害提升</t>
+          <t xml:space="preserve">進一步強化雙刀傷害，額外 +{pct}% 物理傷害</t>
         </is>
       </c>
     </row>
@@ -2748,347 +2709,308 @@
         <v>10</v>
       </c>
       <c r="H55">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="I55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|550</t>
+          <t xml:space="preserve">0|400</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風亂舞</t>
+          <t xml:space="preserve">狂暴之舞</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":3,"secPer":0.3,"gap":0.35}</t>
+          <t xml:space="preserve">{"cr":100,"crPer":10,"add":1,"addPer":0.1,"sec":6}</t>
         </is>
       </c>
       <c r="M55">
-        <v>5000000</v>
+        <v>800000</v>
       </c>
       <c r="N55">
         <v>1.5</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve">化身暴風在敵人間穿梭 {sec} 秒：每 {gap} 秒自動施放 1 次雙刀亂舞；期間無法普攻但可施放技能</t>
+          <t xml:space="preserve">讓你的暴擊率 +{cr}%、連擊數 +{add}，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">counter</t>
+          <t xml:space="preserve">dualdance</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">反擊</t>
+          <t xml:space="preserve">雙刀亂舞</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">🛡️</t>
+          <t xml:space="preserve">⚔️</t>
         </is>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H56">
+        <v>100</v>
+      </c>
+      <c r="I56">
         <v>5</v>
       </c>
-      <c r="I56">
-        <v>1</v>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|300</t>
+          <t xml:space="preserve">0|450</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">反擊</t>
+          <t xml:space="preserve">鐵血之舞</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":35,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":3.5,"pctPer":0.35,"sec":3,"gap":0.35,"m":5}</t>
         </is>
       </c>
       <c r="M56">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="N56">
         <v>1.5</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve">被動：受到傷害時有 {chance}% 機率對攻擊者反擊，造成 {pct}% 普攻傷害</t>
+          <t xml:space="preserve">施放雙刀亂舞時使你以及附近 {m} 米內的所有敵人流血：每 {gap} 秒造成最大生命值 {pct}% 傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">counter</t>
+          <t xml:space="preserve">dualdance</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">反擊</t>
+          <t xml:space="preserve">雙刀亂舞</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">🛡️</t>
+          <t xml:space="preserve">⚔️</t>
         </is>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H57">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|350</t>
+          <t xml:space="preserve">0|500</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">招架</t>
+          <t xml:space="preserve">嗜血狂化</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"mult":300,"multPer":30}</t>
+          <t xml:space="preserve">{"pct":0.25,"pctPer":0.025,"sec":6}</t>
         </is>
       </c>
       <c r="M57">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="N57">
         <v>1.5</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋時必定對敵人反擊，造成「格擋減傷值 × {mult}%」的普攻傷害</t>
+          <t xml:space="preserve">施放雙刀亂舞後 {sec} 秒內，生命值或護盾每減少 1%，獲得 {pct}% 技能傷害提升</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">counter</t>
+          <t xml:space="preserve">dualdance</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">反擊</t>
+          <t xml:space="preserve">雙刀亂舞</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">🛡️</t>
+          <t xml:space="preserve">⚔️</t>
         </is>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H58">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="I58">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|400</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化反擊</t>
+          <t xml:space="preserve">暴風亂舞</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":5}</t>
+          <t xml:space="preserve">{"sec":3,"secPer":0.3,"gap":0.35}</t>
         </is>
       </c>
       <c r="M58">
-        <v>400000</v>
+        <v>5000000</v>
       </c>
       <c r="N58">
         <v>1.5</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步提升反擊傷害，額外 +{pct}% 反擊普攻傷害</t>
+          <t xml:space="preserve">化身暴風在敵人間穿梭 {sec} 秒：每 {gap} 秒自動施放 1 次雙刀亂舞；期間無法普攻但可施放技能</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">counter</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">反擊</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="G59">
-        <v>0</v>
+          <t xml:space="preserve">dualdance</t>
+        </is>
       </c>
       <c r="H59">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I59">
-        <v>4</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|450</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">反擊盾</t>
+          <t xml:space="preserve">毀滅之舞</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":1,"pctPer":0.1}</t>
+          <t xml:space="preserve">{"hpPct":10,"hpPctPer":-0.5,"pct":200,"pctPer":20}</t>
         </is>
       </c>
       <c r="M59">
-        <v>800000</v>
+        <v>10000000</v>
       </c>
       <c r="N59">
         <v>1.5</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">觸發反擊時，回復自身最大生命 {pct}% 的護盾</t>
+          <t xml:space="preserve">每施放 1 次雙刀亂舞就失去當下 {hpPct}% 生命值（不會致死），但雙刀亂舞的傷害提高 {pct}%</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doomDance</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">counter</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">反擊</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="G60">
-        <v>0</v>
+          <t xml:space="preserve">dualdance</t>
+        </is>
       </c>
       <c r="H60">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="I60">
-        <v>5</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|500</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">破甲擊</t>
+          <t xml:space="preserve">火之神樂</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":35,"def":15,"sec":4,"secPer":0.4,"max":4}</t>
+          <t xml:space="preserve">{"pct":10,"pctPer":1,"gap":0.5,"dur":6,"maxStacks":20}</t>
         </is>
       </c>
       <c r="M60">
-        <v>1500000</v>
+        <v>10000000</v>
       </c>
       <c r="N60">
         <v>1.5</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">格擋時有 {chance}% 機率造成破甲：防禦 -{def}%，持續 {sec} 秒，最多疊 {max} 層（疊層時重置時間）</t>
+          <t xml:space="preserve">雙刀亂舞附加火焰：每次命中堆疊 1 層【神樂灼焰】，每層每 {gap} 秒造成 {pct}% 火屬性傷害，最多 {maxStacks} 層，持續 {dur} 秒</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flameKagura</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">counter</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">反擊</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🛡️</t>
-        </is>
-      </c>
-      <c r="G61">
-        <v>0</v>
+          <t xml:space="preserve">dualdance</t>
+        </is>
       </c>
       <c r="H61">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="I61">
-        <v>6</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|550</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">二次反擊</t>
+          <t xml:space="preserve">修羅亂舞</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":50,"chancePer":5,"count":2}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M61">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="N61">
         <v>1.5</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">反擊時有 {chance}% 機率再追加 {count} 次反擊（追加反擊不會再觸發反擊）</t>
+          <t xml:space="preserve">讓你可以同時裝備兩把雙手武器（主手與副手各一把），且雙手武器的詞條效果提升 {pct}%</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asuraDance</t>
         </is>
       </c>
     </row>
@@ -3112,347 +3034,347 @@
         <v>0</v>
       </c>
       <c r="H62">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I62">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|600</t>
+          <t xml:space="preserve">0|300</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂化反殺</t>
+          <t xml:space="preserve">反擊</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"m":80}</t>
+          <t xml:space="preserve">{"chance":35,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M62">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N62">
         <v>1.5</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">每次反擊時，額外對 {m} 米內隨機 {count} 個敵人反擊，造成 {pct}% 普攻傷害（不會再觸發反擊）</t>
+          <t xml:space="preserve">被動：受到傷害時有 {chance}% 機率對攻擊者反擊，造成 {pct}% 普攻傷害</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">bloodrage</t>
+          <t xml:space="preserve">counter</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血狂怒</t>
+          <t xml:space="preserve">反擊</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">💢</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="G63">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|400</t>
+          <t xml:space="preserve">0|350</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血狂怒</t>
+          <t xml:space="preserve">招架</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":8}</t>
+          <t xml:space="preserve">{"mult":300,"multPer":30}</t>
         </is>
       </c>
       <c r="M63">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N63">
         <v>1.5</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻速額外 +{pct}%（乘算，不受攻速上限限制），持續 {sec} 秒</t>
+          <t xml:space="preserve">格擋時必定對敵人反擊，造成「格擋減傷值 × {mult}%」的普攻傷害</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">bloodrage</t>
+          <t xml:space="preserve">counter</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血狂怒</t>
+          <t xml:space="preserve">反擊</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">💢</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="G64">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|450</t>
+          <t xml:space="preserve">0|400</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂暴</t>
+          <t xml:space="preserve">強化反擊</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":5}</t>
         </is>
       </c>
       <c r="M64">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N64">
         <v>1.5</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間爆擊傷害額外 +{pct}%（乘算）</t>
+          <t xml:space="preserve">進一步提升反擊傷害，額外 +{pct}% 反擊普攻傷害</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">bloodrage</t>
+          <t xml:space="preserve">counter</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血狂怒</t>
+          <t xml:space="preserve">反擊</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">💢</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="G65">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|500</t>
+          <t xml:space="preserve">0|450</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒</t>
+          <t xml:space="preserve">反擊盾</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"pct":1,"pctPer":0.1}</t>
         </is>
       </c>
       <c r="M65">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N65">
         <v>1.5</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間總傷害額外 +{pct}%（乘算）</t>
+          <t xml:space="preserve">觸發反擊時，回復自身最大生命 {pct}% 的護盾</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">bloodrage</t>
+          <t xml:space="preserve">counter</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血狂怒</t>
+          <t xml:space="preserve">反擊</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">💢</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
         <v>60</v>
       </c>
-      <c r="H66">
-        <v>80</v>
-      </c>
       <c r="I66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|550</t>
+          <t xml:space="preserve">0|500</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂化連殺</t>
+          <t xml:space="preserve">破甲擊</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":0.5,"addPer":0.1,"kill":0.1,"killMax":5}</t>
+          <t xml:space="preserve">{"chance":35,"def":15,"sec":4,"secPer":0.4,"max":4}</t>
         </is>
       </c>
       <c r="M66">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N66">
         <v>1.5</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間基礎連擊數 +{add}，且每擊殺 1 個敵人再 +{kill}（累計上限 +{killMax}；不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">格擋時有 {chance}% 機率造成破甲：防禦 -{def}%，持續 {sec} 秒，最多疊 {max} 層（疊層時重置時間）</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">bloodrage</t>
+          <t xml:space="preserve">counter</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血狂怒</t>
+          <t xml:space="preserve">反擊</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">💢</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="G67">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|600</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血反震</t>
+          <t xml:space="preserve">二次反擊</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"chance":50,"chancePer":5,"count":2}</t>
         </is>
       </c>
       <c r="M67">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N67">
         <v>1.5</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間反震傷害提高 {pct}%（乘算，可與其它反震加成疊加）</t>
+          <t xml:space="preserve">反擊時有 {chance}% 機率再追加 {count} 次反擊（追加反擊不會再觸發反擊）</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">bloodrage</t>
+          <t xml:space="preserve">counter</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血狂怒</t>
+          <t xml:space="preserve">反擊</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">💢</t>
+          <t xml:space="preserve">🛡️</t>
         </is>
       </c>
       <c r="G68">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|650</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">血飲術</t>
+          <t xml:space="preserve">狂化反殺</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"self":1,"m":80}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"m":80}</t>
         </is>
       </c>
       <c r="M68">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N68">
         <v>1.5</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間傷害額外提高 {pct}%（乘算），但 {m} 米內的敵人每次受傷都會使你損失最大生命 {self}%（直接扣血，無法被護盾吸收）</t>
+          <t xml:space="preserve">每次反擊時，額外對 {m} 米內隨機 {count} 個敵人反擊，造成 {pct}% 普攻傷害（不會再觸發反擊）</t>
         </is>
       </c>
     </row>
@@ -3476,407 +3398,347 @@
         <v>60</v>
       </c>
       <c r="H69">
-        <v>240</v>
+        <v>25</v>
       </c>
       <c r="I69">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|700</t>
+          <t xml:space="preserve">0|400</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂血盛宴</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":0.5,"pct":1,"pctPer":0.1,"count":1}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":8}</t>
         </is>
       </c>
       <c r="M69">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N69">
         <v>1.5</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間每擊殺 1 個敵人，持續時間延長 {sec} 秒；且生命值每減少 1%，傷害額外 +{pct}%（乘算，無限疊加），每 1 連擊數使普攻可同時攻擊 1 個敵人（無限疊加）</t>
+          <t xml:space="preserve">攻速額外 +{pct}%（乘算，不受攻速上限限制），持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
+          <t xml:space="preserve">bloodrage</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">💢</t>
         </is>
       </c>
       <c r="G70">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H70">
         <v>40</v>
       </c>
       <c r="I70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|1</t>
+          <t xml:space="preserve">0|450</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">狂暴</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":15,"m":6,"castM":30}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M70">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N70">
         <v>1.5</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">射出一顆火球（射程 {castM} 米），命中時爆炸，對目標及 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+          <t xml:space="preserve">狂怒期間爆擊傷害額外 +{pct}%（乘算）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
+          <t xml:space="preserve">bloodrage</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">💢</t>
         </is>
       </c>
       <c r="G71">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H71">
         <v>60</v>
       </c>
       <c r="I71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|1</t>
+          <t xml:space="preserve">0|500</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃燒</t>
+          <t xml:space="preserve">狂怒</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dotPct":20,"dotPctPer":2,"dotSec":5,"dotGap":0.5}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M71">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N71">
         <v>1.5</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve">被火球擊中的敵人陷入燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
+          <t xml:space="preserve">狂怒期間總傷害額外 +{pct}%（乘算）</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
+          <t xml:space="preserve">bloodrage</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">💢</t>
         </is>
       </c>
       <c r="G72">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H72">
         <v>80</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|50</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球爆裂</t>
+          <t xml:space="preserve">狂化連殺</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"count":3,"m":20}</t>
+          <t xml:space="preserve">{"add":0.5,"addPer":0.1,"kill":0.1,"killMax":5}</t>
         </is>
       </c>
       <c r="M72">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N72">
         <v>1.5</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球爆炸後分裂出 {count} 個小火球，射向目標 {m} 米內的敵人，每個造成原始火球 {pct}% 的傷害</t>
+          <t xml:space="preserve">狂怒期間基礎連擊數 +{add}，且每擊殺 1 個敵人再 +{kill}（累計上限 +{killMax}；不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
+          <t xml:space="preserve">bloodrage</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">💢</t>
         </is>
       </c>
       <c r="G73">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H73">
         <v>100</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|100</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化燃燒</t>
+          <t xml:space="preserve">嗜血反震</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":0.4,"gapPer":-0.015}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M73">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N73">
         <v>1.5</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃燒的作用間隔縮短至 {gap} 秒（跳得更快＝總傷更高）</t>
+          <t xml:space="preserve">狂怒期間反震傷害提高 {pct}%（乘算，可與其它反震加成疊加）</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
+          <t xml:space="preserve">bloodrage</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">💢</t>
         </is>
       </c>
       <c r="G74">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H74">
         <v>140</v>
       </c>
       <c r="I74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|150</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">爆燃</t>
+          <t xml:space="preserve">血飲術</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"m":12}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"self":1,"m":80}</t>
         </is>
       </c>
       <c r="M74">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N74">
         <v>1.5</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃燒結束或敵人死亡時爆炸，對我方 {m} 米內的 {count} 個敵人造成該敵人整段燃燒累積傷害 {pct}% 的傷害</t>
+          <t xml:space="preserve">狂怒期間傷害額外提高 {pct}%（乘算），但 {m} 米內的敵人每次受傷都會使你損失最大生命 {self}%（直接扣血，無法被護盾吸收）</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
+          <t xml:space="preserve">bloodrage</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">💢</t>
         </is>
       </c>
       <c r="G75">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H75">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|200</t>
+          <t xml:space="preserve">0|700</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">火焰增幅</t>
+          <t xml:space="preserve">狂血盛宴</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":0.25,"pctPer":0.025,"sec":4,"m":20}</t>
+          <t xml:space="preserve">{"sec":0.5,"pct":1,"pctPer":0.1,"count":1}</t>
         </is>
       </c>
       <c r="M75">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N75">
         <v>1.5</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">我方 {m} 米內每有 1 次燃燒作用，你的火焰傷害 +{pct}%，持續 {sec} 秒（無限疊加，每次疊加時重置時間）</t>
+          <t xml:space="preserve">狂怒期間每擊殺 1 個敵人，持續時間延長 {sec} 秒；且生命值每減少 1%，傷害額外 +{pct}%（乘算，無限疊加），每 1 連擊數使普攻可同時攻擊 1 個敵人（無限疊加）</t>
         </is>
       </c>
     </row>
@@ -3910,52 +3772,52 @@
         <v>14</v>
       </c>
       <c r="H76">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="I76">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|250</t>
+          <t xml:space="preserve">0|1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">殞石術</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":15,"castM":20}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":15,"m":6,"castM":30}</t>
         </is>
       </c>
       <c r="M76">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N76">
         <v>1.5</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為召喚 {count} 顆巨大火殞石從天而降（射程 {castM} 米），每顆對目標 {m} 米內的敵人造成 {pct}% 火焰傷害，且殞石造成的燃燒傷害為 2 倍（第 2~6 階效果仍然生效）</t>
+          <t xml:space="preserve">射出一顆火球（射程 {castM} 米），命中時爆炸，對目標及 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3972,52 +3834,52 @@
         <v>14</v>
       </c>
       <c r="H77">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|50</t>
+          <t xml:space="preserve">0|1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">燃燒</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":60,"pctPer":6,"hits":5,"m":3,"castM":30,"sec":2.5}</t>
+          <t xml:space="preserve">{"dotPct":20,"dotPctPer":2,"dotSec":5,"dotGap":0.5}</t>
         </is>
       </c>
       <c r="M77">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N77">
         <v>1.5</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">在敵人腳下召喚一道火柱（射程 {castM} 米），對目標 {m} 米內的敵人連續造成 {hits} 段傷害，每段 {pct}% 火焰傷害（全程約 {sec} 秒）</t>
+          <t xml:space="preserve">被火球擊中的敵人陷入燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4034,52 +3896,52 @@
         <v>14</v>
       </c>
       <c r="H78">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|100</t>
+          <t xml:space="preserve">0|50</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍捲噴發</t>
+          <t xml:space="preserve">火球爆裂</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":10,"pctPer":2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"count":3,"m":20}</t>
         </is>
       </c>
       <c r="M78">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N78">
         <v>1.5</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">火柱的傷害範圍擴大 {pct}%</t>
+          <t xml:space="preserve">火球爆炸後分裂出 {count} 個小火球，射向目標 {m} 米內的敵人，每個造成原始火球 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4096,52 +3958,52 @@
         <v>14</v>
       </c>
       <c r="H79">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|150</t>
+          <t xml:space="preserve">0|100</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重龍捲</t>
+          <t xml:space="preserve">強化燃燒</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":20,"pctPer":2,"m":20}</t>
+          <t xml:space="preserve">{"gap":0.4,"gapPer":-0.015}</t>
         </is>
       </c>
       <c r="M79">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N79">
         <v>1.5</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">可同時對 {m} 米內的 {count} 個目標施放火柱，且火焰傷害額外 +{pct}%</t>
+          <t xml:space="preserve">燃燒的作用間隔縮短至 {gap} 秒（跳得更快＝總傷更高）</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4158,52 +4020,52 @@
         <v>14</v>
       </c>
       <c r="H80">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="I80">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|200</t>
+          <t xml:space="preserve">0|150</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃燒</t>
+          <t xml:space="preserve">爆燃</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":20,"chancePer":2,"dotPct":20,"dotSec":4,"dotGap":0.5}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"m":12}</t>
         </is>
       </c>
       <c r="M80">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N80">
         <v>1.5</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">火柱每次作用時有 {chance}% 機率使敵人燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
+          <t xml:space="preserve">燃燒結束或敵人死亡時爆炸，對我方 {m} 米內的 {count} 個敵人造成該敵人整段燃燒累積傷害 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4220,52 +4082,52 @@
         <v>14</v>
       </c>
       <c r="H81">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="I81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|250</t>
+          <t xml:space="preserve">0|200</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">烈焰衝擊</t>
+          <t xml:space="preserve">火焰增幅</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"m":6}</t>
+          <t xml:space="preserve">{"pct":0.25,"pctPer":0.025,"sec":4,"m":20}</t>
         </is>
       </c>
       <c r="M81">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N81">
         <v>1.5</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲或火牆消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+          <t xml:space="preserve">我方 {m} 米內每有 1 次燃燒作用，你的火焰傷害 +{pct}%，持續 {sec} 秒（無限疊加，每次疊加時重置時間）</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4282,35 +4144,35 @@
         <v>14</v>
       </c>
       <c r="H82">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="I82">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|300</t>
+          <t xml:space="preserve">0|250</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">重生</t>
+          <t xml:space="preserve">殞石術</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":20}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":15,"castM":20}</t>
         </is>
       </c>
       <c r="M82">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N82">
         <v>1.5</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">火柱消失後有 {chance}% 機率在我方 {m} 米內的敵人身上重生</t>
+          <t xml:space="preserve">改為召喚 {count} 顆巨大火殞石從天而降（射程 {castM} 米），每顆對目標 {m} 米內的敵人造成 {pct}% 火焰傷害，且殞石造成的燃燒傷害為 2 倍（第 2~6 階效果仍然生效）</t>
         </is>
       </c>
     </row>
@@ -4344,57 +4206,52 @@
         <v>14</v>
       </c>
       <c r="H83">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="I83">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|350</t>
+          <t xml:space="preserve">0|50</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">無限火牆</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":3,"hits":8,"pct":100,"pctPer":10,"len":18,"wid":6,"respawn":1}</t>
+          <t xml:space="preserve">{"pct":60,"pctPer":6,"hits":5,"m":3,"castM":30,"sec":2.5}</t>
         </is>
       </c>
       <c r="M83">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N83">
         <v>1.5</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為施放 {count} 道火牆（橫向 {len}×{wid} 米），每道造成 {hits} 段 {pct}% 火焰傷害；每道火牆消失後再召喚 1 道（僅能再觸發一次；第 2~6 階效果仍然生效）</t>
+          <t xml:space="preserve">在敵人腳下召喚一道火柱（射程 {castM} 米），對目標 {m} 米內的敵人連續造成 {hits} 段傷害，每段 {pct}% 火焰傷害（全程約 {sec} 秒）</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4408,13 +4265,13 @@
         </is>
       </c>
       <c r="G84">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H84">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4423,45 +4280,40 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">龍捲噴發</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"count":2,"sec":4,"m":8,"rps":0.455,"castM":8}</t>
+          <t xml:space="preserve">{"pct":10,"pctPer":2}</t>
         </is>
       </c>
       <c r="M84">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N84">
         <v>1.5</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">召喚 {count} 團火狩環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">火柱的傷害範圍擴大 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4475,13 +4327,13 @@
         </is>
       </c>
       <c r="G85">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H85">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4490,45 +4342,40 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化火狩</t>
+          <t xml:space="preserve">雙重龍捲</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"count":2,"pct":20,"pctPer":2,"m":20}</t>
         </is>
       </c>
       <c r="M85">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N85">
         <v>1.5</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩的體積與環繞範圍同步擴大 {pct}%</t>
+          <t xml:space="preserve">可同時對 {m} 米內的 {count} 個目標施放火柱，且火焰傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4542,13 +4389,13 @@
         </is>
       </c>
       <c r="G86">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H86">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4557,45 +4404,40 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">伴生火狩</t>
+          <t xml:space="preserve">燃燒</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":20,"chancePer":2,"m":1}</t>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"dotPct":20,"dotSec":4,"dotGap":0.5}</t>
         </is>
       </c>
       <c r="M86">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N86">
         <v>1.5</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩命中時有 {chance}% 機率在其後方 {m} 米處伴生一團火狩（每團只能伴生一次，伴生出的不再伴生）</t>
+          <t xml:space="preserve">火柱每次作用時有 {chance}% 機率使敵人燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4609,13 +4451,13 @@
         </is>
       </c>
       <c r="G87">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H87">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="I87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4624,45 +4466,40 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重火狩</t>
+          <t xml:space="preserve">烈焰衝擊</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":3,"pct":120,"pctPer":12,"sec":4}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"m":6}</t>
         </is>
       </c>
       <c r="M87">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N87">
         <v>1.5</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為召喚 {count} 團火狩，每團造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">火龍捲或火牆消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4676,13 +4513,13 @@
         </is>
       </c>
       <c r="G88">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H88">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="I88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4691,45 +4528,40 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">極速火狩</t>
+          <t xml:space="preserve">重生</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
+          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":20}</t>
         </is>
       </c>
       <c r="M88">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N88">
         <v>1.5</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩的旋轉速度 +{pct}%</t>
+          <t xml:space="preserve">火柱消失後有 {chance}% 機率在我方 {m} 米內的敵人身上重生</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4743,13 +4575,13 @@
         </is>
       </c>
       <c r="G89">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H89">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="I89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4758,23 +4590,23 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">再生</t>
+          <t xml:space="preserve">無限火牆</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":0.4,"secPer":0.04}</t>
+          <t xml:space="preserve">{"count":3,"hits":8,"pct":100,"pctPer":10,"len":18,"wid":6,"respawn":1}</t>
         </is>
       </c>
       <c r="M89">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N89">
         <v>1.5</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩每擊殺 1 個敵人，全部火狩的持續時間延長 {sec} 秒</t>
+          <t xml:space="preserve">改為施放 {count} 道火牆（橫向 {len}×{wid} 米），每道造成 {hits} 段 {pct}% 火焰傷害；每道火牆消失後再召喚 1 道（僅能再觸發一次；第 2~6 階效果仍然生效）</t>
         </is>
       </c>
     </row>
@@ -4813,52 +4645,57 @@
         <v>26</v>
       </c>
       <c r="H90">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="I90">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|400</t>
+          <t xml:space="preserve">0|100</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">狩神之舞</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"rings":2,"pct":150,"pctPer":15,"sec":6,"m":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"count":2,"sec":4,"m":8,"rps":0.455,"castM":8}</t>
         </is>
       </c>
       <c r="M90">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N90">
         <v>1.5</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為一次施放 {rings} 道火狩（外圈距內圈 {m} 米、兩道旋轉方向相反），每團造成 {pct}% 火焰傷害、出現時自帶伴生，持續 {sec} 秒</t>
+          <t xml:space="preserve">召喚 {count} 團火狩環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4868,17 +4705,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G91">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H91">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4887,40 +4724,45 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">強化火狩</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"sec":10,"castM":30}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M91">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N91">
         <v>1.5</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放岩甲強化自身，獲得最大生命值 {pct}% 的岩甲護盾，持續 {sec} 秒</t>
+          <t xml:space="preserve">火狩的體積與環繞範圍同步擴大 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4930,17 +4772,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G92">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H92">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4949,40 +4791,45 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化岩甲</t>
+          <t xml:space="preserve">伴生火狩</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"m":1}</t>
         </is>
       </c>
       <c r="M92">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N92">
         <v>1.5</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化岩甲，額外獲得最大生命值 {pct}% 的岩甲護盾（與第 1 階累加）</t>
+          <t xml:space="preserve">火狩命中時有 {chance}% 機率在其後方 {m} 米處伴生一團火狩（每團只能伴生一次，伴生出的不再伴生）</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4992,17 +4839,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G93">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H93">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5011,40 +4858,45 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲尖刺</t>
+          <t xml:space="preserve">三重火狩</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":5,"pctPer":0.5}</t>
+          <t xml:space="preserve">{"count":3,"pct":120,"pctPer":12,"sec":4}</t>
         </is>
       </c>
       <c r="M93">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N93">
         <v>1.5</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，攻擊你的敵人會遭受你最大生命值 {pct}% 的地系傷害（獨立於反震，兩者各自結算）</t>
+          <t xml:space="preserve">改為召喚 {count} 團火狩，每團造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5054,17 +4906,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G94">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H94">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="I94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5073,40 +4925,45 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">護盾增幅</t>
+          <t xml:space="preserve">極速火狩</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
         </is>
       </c>
       <c r="M94">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N94">
         <v>1.5</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t xml:space="preserve">主動型被動（裝配到技能列即恆時生效）：你獲得的所有護盾效率額外 +{pct}%（乘算）</t>
+          <t xml:space="preserve">火狩的旋轉速度 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5116,17 +4973,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G95">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H95">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="I95">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5135,40 +4992,45 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩之再生</t>
+          <t xml:space="preserve">再生</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":1,"pctPer":0.1}</t>
+          <t xml:space="preserve">{"sec":0.4,"secPer":0.04}</t>
         </is>
       </c>
       <c r="M95">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N95">
         <v>1.5</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 生命值即獲得最大生命 {pct}% 的護盾</t>
+          <t xml:space="preserve">火狩每擊殺 1 個敵人，全部火狩的持續時間延長 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5178,17 +5040,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G96">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H96">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="I96">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5197,23 +5059,23 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲增幅</t>
+          <t xml:space="preserve">狩神之舞</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":0.5,"pctPer":0.05,"max":30,"sec":3}</t>
+          <t xml:space="preserve">{"rings":2,"pct":150,"pctPer":15,"sec":6,"m":6}</t>
         </is>
       </c>
       <c r="M96">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N96">
         <v>1.5</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 護盾即獲得 {pct}% 傷害增幅（乘算），最多疊 {max} 層，持續 {sec} 秒</t>
+          <t xml:space="preserve">改為一次施放 {rings} 道火狩（外圈距內圈 {m} 米、兩道旋轉方向相反），每團造成 {pct}% 火焰傷害、出現時自帶伴生，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -5250,54 +5112,49 @@
         <v>40</v>
       </c>
       <c r="I97">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|450</t>
+          <t xml:space="preserve">0|150</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">天地逆返</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"sec":10,"castM":30}</t>
         </is>
       </c>
       <c r="M97">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N97">
         <v>1.5</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，護盾剩餘量越低則傷害減免越高，護盾歸零時最高額外 +{pct}% 傷害減免（乘算）</t>
+          <t xml:space="preserve">施放岩甲強化自身，獲得最大生命值 {pct}% 的岩甲護盾，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5311,13 +5168,13 @@
         </is>
       </c>
       <c r="G98">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H98">
         <v>40</v>
       </c>
       <c r="I98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5326,45 +5183,40 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">強化岩甲</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.4,"castM":20,"move":30,"aspd":50}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M98">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N98">
         <v>1.5</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t xml:space="preserve">在敵人腳下召喚一片 12×12 米的沼澤（射程 {castM} 米），沼澤中的敵人陷入緩速（移動速度 -{move}%、攻速 -{aspd}%），持續 {sec} 秒</t>
+          <t xml:space="preserve">進一步強化岩甲，額外獲得最大生命值 {pct}% 的岩甲護盾（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5378,13 +5230,13 @@
         </is>
       </c>
       <c r="G99">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H99">
         <v>40</v>
       </c>
       <c r="I99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -5393,45 +5245,40 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛弱</t>
+          <t xml:space="preserve">岩甲尖刺</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"pct":5,"pctPer":0.5}</t>
         </is>
       </c>
       <c r="M99">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N99">
         <v>1.5</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t xml:space="preserve">受泥沼緩速影響的敵人，受到的傷害提高 {pct}%</t>
+          <t xml:space="preserve">岩甲護盾存在期間，攻擊你的敵人會遭受你最大生命值 {pct}% 的地系傷害（獨立於反震，兩者各自結算）</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5445,13 +5292,13 @@
         </is>
       </c>
       <c r="G100">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H100">
         <v>40</v>
       </c>
       <c r="I100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5460,45 +5307,40 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒沼術</t>
+          <t xml:space="preserve">護盾增幅</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dotPct":25,"dotPctPer":2.5,"dotGap":0.5}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M100">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N100">
         <v>1.5</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤持續放出毒氣：沼澤中的敵人每 {dotGap} 秒受到魔法攻擊 {dotPct}% 的毒性傷害</t>
+          <t xml:space="preserve">主動型被動（裝配到技能列即恆時生效）：你獲得的所有護盾效率額外 +{pct}%（乘算）</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5512,13 +5354,13 @@
         </is>
       </c>
       <c r="G101">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H101">
         <v>40</v>
       </c>
       <c r="I101">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5527,45 +5369,40 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒沼增生</t>
+          <t xml:space="preserve">岩之再生</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":40}</t>
+          <t xml:space="preserve">{"pct":1,"pctPer":0.1}</t>
         </is>
       </c>
       <c r="M101">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N101">
         <v>1.5</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤結束時傳染給 {m} 米內較近的敵人，最多傳染 {add} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 生命值即獲得最大生命 {pct}% 的護盾</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5579,13 +5416,13 @@
         </is>
       </c>
       <c r="G102">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H102">
         <v>40</v>
       </c>
       <c r="I102">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5594,45 +5431,40 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤漫延</t>
+          <t xml:space="preserve">岩甲增幅</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":6,"pct":40,"pctPer":4,"growSec":4}</t>
+          <t xml:space="preserve">{"pct":0.5,"pctPer":0.05,"max":30,"sec":3}</t>
         </is>
       </c>
       <c r="M102">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N102">
         <v>1.5</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤持續時間提高至 {sec} 秒，且在 {growSec} 秒內逐步擴大，最大擴增 {pct}%</t>
+          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 護盾即獲得 {pct}% 傷害增幅（乘算），最多疊 {max} 層，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5646,13 +5478,13 @@
         </is>
       </c>
       <c r="G103">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H103">
         <v>40</v>
       </c>
       <c r="I103">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5661,23 +5493,23 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">重力泥沼</t>
+          <t xml:space="preserve">天地逆返</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"move":50,"aspd":75,"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M103">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N103">
         <v>1.5</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t xml:space="preserve">緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%（與第 2 階累加）</t>
+          <t xml:space="preserve">岩甲護盾存在期間，護盾剩餘量越低則傷害減免越高，護盾歸零時最高額外 +{pct}% 傷害減免（乘算）</t>
         </is>
       </c>
     </row>
@@ -5719,49 +5551,54 @@
         <v>40</v>
       </c>
       <c r="I104">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|500</t>
+          <t xml:space="preserve">0|200</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">熔岩沼</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":8,"pct":20,"pctPer":2,"dotPct":70,"dotPctPer":7,"dotGap":0.4}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.4,"castM":20,"move":30,"aspd":50}</t>
         </is>
       </c>
       <c r="M104">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N104">
         <v>1.5</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤轉變為岩漿：持續時間提高至 {sec} 秒、範圍再擴增 {pct}%（與第 5 階累加），其中的目標每 {dotGap} 秒額外受到魔法攻擊 {dotPct}% 的火焰傷害</t>
+          <t xml:space="preserve">在敵人腳下召喚一片 12×12 米的沼澤（射程 {castM} 米），沼澤中的敵人陷入緩速（移動速度 -{move}%、攻速 -{aspd}%），持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5775,13 +5612,13 @@
         </is>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5790,40 +5627,45 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">虛弱</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":10,"pctPer":1,"hp":20,"hpPer":2}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M105">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N105">
         <v>1.5</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t xml:space="preserve">主動型被動：自身傷害減免額外 +{pct}%、生命上限額外 +{hp}%（皆為乘算）</t>
+          <t xml:space="preserve">受泥沼緩速影響的敵人，受到的傷害提高 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5837,13 +5679,13 @@
         </is>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H106">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5852,40 +5694,45 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地祝福</t>
+          <t xml:space="preserve">毒沼術</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
+          <t xml:space="preserve">{"dotPct":25,"dotPctPer":2.5,"dotGap":0.5}</t>
         </is>
       </c>
       <c r="M106">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N106">
         <v>1.5</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t xml:space="preserve">全屬性傷害額外 +{pct}%（與所有屬性增傷效果為額外的乘法計算）</t>
+          <t xml:space="preserve">沼澤持續放出毒氣：沼澤中的敵人每 {dotGap} 秒受到魔法攻擊 {dotPct}% 的毒性傷害</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5899,13 +5746,13 @@
         </is>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H107">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I107">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5914,40 +5761,45 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命再生</t>
+          <t xml:space="preserve">毒沼增生</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":40}</t>
         </is>
       </c>
       <c r="M107">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N107">
         <v>1.5</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命回復額外 +{pct}%、吸血額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
+          <t xml:space="preserve">沼澤結束時傳染給 {m} 米內較近的敵人，最多傳染 {add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5961,13 +5813,13 @@
         </is>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H108">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I108">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5976,40 +5828,45 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔力再生</t>
+          <t xml:space="preserve">沼澤漫延</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
+          <t xml:space="preserve">{"sec":6,"pct":40,"pctPer":4,"growSec":4}</t>
         </is>
       </c>
       <c r="M108">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N108">
         <v>1.5</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t xml:space="preserve">法力回復額外 +{pct}%、吸魔額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
+          <t xml:space="preserve">沼澤持續時間提高至 {sec} 秒，且在 {growSec} 秒內逐步擴大，最大擴增 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6023,13 +5880,13 @@
         </is>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H109">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I109">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -6038,40 +5895,45 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法盾</t>
+          <t xml:space="preserve">重力泥沼</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+          <t xml:space="preserve">{"move":50,"aspd":75,"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M109">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N109">
         <v>1.5</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t xml:space="preserve">你的生命減少時，其中 {pct}% 改由消耗法力承擔（法力不足時只轉換付得起的部分，餘額仍扣生命）</t>
+          <t xml:space="preserve">緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%（與第 2 階累加）</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6085,13 +5947,13 @@
         </is>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H110">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I110">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -6100,23 +5962,23 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命反射之盾</t>
+          <t xml:space="preserve">熔岩沼</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":1,"pctPer":0.1,"m":20,"count":1}</t>
+          <t xml:space="preserve">{"sec":8,"pct":20,"pctPer":2,"dotPct":70,"dotPctPer":7,"dotGap":0.4}</t>
         </is>
       </c>
       <c r="M110">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N110">
         <v>1.5</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t xml:space="preserve">你每消耗 1% 生命或護盾，{m} 米內的 {count} 個敵人同步損失 {pct}% 最大生命</t>
+          <t xml:space="preserve">沼澤轉變為岩漿：持續時間提高至 {sec} 秒、範圍再擴增 {pct}%（與第 5 階累加），其中的目標每 {dotGap} 秒額外受到魔法攻擊 {dotPct}% 的火焰傷害</t>
         </is>
       </c>
     </row>
@@ -6150,52 +6012,52 @@
         <v>0</v>
       </c>
       <c r="H111">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I111">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|550</t>
+          <t xml:space="preserve">0|250</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">天地共生</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":8,"sec":5,"cd":60,"cdPer":-3}</t>
+          <t xml:space="preserve">{"pct":10,"pctPer":1,"hp":20,"hpPer":2}</t>
         </is>
       </c>
       <c r="M111">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N111">
         <v>1.5</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve">死亡時原地復活並回復 {pct}% 生命，復活後 {sec} 秒無敵；此招自身冷卻 {cd} 秒（顯示於技能格）</t>
+          <t xml:space="preserve">主動型被動：自身傷害減免額外 +{pct}%、生命上限額外 +{hp}%（皆為乘算）</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6205,17 +6067,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G112">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -6224,40 +6086,40 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地祝福</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":4,"m":30,"castM":30}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
         </is>
       </c>
       <c r="M112">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N112">
         <v>1.5</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t xml:space="preserve">丟出一道閃電鏈（射程 {castM} 米），在最多 {count} 個目標間彈射（每段彈射範圍 {m} 米），每擊造成 {pct}% 雷電傷害</t>
+          <t xml:space="preserve">全屬性傷害額外 +{pct}%（與所有屬性增傷效果為額外的乘法計算）</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6267,17 +6129,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G113">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -6286,40 +6148,40 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化閃電</t>
+          <t xml:space="preserve">生命再生</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
         </is>
       </c>
       <c r="M113">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N113">
         <v>1.5</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化閃電威力，閃電鏈傷害進一步 +{pct}% 雷電傷害</t>
+          <t xml:space="preserve">生命回復額外 +{pct}%、吸血額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6329,17 +6191,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G114">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6348,40 +6210,40 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷鳴術</t>
+          <t xml:space="preserve">魔力再生</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
         </is>
       </c>
       <c r="M114">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N114">
         <v>1.5</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t xml:space="preserve">被閃電鏈擊中的敵人額外再受到 {add} 次雷電傷害（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">法力回復額外 +{pct}%、吸魔額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6391,17 +6253,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G115">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I115">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -6410,40 +6272,40 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化連鎖</t>
+          <t xml:space="preserve">魔法盾</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M115">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N115">
         <v>1.5</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電鏈的彈射數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">你的生命減少時，其中 {pct}% 改由消耗法力承擔（法力不足時只轉換付得起的部分，餘額仍扣生命）</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6453,17 +6315,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G116">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I116">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -6472,40 +6334,40 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">電殛擴散</t>
+          <t xml:space="preserve">生命反射之盾</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":2.5,"count":1,"m":6}</t>
+          <t xml:space="preserve">{"pct":1,"pctPer":0.1,"m":20,"count":1}</t>
         </is>
       </c>
       <c r="M116">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N116">
         <v>1.5</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電鏈每次彈射時，額外對 {m} 米內的 {count} 個敵人造成閃電鏈 {pct}% 的雷電傷害</t>
+          <t xml:space="preserve">你每消耗 1% 生命或護盾，{m} 米內的 {count} 個敵人同步損失 {pct}% 最大生命</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6515,17 +6377,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G117">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I117">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -6534,23 +6396,23 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷幻身</t>
+          <t xml:space="preserve">天地共生</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":8,"sec":5,"cd":60,"cdPer":-3}</t>
         </is>
       </c>
       <c r="M117">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N117">
         <v>1.5</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電鏈傷害額外 +{pct}% 雷電傷害；沒有其它彈射目標時可用自身當中繼點繼續彈射（彈到自身不消耗彈射數）</t>
+          <t xml:space="preserve">死亡時原地復活並回復 {pct}% 生命，復活後 {sec} 秒無敵；此招自身冷卻 {cd} 秒（顯示於技能格）</t>
         </is>
       </c>
     </row>
@@ -6587,49 +6449,49 @@
         <v>40</v>
       </c>
       <c r="I118">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|600</t>
+          <t xml:space="preserve">0|300</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電暴風</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":3,"add":1,"addPer":0.1,"pct":100,"pctPer":10,"chance":20}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":4,"m":30,"castM":30}</t>
         </is>
       </c>
       <c r="M118">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N118">
         <v>1.5</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t xml:space="preserve">同時發射 {count} 道閃電鏈，彈射數額外 +{add} 次，且閃電傷害額外 +{pct}%；每次彈射有 {chance}% 機率生成 1 條閃電鏈</t>
+          <t xml:space="preserve">丟出一道閃電鏈（射程 {castM} 米），在最多 {count} 個目標間彈射（每段彈射範圍 {m} 米），每擊造成 {pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6643,13 +6505,13 @@
         </is>
       </c>
       <c r="G119">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H119">
         <v>40</v>
       </c>
       <c r="I119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -6658,40 +6520,40 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">強化閃電</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"count":2,"gap":0.2,"castM":30}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M119">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N119">
         <v>1.5</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 {castM} 米內的 {count} 個目標降下落雷（每道間隔 {gap} 秒），每道造成 {pct}% 雷電傷害</t>
+          <t xml:space="preserve">強化閃電威力，閃電鏈傷害進一步 +{pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6705,13 +6567,13 @@
         </is>
       </c>
       <c r="G120">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H120">
         <v>40</v>
       </c>
       <c r="I120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6720,7 +6582,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷連鎖</t>
+          <t xml:space="preserve">雷鳴術</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -6729,31 +6591,31 @@
         </is>
       </c>
       <c r="M120">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N120">
         <v>1.5</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊目標額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">被閃電鏈擊中的敵人額外再受到 {add} 次雷電傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6767,13 +6629,13 @@
         </is>
       </c>
       <c r="G121">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H121">
         <v>40</v>
       </c>
       <c r="I121">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6782,40 +6644,40 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重落雷</t>
+          <t xml:space="preserve">強化連鎖</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
         </is>
       </c>
       <c r="M121">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N121">
         <v>1.5</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t xml:space="preserve">對每個目標的攻擊次數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">閃電鏈的彈射數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6829,13 +6691,13 @@
         </is>
       </c>
       <c r="G122">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H122">
         <v>40</v>
       </c>
       <c r="I122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6844,40 +6706,40 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電增幅</t>
+          <t xml:space="preserve">電殛擴散</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5,"count":1,"m":6}</t>
         </is>
       </c>
       <c r="M122">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N122">
         <v>1.5</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化落雷傷害，額外 +{pct}% 雷電傷害</t>
+          <t xml:space="preserve">閃電鏈每次彈射時，額外對 {m} 米內的 {count} 個敵人造成閃電鏈 {pct}% 的雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6891,13 +6753,13 @@
         </is>
       </c>
       <c r="G123">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H123">
         <v>40</v>
       </c>
       <c r="I123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6906,40 +6768,40 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電脈衝</t>
+          <t xml:space="preserve">雷幻身</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":1.5,"secPer":0.15,"count":2,"m":6}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M123">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N123">
         <v>1.5</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷落地時產生衝擊波，震暈目標本身與 {m} 米內共 {count} 個敵人 {sec} 秒</t>
+          <t xml:space="preserve">閃電鏈傷害額外 +{pct}% 雷電傷害；沒有其它彈射目標時可用自身當中繼點繼續彈射（彈到自身不消耗彈射數）</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6953,13 +6815,13 @@
         </is>
       </c>
       <c r="G124">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H124">
         <v>40</v>
       </c>
       <c r="I124">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6968,23 +6830,23 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">迅雷重生</t>
+          <t xml:space="preserve">雷電暴風</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":20,"chancePer":2,"max":5}</t>
+          <t xml:space="preserve">{"count":3,"add":1,"addPer":0.1,"pct":100,"pctPer":10,"chance":20}</t>
         </is>
       </c>
       <c r="M124">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N124">
         <v>1.5</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t xml:space="preserve">每道落雷結束後有 {chance}% 機率再產生 1 道落雷（同一次施放最多再生 {max} 道）</t>
+          <t xml:space="preserve">同時發射 {count} 道閃電鏈，彈射數額外 +{add} 次，且閃電傷害額外 +{pct}%；每次彈射有 {chance}% 機率生成 1 條閃電鏈</t>
         </is>
       </c>
     </row>
@@ -7021,54 +6883,49 @@
         <v>40</v>
       </c>
       <c r="I125">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|650</t>
+          <t xml:space="preserve">0|350</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">殛道落電</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"mult":2,"pct":50,"pctPer":5,"m":6}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"count":2,"gap":0.2,"castM":30}</t>
         </is>
       </c>
       <c r="M125">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N125">
         <v>1.5</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷擊中時對目標 {m} 米內的所有敵人造成傷害；攻擊次數與目標數量 ×{mult}，且命中暈眩中的敵人時傷害額外 +{pct}%（與原傷害乘算）</t>
+          <t xml:space="preserve">對 {castM} 米內的 {count} 個目標降下落雷（每道間隔 {gap} 秒），每道造成 {pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7082,13 +6939,13 @@
         </is>
       </c>
       <c r="G126">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H126">
         <v>40</v>
       </c>
       <c r="I126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -7097,45 +6954,40 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷連鎖</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"gap":0.35,"sec":2,"m":3,"speed":6,"castM":30}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M126">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N126">
         <v>1.5</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t xml:space="preserve">召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
+          <t xml:space="preserve">攻擊目標額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7149,13 +7001,13 @@
         </is>
       </c>
       <c r="G127">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H127">
         <v>40</v>
       </c>
       <c r="I127">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -7164,45 +7016,40 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">擴增雷球</t>
+          <t xml:space="preserve">雙重落雷</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M127">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N127">
         <v>1.5</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球的體積擴大 {pct}%</t>
+          <t xml:space="preserve">對每個目標的攻擊次數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7216,13 +7063,13 @@
         </is>
       </c>
       <c r="G128">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H128">
         <v>40</v>
       </c>
       <c r="I128">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -7231,45 +7078,40 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">多重雷球</t>
+          <t xml:space="preserve">閃電增幅</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M128">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N128">
         <v>1.5</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球數量額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">進一步強化落雷傷害，額外 +{pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7283,13 +7125,13 @@
         </is>
       </c>
       <c r="G129">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H129">
         <v>40</v>
       </c>
       <c r="I129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -7298,45 +7140,40 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">環體電球</t>
+          <t xml:space="preserve">雷電脈衝</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":100,"pctPer":10,"sec":6,"m":8,"rps":0.7}</t>
+          <t xml:space="preserve">{"sec":1.5,"secPer":0.15,"count":2,"m":6}</t>
         </is>
       </c>
       <c r="M129">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N129">
         <v>1.5</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 {count} 個電球環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">落雷落地時產生衝擊波，震暈目標本身與 {m} 米內共 {count} 個敵人 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7350,13 +7187,13 @@
         </is>
       </c>
       <c r="G130">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H130">
         <v>40</v>
       </c>
       <c r="I130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -7365,45 +7202,40 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化雷球</t>
+          <t xml:space="preserve">迅雷重生</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"max":5}</t>
         </is>
       </c>
       <c r="M130">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N130">
         <v>1.5</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有雷球與電球的雷電傷害額外 +{pct}%</t>
+          <t xml:space="preserve">每道落雷結束後有 {chance}% 機率再產生 1 道落雷（同一次施放最多再生 {max} 道）</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7417,13 +7249,13 @@
         </is>
       </c>
       <c r="G131">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H131">
         <v>40</v>
       </c>
       <c r="I131">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -7432,23 +7264,23 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">伴生雷球</t>
+          <t xml:space="preserve">殛道落電</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"sec":2}</t>
+          <t xml:space="preserve">{"mult":2,"pct":50,"pctPer":5,"m":6}</t>
         </is>
       </c>
       <c r="M131">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N131">
         <v>1.5</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t xml:space="preserve">環體電球命中時有 {chance}% 機率在該處生成一個靜止雷球，持續 {sec} 秒（每次作用只判定一次機率）</t>
+          <t xml:space="preserve">落雷擊中時對目標 {m} 米內的所有敵人造成傷害；攻擊次數與目標數量 ×{mult}，且命中暈眩中的敵人時傷害額外 +{pct}%（與原傷害乘算）</t>
         </is>
       </c>
     </row>
@@ -7490,49 +7322,54 @@
         <v>40</v>
       </c>
       <c r="I132">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|700</t>
+          <t xml:space="preserve">0|400</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷殞天落</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":300,"pctPer":30,"m":15,"sec":3}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"gap":0.35,"sec":2,"m":3,"speed":6,"castM":30}</t>
         </is>
       </c>
       <c r="M132">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N132">
         <v>1.5</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 {count} 個巨大雷球從天而降，各對 {m} 米內的敵人造成 {pct}% 雷電傷害，並以衝擊波擊暈 {sec} 秒</t>
+          <t xml:space="preserve">召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7542,17 +7379,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G133">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H133">
         <v>40</v>
       </c>
       <c r="I133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -7561,40 +7398,45 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">擴增雷球</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"deg":15,"castM":30,"speed":45}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M133">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N133">
         <v>1.5</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">雷球的體積擴大 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7604,17 +7446,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G134">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H134">
         <v>40</v>
       </c>
       <c r="I134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -7623,40 +7465,45 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜箭</t>
+          <t xml:space="preserve">多重雷球</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"frostPct":50,"frostPctPer":5,"stacks":1}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M134">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N134">
         <v>1.5</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
+          <t xml:space="preserve">雷球數量額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7666,17 +7513,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G135">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H135">
         <v>40</v>
       </c>
       <c r="I135">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -7685,40 +7532,45 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰系強化</t>
+          <t xml:space="preserve">環體電球</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"count":2,"pct":100,"pctPer":10,"sec":6,"m":8,"rps":0.7}</t>
         </is>
       </c>
       <c r="M135">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N135">
         <v>1.5</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
+          <t xml:space="preserve">額外召喚 {count} 個電球環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7728,17 +7580,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G136">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H136">
         <v>40</v>
       </c>
       <c r="I136">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -7747,40 +7599,45 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">貫穿冰箭</t>
+          <t xml:space="preserve">強化雷球</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":10,"mPer":2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M136">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N136">
         <v>1.5</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
+          <t xml:space="preserve">所有雷球與電球的雷電傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7790,17 +7647,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G137">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H137">
         <v>40</v>
       </c>
       <c r="I137">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -7809,40 +7666,45 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰箭散射</t>
+          <t xml:space="preserve">伴生雷球</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"sec":2}</t>
         </is>
       </c>
       <c r="M137">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N137">
         <v>1.5</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
+          <t xml:space="preserve">環體電球命中時有 {chance}% 機率在該處生成一個靜止雷球，持續 {sec} 秒（每次作用只判定一次機率）</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7852,17 +7714,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G138">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H138">
         <v>40</v>
       </c>
       <c r="I138">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -7871,23 +7733,23 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜凍結</t>
+          <t xml:space="preserve">雷殞天落</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":1,"stacksPer":0.4}</t>
+          <t xml:space="preserve">{"count":2,"pct":300,"pctPer":30,"m":15,"sec":3}</t>
         </is>
       </c>
       <c r="M138">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N138">
         <v>1.5</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
+          <t xml:space="preserve">額外召喚 {count} 個巨大雷球從天而降，各對 {m} 米內的敵人造成 {pct}% 雷電傷害，並以衝擊波擊暈 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -7924,49 +7786,49 @@
         <v>40</v>
       </c>
       <c r="I139">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|750</t>
+          <t xml:space="preserve">0|450</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰爆裂箭</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"m":6,"chaseM":30,"bodyM":1.5,"gap":0.1,"waves":3,"waveGap":0.3}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"deg":15,"castM":30,"speed":45}</t>
         </is>
       </c>
       <c r="M139">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N139">
         <v>1.5</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7980,13 +7842,13 @@
         </is>
       </c>
       <c r="G140">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H140">
         <v>40</v>
       </c>
       <c r="I140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7995,40 +7857,40 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒霜箭</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"arcM":8}</t>
+          <t xml:space="preserve">{"frostPct":50,"frostPctPer":5,"stacks":1}</t>
         </is>
       </c>
       <c r="M140">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N140">
         <v>1.5</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8042,13 +7904,13 @@
         </is>
       </c>
       <c r="G141">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H141">
         <v>40</v>
       </c>
       <c r="I141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -8057,40 +7919,40 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰逆轉</t>
+          <t xml:space="preserve">冰系強化</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M141">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N141">
         <v>1.5</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
+          <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8104,13 +7966,13 @@
         </is>
       </c>
       <c r="G142">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H142">
         <v>40</v>
       </c>
       <c r="I142">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -8119,40 +7981,40 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒流彈</t>
+          <t xml:space="preserve">貫穿冰箭</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"frostPct":50,"frostPctPer":20,"stacks":1}</t>
+          <t xml:space="preserve">{"m":10,"mPer":2}</t>
         </is>
       </c>
       <c r="M142">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N142">
         <v>1.5</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
+          <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8166,13 +8028,13 @@
         </is>
       </c>
       <c r="G143">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H143">
         <v>40</v>
       </c>
       <c r="I143">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8181,40 +8043,40 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒流爆散</t>
+          <t xml:space="preserve">冰箭散射</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":8,"bounce":2,"bouncePer":0.2}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M143">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N143">
         <v>1.5</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8228,13 +8090,13 @@
         </is>
       </c>
       <c r="G144">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H144">
         <v>40</v>
       </c>
       <c r="I144">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -8243,40 +8105,40 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜擴散</t>
+          <t xml:space="preserve">寒霜凍結</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":10,"count":1}</t>
+          <t xml:space="preserve">{"stacks":1,"stacksPer":0.4}</t>
         </is>
       </c>
       <c r="M144">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N144">
         <v>1.5</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
+          <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8290,13 +8152,13 @@
         </is>
       </c>
       <c r="G145">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H145">
         <v>40</v>
       </c>
       <c r="I145">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -8305,23 +8167,23 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重流水</t>
+          <t xml:space="preserve">寒冰爆裂箭</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"m":6,"chaseM":30,"bodyM":1.5,"gap":0.1,"waves":3,"waveGap":0.3}</t>
         </is>
       </c>
       <c r="M145">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N145">
         <v>1.5</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
+          <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
@@ -8358,49 +8220,49 @@
         <v>40</v>
       </c>
       <c r="I146">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|800</t>
+          <t xml:space="preserve">0|500</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">水龍捲</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"m":5,"side":10,"frozen":2,"gap":0.35}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"arcM":8}</t>
         </is>
       </c>
       <c r="M146">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N146">
         <v>1.5</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
+          <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8414,13 +8276,13 @@
         </is>
       </c>
       <c r="G147">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H147">
         <v>40</v>
       </c>
       <c r="I147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -8429,40 +8291,40 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">寒冰逆轉</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":6}</t>
         </is>
       </c>
       <c r="M147">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N147">
         <v>1.5</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
+          <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8476,13 +8338,13 @@
         </is>
       </c>
       <c r="G148">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H148">
         <v>40</v>
       </c>
       <c r="I148">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -8491,40 +8353,40 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜衝擊</t>
+          <t xml:space="preserve">寒流彈</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"frostPct":50,"frostPctPer":20,"stacks":1}</t>
         </is>
       </c>
       <c r="M148">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N148">
         <v>1.5</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
+          <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8538,13 +8400,13 @@
         </is>
       </c>
       <c r="G149">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H149">
         <v>40</v>
       </c>
       <c r="I149">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -8553,40 +8415,40 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰體</t>
+          <t xml:space="preserve">寒流爆散</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":1}</t>
+          <t xml:space="preserve">{"m":8,"bounce":2,"bouncePer":0.2}</t>
         </is>
       </c>
       <c r="M149">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N149">
         <v>1.5</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
+          <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8600,13 +8462,13 @@
         </is>
       </c>
       <c r="G150">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H150">
         <v>40</v>
       </c>
       <c r="I150">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -8615,40 +8477,40 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">極致寒霜</t>
+          <t xml:space="preserve">寒霜擴散</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
+          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":10,"count":1}</t>
         </is>
       </c>
       <c r="M150">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N150">
         <v>1.5</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
+          <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8662,13 +8524,13 @@
         </is>
       </c>
       <c r="G151">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H151">
         <v>40</v>
       </c>
       <c r="I151">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -8677,40 +8539,40 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重新星</t>
+          <t xml:space="preserve">三重流水</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
         </is>
       </c>
       <c r="M151">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N151">
         <v>1.5</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8724,13 +8586,13 @@
         </is>
       </c>
       <c r="G152">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H152">
         <v>40</v>
       </c>
       <c r="I152">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -8739,23 +8601,23 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">死亡新星</t>
+          <t xml:space="preserve">水龍捲</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
+          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"m":5,"side":10,"frozen":2,"gap":0.35}</t>
         </is>
       </c>
       <c r="M152">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N152">
         <v>1.5</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
+          <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
         </is>
       </c>
     </row>
@@ -8792,54 +8654,49 @@
         <v>40</v>
       </c>
       <c r="I153">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|850</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風雪</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
         </is>
       </c>
       <c r="M153">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N153">
         <v>1.5</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
+          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8849,17 +8706,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G154">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H154">
         <v>40</v>
       </c>
       <c r="I154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -8868,45 +8725,40 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜衝擊</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
+          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M154">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N154">
         <v>1.5</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8916,17 +8768,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G155">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H155">
         <v>40</v>
       </c>
       <c r="I155">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8935,45 +8787,40 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">巨型風刃</t>
+          <t xml:space="preserve">寒冰體</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
+          <t xml:space="preserve">{"stacks":1}</t>
         </is>
       </c>
       <c r="M155">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N155">
         <v>1.5</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
+          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8983,17 +8830,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G156">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H156">
         <v>40</v>
       </c>
       <c r="I156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -9002,45 +8849,40 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重風刃</t>
+          <t xml:space="preserve">極致寒霜</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
+          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
         </is>
       </c>
       <c r="M156">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N156">
         <v>1.5</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
+          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9050,17 +8892,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G157">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H157">
         <v>40</v>
       </c>
       <c r="I157">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -9069,45 +8911,40 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂披風</t>
+          <t xml:space="preserve">三重新星</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
         </is>
       </c>
       <c r="M157">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N157">
         <v>1.5</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
+          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9117,17 +8954,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G158">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H158">
         <v>40</v>
       </c>
       <c r="I158">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -9136,45 +8973,40 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">追跡風刃</t>
+          <t xml:space="preserve">死亡新星</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
+          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
         </is>
       </c>
       <c r="M158">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N158">
         <v>1.5</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
+          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9184,17 +9016,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G159">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H159">
         <v>40</v>
       </c>
       <c r="I159">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -9203,23 +9035,23 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂風碎裂</t>
+          <t xml:space="preserve">暴風雪</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
         </is>
       </c>
       <c r="M159">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N159">
         <v>1.5</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
+          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -9261,49 +9093,54 @@
         <v>40</v>
       </c>
       <c r="I160">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|900</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風真空刃</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
         </is>
       </c>
       <c r="M160">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N160">
         <v>1.5</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
+          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9323,7 +9160,7 @@
         <v>40</v>
       </c>
       <c r="I161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -9332,40 +9169,45 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">巨型風刃</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
+          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
         </is>
       </c>
       <c r="M161">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N161">
         <v>1.5</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9385,7 +9227,7 @@
         <v>40</v>
       </c>
       <c r="I162">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -9394,40 +9236,45 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空爆震</t>
+          <t xml:space="preserve">雙重風刃</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
         </is>
       </c>
       <c r="M162">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N162">
         <v>1.5</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9447,7 +9294,7 @@
         <v>40</v>
       </c>
       <c r="I163">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -9456,40 +9303,45 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切</t>
+          <t xml:space="preserve">亂披風</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
         </is>
       </c>
       <c r="M163">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N163">
         <v>1.5</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9509,7 +9361,7 @@
         <v>40</v>
       </c>
       <c r="I164">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -9518,40 +9370,45 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋斬</t>
+          <t xml:space="preserve">追跡風刃</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
         </is>
       </c>
       <c r="M164">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N164">
         <v>1.5</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
+          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9571,7 +9428,7 @@
         <v>40</v>
       </c>
       <c r="I165">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -9580,40 +9437,45 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋三重奏</t>
+          <t xml:space="preserve">狂風碎裂</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
+          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
         </is>
       </c>
       <c r="M165">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N165">
         <v>1.5</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9633,7 +9495,7 @@
         <v>40</v>
       </c>
       <c r="I166">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -9642,23 +9504,23 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">無限風切</t>
+          <t xml:space="preserve">暴風真空刃</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
         </is>
       </c>
       <c r="M166">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N166">
         <v>1.5</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
+          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
@@ -9695,49 +9557,49 @@
         <v>40</v>
       </c>
       <c r="I167">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|950</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛空斬</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
         </is>
       </c>
       <c r="M167">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N167">
         <v>1.5</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9751,13 +9613,13 @@
         </is>
       </c>
       <c r="G168">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H168">
         <v>40</v>
       </c>
       <c r="I168">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -9766,40 +9628,40 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空爆震</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
         </is>
       </c>
       <c r="M168">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N168">
         <v>1.5</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9813,13 +9675,13 @@
         </is>
       </c>
       <c r="G169">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H169">
         <v>40</v>
       </c>
       <c r="I169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -9828,40 +9690,40 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風撕裂</t>
+          <t xml:space="preserve">風切</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
         </is>
       </c>
       <c r="M169">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N169">
         <v>1.5</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9875,13 +9737,13 @@
         </is>
       </c>
       <c r="G170">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H170">
         <v>40</v>
       </c>
       <c r="I170">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -9890,40 +9752,40 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂風切</t>
+          <t xml:space="preserve">迴旋斬</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
         </is>
       </c>
       <c r="M170">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N170">
         <v>1.5</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9937,13 +9799,13 @@
         </is>
       </c>
       <c r="G171">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H171">
         <v>40</v>
       </c>
       <c r="I171">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -9952,40 +9814,40 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風之刃</t>
+          <t xml:space="preserve">迴旋三重奏</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
         </is>
       </c>
       <c r="M171">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N171">
         <v>1.5</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9999,13 +9861,13 @@
         </is>
       </c>
       <c r="G172">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H172">
         <v>40</v>
       </c>
       <c r="I172">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -10014,40 +9876,40 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切擴散</t>
+          <t xml:space="preserve">無限風切</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M172">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N172">
         <v>1.5</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10061,13 +9923,13 @@
         </is>
       </c>
       <c r="G173">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H173">
         <v>40</v>
       </c>
       <c r="I173">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -10076,23 +9938,23 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">颶風屏障</t>
+          <t xml:space="preserve">虛空斬</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
         </is>
       </c>
       <c r="M173">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N173">
         <v>1.5</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -10129,30 +9991,402 @@
         <v>40</v>
       </c>
       <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|700</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+        </is>
+      </c>
+      <c r="M174">
+        <v>100000</v>
+      </c>
+      <c r="N174">
+        <v>1.5</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G175">
+        <v>24</v>
+      </c>
+      <c r="H175">
+        <v>40</v>
+      </c>
+      <c r="I175">
+        <v>2</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|750</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風撕裂</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+        </is>
+      </c>
+      <c r="M175">
+        <v>200000</v>
+      </c>
+      <c r="N175">
+        <v>1.5</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G176">
+        <v>24</v>
+      </c>
+      <c r="H176">
+        <v>40</v>
+      </c>
+      <c r="I176">
+        <v>3</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|800</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亂風切</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M176">
+        <v>400000</v>
+      </c>
+      <c r="N176">
+        <v>1.5</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G177">
+        <v>24</v>
+      </c>
+      <c r="H177">
+        <v>40</v>
+      </c>
+      <c r="I177">
+        <v>4</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|850</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風之刃</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+        </is>
+      </c>
+      <c r="M177">
+        <v>800000</v>
+      </c>
+      <c r="N177">
+        <v>1.5</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G178">
+        <v>24</v>
+      </c>
+      <c r="H178">
+        <v>40</v>
+      </c>
+      <c r="I178">
+        <v>5</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|900</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切擴散</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+        </is>
+      </c>
+      <c r="M178">
+        <v>1500000</v>
+      </c>
+      <c r="N178">
+        <v>1.5</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G179">
+        <v>24</v>
+      </c>
+      <c r="H179">
+        <v>40</v>
+      </c>
+      <c r="I179">
+        <v>6</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|950</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">颶風屏障</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+        </is>
+      </c>
+      <c r="M179">
+        <v>3000000</v>
+      </c>
+      <c r="N179">
+        <v>1.5</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G180">
+        <v>24</v>
+      </c>
+      <c r="H180">
+        <v>40</v>
+      </c>
+      <c r="I180">
         <v>7</v>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="J180" t="inlineStr">
         <is>
           <t xml:space="preserve">0|1000</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t xml:space="preserve">暴風神體</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">{"red":99,"sec":2,"secPer":0.2,"pct":100,"pctPer":10}</t>
         </is>
       </c>
-      <c r="M174">
+      <c r="M180">
         <v>5000000</v>
       </c>
-      <c r="N174">
-        <v>1.5</v>
-      </c>
-      <c r="O174" t="inlineStr">
+      <c r="N180">
+        <v>1.5</v>
+      </c>
+      <c r="O180" t="inlineStr">
         <is>
           <t xml:space="preserve">施放暴風屏障時同時召喚風暴之神附體：{sec} 秒內傷害減免 +{red}%，且自身的風系傷害額外 ×(1+{pct}%)</t>
         </is>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -3381,156 +3381,117 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">bloodrage</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">嗜血狂怒</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">💢</t>
-        </is>
-      </c>
-      <c r="G69">
-        <v>60</v>
+          <t xml:space="preserve">counter</t>
+        </is>
       </c>
       <c r="H69">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="I69">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|400</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血狂怒</t>
+          <t xml:space="preserve">神聖之體</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":8}</t>
+          <t xml:space="preserve">{"count":10,"pct":400,"pctPer":40,"m":8}</t>
         </is>
       </c>
       <c r="M69">
-        <v>100000</v>
+        <v>10000000</v>
       </c>
       <c r="N69">
         <v>1.5</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻速額外 +{pct}%（乘算，不受攻速上限限制），持續 {sec} 秒</t>
+          <t xml:space="preserve">每 {count} 次反擊後朝目標射出一顆光彈，對其周圍 {m} 米內的敵人造成 {pct}% 神聖傷害</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holyBody</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">bloodrage</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">嗜血狂怒</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">💢</t>
-        </is>
-      </c>
-      <c r="G70">
-        <v>60</v>
+          <t xml:space="preserve">counter</t>
+        </is>
       </c>
       <c r="H70">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I70">
-        <v>2</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|450</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂暴</t>
+          <t xml:space="preserve">不屈鬥魂</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"pct":2000,"pctPer":200,"m":30,"sec":5,"cd":60}</t>
         </is>
       </c>
       <c r="M70">
-        <v>200000</v>
+        <v>10000000</v>
       </c>
       <c r="N70">
         <v>1.5</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間爆擊傷害額外 +{pct}%（乘算）</t>
+          <t xml:space="preserve">死亡時對 {m} 米內的所有敵人造成 {pct}% 地系傷害，並在 {sec} 秒後原地復活繼續戰鬥（不算戰鬥失敗）；冷卻 {cd} 秒</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">indomitable</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">bloodrage</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">嗜血狂怒</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">💢</t>
-        </is>
-      </c>
-      <c r="G71">
-        <v>60</v>
+          <t xml:space="preserve">counter</t>
+        </is>
       </c>
       <c r="H71">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="I71">
-        <v>3</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|500</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒</t>
+          <t xml:space="preserve">戰神體</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"sec":1,"secPer":0.1}</t>
         </is>
       </c>
       <c r="M71">
-        <v>400000</v>
+        <v>10000000</v>
       </c>
       <c r="N71">
         <v>1.5</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間總傷害額外 +{pct}%（乘算）</t>
+          <t xml:space="preserve">你在 {sec} 秒內損失的生命百分比，會在接下來 {sec} 秒內的反擊中一併附加到敵人身上</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">warGodBody</t>
         </is>
       </c>
     </row>
@@ -3554,35 +3515,35 @@
         <v>60</v>
       </c>
       <c r="H72">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="I72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|550</t>
+          <t xml:space="preserve">0|400</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂化連殺</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":0.5,"addPer":0.1,"kill":0.1,"killMax":5}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":8}</t>
         </is>
       </c>
       <c r="M72">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="N72">
         <v>1.5</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間基礎連擊數 +{add}，且每擊殺 1 個敵人再 +{kill}（累計上限 +{killMax}；不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">攻速額外 +{pct}%（乘算，不受攻速上限限制），持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -3606,19 +3567,19 @@
         <v>60</v>
       </c>
       <c r="H73">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|600</t>
+          <t xml:space="preserve">0|450</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">嗜血反震</t>
+          <t xml:space="preserve">狂暴</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -3627,14 +3588,14 @@
         </is>
       </c>
       <c r="M73">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="N73">
         <v>1.5</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間反震傷害提高 {pct}%（乘算，可與其它反震加成疊加）</t>
+          <t xml:space="preserve">狂怒期間爆擊傷害額外 +{pct}%（乘算）</t>
         </is>
       </c>
     </row>
@@ -3658,35 +3619,35 @@
         <v>60</v>
       </c>
       <c r="H74">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="I74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|650</t>
+          <t xml:space="preserve">0|500</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">血飲術</t>
+          <t xml:space="preserve">狂怒</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"self":1,"m":80}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M74">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="N74">
         <v>1.5</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間傷害額外提高 {pct}%（乘算），但 {m} 米內的敵人每次受傷都會使你損失最大生命 {self}%（直接扣血，無法被護盾吸收）</t>
+          <t xml:space="preserve">狂怒期間總傷害額外 +{pct}%（乘算）</t>
         </is>
       </c>
     </row>
@@ -3710,407 +3671,308 @@
         <v>60</v>
       </c>
       <c r="H75">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="I75">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|700</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂血盛宴</t>
+          <t xml:space="preserve">狂化連殺</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":0.5,"pct":1,"pctPer":0.1,"count":1}</t>
+          <t xml:space="preserve">{"add":0.5,"addPer":0.1,"kill":0.1,"killMax":5}</t>
         </is>
       </c>
       <c r="M75">
-        <v>5000000</v>
+        <v>800000</v>
       </c>
       <c r="N75">
         <v>1.5</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂怒期間每擊殺 1 個敵人，持續時間延長 {sec} 秒；且生命值每減少 1%，傷害額外 +{pct}%（乘算，無限疊加），每 1 連擊數使普攻可同時攻擊 1 個敵人（無限疊加）</t>
+          <t xml:space="preserve">狂怒期間基礎連擊數 +{add}，且每擊殺 1 個敵人再 +{kill}（累計上限 +{killMax}；不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
+          <t xml:space="preserve">bloodrage</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">💢</t>
         </is>
       </c>
       <c r="G76">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H76">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I76">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|1</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血反震</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":15,"m":6,"castM":30}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M76">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="N76">
         <v>1.5</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">射出一顆火球（射程 {castM} 米），命中時爆炸，對目標及 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+          <t xml:space="preserve">狂怒期間反震傷害提高 {pct}%（乘算，可與其它反震加成疊加）</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
+          <t xml:space="preserve">bloodrage</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">💢</t>
         </is>
       </c>
       <c r="G77">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H77">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="I77">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|1</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃燒</t>
+          <t xml:space="preserve">血飲術</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dotPct":20,"dotPctPer":2,"dotSec":5,"dotGap":0.5}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"self":1,"m":80}</t>
         </is>
       </c>
       <c r="M77">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="N77">
         <v>1.5</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">被火球擊中的敵人陷入燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
+          <t xml:space="preserve">狂怒期間傷害額外提高 {pct}%（乘算），但 {m} 米內的敵人每次受傷都會使你損失最大生命 {self}%（直接扣血，無法被護盾吸收）</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
+          <t xml:space="preserve">bloodrage</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球術</t>
+          <t xml:space="preserve">嗜血狂怒</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">💢</t>
         </is>
       </c>
       <c r="G78">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H78">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|50</t>
+          <t xml:space="preserve">0|700</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球爆裂</t>
+          <t xml:space="preserve">狂血盛宴</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"count":3,"m":20}</t>
+          <t xml:space="preserve">{"sec":0.5,"pct":1,"pctPer":0.1,"count":1}</t>
         </is>
       </c>
       <c r="M78">
-        <v>400000</v>
+        <v>5000000</v>
       </c>
       <c r="N78">
         <v>1.5</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">火球爆炸後分裂出 {count} 個小火球，射向目標 {m} 米內的敵人，每個造成原始火球 {pct}% 的傷害</t>
+          <t xml:space="preserve">狂怒期間每擊殺 1 個敵人，持續時間延長 {sec} 秒；且生命值每減少 1%，傷害額外 +{pct}%（乘算，無限疊加），每 1 連擊數使普攻可同時攻擊 1 個敵人（無限疊加）</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火球術</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
-        </is>
-      </c>
-      <c r="G79">
-        <v>14</v>
+          <t xml:space="preserve">bloodrage</t>
+        </is>
       </c>
       <c r="H79">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I79">
-        <v>4</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|100</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化燃燒</t>
+          <t xml:space="preserve">殺神降臨</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":0.4,"gapPer":-0.015}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"m":8}</t>
         </is>
       </c>
       <c r="M79">
-        <v>800000</v>
+        <v>10000000</v>
       </c>
       <c r="N79">
         <v>1.5</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃燒的作用間隔縮短至 {gap} 秒（跳得更快＝總傷更高）</t>
+          <t xml:space="preserve">狂怒期間普攻傷害 +{pct}%，且同時對目標周圍 {m} 米內的所有敵人造成傷害</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slayerAdvent</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火球術</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
-        </is>
-      </c>
-      <c r="G80">
-        <v>14</v>
+          <t xml:space="preserve">bloodrage</t>
+        </is>
       </c>
       <c r="H80">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="I80">
-        <v>5</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|150</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">爆燃</t>
+          <t xml:space="preserve">戰神屠錄</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"m":12}</t>
+          <t xml:space="preserve">{"pct":4,"maxStacks":100,"maxStacksPer":10}</t>
         </is>
       </c>
       <c r="M80">
-        <v>1500000</v>
+        <v>10000000</v>
       </c>
       <c r="N80">
         <v>1.5</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃燒結束或敵人死亡時爆炸，對我方 {m} 米內的 {count} 個敵人造成該敵人整段燃燒累積傷害 {pct}% 的傷害</t>
+          <t xml:space="preserve">狂怒期間你無法獲得護盾，但每殺死 1 個敵人使你造成的所有傷害 +{pct}%，最多 {maxStacks} 層，持續到你死亡為止</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">warGodRoll</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">fireball</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火球術</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🔥</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
-        </is>
-      </c>
-      <c r="G81">
-        <v>14</v>
+          <t xml:space="preserve">bloodrage</t>
+        </is>
       </c>
       <c r="H81">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I81">
-        <v>6</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|200</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">火焰增幅</t>
+          <t xml:space="preserve">阿修羅霸王拳</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":0.25,"pctPer":0.025,"sec":4,"m":20}</t>
+          <t xml:space="preserve">{"pct":500,"pctPer":50,"sec":1,"secPer":0.1,"gap":10}</t>
         </is>
       </c>
       <c r="M81">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="N81">
         <v>1.5</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">我方 {m} 米內每有 1 次燃燒作用，你的火焰傷害 +{pct}%，持續 {sec} 秒（無限疊加，每次疊加時重置時間）</t>
+          <t xml:space="preserve">每 {gap} 秒，你造成的所有傷害 +{pct}%，持續 {sec} 秒</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asuraFist</t>
         </is>
       </c>
     </row>
@@ -4144,52 +4006,52 @@
         <v>14</v>
       </c>
       <c r="H82">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="I82">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|250</t>
+          <t xml:space="preserve">0|1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">殞石術</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":15,"castM":20}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":15,"m":6,"castM":30}</t>
         </is>
       </c>
       <c r="M82">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N82">
         <v>1.5</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為召喚 {count} 顆巨大火殞石從天而降（射程 {castM} 米），每顆對目標 {m} 米內的敵人造成 {pct}% 火焰傷害，且殞石造成的燃燒傷害為 2 倍（第 2~6 階效果仍然生效）</t>
+          <t xml:space="preserve">射出一顆火球（射程 {castM} 米），命中時爆炸，對目標及 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4206,52 +4068,52 @@
         <v>14</v>
       </c>
       <c r="H83">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|50</t>
+          <t xml:space="preserve">0|1</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">燃燒</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":60,"pctPer":6,"hits":5,"m":3,"castM":30,"sec":2.5}</t>
+          <t xml:space="preserve">{"dotPct":20,"dotPctPer":2,"dotSec":5,"dotGap":0.5}</t>
         </is>
       </c>
       <c r="M83">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N83">
         <v>1.5</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">在敵人腳下召喚一道火柱（射程 {castM} 米），對目標 {m} 米內的敵人連續造成 {hits} 段傷害，每段 {pct}% 火焰傷害（全程約 {sec} 秒）</t>
+          <t xml:space="preserve">被火球擊中的敵人陷入燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4268,52 +4130,52 @@
         <v>14</v>
       </c>
       <c r="H84">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|100</t>
+          <t xml:space="preserve">0|50</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍捲噴發</t>
+          <t xml:space="preserve">火球爆裂</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":10,"pctPer":2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"count":3,"m":20}</t>
         </is>
       </c>
       <c r="M84">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N84">
         <v>1.5</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">火柱的傷害範圍擴大 {pct}%</t>
+          <t xml:space="preserve">火球爆炸後分裂出 {count} 個小火球，射向目標 {m} 米內的敵人，每個造成原始火球 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4330,52 +4192,52 @@
         <v>14</v>
       </c>
       <c r="H85">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|150</t>
+          <t xml:space="preserve">0|100</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重龍捲</t>
+          <t xml:space="preserve">強化燃燒</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":20,"pctPer":2,"m":20}</t>
+          <t xml:space="preserve">{"gap":0.4,"gapPer":-0.015}</t>
         </is>
       </c>
       <c r="M85">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N85">
         <v>1.5</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve">可同時對 {m} 米內的 {count} 個目標施放火柱，且火焰傷害額外 +{pct}%</t>
+          <t xml:space="preserve">燃燒的作用間隔縮短至 {gap} 秒（跳得更快＝總傷更高）</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4392,52 +4254,52 @@
         <v>14</v>
       </c>
       <c r="H86">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="I86">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|200</t>
+          <t xml:space="preserve">0|150</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">燃燒</t>
+          <t xml:space="preserve">爆燃</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":20,"chancePer":2,"dotPct":20,"dotSec":4,"dotGap":0.5}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"m":12}</t>
         </is>
       </c>
       <c r="M86">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N86">
         <v>1.5</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">火柱每次作用時有 {chance}% 機率使敵人燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
+          <t xml:space="preserve">燃燒結束或敵人死亡時爆炸，對我方 {m} 米內的 {count} 個敵人造成該敵人整段燃燒累積傷害 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4454,52 +4316,52 @@
         <v>14</v>
       </c>
       <c r="H87">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="I87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|250</t>
+          <t xml:space="preserve">0|200</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">烈焰衝擊</t>
+          <t xml:space="preserve">火焰增幅</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"m":6}</t>
+          <t xml:space="preserve">{"pct":0.25,"pctPer":0.025,"sec":4,"m":20}</t>
         </is>
       </c>
       <c r="M87">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N87">
         <v>1.5</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲或火牆消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+          <t xml:space="preserve">我方 {m} 米內每有 1 次燃燒作用，你的火焰傷害 +{pct}%，持續 {sec} 秒（無限疊加，每次疊加時重置時間）</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">firepillar</t>
+          <t xml:space="preserve">fireball</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲</t>
+          <t xml:space="preserve">火球術</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌋</t>
+          <t xml:space="preserve">🔥</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4516,35 +4378,35 @@
         <v>14</v>
       </c>
       <c r="H88">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="I88">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|300</t>
+          <t xml:space="preserve">0|250</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">重生</t>
+          <t xml:space="preserve">殞石術</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":20}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":15,"castM":20}</t>
         </is>
       </c>
       <c r="M88">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N88">
         <v>1.5</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve">火柱消失後有 {chance}% 機率在我方 {m} 米內的敵人身上重生</t>
+          <t xml:space="preserve">改為召喚 {count} 顆巨大火殞石從天而降（射程 {castM} 米），每顆對目標 {m} 米內的敵人造成 {pct}% 火焰傷害，且殞石造成的燃燒傷害為 2 倍（第 2~6 階效果仍然生效）</t>
         </is>
       </c>
     </row>
@@ -4578,57 +4440,52 @@
         <v>14</v>
       </c>
       <c r="H89">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="I89">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|350</t>
+          <t xml:space="preserve">0|50</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">無限火牆</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":3,"hits":8,"pct":100,"pctPer":10,"len":18,"wid":6,"respawn":1}</t>
+          <t xml:space="preserve">{"pct":60,"pctPer":6,"hits":5,"m":3,"castM":30,"sec":2.5}</t>
         </is>
       </c>
       <c r="M89">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N89">
         <v>1.5</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為施放 {count} 道火牆（橫向 {len}×{wid} 米），每道造成 {hits} 段 {pct}% 火焰傷害；每道火牆消失後再召喚 1 道（僅能再觸發一次；第 2~6 階效果仍然生效）</t>
+          <t xml:space="preserve">在敵人腳下召喚一道火柱（射程 {castM} 米），對目標 {m} 米內的敵人連續造成 {hits} 段傷害，每段 {pct}% 火焰傷害（全程約 {sec} 秒）</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4642,13 +4499,13 @@
         </is>
       </c>
       <c r="G90">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H90">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4657,45 +4514,40 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">龍捲噴發</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"count":2,"sec":4,"m":8,"rps":0.455,"castM":8}</t>
+          <t xml:space="preserve">{"pct":10,"pctPer":2}</t>
         </is>
       </c>
       <c r="M90">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N90">
         <v>1.5</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t xml:space="preserve">召喚 {count} 團火狩環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">火柱的傷害範圍擴大 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4709,13 +4561,13 @@
         </is>
       </c>
       <c r="G91">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H91">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4724,45 +4576,40 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化火狩</t>
+          <t xml:space="preserve">雙重龍捲</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"count":2,"pct":20,"pctPer":2,"m":20}</t>
         </is>
       </c>
       <c r="M91">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N91">
         <v>1.5</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩的體積與環繞範圍同步擴大 {pct}%</t>
+          <t xml:space="preserve">可同時對 {m} 米內的 {count} 個目標施放火柱，且火焰傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4776,13 +4623,13 @@
         </is>
       </c>
       <c r="G92">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H92">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I92">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4791,45 +4638,40 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">伴生火狩</t>
+          <t xml:space="preserve">燃燒</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":20,"chancePer":2,"m":1}</t>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"dotPct":20,"dotSec":4,"dotGap":0.5}</t>
         </is>
       </c>
       <c r="M92">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N92">
         <v>1.5</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩命中時有 {chance}% 機率在其後方 {m} 米處伴生一團火狩（每團只能伴生一次，伴生出的不再伴生）</t>
+          <t xml:space="preserve">火柱每次作用時有 {chance}% 機率使敵人燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4843,13 +4685,13 @@
         </is>
       </c>
       <c r="G93">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H93">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="I93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4858,45 +4700,40 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重火狩</t>
+          <t xml:space="preserve">烈焰衝擊</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":3,"pct":120,"pctPer":12,"sec":4}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"m":6}</t>
         </is>
       </c>
       <c r="M93">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N93">
         <v>1.5</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為召喚 {count} 團火狩，每團造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">火龍捲或火牆消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4910,13 +4747,13 @@
         </is>
       </c>
       <c r="G94">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H94">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="I94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4925,45 +4762,40 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">極速火狩</t>
+          <t xml:space="preserve">重生</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
+          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":20}</t>
         </is>
       </c>
       <c r="M94">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N94">
         <v>1.5</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩的旋轉速度 +{pct}%</t>
+          <t xml:space="preserve">火柱消失後有 {chance}% 機率在我方 {m} 米內的敵人身上重生</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">firehunt</t>
+          <t xml:space="preserve">firepillar</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩</t>
+          <t xml:space="preserve">火龍捲</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">☄️</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3*3</t>
+          <t xml:space="preserve">🌋</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4977,13 +4809,13 @@
         </is>
       </c>
       <c r="G95">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H95">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="I95">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4992,23 +4824,23 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">再生</t>
+          <t xml:space="preserve">無限火牆</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":0.4,"secPer":0.04}</t>
+          <t xml:space="preserve">{"count":3,"hits":8,"pct":100,"pctPer":10,"len":18,"wid":6,"respawn":1}</t>
         </is>
       </c>
       <c r="M95">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N95">
         <v>1.5</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve">火狩每擊殺 1 個敵人，全部火狩的持續時間延長 {sec} 秒</t>
+          <t xml:space="preserve">改為施放 {count} 道火牆（橫向 {len}×{wid} 米），每道造成 {hits} 段 {pct}% 火焰傷害；每道火牆消失後再召喚 1 道（僅能再觸發一次；第 2~6 階效果仍然生效）</t>
         </is>
       </c>
     </row>
@@ -5047,52 +4879,57 @@
         <v>26</v>
       </c>
       <c r="H96">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="I96">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|400</t>
+          <t xml:space="preserve">0|100</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">狩神之舞</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"rings":2,"pct":150,"pctPer":15,"sec":6,"m":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"count":2,"sec":4,"m":8,"rps":0.455,"castM":8}</t>
         </is>
       </c>
       <c r="M96">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N96">
         <v>1.5</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為一次施放 {rings} 道火狩（外圈距內圈 {m} 米、兩道旋轉方向相反），每團造成 {pct}% 火焰傷害、出現時自帶伴生，持續 {sec} 秒</t>
+          <t xml:space="preserve">召喚 {count} 團火狩環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5102,17 +4939,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G97">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H97">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5121,40 +4958,45 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">強化火狩</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"sec":10,"castM":30}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M97">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N97">
         <v>1.5</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放岩甲強化自身，獲得最大生命值 {pct}% 的岩甲護盾，持續 {sec} 秒</t>
+          <t xml:space="preserve">火狩的體積與環繞範圍同步擴大 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5164,17 +5006,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G98">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H98">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5183,40 +5025,45 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化岩甲</t>
+          <t xml:space="preserve">伴生火狩</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"m":1}</t>
         </is>
       </c>
       <c r="M98">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N98">
         <v>1.5</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化岩甲，額外獲得最大生命值 {pct}% 的岩甲護盾（與第 1 階累加）</t>
+          <t xml:space="preserve">火狩命中時有 {chance}% 機率在其後方 {m} 米處伴生一團火狩（每團只能伴生一次，伴生出的不再伴生）</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5226,17 +5073,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G99">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H99">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I99">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -5245,40 +5092,45 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲尖刺</t>
+          <t xml:space="preserve">三重火狩</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":5,"pctPer":0.5}</t>
+          <t xml:space="preserve">{"count":3,"pct":120,"pctPer":12,"sec":4}</t>
         </is>
       </c>
       <c r="M99">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N99">
         <v>1.5</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，攻擊你的敵人會遭受你最大生命值 {pct}% 的地系傷害（獨立於反震，兩者各自結算）</t>
+          <t xml:space="preserve">改為召喚 {count} 團火狩，每團造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5288,17 +5140,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G100">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H100">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="I100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5307,40 +5159,45 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">護盾增幅</t>
+          <t xml:space="preserve">極速火狩</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
         </is>
       </c>
       <c r="M100">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N100">
         <v>1.5</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t xml:space="preserve">主動型被動（裝配到技能列即恆時生效）：你獲得的所有護盾效率額外 +{pct}%（乘算）</t>
+          <t xml:space="preserve">火狩的旋轉速度 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5350,17 +5207,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G101">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H101">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="I101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5369,40 +5226,45 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩之再生</t>
+          <t xml:space="preserve">再生</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":1,"pctPer":0.1}</t>
+          <t xml:space="preserve">{"sec":0.4,"secPer":0.04}</t>
         </is>
       </c>
       <c r="M101">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N101">
         <v>1.5</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 生命值即獲得最大生命 {pct}% 的護盾</t>
+          <t xml:space="preserve">火狩每擊殺 1 個敵人，全部火狩的持續時間延長 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
+          <t xml:space="preserve">firehunt</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">火狩</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">🪨</t>
+          <t xml:space="preserve">☄️</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3*3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5412,17 +5274,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">earth</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="G102">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H102">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="I102">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5431,23 +5293,23 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲增幅</t>
+          <t xml:space="preserve">狩神之舞</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":0.5,"pctPer":0.05,"max":30,"sec":3}</t>
+          <t xml:space="preserve">{"rings":2,"pct":150,"pctPer":15,"sec":6,"m":6}</t>
         </is>
       </c>
       <c r="M102">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N102">
         <v>1.5</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 護盾即獲得 {pct}% 傷害增幅（乘算），最多疊 {max} 層，持續 {sec} 秒</t>
+          <t xml:space="preserve">改為一次施放 {rings} 道火狩（外圈距內圈 {m} 米、兩道旋轉方向相反），每團造成 {pct}% 火焰傷害、出現時自帶伴生，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -5484,54 +5346,49 @@
         <v>40</v>
       </c>
       <c r="I103">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|450</t>
+          <t xml:space="preserve">0|150</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">天地逆返</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"sec":10,"castM":30}</t>
         </is>
       </c>
       <c r="M103">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N103">
         <v>1.5</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，護盾剩餘量越低則傷害減免越高，護盾歸零時最高額外 +{pct}% 傷害減免（乘算）</t>
+          <t xml:space="preserve">施放岩甲強化自身，獲得最大生命值 {pct}% 的岩甲護盾，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5545,13 +5402,13 @@
         </is>
       </c>
       <c r="G104">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H104">
         <v>40</v>
       </c>
       <c r="I104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5560,45 +5417,40 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">強化岩甲</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.4,"castM":20,"move":30,"aspd":50}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M104">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N104">
         <v>1.5</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t xml:space="preserve">在敵人腳下召喚一片 12×12 米的沼澤（射程 {castM} 米），沼澤中的敵人陷入緩速（移動速度 -{move}%、攻速 -{aspd}%），持續 {sec} 秒</t>
+          <t xml:space="preserve">進一步強化岩甲，額外獲得最大生命值 {pct}% 的岩甲護盾（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5612,13 +5464,13 @@
         </is>
       </c>
       <c r="G105">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H105">
         <v>40</v>
       </c>
       <c r="I105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5627,45 +5479,40 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛弱</t>
+          <t xml:space="preserve">岩甲尖刺</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"pct":5,"pctPer":0.5}</t>
         </is>
       </c>
       <c r="M105">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N105">
         <v>1.5</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t xml:space="preserve">受泥沼緩速影響的敵人，受到的傷害提高 {pct}%</t>
+          <t xml:space="preserve">岩甲護盾存在期間，攻擊你的敵人會遭受你最大生命值 {pct}% 的地系傷害（獨立於反震，兩者各自結算）</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5679,13 +5526,13 @@
         </is>
       </c>
       <c r="G106">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H106">
         <v>40</v>
       </c>
       <c r="I106">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5694,45 +5541,40 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒沼術</t>
+          <t xml:space="preserve">護盾增幅</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dotPct":25,"dotPctPer":2.5,"dotGap":0.5}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M106">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N106">
         <v>1.5</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤持續放出毒氣：沼澤中的敵人每 {dotGap} 秒受到魔法攻擊 {dotPct}% 的毒性傷害</t>
+          <t xml:space="preserve">主動型被動（裝配到技能列即恆時生效）：你獲得的所有護盾效率額外 +{pct}%（乘算）</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5746,13 +5588,13 @@
         </is>
       </c>
       <c r="G107">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H107">
         <v>40</v>
       </c>
       <c r="I107">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5761,45 +5603,40 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒沼增生</t>
+          <t xml:space="preserve">岩之再生</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":40}</t>
+          <t xml:space="preserve">{"pct":1,"pctPer":0.1}</t>
         </is>
       </c>
       <c r="M107">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N107">
         <v>1.5</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤結束時傳染給 {m} 米內較近的敵人，最多傳染 {add} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 生命值即獲得最大生命 {pct}% 的護盾</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5813,13 +5650,13 @@
         </is>
       </c>
       <c r="G108">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H108">
         <v>40</v>
       </c>
       <c r="I108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5828,45 +5665,40 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤漫延</t>
+          <t xml:space="preserve">岩甲增幅</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":6,"pct":40,"pctPer":4,"growSec":4}</t>
+          <t xml:space="preserve">{"pct":0.5,"pctPer":0.05,"max":30,"sec":3}</t>
         </is>
       </c>
       <c r="M108">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N108">
         <v>1.5</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤持續時間提高至 {sec} 秒，且在 {growSec} 秒內逐步擴大，最大擴增 {pct}%</t>
+          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 護盾即獲得 {pct}% 傷害增幅（乘算），最多疊 {max} 層，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5880,13 +5712,13 @@
         </is>
       </c>
       <c r="G109">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H109">
         <v>40</v>
       </c>
       <c r="I109">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5895,23 +5727,23 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">重力泥沼</t>
+          <t xml:space="preserve">天地逆返</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"move":50,"aspd":75,"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M109">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N109">
         <v>1.5</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t xml:space="preserve">緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%（與第 2 階累加）</t>
+          <t xml:space="preserve">岩甲護盾存在期間，護盾剩餘量越低則傷害減免越高，護盾歸零時最高額外 +{pct}% 傷害減免（乘算）</t>
         </is>
       </c>
     </row>
@@ -5953,49 +5785,54 @@
         <v>40</v>
       </c>
       <c r="I110">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|500</t>
+          <t xml:space="preserve">0|200</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">熔岩沼</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":8,"pct":20,"pctPer":2,"dotPct":70,"dotPctPer":7,"dotGap":0.4}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.4,"castM":20,"move":30,"aspd":50}</t>
         </is>
       </c>
       <c r="M110">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N110">
         <v>1.5</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤轉變為岩漿：持續時間提高至 {sec} 秒、範圍再擴增 {pct}%（與第 5 階累加），其中的目標每 {dotGap} 秒額外受到魔法攻擊 {dotPct}% 的火焰傷害</t>
+          <t xml:space="preserve">在敵人腳下召喚一片 12×12 米的沼澤（射程 {castM} 米），沼澤中的敵人陷入緩速（移動速度 -{move}%、攻速 -{aspd}%），持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6009,13 +5846,13 @@
         </is>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -6024,40 +5861,45 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">虛弱</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":10,"pctPer":1,"hp":20,"hpPer":2}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M111">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N111">
         <v>1.5</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve">主動型被動：自身傷害減免額外 +{pct}%、生命上限額外 +{hp}%（皆為乘算）</t>
+          <t xml:space="preserve">受泥沼緩速影響的敵人，受到的傷害提高 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6071,13 +5913,13 @@
         </is>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H112">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -6086,40 +5928,45 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地祝福</t>
+          <t xml:space="preserve">毒沼術</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
+          <t xml:space="preserve">{"dotPct":25,"dotPctPer":2.5,"dotGap":0.5}</t>
         </is>
       </c>
       <c r="M112">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N112">
         <v>1.5</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t xml:space="preserve">全屬性傷害額外 +{pct}%（與所有屬性增傷效果為額外的乘法計算）</t>
+          <t xml:space="preserve">沼澤持續放出毒氣：沼澤中的敵人每 {dotGap} 秒受到魔法攻擊 {dotPct}% 的毒性傷害</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6133,13 +5980,13 @@
         </is>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H113">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -6148,40 +5995,45 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命再生</t>
+          <t xml:space="preserve">毒沼增生</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":40}</t>
         </is>
       </c>
       <c r="M113">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N113">
         <v>1.5</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命回復額外 +{pct}%、吸血額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
+          <t xml:space="preserve">沼澤結束時傳染給 {m} 米內較近的敵人，最多傳染 {add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6195,13 +6047,13 @@
         </is>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H114">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6210,40 +6062,45 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔力再生</t>
+          <t xml:space="preserve">沼澤漫延</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
+          <t xml:space="preserve">{"sec":6,"pct":40,"pctPer":4,"growSec":4}</t>
         </is>
       </c>
       <c r="M114">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N114">
         <v>1.5</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t xml:space="preserve">法力回復額外 +{pct}%、吸魔額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
+          <t xml:space="preserve">沼澤持續時間提高至 {sec} 秒，且在 {growSec} 秒內逐步擴大，最大擴增 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6257,13 +6114,13 @@
         </is>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H115">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -6272,40 +6129,45 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法盾</t>
+          <t xml:space="preserve">重力泥沼</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+          <t xml:space="preserve">{"move":50,"aspd":75,"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M115">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N115">
         <v>1.5</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t xml:space="preserve">你的生命減少時，其中 {pct}% 改由消耗法力承擔（法力不足時只轉換付得起的部分，餘額仍扣生命）</t>
+          <t xml:space="preserve">緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%（與第 2 階累加）</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6319,13 +6181,13 @@
         </is>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H116">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I116">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -6334,23 +6196,23 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命反射之盾</t>
+          <t xml:space="preserve">熔岩沼</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":1,"pctPer":0.1,"m":20,"count":1}</t>
+          <t xml:space="preserve">{"sec":8,"pct":20,"pctPer":2,"dotPct":70,"dotPctPer":7,"dotGap":0.4}</t>
         </is>
       </c>
       <c r="M116">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N116">
         <v>1.5</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve">你每消耗 1% 生命或護盾，{m} 米內的 {count} 個敵人同步損失 {pct}% 最大生命</t>
+          <t xml:space="preserve">沼澤轉變為岩漿：持續時間提高至 {sec} 秒、範圍再擴增 {pct}%（與第 5 階累加），其中的目標每 {dotGap} 秒額外受到魔法攻擊 {dotPct}% 的火焰傷害</t>
         </is>
       </c>
     </row>
@@ -6384,52 +6246,52 @@
         <v>0</v>
       </c>
       <c r="H117">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I117">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|550</t>
+          <t xml:space="preserve">0|250</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">天地共生</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":8,"sec":5,"cd":60,"cdPer":-3}</t>
+          <t xml:space="preserve">{"pct":10,"pctPer":1,"hp":20,"hpPer":2}</t>
         </is>
       </c>
       <c r="M117">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N117">
         <v>1.5</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t xml:space="preserve">死亡時原地復活並回復 {pct}% 生命，復活後 {sec} 秒無敵；此招自身冷卻 {cd} 秒（顯示於技能格）</t>
+          <t xml:space="preserve">主動型被動：自身傷害減免額外 +{pct}%、生命上限額外 +{hp}%（皆為乘算）</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6439,17 +6301,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G118">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -6458,40 +6320,40 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地祝福</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":4,"m":30,"castM":30}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
         </is>
       </c>
       <c r="M118">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N118">
         <v>1.5</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t xml:space="preserve">丟出一道閃電鏈（射程 {castM} 米），在最多 {count} 個目標間彈射（每段彈射範圍 {m} 米），每擊造成 {pct}% 雷電傷害</t>
+          <t xml:space="preserve">全屬性傷害額外 +{pct}%（與所有屬性增傷效果為額外的乘法計算）</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6501,17 +6363,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G119">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -6520,40 +6382,40 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化閃電</t>
+          <t xml:space="preserve">生命再生</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
         </is>
       </c>
       <c r="M119">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N119">
         <v>1.5</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化閃電威力，閃電鏈傷害進一步 +{pct}% 雷電傷害</t>
+          <t xml:space="preserve">生命回復額外 +{pct}%、吸血額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6563,17 +6425,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G120">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H120">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6582,40 +6444,40 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷鳴術</t>
+          <t xml:space="preserve">魔力再生</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
         </is>
       </c>
       <c r="M120">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N120">
         <v>1.5</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t xml:space="preserve">被閃電鏈擊中的敵人額外再受到 {add} 次雷電傷害（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">法力回復額外 +{pct}%、吸魔額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6625,17 +6487,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G121">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I121">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6644,40 +6506,40 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化連鎖</t>
+          <t xml:space="preserve">魔法盾</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M121">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N121">
         <v>1.5</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電鏈的彈射數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">你的生命減少時，其中 {pct}% 改由消耗法力承擔（法力不足時只轉換付得起的部分，餘額仍扣生命）</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6687,17 +6549,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G122">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I122">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6706,40 +6568,40 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">電殛擴散</t>
+          <t xml:space="preserve">生命反射之盾</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":2.5,"count":1,"m":6}</t>
+          <t xml:space="preserve">{"pct":1,"pctPer":0.1,"m":20,"count":1}</t>
         </is>
       </c>
       <c r="M122">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N122">
         <v>1.5</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電鏈每次彈射時，額外對 {m} 米內的 {count} 個敵人造成閃電鏈 {pct}% 的雷電傷害</t>
+          <t xml:space="preserve">你每消耗 1% 生命或護盾，{m} 米內的 {count} 個敵人同步損失 {pct}% 最大生命</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6749,17 +6611,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G123">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I123">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6768,23 +6630,23 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷幻身</t>
+          <t xml:space="preserve">天地共生</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":8,"sec":5,"cd":60,"cdPer":-3}</t>
         </is>
       </c>
       <c r="M123">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N123">
         <v>1.5</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電鏈傷害額外 +{pct}% 雷電傷害；沒有其它彈射目標時可用自身當中繼點繼續彈射（彈到自身不消耗彈射數）</t>
+          <t xml:space="preserve">死亡時原地復活並回復 {pct}% 生命，復活後 {sec} 秒無敵；此招自身冷卻 {cd} 秒（顯示於技能格）</t>
         </is>
       </c>
     </row>
@@ -6821,49 +6683,49 @@
         <v>40</v>
       </c>
       <c r="I124">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|600</t>
+          <t xml:space="preserve">0|300</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電暴風</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":3,"add":1,"addPer":0.1,"pct":100,"pctPer":10,"chance":20}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":4,"m":30,"castM":30}</t>
         </is>
       </c>
       <c r="M124">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N124">
         <v>1.5</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t xml:space="preserve">同時發射 {count} 道閃電鏈，彈射數額外 +{add} 次，且閃電傷害額外 +{pct}%；每次彈射有 {chance}% 機率生成 1 條閃電鏈</t>
+          <t xml:space="preserve">丟出一道閃電鏈（射程 {castM} 米），在最多 {count} 個目標間彈射（每段彈射範圍 {m} 米），每擊造成 {pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6877,13 +6739,13 @@
         </is>
       </c>
       <c r="G125">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H125">
         <v>40</v>
       </c>
       <c r="I125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6892,40 +6754,40 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">強化閃電</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"count":2,"gap":0.2,"castM":30}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M125">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N125">
         <v>1.5</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 {castM} 米內的 {count} 個目標降下落雷（每道間隔 {gap} 秒），每道造成 {pct}% 雷電傷害</t>
+          <t xml:space="preserve">強化閃電威力，閃電鏈傷害進一步 +{pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6939,13 +6801,13 @@
         </is>
       </c>
       <c r="G126">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H126">
         <v>40</v>
       </c>
       <c r="I126">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6954,7 +6816,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷連鎖</t>
+          <t xml:space="preserve">雷鳴術</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -6963,31 +6825,31 @@
         </is>
       </c>
       <c r="M126">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N126">
         <v>1.5</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊目標額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">被閃電鏈擊中的敵人額外再受到 {add} 次雷電傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7001,13 +6863,13 @@
         </is>
       </c>
       <c r="G127">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H127">
         <v>40</v>
       </c>
       <c r="I127">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -7016,40 +6878,40 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重落雷</t>
+          <t xml:space="preserve">強化連鎖</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
         </is>
       </c>
       <c r="M127">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N127">
         <v>1.5</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t xml:space="preserve">對每個目標的攻擊次數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">閃電鏈的彈射數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7063,13 +6925,13 @@
         </is>
       </c>
       <c r="G128">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H128">
         <v>40</v>
       </c>
       <c r="I128">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -7078,40 +6940,40 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電增幅</t>
+          <t xml:space="preserve">電殛擴散</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5,"count":1,"m":6}</t>
         </is>
       </c>
       <c r="M128">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N128">
         <v>1.5</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化落雷傷害，額外 +{pct}% 雷電傷害</t>
+          <t xml:space="preserve">閃電鏈每次彈射時，額外對 {m} 米內的 {count} 個敵人造成閃電鏈 {pct}% 的雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7125,13 +6987,13 @@
         </is>
       </c>
       <c r="G129">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H129">
         <v>40</v>
       </c>
       <c r="I129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -7140,40 +7002,40 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電脈衝</t>
+          <t xml:space="preserve">雷幻身</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":1.5,"secPer":0.15,"count":2,"m":6}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M129">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N129">
         <v>1.5</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷落地時產生衝擊波，震暈目標本身與 {m} 米內共 {count} 個敵人 {sec} 秒</t>
+          <t xml:space="preserve">閃電鏈傷害額外 +{pct}% 雷電傷害；沒有其它彈射目標時可用自身當中繼點繼續彈射（彈到自身不消耗彈射數）</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7187,13 +7049,13 @@
         </is>
       </c>
       <c r="G130">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H130">
         <v>40</v>
       </c>
       <c r="I130">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -7202,23 +7064,23 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">迅雷重生</t>
+          <t xml:space="preserve">雷電暴風</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":20,"chancePer":2,"max":5}</t>
+          <t xml:space="preserve">{"count":3,"add":1,"addPer":0.1,"pct":100,"pctPer":10,"chance":20}</t>
         </is>
       </c>
       <c r="M130">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N130">
         <v>1.5</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t xml:space="preserve">每道落雷結束後有 {chance}% 機率再產生 1 道落雷（同一次施放最多再生 {max} 道）</t>
+          <t xml:space="preserve">同時發射 {count} 道閃電鏈，彈射數額外 +{add} 次，且閃電傷害額外 +{pct}%；每次彈射有 {chance}% 機率生成 1 條閃電鏈</t>
         </is>
       </c>
     </row>
@@ -7255,54 +7117,49 @@
         <v>40</v>
       </c>
       <c r="I131">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|650</t>
+          <t xml:space="preserve">0|350</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">殛道落電</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"mult":2,"pct":50,"pctPer":5,"m":6}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"count":2,"gap":0.2,"castM":30}</t>
         </is>
       </c>
       <c r="M131">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N131">
         <v>1.5</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷擊中時對目標 {m} 米內的所有敵人造成傷害；攻擊次數與目標數量 ×{mult}，且命中暈眩中的敵人時傷害額外 +{pct}%（與原傷害乘算）</t>
+          <t xml:space="preserve">對 {castM} 米內的 {count} 個目標降下落雷（每道間隔 {gap} 秒），每道造成 {pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7316,13 +7173,13 @@
         </is>
       </c>
       <c r="G132">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H132">
         <v>40</v>
       </c>
       <c r="I132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -7331,45 +7188,40 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷連鎖</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"gap":0.35,"sec":2,"m":3,"speed":6,"castM":30}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M132">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N132">
         <v>1.5</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t xml:space="preserve">召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
+          <t xml:space="preserve">攻擊目標額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7383,13 +7235,13 @@
         </is>
       </c>
       <c r="G133">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H133">
         <v>40</v>
       </c>
       <c r="I133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -7398,45 +7250,40 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">擴增雷球</t>
+          <t xml:space="preserve">雙重落雷</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M133">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N133">
         <v>1.5</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球的體積擴大 {pct}%</t>
+          <t xml:space="preserve">對每個目標的攻擊次數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7450,13 +7297,13 @@
         </is>
       </c>
       <c r="G134">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H134">
         <v>40</v>
       </c>
       <c r="I134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -7465,45 +7312,40 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">多重雷球</t>
+          <t xml:space="preserve">閃電增幅</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M134">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N134">
         <v>1.5</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球數量額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">進一步強化落雷傷害，額外 +{pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7517,13 +7359,13 @@
         </is>
       </c>
       <c r="G135">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H135">
         <v>40</v>
       </c>
       <c r="I135">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -7532,45 +7374,40 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">環體電球</t>
+          <t xml:space="preserve">雷電脈衝</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":100,"pctPer":10,"sec":6,"m":8,"rps":0.7}</t>
+          <t xml:space="preserve">{"sec":1.5,"secPer":0.15,"count":2,"m":6}</t>
         </is>
       </c>
       <c r="M135">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N135">
         <v>1.5</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 {count} 個電球環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">落雷落地時產生衝擊波，震暈目標本身與 {m} 米內共 {count} 個敵人 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7584,13 +7421,13 @@
         </is>
       </c>
       <c r="G136">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H136">
         <v>40</v>
       </c>
       <c r="I136">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -7599,45 +7436,40 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化雷球</t>
+          <t xml:space="preserve">迅雷重生</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"max":5}</t>
         </is>
       </c>
       <c r="M136">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N136">
         <v>1.5</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有雷球與電球的雷電傷害額外 +{pct}%</t>
+          <t xml:space="preserve">每道落雷結束後有 {chance}% 機率再產生 1 道落雷（同一次施放最多再生 {max} 道）</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7651,13 +7483,13 @@
         </is>
       </c>
       <c r="G137">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H137">
         <v>40</v>
       </c>
       <c r="I137">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -7666,23 +7498,23 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">伴生雷球</t>
+          <t xml:space="preserve">殛道落電</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"sec":2}</t>
+          <t xml:space="preserve">{"mult":2,"pct":50,"pctPer":5,"m":6}</t>
         </is>
       </c>
       <c r="M137">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N137">
         <v>1.5</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t xml:space="preserve">環體電球命中時有 {chance}% 機率在該處生成一個靜止雷球，持續 {sec} 秒（每次作用只判定一次機率）</t>
+          <t xml:space="preserve">落雷擊中時對目標 {m} 米內的所有敵人造成傷害；攻擊次數與目標數量 ×{mult}，且命中暈眩中的敵人時傷害額外 +{pct}%（與原傷害乘算）</t>
         </is>
       </c>
     </row>
@@ -7724,49 +7556,54 @@
         <v>40</v>
       </c>
       <c r="I138">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|700</t>
+          <t xml:space="preserve">0|400</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷殞天落</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":300,"pctPer":30,"m":15,"sec":3}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"gap":0.35,"sec":2,"m":3,"speed":6,"castM":30}</t>
         </is>
       </c>
       <c r="M138">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N138">
         <v>1.5</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 {count} 個巨大雷球從天而降，各對 {m} 米內的敵人造成 {pct}% 雷電傷害，並以衝擊波擊暈 {sec} 秒</t>
+          <t xml:space="preserve">召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7776,17 +7613,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G139">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H139">
         <v>40</v>
       </c>
       <c r="I139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -7795,40 +7632,45 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">擴增雷球</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"deg":15,"castM":30,"speed":45}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M139">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N139">
         <v>1.5</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">雷球的體積擴大 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7838,17 +7680,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G140">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H140">
         <v>40</v>
       </c>
       <c r="I140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7857,40 +7699,45 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜箭</t>
+          <t xml:space="preserve">多重雷球</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"frostPct":50,"frostPctPer":5,"stacks":1}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M140">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N140">
         <v>1.5</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
+          <t xml:space="preserve">雷球數量額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7900,17 +7747,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G141">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H141">
         <v>40</v>
       </c>
       <c r="I141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7919,40 +7766,45 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰系強化</t>
+          <t xml:space="preserve">環體電球</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"count":2,"pct":100,"pctPer":10,"sec":6,"m":8,"rps":0.7}</t>
         </is>
       </c>
       <c r="M141">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N141">
         <v>1.5</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
+          <t xml:space="preserve">額外召喚 {count} 個電球環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7962,17 +7814,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G142">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H142">
         <v>40</v>
       </c>
       <c r="I142">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -7981,40 +7833,45 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">貫穿冰箭</t>
+          <t xml:space="preserve">強化雷球</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":10,"mPer":2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M142">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N142">
         <v>1.5</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
+          <t xml:space="preserve">所有雷球與電球的雷電傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8024,17 +7881,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G143">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H143">
         <v>40</v>
       </c>
       <c r="I143">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8043,40 +7900,45 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰箭散射</t>
+          <t xml:space="preserve">伴生雷球</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"sec":2}</t>
         </is>
       </c>
       <c r="M143">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N143">
         <v>1.5</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
+          <t xml:space="preserve">環體電球命中時有 {chance}% 機率在該處生成一個靜止雷球，持續 {sec} 秒（每次作用只判定一次機率）</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8086,17 +7948,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G144">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H144">
         <v>40</v>
       </c>
       <c r="I144">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -8105,23 +7967,23 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜凍結</t>
+          <t xml:space="preserve">雷殞天落</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":1,"stacksPer":0.4}</t>
+          <t xml:space="preserve">{"count":2,"pct":300,"pctPer":30,"m":15,"sec":3}</t>
         </is>
       </c>
       <c r="M144">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N144">
         <v>1.5</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
+          <t xml:space="preserve">額外召喚 {count} 個巨大雷球從天而降，各對 {m} 米內的敵人造成 {pct}% 雷電傷害，並以衝擊波擊暈 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -8158,49 +8020,49 @@
         <v>40</v>
       </c>
       <c r="I145">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|750</t>
+          <t xml:space="preserve">0|450</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰爆裂箭</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"m":6,"chaseM":30,"bodyM":1.5,"gap":0.1,"waves":3,"waveGap":0.3}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"deg":15,"castM":30,"speed":45}</t>
         </is>
       </c>
       <c r="M145">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N145">
         <v>1.5</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8214,13 +8076,13 @@
         </is>
       </c>
       <c r="G146">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H146">
         <v>40</v>
       </c>
       <c r="I146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -8229,40 +8091,40 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒霜箭</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"arcM":8}</t>
+          <t xml:space="preserve">{"frostPct":50,"frostPctPer":5,"stacks":1}</t>
         </is>
       </c>
       <c r="M146">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N146">
         <v>1.5</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8276,13 +8138,13 @@
         </is>
       </c>
       <c r="G147">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H147">
         <v>40</v>
       </c>
       <c r="I147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -8291,40 +8153,40 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰逆轉</t>
+          <t xml:space="preserve">冰系強化</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M147">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N147">
         <v>1.5</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
+          <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8338,13 +8200,13 @@
         </is>
       </c>
       <c r="G148">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H148">
         <v>40</v>
       </c>
       <c r="I148">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -8353,40 +8215,40 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒流彈</t>
+          <t xml:space="preserve">貫穿冰箭</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"frostPct":50,"frostPctPer":20,"stacks":1}</t>
+          <t xml:space="preserve">{"m":10,"mPer":2}</t>
         </is>
       </c>
       <c r="M148">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N148">
         <v>1.5</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
+          <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8400,13 +8262,13 @@
         </is>
       </c>
       <c r="G149">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H149">
         <v>40</v>
       </c>
       <c r="I149">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -8415,40 +8277,40 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒流爆散</t>
+          <t xml:space="preserve">冰箭散射</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":8,"bounce":2,"bouncePer":0.2}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M149">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N149">
         <v>1.5</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8462,13 +8324,13 @@
         </is>
       </c>
       <c r="G150">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H150">
         <v>40</v>
       </c>
       <c r="I150">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -8477,40 +8339,40 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜擴散</t>
+          <t xml:space="preserve">寒霜凍結</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":10,"count":1}</t>
+          <t xml:space="preserve">{"stacks":1,"stacksPer":0.4}</t>
         </is>
       </c>
       <c r="M150">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N150">
         <v>1.5</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
+          <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8524,13 +8386,13 @@
         </is>
       </c>
       <c r="G151">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H151">
         <v>40</v>
       </c>
       <c r="I151">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -8539,23 +8401,23 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重流水</t>
+          <t xml:space="preserve">寒冰爆裂箭</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"m":6,"chaseM":30,"bodyM":1.5,"gap":0.1,"waves":3,"waveGap":0.3}</t>
         </is>
       </c>
       <c r="M151">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N151">
         <v>1.5</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
+          <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
@@ -8592,49 +8454,49 @@
         <v>40</v>
       </c>
       <c r="I152">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|800</t>
+          <t xml:space="preserve">0|500</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">水龍捲</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"m":5,"side":10,"frozen":2,"gap":0.35}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"arcM":8}</t>
         </is>
       </c>
       <c r="M152">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N152">
         <v>1.5</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
+          <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8648,13 +8510,13 @@
         </is>
       </c>
       <c r="G153">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H153">
         <v>40</v>
       </c>
       <c r="I153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -8663,40 +8525,40 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">寒冰逆轉</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":6}</t>
         </is>
       </c>
       <c r="M153">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N153">
         <v>1.5</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
+          <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8710,13 +8572,13 @@
         </is>
       </c>
       <c r="G154">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H154">
         <v>40</v>
       </c>
       <c r="I154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -8725,40 +8587,40 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜衝擊</t>
+          <t xml:space="preserve">寒流彈</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"frostPct":50,"frostPctPer":20,"stacks":1}</t>
         </is>
       </c>
       <c r="M154">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N154">
         <v>1.5</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
+          <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8772,13 +8634,13 @@
         </is>
       </c>
       <c r="G155">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H155">
         <v>40</v>
       </c>
       <c r="I155">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8787,40 +8649,40 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰體</t>
+          <t xml:space="preserve">寒流爆散</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":1}</t>
+          <t xml:space="preserve">{"m":8,"bounce":2,"bouncePer":0.2}</t>
         </is>
       </c>
       <c r="M155">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N155">
         <v>1.5</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
+          <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8834,13 +8696,13 @@
         </is>
       </c>
       <c r="G156">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H156">
         <v>40</v>
       </c>
       <c r="I156">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -8849,40 +8711,40 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">極致寒霜</t>
+          <t xml:space="preserve">寒霜擴散</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
+          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":10,"count":1}</t>
         </is>
       </c>
       <c r="M156">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N156">
         <v>1.5</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
+          <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8896,13 +8758,13 @@
         </is>
       </c>
       <c r="G157">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H157">
         <v>40</v>
       </c>
       <c r="I157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -8911,40 +8773,40 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重新星</t>
+          <t xml:space="preserve">三重流水</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
         </is>
       </c>
       <c r="M157">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N157">
         <v>1.5</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8958,13 +8820,13 @@
         </is>
       </c>
       <c r="G158">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H158">
         <v>40</v>
       </c>
       <c r="I158">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -8973,23 +8835,23 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">死亡新星</t>
+          <t xml:space="preserve">水龍捲</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
+          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"m":5,"side":10,"frozen":2,"gap":0.35}</t>
         </is>
       </c>
       <c r="M158">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N158">
         <v>1.5</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
+          <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
         </is>
       </c>
     </row>
@@ -9026,54 +8888,49 @@
         <v>40</v>
       </c>
       <c r="I159">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|850</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風雪</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
         </is>
       </c>
       <c r="M159">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N159">
         <v>1.5</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
+          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9083,17 +8940,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G160">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H160">
         <v>40</v>
       </c>
       <c r="I160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -9102,45 +8959,40 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜衝擊</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
+          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M160">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N160">
         <v>1.5</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9150,17 +9002,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G161">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H161">
         <v>40</v>
       </c>
       <c r="I161">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -9169,45 +9021,40 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">巨型風刃</t>
+          <t xml:space="preserve">寒冰體</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
+          <t xml:space="preserve">{"stacks":1}</t>
         </is>
       </c>
       <c r="M161">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N161">
         <v>1.5</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
+          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9217,17 +9064,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G162">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H162">
         <v>40</v>
       </c>
       <c r="I162">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -9236,45 +9083,40 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重風刃</t>
+          <t xml:space="preserve">極致寒霜</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
+          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
         </is>
       </c>
       <c r="M162">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N162">
         <v>1.5</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
+          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9284,17 +9126,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G163">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H163">
         <v>40</v>
       </c>
       <c r="I163">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -9303,45 +9145,40 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂披風</t>
+          <t xml:space="preserve">三重新星</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
         </is>
       </c>
       <c r="M163">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N163">
         <v>1.5</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
+          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9351,17 +9188,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G164">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H164">
         <v>40</v>
       </c>
       <c r="I164">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -9370,45 +9207,40 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">追跡風刃</t>
+          <t xml:space="preserve">死亡新星</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
+          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
         </is>
       </c>
       <c r="M164">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N164">
         <v>1.5</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
+          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9418,17 +9250,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G165">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H165">
         <v>40</v>
       </c>
       <c r="I165">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -9437,23 +9269,23 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂風碎裂</t>
+          <t xml:space="preserve">暴風雪</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
         </is>
       </c>
       <c r="M165">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N165">
         <v>1.5</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
+          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -9495,49 +9327,54 @@
         <v>40</v>
       </c>
       <c r="I166">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|900</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風真空刃</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
         </is>
       </c>
       <c r="M166">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N166">
         <v>1.5</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
+          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9557,7 +9394,7 @@
         <v>40</v>
       </c>
       <c r="I167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -9566,40 +9403,45 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">巨型風刃</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
+          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
         </is>
       </c>
       <c r="M167">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N167">
         <v>1.5</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9619,7 +9461,7 @@
         <v>40</v>
       </c>
       <c r="I168">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -9628,40 +9470,45 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空爆震</t>
+          <t xml:space="preserve">雙重風刃</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
         </is>
       </c>
       <c r="M168">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N168">
         <v>1.5</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9681,7 +9528,7 @@
         <v>40</v>
       </c>
       <c r="I169">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -9690,40 +9537,45 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切</t>
+          <t xml:space="preserve">亂披風</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
         </is>
       </c>
       <c r="M169">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N169">
         <v>1.5</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9743,7 +9595,7 @@
         <v>40</v>
       </c>
       <c r="I170">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -9752,40 +9604,45 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋斬</t>
+          <t xml:space="preserve">追跡風刃</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
         </is>
       </c>
       <c r="M170">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N170">
         <v>1.5</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
+          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9805,7 +9662,7 @@
         <v>40</v>
       </c>
       <c r="I171">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -9814,40 +9671,45 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋三重奏</t>
+          <t xml:space="preserve">狂風碎裂</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
+          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
         </is>
       </c>
       <c r="M171">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N171">
         <v>1.5</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9867,7 +9729,7 @@
         <v>40</v>
       </c>
       <c r="I172">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -9876,23 +9738,23 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">無限風切</t>
+          <t xml:space="preserve">暴風真空刃</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
         </is>
       </c>
       <c r="M172">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N172">
         <v>1.5</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
+          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
@@ -9929,49 +9791,49 @@
         <v>40</v>
       </c>
       <c r="I173">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|950</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛空斬</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
         </is>
       </c>
       <c r="M173">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N173">
         <v>1.5</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9985,13 +9847,13 @@
         </is>
       </c>
       <c r="G174">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H174">
         <v>40</v>
       </c>
       <c r="I174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -10000,40 +9862,40 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空爆震</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
         </is>
       </c>
       <c r="M174">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N174">
         <v>1.5</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10047,13 +9909,13 @@
         </is>
       </c>
       <c r="G175">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H175">
         <v>40</v>
       </c>
       <c r="I175">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -10062,40 +9924,40 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風撕裂</t>
+          <t xml:space="preserve">風切</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
         </is>
       </c>
       <c r="M175">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N175">
         <v>1.5</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10109,13 +9971,13 @@
         </is>
       </c>
       <c r="G176">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H176">
         <v>40</v>
       </c>
       <c r="I176">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -10124,40 +9986,40 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂風切</t>
+          <t xml:space="preserve">迴旋斬</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
         </is>
       </c>
       <c r="M176">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N176">
         <v>1.5</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10171,13 +10033,13 @@
         </is>
       </c>
       <c r="G177">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H177">
         <v>40</v>
       </c>
       <c r="I177">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -10186,40 +10048,40 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風之刃</t>
+          <t xml:space="preserve">迴旋三重奏</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
         </is>
       </c>
       <c r="M177">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N177">
         <v>1.5</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10233,13 +10095,13 @@
         </is>
       </c>
       <c r="G178">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H178">
         <v>40</v>
       </c>
       <c r="I178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -10248,40 +10110,40 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切擴散</t>
+          <t xml:space="preserve">無限風切</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M178">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N178">
         <v>1.5</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10295,13 +10157,13 @@
         </is>
       </c>
       <c r="G179">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H179">
         <v>40</v>
       </c>
       <c r="I179">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -10310,23 +10172,23 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">颶風屏障</t>
+          <t xml:space="preserve">虛空斬</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
         </is>
       </c>
       <c r="M179">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N179">
         <v>1.5</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -10363,30 +10225,402 @@
         <v>40</v>
       </c>
       <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|700</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+        </is>
+      </c>
+      <c r="M180">
+        <v>100000</v>
+      </c>
+      <c r="N180">
+        <v>1.5</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G181">
+        <v>24</v>
+      </c>
+      <c r="H181">
+        <v>40</v>
+      </c>
+      <c r="I181">
+        <v>2</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|750</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風撕裂</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+        </is>
+      </c>
+      <c r="M181">
+        <v>200000</v>
+      </c>
+      <c r="N181">
+        <v>1.5</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G182">
+        <v>24</v>
+      </c>
+      <c r="H182">
+        <v>40</v>
+      </c>
+      <c r="I182">
+        <v>3</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|800</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亂風切</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M182">
+        <v>400000</v>
+      </c>
+      <c r="N182">
+        <v>1.5</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G183">
+        <v>24</v>
+      </c>
+      <c r="H183">
+        <v>40</v>
+      </c>
+      <c r="I183">
+        <v>4</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|850</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風之刃</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+        </is>
+      </c>
+      <c r="M183">
+        <v>800000</v>
+      </c>
+      <c r="N183">
+        <v>1.5</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G184">
+        <v>24</v>
+      </c>
+      <c r="H184">
+        <v>40</v>
+      </c>
+      <c r="I184">
+        <v>5</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|900</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切擴散</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+        </is>
+      </c>
+      <c r="M184">
+        <v>1500000</v>
+      </c>
+      <c r="N184">
+        <v>1.5</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G185">
+        <v>24</v>
+      </c>
+      <c r="H185">
+        <v>40</v>
+      </c>
+      <c r="I185">
+        <v>6</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|950</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">颶風屏障</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+        </is>
+      </c>
+      <c r="M185">
+        <v>3000000</v>
+      </c>
+      <c r="N185">
+        <v>1.5</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G186">
+        <v>24</v>
+      </c>
+      <c r="H186">
+        <v>40</v>
+      </c>
+      <c r="I186">
         <v>7</v>
       </c>
-      <c r="J180" t="inlineStr">
+      <c r="J186" t="inlineStr">
         <is>
           <t xml:space="preserve">0|1000</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="K186" t="inlineStr">
         <is>
           <t xml:space="preserve">暴風神體</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">{"red":99,"sec":2,"secPer":0.2,"pct":100,"pctPer":10}</t>
         </is>
       </c>
-      <c r="M180">
+      <c r="M186">
         <v>5000000</v>
       </c>
-      <c r="N180">
-        <v>1.5</v>
-      </c>
-      <c r="O180" t="inlineStr">
+      <c r="N186">
+        <v>1.5</v>
+      </c>
+      <c r="O186" t="inlineStr">
         <is>
           <t xml:space="preserve">施放暴風屏障時同時召喚風暴之神附體：{sec} 秒內傷害減免 +{red}%，且自身的風系傷害額外 ×(1+{pct}%)</t>
         </is>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="Rbe701809772a49c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="R17e9d3b8c6364ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills2" sheetId="1" r:id="Re6b899a1c0874899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="欄位定義" sheetId="2" r:id="Rc3fab0128215449e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -384,9 +384,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">{"pct":50,"pctPer":5,"m":45}</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每次施放飛刀時額外射出 1 支無限飛刀，追擊周圍 {m} 米內的任意敵人：傷害提高 {pct}%，且彈射次數不受限制（場上每個敵人各被命中一次）</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">soulhunterBlade</x:t>
@@ -3432,22 +3429,22 @@
       <x:c r="N31">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="O31" t="s">
+      <x:c r="O31" t="str">
+        <x:v>每次施放飛刀時額外射出 1 支無限飛刀，追擊周圍 {m} 米內的任意敵人：傷害提高 {pct}%，彈射次數不受限制；只有一個目標時會貫穿後繞回再次攻擊，不會停留原地重複傷害</x:v>
+      </x:c>
+      <x:c r="P31" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="P31" t="s">
-        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="14.25">
       <x:c r="A32" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B32" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B32" t="s">
+      <x:c r="C32" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="C32" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="G32">
         <x:v>6</x:v>
@@ -3462,10 +3459,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="K32" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="L32" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="M32">
         <x:v>100000</x:v>
@@ -3474,18 +3471,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O32" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="14.25">
       <x:c r="A33" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B33" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B33" t="s">
+      <x:c r="C33" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="C33" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="G33">
         <x:v>6</x:v>
@@ -3500,10 +3497,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="K33" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="L33" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="L33" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="M33">
         <x:v>200000</x:v>
@@ -3512,18 +3509,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O33" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="14.25">
       <x:c r="A34" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B34" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B34" t="s">
+      <x:c r="C34" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="C34" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="G34">
         <x:v>6</x:v>
@@ -3538,10 +3535,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K34" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="L34" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="L34" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="M34">
         <x:v>400000</x:v>
@@ -3555,13 +3552,13 @@
     </x:row>
     <x:row r="35" ht="14.25">
       <x:c r="A35" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B35" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B35" t="s">
+      <x:c r="C35" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="C35" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="G35">
         <x:v>6</x:v>
@@ -3579,7 +3576,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L35" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="M35">
         <x:v>800000</x:v>
@@ -3588,18 +3585,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O35" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="14.25">
       <x:c r="A36" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B36" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B36" t="s">
+      <x:c r="C36" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="C36" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="G36">
         <x:v>6</x:v>
@@ -3614,10 +3611,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K36" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="L36" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="L36" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="M36">
         <x:v>1500000</x:v>
@@ -3626,18 +3623,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O36" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="14.25">
       <x:c r="A37" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B37" t="s">
+      <x:c r="C37" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="C37" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="G37">
         <x:v>6</x:v>
@@ -3652,10 +3649,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K37" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="L37" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="L37" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="M37">
         <x:v>3000000</x:v>
@@ -3664,18 +3661,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O37" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="14.25">
       <x:c r="A38" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B38" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B38" t="s">
+      <x:c r="C38" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="C38" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="G38">
         <x:v>6</x:v>
@@ -3687,13 +3684,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J38" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="K38" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="K38" t="s">
+      <x:c r="L38" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="L38" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="M38">
         <x:v>5000000</x:v>
@@ -3702,12 +3699,12 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O38" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="14.25">
       <x:c r="A39" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H39">
         <x:v>300</x:v>
@@ -3716,10 +3713,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K39" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="L39" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="L39" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="M39">
         <x:v>10000000</x:v>
@@ -3728,15 +3725,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O39" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="P39" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="P39" t="s">
-        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="14.25">
       <x:c r="A40" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H40">
         <x:v>300</x:v>
@@ -3745,10 +3742,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K40" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="L40" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="L40" t="s">
-        <x:v>154</x:v>
       </x:c>
       <x:c r="M40">
         <x:v>10000000</x:v>
@@ -3757,15 +3754,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O40" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="P40" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="P40" t="s">
-        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="14.25">
       <x:c r="A41" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H41">
         <x:v>300</x:v>
@@ -3774,7 +3771,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K41" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="L41" t="s">
         <x:v>66</x:v>
@@ -3786,21 +3783,21 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O41" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="P41" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="P41" t="s">
-        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="14.25">
       <x:c r="A42" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B42" t="s">
+      <x:c r="C42" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="C42" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="G42">
         <x:v>8</x:v>
@@ -3815,10 +3812,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K42" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="L42" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="M42">
         <x:v>100000</x:v>
@@ -3827,18 +3824,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O42" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="14.25">
       <x:c r="A43" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B43" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B43" t="s">
+      <x:c r="C43" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="C43" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="G43">
         <x:v>8</x:v>
@@ -3853,10 +3850,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K43" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="L43" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="L43" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="M43">
         <x:v>200000</x:v>
@@ -3865,18 +3862,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O43" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="14.25">
       <x:c r="A44" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B44" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B44" t="s">
+      <x:c r="C44" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="C44" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="G44">
         <x:v>8</x:v>
@@ -3891,10 +3888,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K44" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="L44" t="s">
         <x:v>168</x:v>
-      </x:c>
-      <x:c r="L44" t="s">
-        <x:v>169</x:v>
       </x:c>
       <x:c r="M44">
         <x:v>400000</x:v>
@@ -3903,18 +3900,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O44" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="14.25">
       <x:c r="A45" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B45" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B45" t="s">
+      <x:c r="C45" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="C45" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="G45">
         <x:v>8</x:v>
@@ -3929,10 +3926,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K45" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="L45" t="s">
         <x:v>171</x:v>
-      </x:c>
-      <x:c r="L45" t="s">
-        <x:v>172</x:v>
       </x:c>
       <x:c r="M45">
         <x:v>800000</x:v>
@@ -3941,18 +3938,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O45" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="14.25">
       <x:c r="A46" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B46" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B46" t="s">
+      <x:c r="C46" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="C46" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="G46">
         <x:v>8</x:v>
@@ -3964,13 +3961,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J46" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K46" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="L46" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="L46" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="M46">
         <x:v>1500000</x:v>
@@ -3979,18 +3976,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O46" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="14.25">
       <x:c r="A47" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B47" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B47" t="s">
+      <x:c r="C47" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="C47" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="G47">
         <x:v>8</x:v>
@@ -4002,13 +3999,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J47" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="K47" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="K47" t="s">
+      <x:c r="L47" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="L47" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="M47">
         <x:v>3000000</x:v>
@@ -4017,18 +4014,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O47" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="14.25">
       <x:c r="A48" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B48" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B48" t="s">
+      <x:c r="C48" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="C48" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="G48">
         <x:v>8</x:v>
@@ -4040,13 +4037,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J48" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="K48" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="K48" t="s">
+      <x:c r="L48" t="s">
         <x:v>182</x:v>
-      </x:c>
-      <x:c r="L48" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="M48">
         <x:v>5000000</x:v>
@@ -4055,12 +4052,12 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O48" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="14.25">
       <x:c r="A49" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H49">
         <x:v>300</x:v>
@@ -4069,10 +4066,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K49" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="L49" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="L49" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="M49">
         <x:v>10000000</x:v>
@@ -4081,15 +4078,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O49" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="P49" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="P49" t="s">
-        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="14.25">
       <x:c r="A50" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H50">
         <x:v>300</x:v>
@@ -4098,10 +4095,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K50" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="L50" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="L50" t="s">
-        <x:v>190</x:v>
       </x:c>
       <x:c r="M50">
         <x:v>10000000</x:v>
@@ -4110,15 +4107,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O50" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="P50" t="s">
         <x:v>191</x:v>
-      </x:c>
-      <x:c r="P50" t="s">
-        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="14.25">
       <x:c r="A51" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H51">
         <x:v>300</x:v>
@@ -4127,10 +4124,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K51" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="L51" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="L51" t="s">
-        <x:v>194</x:v>
       </x:c>
       <x:c r="M51">
         <x:v>10000000</x:v>
@@ -4139,21 +4136,21 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O51" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="P51" t="s">
         <x:v>195</x:v>
-      </x:c>
-      <x:c r="P51" t="s">
-        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="14.25">
       <x:c r="A52" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B52" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B52" t="s">
+      <x:c r="C52" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="C52" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="G52">
         <x:v>10</x:v>
@@ -4168,10 +4165,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K52" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="L52" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="M52">
         <x:v>100000</x:v>
@@ -4180,18 +4177,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O52" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="14.25">
       <x:c r="A53" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B53" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B53" t="s">
+      <x:c r="C53" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="C53" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="G53">
         <x:v>10</x:v>
@@ -4206,10 +4203,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K53" t="s">
-        <x:v>202</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="L53" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="M53">
         <x:v>200000</x:v>
@@ -4218,18 +4215,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O53" t="s">
-        <x:v>203</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="14.25">
       <x:c r="A54" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B54" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B54" t="s">
+      <x:c r="C54" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="C54" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="G54">
         <x:v>10</x:v>
@@ -4244,10 +4241,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K54" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="L54" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="L54" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="M54">
         <x:v>400000</x:v>
@@ -4256,18 +4253,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O54" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="14.25">
       <x:c r="A55" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B55" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B55" t="s">
+      <x:c r="C55" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="C55" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="G55">
         <x:v>10</x:v>
@@ -4279,13 +4276,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J55" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K55" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="L55" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="L55" t="s">
-        <x:v>208</x:v>
       </x:c>
       <x:c r="M55">
         <x:v>800000</x:v>
@@ -4294,18 +4291,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O55" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="14.25">
       <x:c r="A56" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B56" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B56" t="s">
+      <x:c r="C56" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="C56" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="G56">
         <x:v>10</x:v>
@@ -4317,13 +4314,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J56" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K56" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="L56" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="L56" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="M56">
         <x:v>1500000</x:v>
@@ -4332,18 +4329,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O56" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="14.25">
       <x:c r="A57" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B57" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B57" t="s">
+      <x:c r="C57" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="C57" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="G57">
         <x:v>10</x:v>
@@ -4355,13 +4352,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J57" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K57" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="L57" t="s">
         <x:v>213</x:v>
-      </x:c>
-      <x:c r="L57" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="M57">
         <x:v>3000000</x:v>
@@ -4370,18 +4367,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O57" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="14.25">
       <x:c r="A58" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B58" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B58" t="s">
+      <x:c r="C58" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="C58" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="G58">
         <x:v>10</x:v>
@@ -4393,13 +4390,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J58" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K58" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="K58" t="s">
+      <x:c r="L58" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="L58" t="s">
-        <x:v>218</x:v>
       </x:c>
       <x:c r="M58">
         <x:v>5000000</x:v>
@@ -4408,12 +4405,12 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O58" t="s">
-        <x:v>219</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="14.25">
       <x:c r="A59" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H59">
         <x:v>300</x:v>
@@ -4422,10 +4419,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K59" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="L59" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="L59" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="M59">
         <x:v>10000000</x:v>
@@ -4434,15 +4431,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O59" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="P59" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="P59" t="s">
-        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="14.25">
       <x:c r="A60" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H60">
         <x:v>300</x:v>
@@ -4451,10 +4448,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K60" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="L60" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="L60" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="M60">
         <x:v>10000000</x:v>
@@ -4463,15 +4460,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O60" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P60" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="P60" t="s">
-        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="14.25">
       <x:c r="A61" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H61">
         <x:v>300</x:v>
@@ -4480,7 +4477,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K61" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="L61" t="s">
         <x:v>116</x:v>
@@ -4492,21 +4489,21 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O61" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="P61" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="P61" t="s">
-        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="14.25">
       <x:c r="A62" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B62" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B62" t="s">
+      <x:c r="C62" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="C62" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="G62">
         <x:v>0</x:v>
@@ -4521,10 +4518,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K62" t="s">
-        <x:v>232</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="L62" t="s">
-        <x:v>234</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="M62">
         <x:v>100000</x:v>
@@ -4533,18 +4530,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O62" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="14.25">
       <x:c r="A63" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B63" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B63" t="s">
+      <x:c r="C63" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="C63" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="G63">
         <x:v>0</x:v>
@@ -4559,10 +4556,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K63" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="L63" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="L63" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="M63">
         <x:v>200000</x:v>
@@ -4571,18 +4568,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O63" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="14.25">
       <x:c r="A64" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B64" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B64" t="s">
+      <x:c r="C64" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="C64" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="G64">
         <x:v>0</x:v>
@@ -4594,13 +4591,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J64" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K64" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="L64" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="L64" t="s">
-        <x:v>240</x:v>
       </x:c>
       <x:c r="M64">
         <x:v>400000</x:v>
@@ -4609,18 +4606,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O64" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="14.25">
       <x:c r="A65" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B65" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B65" t="s">
+      <x:c r="C65" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="C65" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="G65">
         <x:v>0</x:v>
@@ -4632,13 +4629,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J65" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K65" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="L65" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="L65" t="s">
-        <x:v>243</x:v>
       </x:c>
       <x:c r="M65">
         <x:v>800000</x:v>
@@ -4647,18 +4644,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O65" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="14.25">
       <x:c r="A66" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B66" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B66" t="s">
+      <x:c r="C66" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="C66" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="G66">
         <x:v>0</x:v>
@@ -4670,13 +4667,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J66" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K66" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="L66" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="L66" t="s">
-        <x:v>246</x:v>
       </x:c>
       <x:c r="M66">
         <x:v>1500000</x:v>
@@ -4685,18 +4682,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O66" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="14.25">
       <x:c r="A67" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B67" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B67" t="s">
+      <x:c r="C67" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="C67" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="G67">
         <x:v>0</x:v>
@@ -4708,13 +4705,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J67" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K67" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="L67" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="L67" t="s">
-        <x:v>249</x:v>
       </x:c>
       <x:c r="M67">
         <x:v>3000000</x:v>
@@ -4723,18 +4720,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O67" t="s">
-        <x:v>250</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="14.25">
       <x:c r="A68" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B68" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B68" t="s">
+      <x:c r="C68" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="C68" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="G68">
         <x:v>0</x:v>
@@ -4746,13 +4743,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J68" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K68" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="K68" t="s">
+      <x:c r="L68" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="L68" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="M68">
         <x:v>5000000</x:v>
@@ -4761,12 +4758,12 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O68" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="14.25">
       <x:c r="A69" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H69">
         <x:v>300</x:v>
@@ -4775,10 +4772,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K69" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="L69" t="s">
         <x:v>255</x:v>
-      </x:c>
-      <x:c r="L69" t="s">
-        <x:v>256</x:v>
       </x:c>
       <x:c r="M69">
         <x:v>10000000</x:v>
@@ -4787,15 +4784,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O69" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="P69" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="P69" t="s">
-        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="14.25">
       <x:c r="A70" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H70">
         <x:v>300</x:v>
@@ -4804,10 +4801,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K70" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="L70" t="s">
         <x:v>259</x:v>
-      </x:c>
-      <x:c r="L70" t="s">
-        <x:v>260</x:v>
       </x:c>
       <x:c r="M70">
         <x:v>10000000</x:v>
@@ -4816,15 +4813,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O70" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="P70" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="P70" t="s">
-        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="14.25">
       <x:c r="A71" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H71">
         <x:v>300</x:v>
@@ -4833,10 +4830,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K71" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="L71" t="s">
         <x:v>263</x:v>
-      </x:c>
-      <x:c r="L71" t="s">
-        <x:v>264</x:v>
       </x:c>
       <x:c r="M71">
         <x:v>10000000</x:v>
@@ -4845,21 +4842,21 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O71" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="P71" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="P71" t="s">
-        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="14.25">
       <x:c r="A72" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B72" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="B72" t="s">
+      <x:c r="C72" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="C72" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="G72">
         <x:v>60</x:v>
@@ -4871,13 +4868,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J72" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K72" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="L72" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="M72">
         <x:v>100000</x:v>
@@ -4886,18 +4883,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O72" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="14.25">
       <x:c r="A73" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B73" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="B73" t="s">
+      <x:c r="C73" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="C73" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="G73">
         <x:v>60</x:v>
@@ -4909,10 +4906,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J73" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K73" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="L73" t="s">
         <x:v>116</x:v>
@@ -4924,18 +4921,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O73" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="14.25">
       <x:c r="A74" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B74" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="B74" t="s">
+      <x:c r="C74" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="C74" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="G74">
         <x:v>60</x:v>
@@ -4947,10 +4944,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J74" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K74" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="L74" t="s">
         <x:v>116</x:v>
@@ -4962,18 +4959,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O74" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="14.25">
       <x:c r="A75" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B75" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="B75" t="s">
+      <x:c r="C75" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="C75" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="G75">
         <x:v>60</x:v>
@@ -4985,13 +4982,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J75" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K75" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="L75" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="L75" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="M75">
         <x:v>800000</x:v>
@@ -5000,18 +4997,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O75" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="14.25">
       <x:c r="A76" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B76" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="B76" t="s">
+      <x:c r="C76" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="C76" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="G76">
         <x:v>60</x:v>
@@ -5023,10 +5020,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J76" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K76" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="L76" t="s">
         <x:v>116</x:v>
@@ -5038,18 +5035,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O76" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="14.25">
       <x:c r="A77" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B77" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="B77" t="s">
+      <x:c r="C77" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="C77" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="G77">
         <x:v>60</x:v>
@@ -5061,13 +5058,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J77" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K77" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="K77" t="s">
+      <x:c r="L77" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="L77" t="s">
-        <x:v>283</x:v>
       </x:c>
       <x:c r="M77">
         <x:v>3000000</x:v>
@@ -5076,18 +5073,18 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O77" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="14.25">
       <x:c r="A78" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B78" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="B78" t="s">
+      <x:c r="C78" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="C78" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="G78">
         <x:v>60</x:v>
@@ -5099,13 +5096,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J78" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="K78" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="K78" t="s">
+      <x:c r="L78" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="L78" t="s">
-        <x:v>287</x:v>
       </x:c>
       <x:c r="M78">
         <x:v>5000000</x:v>
@@ -5114,12 +5111,12 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O78" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="14.25">
       <x:c r="A79" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="H79">
         <x:v>300</x:v>
@@ -5128,10 +5125,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="K79" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="L79" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="L79" t="s">
-        <x:v>290</x:v>
       </x:c>
       <x:c r="M79">
         <x:v>10000000</x:v>
@@ -5140,15 +5137,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O79" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="P79" t="s">
         <x:v>291</x:v>
-      </x:c>
-      <x:c r="P79" t="s">
-        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="14.25">
       <x:c r="A80" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="H80">
         <x:v>300</x:v>
@@ -5157,10 +5154,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="K80" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="L80" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="L80" t="s">
-        <x:v>294</x:v>
       </x:c>
       <x:c r="M80">
         <x:v>10000000</x:v>
@@ -5169,15 +5166,15 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O80" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="P80" t="s">
         <x:v>295</x:v>
-      </x:c>
-      <x:c r="P80" t="s">
-        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="14.25">
       <x:c r="A81" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="H81">
         <x:v>300</x:v>
@@ -5186,10 +5183,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K81" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="L81" t="s">
         <x:v>297</x:v>
-      </x:c>
-      <x:c r="L81" t="s">
-        <x:v>298</x:v>
       </x:c>
       <x:c r="M81">
         <x:v>10000000</x:v>
@@ -5198,27 +5195,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O81" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="P81" t="s">
         <x:v>299</x:v>
-      </x:c>
-      <x:c r="P81" t="s">
-        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="14.25">
       <x:c r="A82" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B82" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B82" t="s">
+      <x:c r="C82" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C82" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="E82" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F82" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F82" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G82">
         <x:v>14</x:v>
@@ -5233,10 +5230,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K82" t="s">
-        <x:v>302</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="L82" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="M82">
         <x:v>100000</x:v>
@@ -5245,24 +5242,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O82" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="14.25">
       <x:c r="A83" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B83" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B83" t="s">
+      <x:c r="C83" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C83" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="E83" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F83" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F83" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G83">
         <x:v>14</x:v>
@@ -5277,10 +5274,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="K83" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="L83" t="s">
         <x:v>308</x:v>
-      </x:c>
-      <x:c r="L83" t="s">
-        <x:v>309</x:v>
       </x:c>
       <x:c r="M83">
         <x:v>200000</x:v>
@@ -5289,24 +5286,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O83" t="s">
-        <x:v>310</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="14.25">
       <x:c r="A84" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B84" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B84" t="s">
+      <x:c r="C84" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C84" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="E84" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F84" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F84" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G84">
         <x:v>14</x:v>
@@ -5321,10 +5318,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="K84" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="L84" t="s">
         <x:v>311</x:v>
-      </x:c>
-      <x:c r="L84" t="s">
-        <x:v>312</x:v>
       </x:c>
       <x:c r="M84">
         <x:v>400000</x:v>
@@ -5333,24 +5330,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O84" t="s">
-        <x:v>313</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="14.25">
       <x:c r="A85" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B85" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B85" t="s">
+      <x:c r="C85" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C85" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="E85" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F85" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F85" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G85">
         <x:v>14</x:v>
@@ -5365,10 +5362,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="K85" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="L85" t="s">
         <x:v>314</x:v>
-      </x:c>
-      <x:c r="L85" t="s">
-        <x:v>315</x:v>
       </x:c>
       <x:c r="M85">
         <x:v>800000</x:v>
@@ -5377,24 +5374,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O85" t="s">
-        <x:v>316</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="14.25">
       <x:c r="A86" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B86" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B86" t="s">
+      <x:c r="C86" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C86" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="E86" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F86" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F86" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G86">
         <x:v>14</x:v>
@@ -5409,10 +5406,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="K86" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="L86" t="s">
         <x:v>317</x:v>
-      </x:c>
-      <x:c r="L86" t="s">
-        <x:v>318</x:v>
       </x:c>
       <x:c r="M86">
         <x:v>1500000</x:v>
@@ -5421,24 +5418,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O86" t="s">
-        <x:v>319</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="14.25">
       <x:c r="A87" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B87" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B87" t="s">
+      <x:c r="C87" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C87" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="E87" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F87" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F87" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G87">
         <x:v>14</x:v>
@@ -5453,10 +5450,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K87" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="L87" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="L87" t="s">
-        <x:v>321</x:v>
       </x:c>
       <x:c r="M87">
         <x:v>3000000</x:v>
@@ -5465,24 +5462,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O87" t="s">
-        <x:v>322</x:v>
+        <x:v>321</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="14.25">
       <x:c r="A88" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B88" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="B88" t="s">
+      <x:c r="C88" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="C88" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="E88" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F88" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F88" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G88">
         <x:v>14</x:v>
@@ -5497,10 +5494,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K88" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="L88" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="L88" t="s">
-        <x:v>324</x:v>
       </x:c>
       <x:c r="M88">
         <x:v>5000000</x:v>
@@ -5509,24 +5506,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O88" t="s">
-        <x:v>325</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="14.25">
       <x:c r="A89" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B89" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B89" t="s">
+      <x:c r="C89" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="C89" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="E89" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F89" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F89" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G89">
         <x:v>14</x:v>
@@ -5541,10 +5538,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="K89" t="s">
-        <x:v>327</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="L89" t="s">
-        <x:v>329</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="M89">
         <x:v>100000</x:v>
@@ -5553,24 +5550,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O89" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="14.25">
       <x:c r="A90" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B90" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B90" t="s">
+      <x:c r="C90" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="C90" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="E90" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F90" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F90" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G90">
         <x:v>14</x:v>
@@ -5585,10 +5582,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="K90" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="L90" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="M90">
         <x:v>200000</x:v>
@@ -5597,24 +5594,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O90" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="14.25">
       <x:c r="A91" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B91" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B91" t="s">
+      <x:c r="C91" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="C91" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="E91" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F91" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F91" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G91">
         <x:v>14</x:v>
@@ -5629,10 +5626,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="K91" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="L91" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="L91" t="s">
-        <x:v>334</x:v>
       </x:c>
       <x:c r="M91">
         <x:v>400000</x:v>
@@ -5641,24 +5638,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O91" t="s">
-        <x:v>335</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="14.25">
       <x:c r="A92" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B92" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B92" t="s">
+      <x:c r="C92" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="C92" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="E92" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F92" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F92" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G92">
         <x:v>14</x:v>
@@ -5673,10 +5670,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K92" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="L92" t="s">
-        <x:v>336</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="M92">
         <x:v>800000</x:v>
@@ -5685,24 +5682,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O92" t="s">
-        <x:v>337</x:v>
+        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="14.25">
       <x:c r="A93" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B93" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B93" t="s">
+      <x:c r="C93" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="C93" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="E93" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F93" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F93" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G93">
         <x:v>14</x:v>
@@ -5717,10 +5714,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K93" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="L93" t="s">
         <x:v>338</x:v>
-      </x:c>
-      <x:c r="L93" t="s">
-        <x:v>339</x:v>
       </x:c>
       <x:c r="M93">
         <x:v>1500000</x:v>
@@ -5729,24 +5726,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O93" t="s">
-        <x:v>340</x:v>
+        <x:v>339</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="14.25">
       <x:c r="A94" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B94" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B94" t="s">
+      <x:c r="C94" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="C94" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="E94" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F94" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F94" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G94">
         <x:v>14</x:v>
@@ -5761,10 +5758,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K94" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="L94" t="s">
         <x:v>341</x:v>
-      </x:c>
-      <x:c r="L94" t="s">
-        <x:v>342</x:v>
       </x:c>
       <x:c r="M94">
         <x:v>3000000</x:v>
@@ -5773,24 +5770,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O94" t="s">
-        <x:v>343</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="14.25">
       <x:c r="A95" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B95" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B95" t="s">
+      <x:c r="C95" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="C95" t="s">
-        <x:v>328</x:v>
-      </x:c>
       <x:c r="E95" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F95" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F95" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G95">
         <x:v>14</x:v>
@@ -5805,10 +5802,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K95" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="L95" t="s">
         <x:v>344</x:v>
-      </x:c>
-      <x:c r="L95" t="s">
-        <x:v>345</x:v>
       </x:c>
       <x:c r="M95">
         <x:v>5000000</x:v>
@@ -5817,27 +5814,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O95" t="s">
-        <x:v>346</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="14.25">
       <x:c r="A96" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B96" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="B96" t="s">
+      <x:c r="C96" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="C96" t="s">
+      <x:c r="D96" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="D96" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="E96" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F96" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F96" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G96">
         <x:v>26</x:v>
@@ -5852,10 +5849,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="K96" t="s">
-        <x:v>348</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="L96" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="M96">
         <x:v>100000</x:v>
@@ -5864,27 +5861,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O96" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="14.25">
       <x:c r="A97" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B97" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="B97" t="s">
+      <x:c r="C97" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="C97" t="s">
+      <x:c r="D97" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="D97" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="E97" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F97" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F97" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G97">
         <x:v>26</x:v>
@@ -5899,10 +5896,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="K97" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="L97" t="s">
         <x:v>353</x:v>
-      </x:c>
-      <x:c r="L97" t="s">
-        <x:v>354</x:v>
       </x:c>
       <x:c r="M97">
         <x:v>200000</x:v>
@@ -5911,27 +5908,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O97" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="14.25">
       <x:c r="A98" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B98" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="B98" t="s">
+      <x:c r="C98" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="C98" t="s">
+      <x:c r="D98" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="D98" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="E98" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F98" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F98" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G98">
         <x:v>26</x:v>
@@ -5946,10 +5943,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K98" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="L98" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="L98" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="M98">
         <x:v>400000</x:v>
@@ -5958,27 +5955,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O98" t="s">
-        <x:v>358</x:v>
+        <x:v>357</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="14.25">
       <x:c r="A99" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B99" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="B99" t="s">
+      <x:c r="C99" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="C99" t="s">
+      <x:c r="D99" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="D99" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="E99" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F99" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F99" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G99">
         <x:v>26</x:v>
@@ -5993,10 +5990,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K99" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="L99" t="s">
         <x:v>359</x:v>
-      </x:c>
-      <x:c r="L99" t="s">
-        <x:v>360</x:v>
       </x:c>
       <x:c r="M99">
         <x:v>800000</x:v>
@@ -6005,27 +6002,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O99" t="s">
-        <x:v>361</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="14.25">
       <x:c r="A100" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B100" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="B100" t="s">
+      <x:c r="C100" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="C100" t="s">
+      <x:c r="D100" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="D100" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="E100" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F100" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F100" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G100">
         <x:v>26</x:v>
@@ -6040,10 +6037,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K100" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="L100" t="s">
         <x:v>362</x:v>
-      </x:c>
-      <x:c r="L100" t="s">
-        <x:v>363</x:v>
       </x:c>
       <x:c r="M100">
         <x:v>1500000</x:v>
@@ -6052,27 +6049,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O100" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="14.25">
       <x:c r="A101" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B101" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="B101" t="s">
+      <x:c r="C101" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="C101" t="s">
+      <x:c r="D101" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="D101" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="E101" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F101" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F101" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G101">
         <x:v>26</x:v>
@@ -6087,10 +6084,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K101" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="L101" t="s">
         <x:v>365</x:v>
-      </x:c>
-      <x:c r="L101" t="s">
-        <x:v>366</x:v>
       </x:c>
       <x:c r="M101">
         <x:v>3000000</x:v>
@@ -6099,27 +6096,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O101" t="s">
-        <x:v>367</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="14.25">
       <x:c r="A102" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B102" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="B102" t="s">
+      <x:c r="C102" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="C102" t="s">
+      <x:c r="D102" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="D102" t="s">
-        <x:v>350</x:v>
-      </x:c>
       <x:c r="E102" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F102" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="F102" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="G102">
         <x:v>26</x:v>
@@ -6131,13 +6128,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J102" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K102" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="L102" t="s">
         <x:v>368</x:v>
-      </x:c>
-      <x:c r="L102" t="s">
-        <x:v>369</x:v>
       </x:c>
       <x:c r="M102">
         <x:v>5000000</x:v>
@@ -6146,24 +6143,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O102" t="s">
-        <x:v>370</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="14.25">
       <x:c r="A103" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B103" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B103" t="s">
+      <x:c r="C103" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="C103" t="s">
+      <x:c r="E103" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F103" t="s">
         <x:v>373</x:v>
-      </x:c>
-      <x:c r="E103" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F103" t="s">
-        <x:v>374</x:v>
       </x:c>
       <x:c r="G103">
         <x:v>25</x:v>
@@ -6178,10 +6175,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="K103" t="s">
-        <x:v>372</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="L103" t="s">
-        <x:v>375</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="M103">
         <x:v>100000</x:v>
@@ -6190,24 +6187,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O103" t="s">
-        <x:v>376</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="14.25">
       <x:c r="A104" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B104" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B104" t="s">
+      <x:c r="C104" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="C104" t="s">
+      <x:c r="E104" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F104" t="s">
         <x:v>373</x:v>
-      </x:c>
-      <x:c r="E104" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F104" t="s">
-        <x:v>374</x:v>
       </x:c>
       <x:c r="G104">
         <x:v>25</x:v>
@@ -6222,7 +6219,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K104" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="L104" t="s">
         <x:v>116</x:v>
@@ -6234,24 +6231,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O104" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="14.25">
       <x:c r="A105" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B105" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B105" t="s">
+      <x:c r="C105" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="C105" t="s">
+      <x:c r="E105" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F105" t="s">
         <x:v>373</x:v>
-      </x:c>
-      <x:c r="E105" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F105" t="s">
-        <x:v>374</x:v>
       </x:c>
       <x:c r="G105">
         <x:v>25</x:v>
@@ -6266,10 +6263,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K105" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="L105" t="s">
         <x:v>379</x:v>
-      </x:c>
-      <x:c r="L105" t="s">
-        <x:v>380</x:v>
       </x:c>
       <x:c r="M105">
         <x:v>400000</x:v>
@@ -6278,24 +6275,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O105" t="s">
-        <x:v>381</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="14.25">
       <x:c r="A106" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B106" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B106" t="s">
+      <x:c r="C106" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="C106" t="s">
+      <x:c r="E106" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F106" t="s">
         <x:v>373</x:v>
-      </x:c>
-      <x:c r="E106" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F106" t="s">
-        <x:v>374</x:v>
       </x:c>
       <x:c r="G106">
         <x:v>25</x:v>
@@ -6310,10 +6307,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K106" t="s">
-        <x:v>382</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="L106" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="M106">
         <x:v>800000</x:v>
@@ -6322,24 +6319,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O106" t="s">
-        <x:v>383</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="14.25">
       <x:c r="A107" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B107" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B107" t="s">
+      <x:c r="C107" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="C107" t="s">
+      <x:c r="E107" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F107" t="s">
         <x:v>373</x:v>
-      </x:c>
-      <x:c r="E107" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F107" t="s">
-        <x:v>374</x:v>
       </x:c>
       <x:c r="G107">
         <x:v>25</x:v>
@@ -6354,10 +6351,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K107" t="s">
-        <x:v>384</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="L107" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="M107">
         <x:v>1500000</x:v>
@@ -6366,24 +6363,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O107" t="s">
-        <x:v>385</x:v>
+        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="14.25">
       <x:c r="A108" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B108" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B108" t="s">
+      <x:c r="C108" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="C108" t="s">
+      <x:c r="E108" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F108" t="s">
         <x:v>373</x:v>
-      </x:c>
-      <x:c r="E108" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F108" t="s">
-        <x:v>374</x:v>
       </x:c>
       <x:c r="G108">
         <x:v>25</x:v>
@@ -6395,13 +6392,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J108" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K108" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="L108" t="s">
         <x:v>386</x:v>
-      </x:c>
-      <x:c r="L108" t="s">
-        <x:v>387</x:v>
       </x:c>
       <x:c r="M108">
         <x:v>3000000</x:v>
@@ -6410,24 +6407,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O108" t="s">
-        <x:v>388</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="14.25">
       <x:c r="A109" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B109" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B109" t="s">
+      <x:c r="C109" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="C109" t="s">
+      <x:c r="E109" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F109" t="s">
         <x:v>373</x:v>
-      </x:c>
-      <x:c r="E109" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F109" t="s">
-        <x:v>374</x:v>
       </x:c>
       <x:c r="G109">
         <x:v>25</x:v>
@@ -6439,13 +6436,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J109" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K109" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="L109" t="s">
         <x:v>389</x:v>
-      </x:c>
-      <x:c r="L109" t="s">
-        <x:v>390</x:v>
       </x:c>
       <x:c r="M109">
         <x:v>5000000</x:v>
@@ -6454,27 +6451,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O109" t="s">
-        <x:v>391</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="14.25">
       <x:c r="A110" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B110" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B110" t="s">
+      <x:c r="C110" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C110" t="s">
+      <x:c r="D110" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="D110" t="s">
-        <x:v>395</x:v>
-      </x:c>
       <x:c r="E110" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F110" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G110">
         <x:v>18</x:v>
@@ -6489,10 +6486,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="K110" t="s">
-        <x:v>393</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="L110" t="s">
-        <x:v>396</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="M110">
         <x:v>100000</x:v>
@@ -6501,27 +6498,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O110" t="s">
-        <x:v>397</x:v>
+        <x:v>396</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="14.25">
       <x:c r="A111" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B111" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B111" t="s">
+      <x:c r="C111" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C111" t="s">
+      <x:c r="D111" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="D111" t="s">
-        <x:v>395</x:v>
-      </x:c>
       <x:c r="E111" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F111" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G111">
         <x:v>18</x:v>
@@ -6536,10 +6533,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K111" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="L111" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="M111">
         <x:v>200000</x:v>
@@ -6548,27 +6545,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O111" t="s">
-        <x:v>398</x:v>
+        <x:v>397</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="14.25">
       <x:c r="A112" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B112" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B112" t="s">
+      <x:c r="C112" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C112" t="s">
+      <x:c r="D112" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="D112" t="s">
-        <x:v>395</x:v>
-      </x:c>
       <x:c r="E112" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F112" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G112">
         <x:v>18</x:v>
@@ -6583,10 +6580,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K112" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="L112" t="s">
         <x:v>399</x:v>
-      </x:c>
-      <x:c r="L112" t="s">
-        <x:v>400</x:v>
       </x:c>
       <x:c r="M112">
         <x:v>400000</x:v>
@@ -6595,27 +6592,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O112" t="s">
-        <x:v>401</x:v>
+        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="14.25">
       <x:c r="A113" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B113" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B113" t="s">
+      <x:c r="C113" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C113" t="s">
+      <x:c r="D113" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="D113" t="s">
-        <x:v>395</x:v>
-      </x:c>
       <x:c r="E113" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F113" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G113">
         <x:v>18</x:v>
@@ -6630,10 +6627,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K113" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="L113" t="s">
         <x:v>402</x:v>
-      </x:c>
-      <x:c r="L113" t="s">
-        <x:v>403</x:v>
       </x:c>
       <x:c r="M113">
         <x:v>800000</x:v>
@@ -6642,27 +6639,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O113" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="14.25">
       <x:c r="A114" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B114" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B114" t="s">
+      <x:c r="C114" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C114" t="s">
+      <x:c r="D114" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="D114" t="s">
-        <x:v>395</x:v>
-      </x:c>
       <x:c r="E114" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F114" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G114">
         <x:v>18</x:v>
@@ -6674,13 +6671,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J114" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K114" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="L114" t="s">
         <x:v>405</x:v>
-      </x:c>
-      <x:c r="L114" t="s">
-        <x:v>406</x:v>
       </x:c>
       <x:c r="M114">
         <x:v>1500000</x:v>
@@ -6689,27 +6686,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O114" t="s">
-        <x:v>407</x:v>
+        <x:v>406</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="14.25">
       <x:c r="A115" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B115" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B115" t="s">
+      <x:c r="C115" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C115" t="s">
+      <x:c r="D115" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="D115" t="s">
-        <x:v>395</x:v>
-      </x:c>
       <x:c r="E115" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F115" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G115">
         <x:v>18</x:v>
@@ -6721,13 +6718,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J115" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K115" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="L115" t="s">
         <x:v>408</x:v>
-      </x:c>
-      <x:c r="L115" t="s">
-        <x:v>409</x:v>
       </x:c>
       <x:c r="M115">
         <x:v>3000000</x:v>
@@ -6736,27 +6733,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O115" t="s">
-        <x:v>410</x:v>
+        <x:v>409</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="14.25">
       <x:c r="A116" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B116" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B116" t="s">
+      <x:c r="C116" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C116" t="s">
+      <x:c r="D116" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="D116" t="s">
-        <x:v>395</x:v>
-      </x:c>
       <x:c r="E116" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F116" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G116">
         <x:v>18</x:v>
@@ -6768,13 +6765,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J116" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K116" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="L116" t="s">
         <x:v>411</x:v>
-      </x:c>
-      <x:c r="L116" t="s">
-        <x:v>412</x:v>
       </x:c>
       <x:c r="M116">
         <x:v>5000000</x:v>
@@ -6783,24 +6780,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O116" t="s">
-        <x:v>413</x:v>
+        <x:v>412</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="14.25">
       <x:c r="A117" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B117" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B117" t="s">
+      <x:c r="C117" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C117" t="s">
-        <x:v>416</x:v>
-      </x:c>
       <x:c r="E117" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F117" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G117">
         <x:v>0</x:v>
@@ -6815,10 +6812,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K117" t="s">
-        <x:v>415</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="L117" t="s">
-        <x:v>417</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="M117">
         <x:v>100000</x:v>
@@ -6827,24 +6824,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O117" t="s">
-        <x:v>418</x:v>
+        <x:v>417</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="14.25">
       <x:c r="A118" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B118" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B118" t="s">
+      <x:c r="C118" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C118" t="s">
-        <x:v>416</x:v>
-      </x:c>
       <x:c r="E118" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F118" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G118">
         <x:v>0</x:v>
@@ -6859,10 +6856,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K118" t="s">
-        <x:v>419</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="L118" t="s">
-        <x:v>363</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="M118">
         <x:v>200000</x:v>
@@ -6871,24 +6868,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O118" t="s">
-        <x:v>420</x:v>
+        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="14.25">
       <x:c r="A119" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B119" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B119" t="s">
+      <x:c r="C119" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C119" t="s">
-        <x:v>416</x:v>
-      </x:c>
       <x:c r="E119" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F119" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G119">
         <x:v>0</x:v>
@@ -6903,10 +6900,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K119" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="L119" t="s">
         <x:v>421</x:v>
-      </x:c>
-      <x:c r="L119" t="s">
-        <x:v>422</x:v>
       </x:c>
       <x:c r="M119">
         <x:v>400000</x:v>
@@ -6915,24 +6912,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O119" t="s">
-        <x:v>423</x:v>
+        <x:v>422</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="14.25">
       <x:c r="A120" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B120" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B120" t="s">
+      <x:c r="C120" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C120" t="s">
-        <x:v>416</x:v>
-      </x:c>
       <x:c r="E120" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F120" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G120">
         <x:v>0</x:v>
@@ -6944,13 +6941,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J120" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K120" t="s">
-        <x:v>424</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="L120" t="s">
-        <x:v>422</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="M120">
         <x:v>800000</x:v>
@@ -6959,24 +6956,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O120" t="s">
-        <x:v>425</x:v>
+        <x:v>424</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="14.25">
       <x:c r="A121" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B121" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B121" t="s">
+      <x:c r="C121" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C121" t="s">
-        <x:v>416</x:v>
-      </x:c>
       <x:c r="E121" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F121" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G121">
         <x:v>0</x:v>
@@ -6988,13 +6985,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J121" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K121" t="s">
-        <x:v>426</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="L121" t="s">
-        <x:v>390</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="M121">
         <x:v>1500000</x:v>
@@ -7003,24 +7000,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O121" t="s">
-        <x:v>427</x:v>
+        <x:v>426</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="14.25">
       <x:c r="A122" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B122" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B122" t="s">
+      <x:c r="C122" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C122" t="s">
-        <x:v>416</x:v>
-      </x:c>
       <x:c r="E122" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F122" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G122">
         <x:v>0</x:v>
@@ -7032,13 +7029,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J122" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K122" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="L122" t="s">
         <x:v>428</x:v>
-      </x:c>
-      <x:c r="L122" t="s">
-        <x:v>429</x:v>
       </x:c>
       <x:c r="M122">
         <x:v>3000000</x:v>
@@ -7047,24 +7044,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O122" t="s">
-        <x:v>430</x:v>
+        <x:v>429</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="14.25">
       <x:c r="A123" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B123" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B123" t="s">
+      <x:c r="C123" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C123" t="s">
-        <x:v>416</x:v>
-      </x:c>
       <x:c r="E123" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F123" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="G123">
         <x:v>0</x:v>
@@ -7076,13 +7073,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J123" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K123" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="L123" t="s">
         <x:v>431</x:v>
-      </x:c>
-      <x:c r="L123" t="s">
-        <x:v>432</x:v>
       </x:c>
       <x:c r="M123">
         <x:v>5000000</x:v>
@@ -7091,24 +7088,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O123" t="s">
-        <x:v>433</x:v>
+        <x:v>432</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="14.25">
       <x:c r="A124" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B124" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B124" t="s">
+      <x:c r="C124" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="C124" t="s">
+      <x:c r="E124" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F124" t="s">
         <x:v>436</x:v>
-      </x:c>
-      <x:c r="E124" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F124" t="s">
-        <x:v>437</x:v>
       </x:c>
       <x:c r="G124">
         <x:v>18</x:v>
@@ -7123,10 +7120,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="K124" t="s">
-        <x:v>435</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="L124" t="s">
-        <x:v>438</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="M124">
         <x:v>100000</x:v>
@@ -7135,24 +7132,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O124" t="s">
-        <x:v>439</x:v>
+        <x:v>438</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="14.25">
       <x:c r="A125" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B125" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B125" t="s">
+      <x:c r="C125" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="C125" t="s">
+      <x:c r="E125" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F125" t="s">
         <x:v>436</x:v>
-      </x:c>
-      <x:c r="E125" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F125" t="s">
-        <x:v>437</x:v>
       </x:c>
       <x:c r="G125">
         <x:v>18</x:v>
@@ -7167,7 +7164,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K125" t="s">
-        <x:v>440</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="L125" t="s">
         <x:v>66</x:v>
@@ -7179,24 +7176,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O125" t="s">
-        <x:v>441</x:v>
+        <x:v>440</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="14.25">
       <x:c r="A126" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B126" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B126" t="s">
+      <x:c r="C126" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="C126" t="s">
+      <x:c r="E126" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F126" t="s">
         <x:v>436</x:v>
-      </x:c>
-      <x:c r="E126" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F126" t="s">
-        <x:v>437</x:v>
       </x:c>
       <x:c r="G126">
         <x:v>18</x:v>
@@ -7208,13 +7205,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J126" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K126" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="L126" t="s">
         <x:v>442</x:v>
-      </x:c>
-      <x:c r="L126" t="s">
-        <x:v>443</x:v>
       </x:c>
       <x:c r="M126">
         <x:v>400000</x:v>
@@ -7223,24 +7220,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O126" t="s">
-        <x:v>444</x:v>
+        <x:v>443</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="14.25">
       <x:c r="A127" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B127" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B127" t="s">
+      <x:c r="C127" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="C127" t="s">
+      <x:c r="E127" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F127" t="s">
         <x:v>436</x:v>
-      </x:c>
-      <x:c r="E127" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F127" t="s">
-        <x:v>437</x:v>
       </x:c>
       <x:c r="G127">
         <x:v>18</x:v>
@@ -7252,13 +7249,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J127" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K127" t="s">
-        <x:v>445</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="L127" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="M127">
         <x:v>800000</x:v>
@@ -7267,24 +7264,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O127" t="s">
-        <x:v>446</x:v>
+        <x:v>445</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="14.25">
       <x:c r="A128" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B128" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B128" t="s">
+      <x:c r="C128" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="C128" t="s">
+      <x:c r="E128" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F128" t="s">
         <x:v>436</x:v>
-      </x:c>
-      <x:c r="E128" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F128" t="s">
-        <x:v>437</x:v>
       </x:c>
       <x:c r="G128">
         <x:v>18</x:v>
@@ -7296,13 +7293,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J128" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K128" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="L128" t="s">
         <x:v>447</x:v>
-      </x:c>
-      <x:c r="L128" t="s">
-        <x:v>448</x:v>
       </x:c>
       <x:c r="M128">
         <x:v>1500000</x:v>
@@ -7311,24 +7308,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O128" t="s">
-        <x:v>449</x:v>
+        <x:v>448</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="14.25">
       <x:c r="A129" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B129" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B129" t="s">
+      <x:c r="C129" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="C129" t="s">
+      <x:c r="E129" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F129" t="s">
         <x:v>436</x:v>
-      </x:c>
-      <x:c r="E129" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F129" t="s">
-        <x:v>437</x:v>
       </x:c>
       <x:c r="G129">
         <x:v>18</x:v>
@@ -7340,10 +7337,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J129" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K129" t="s">
-        <x:v>450</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="L129" t="s">
         <x:v>66</x:v>
@@ -7355,24 +7352,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O129" t="s">
-        <x:v>451</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="14.25">
       <x:c r="A130" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B130" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B130" t="s">
+      <x:c r="C130" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="C130" t="s">
+      <x:c r="E130" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F130" t="s">
         <x:v>436</x:v>
-      </x:c>
-      <x:c r="E130" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F130" t="s">
-        <x:v>437</x:v>
       </x:c>
       <x:c r="G130">
         <x:v>18</x:v>
@@ -7384,13 +7381,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J130" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K130" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="L130" t="s">
         <x:v>452</x:v>
-      </x:c>
-      <x:c r="L130" t="s">
-        <x:v>453</x:v>
       </x:c>
       <x:c r="M130">
         <x:v>5000000</x:v>
@@ -7399,24 +7396,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O130" t="s">
-        <x:v>454</x:v>
+        <x:v>453</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="14.25">
       <x:c r="A131" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B131" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="B131" t="s">
+      <x:c r="C131" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="C131" t="s">
-        <x:v>457</x:v>
-      </x:c>
       <x:c r="E131" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F131" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G131">
         <x:v>14</x:v>
@@ -7431,10 +7428,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="K131" t="s">
-        <x:v>456</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="L131" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="M131">
         <x:v>100000</x:v>
@@ -7443,24 +7440,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O131" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="14.25">
       <x:c r="A132" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B132" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="B132" t="s">
+      <x:c r="C132" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="C132" t="s">
-        <x:v>457</x:v>
-      </x:c>
       <x:c r="E132" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F132" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G132">
         <x:v>14</x:v>
@@ -7472,13 +7469,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J132" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K132" t="s">
-        <x:v>460</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="L132" t="s">
-        <x:v>443</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="M132">
         <x:v>200000</x:v>
@@ -7487,24 +7484,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O132" t="s">
-        <x:v>461</x:v>
+        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="14.25">
       <x:c r="A133" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B133" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="B133" t="s">
+      <x:c r="C133" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="C133" t="s">
-        <x:v>457</x:v>
-      </x:c>
       <x:c r="E133" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F133" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G133">
         <x:v>14</x:v>
@@ -7516,13 +7513,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J133" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K133" t="s">
-        <x:v>462</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="L133" t="s">
-        <x:v>443</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="M133">
         <x:v>400000</x:v>
@@ -7531,24 +7528,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O133" t="s">
-        <x:v>463</x:v>
+        <x:v>462</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="14.25">
       <x:c r="A134" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B134" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="B134" t="s">
+      <x:c r="C134" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="C134" t="s">
-        <x:v>457</x:v>
-      </x:c>
       <x:c r="E134" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F134" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G134">
         <x:v>14</x:v>
@@ -7560,13 +7557,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J134" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K134" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="L134" t="s">
         <x:v>464</x:v>
-      </x:c>
-      <x:c r="L134" t="s">
-        <x:v>465</x:v>
       </x:c>
       <x:c r="M134">
         <x:v>800000</x:v>
@@ -7575,24 +7572,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O134" t="s">
-        <x:v>466</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="14.25">
       <x:c r="A135" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B135" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="B135" t="s">
+      <x:c r="C135" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="C135" t="s">
-        <x:v>457</x:v>
-      </x:c>
       <x:c r="E135" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F135" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G135">
         <x:v>14</x:v>
@@ -7604,13 +7601,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J135" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K135" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="L135" t="s">
         <x:v>467</x:v>
-      </x:c>
-      <x:c r="L135" t="s">
-        <x:v>468</x:v>
       </x:c>
       <x:c r="M135">
         <x:v>1500000</x:v>
@@ -7619,24 +7616,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O135" t="s">
-        <x:v>469</x:v>
+        <x:v>468</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="14.25">
       <x:c r="A136" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B136" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="B136" t="s">
+      <x:c r="C136" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="C136" t="s">
-        <x:v>457</x:v>
-      </x:c>
       <x:c r="E136" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F136" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G136">
         <x:v>14</x:v>
@@ -7648,13 +7645,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J136" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K136" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="L136" t="s">
         <x:v>470</x:v>
-      </x:c>
-      <x:c r="L136" t="s">
-        <x:v>471</x:v>
       </x:c>
       <x:c r="M136">
         <x:v>3000000</x:v>
@@ -7663,24 +7660,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O136" t="s">
-        <x:v>472</x:v>
+        <x:v>471</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="14.25">
       <x:c r="A137" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B137" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="B137" t="s">
+      <x:c r="C137" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="C137" t="s">
-        <x:v>457</x:v>
-      </x:c>
       <x:c r="E137" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F137" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G137">
         <x:v>14</x:v>
@@ -7692,13 +7689,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J137" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K137" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="L137" t="s">
         <x:v>473</x:v>
-      </x:c>
-      <x:c r="L137" t="s">
-        <x:v>474</x:v>
       </x:c>
       <x:c r="M137">
         <x:v>5000000</x:v>
@@ -7707,27 +7704,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O137" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="14.25">
       <x:c r="A138" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B138" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="B138" t="s">
+      <x:c r="C138" t="s">
         <x:v>477</x:v>
       </x:c>
-      <x:c r="C138" t="s">
+      <x:c r="D138" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="D138" t="s">
-        <x:v>479</x:v>
-      </x:c>
       <x:c r="E138" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F138" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G138">
         <x:v>20</x:v>
@@ -7739,13 +7736,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J138" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K138" t="s">
-        <x:v>477</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="L138" t="s">
-        <x:v>480</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="M138">
         <x:v>100000</x:v>
@@ -7754,27 +7751,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O138" t="s">
-        <x:v>481</x:v>
+        <x:v>480</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="14.25">
       <x:c r="A139" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B139" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="B139" t="s">
+      <x:c r="C139" t="s">
         <x:v>477</x:v>
       </x:c>
-      <x:c r="C139" t="s">
+      <x:c r="D139" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="D139" t="s">
-        <x:v>479</x:v>
-      </x:c>
       <x:c r="E139" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F139" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G139">
         <x:v>20</x:v>
@@ -7786,13 +7783,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J139" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K139" t="s">
-        <x:v>482</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="L139" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="M139">
         <x:v>200000</x:v>
@@ -7801,27 +7798,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O139" t="s">
-        <x:v>483</x:v>
+        <x:v>482</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="14.25">
       <x:c r="A140" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B140" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="B140" t="s">
+      <x:c r="C140" t="s">
         <x:v>477</x:v>
       </x:c>
-      <x:c r="C140" t="s">
+      <x:c r="D140" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="D140" t="s">
-        <x:v>479</x:v>
-      </x:c>
       <x:c r="E140" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F140" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G140">
         <x:v>20</x:v>
@@ -7833,13 +7830,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J140" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K140" t="s">
-        <x:v>484</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="L140" t="s">
-        <x:v>443</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="M140">
         <x:v>400000</x:v>
@@ -7848,27 +7845,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O140" t="s">
-        <x:v>485</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="14.25">
       <x:c r="A141" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B141" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="B141" t="s">
+      <x:c r="C141" t="s">
         <x:v>477</x:v>
       </x:c>
-      <x:c r="C141" t="s">
+      <x:c r="D141" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="D141" t="s">
-        <x:v>479</x:v>
-      </x:c>
       <x:c r="E141" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F141" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G141">
         <x:v>20</x:v>
@@ -7880,13 +7877,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J141" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K141" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="L141" t="s">
         <x:v>486</x:v>
-      </x:c>
-      <x:c r="L141" t="s">
-        <x:v>487</x:v>
       </x:c>
       <x:c r="M141">
         <x:v>800000</x:v>
@@ -7895,27 +7892,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O141" t="s">
-        <x:v>488</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="14.25">
       <x:c r="A142" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B142" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="B142" t="s">
+      <x:c r="C142" t="s">
         <x:v>477</x:v>
       </x:c>
-      <x:c r="C142" t="s">
+      <x:c r="D142" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="D142" t="s">
-        <x:v>479</x:v>
-      </x:c>
       <x:c r="E142" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F142" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G142">
         <x:v>20</x:v>
@@ -7927,13 +7924,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J142" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K142" t="s">
-        <x:v>489</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="L142" t="s">
-        <x:v>390</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="M142">
         <x:v>1500000</x:v>
@@ -7942,27 +7939,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O142" t="s">
-        <x:v>490</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="14.25">
       <x:c r="A143" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B143" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="B143" t="s">
+      <x:c r="C143" t="s">
         <x:v>477</x:v>
       </x:c>
-      <x:c r="C143" t="s">
+      <x:c r="D143" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="D143" t="s">
-        <x:v>479</x:v>
-      </x:c>
       <x:c r="E143" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F143" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G143">
         <x:v>20</x:v>
@@ -7974,13 +7971,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J143" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K143" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="L143" t="s">
         <x:v>491</x:v>
-      </x:c>
-      <x:c r="L143" t="s">
-        <x:v>492</x:v>
       </x:c>
       <x:c r="M143">
         <x:v>3000000</x:v>
@@ -7989,27 +7986,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O143" t="s">
-        <x:v>493</x:v>
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="14.25">
       <x:c r="A144" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B144" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="B144" t="s">
+      <x:c r="C144" t="s">
         <x:v>477</x:v>
       </x:c>
-      <x:c r="C144" t="s">
+      <x:c r="D144" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="D144" t="s">
-        <x:v>479</x:v>
-      </x:c>
       <x:c r="E144" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F144" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="G144">
         <x:v>20</x:v>
@@ -8021,13 +8018,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J144" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="K144" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="L144" t="s">
         <x:v>494</x:v>
-      </x:c>
-      <x:c r="L144" t="s">
-        <x:v>495</x:v>
       </x:c>
       <x:c r="M144">
         <x:v>5000000</x:v>
@@ -8036,24 +8033,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O144" t="s">
-        <x:v>496</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="14.25">
       <x:c r="A145" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B145" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="B145" t="s">
+      <x:c r="C145" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="C145" t="s">
+      <x:c r="E145" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F145" t="s">
         <x:v>499</x:v>
-      </x:c>
-      <x:c r="E145" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F145" t="s">
-        <x:v>500</x:v>
       </x:c>
       <x:c r="G145">
         <x:v>18</x:v>
@@ -8065,13 +8062,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J145" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K145" t="s">
-        <x:v>498</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="L145" t="s">
-        <x:v>501</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="M145">
         <x:v>100000</x:v>
@@ -8080,24 +8077,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O145" t="s">
-        <x:v>502</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="14.25">
       <x:c r="A146" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B146" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="B146" t="s">
+      <x:c r="C146" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="C146" t="s">
+      <x:c r="E146" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F146" t="s">
         <x:v>499</x:v>
-      </x:c>
-      <x:c r="E146" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F146" t="s">
-        <x:v>500</x:v>
       </x:c>
       <x:c r="G146">
         <x:v>18</x:v>
@@ -8109,13 +8106,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J146" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K146" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="L146" t="s">
         <x:v>503</x:v>
-      </x:c>
-      <x:c r="L146" t="s">
-        <x:v>504</x:v>
       </x:c>
       <x:c r="M146">
         <x:v>200000</x:v>
@@ -8124,24 +8121,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O146" t="s">
-        <x:v>505</x:v>
+        <x:v>504</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="14.25">
       <x:c r="A147" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B147" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="B147" t="s">
+      <x:c r="C147" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="C147" t="s">
+      <x:c r="E147" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F147" t="s">
         <x:v>499</x:v>
-      </x:c>
-      <x:c r="E147" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F147" t="s">
-        <x:v>500</x:v>
       </x:c>
       <x:c r="G147">
         <x:v>18</x:v>
@@ -8153,13 +8150,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J147" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K147" t="s">
-        <x:v>506</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="L147" t="s">
-        <x:v>465</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="M147">
         <x:v>400000</x:v>
@@ -8168,24 +8165,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O147" t="s">
-        <x:v>507</x:v>
+        <x:v>506</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="14.25">
       <x:c r="A148" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B148" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="B148" t="s">
+      <x:c r="C148" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="C148" t="s">
+      <x:c r="E148" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F148" t="s">
         <x:v>499</x:v>
-      </x:c>
-      <x:c r="E148" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F148" t="s">
-        <x:v>500</x:v>
       </x:c>
       <x:c r="G148">
         <x:v>18</x:v>
@@ -8197,13 +8194,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J148" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K148" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="L148" t="s">
         <x:v>508</x:v>
-      </x:c>
-      <x:c r="L148" t="s">
-        <x:v>509</x:v>
       </x:c>
       <x:c r="M148">
         <x:v>800000</x:v>
@@ -8212,24 +8209,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O148" t="s">
-        <x:v>510</x:v>
+        <x:v>509</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="14.25">
       <x:c r="A149" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B149" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="B149" t="s">
+      <x:c r="C149" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="C149" t="s">
+      <x:c r="E149" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F149" t="s">
         <x:v>499</x:v>
-      </x:c>
-      <x:c r="E149" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F149" t="s">
-        <x:v>500</x:v>
       </x:c>
       <x:c r="G149">
         <x:v>18</x:v>
@@ -8241,13 +8238,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J149" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K149" t="s">
-        <x:v>511</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="L149" t="s">
-        <x:v>443</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="M149">
         <x:v>1500000</x:v>
@@ -8256,24 +8253,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O149" t="s">
-        <x:v>512</x:v>
+        <x:v>511</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="14.25">
       <x:c r="A150" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B150" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="B150" t="s">
+      <x:c r="C150" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="C150" t="s">
+      <x:c r="E150" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F150" t="s">
         <x:v>499</x:v>
-      </x:c>
-      <x:c r="E150" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F150" t="s">
-        <x:v>500</x:v>
       </x:c>
       <x:c r="G150">
         <x:v>18</x:v>
@@ -8285,13 +8282,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J150" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="K150" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="L150" t="s">
         <x:v>513</x:v>
-      </x:c>
-      <x:c r="L150" t="s">
-        <x:v>514</x:v>
       </x:c>
       <x:c r="M150">
         <x:v>3000000</x:v>
@@ -8300,24 +8297,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O150" t="s">
-        <x:v>515</x:v>
+        <x:v>514</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="14.25">
       <x:c r="A151" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B151" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="B151" t="s">
+      <x:c r="C151" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="C151" t="s">
+      <x:c r="E151" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F151" t="s">
         <x:v>499</x:v>
-      </x:c>
-      <x:c r="E151" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F151" t="s">
-        <x:v>500</x:v>
       </x:c>
       <x:c r="G151">
         <x:v>18</x:v>
@@ -8329,13 +8326,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J151" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="K151" t="s">
         <x:v>516</x:v>
       </x:c>
-      <x:c r="K151" t="s">
+      <x:c r="L151" t="s">
         <x:v>517</x:v>
-      </x:c>
-      <x:c r="L151" t="s">
-        <x:v>518</x:v>
       </x:c>
       <x:c r="M151">
         <x:v>5000000</x:v>
@@ -8344,24 +8341,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O151" t="s">
-        <x:v>519</x:v>
+        <x:v>518</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="14.25">
       <x:c r="A152" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B152" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="B152" t="s">
+      <x:c r="C152" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="C152" t="s">
-        <x:v>522</x:v>
-      </x:c>
       <x:c r="E152" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F152" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G152">
         <x:v>14</x:v>
@@ -8373,13 +8370,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J152" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K152" t="s">
-        <x:v>521</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="L152" t="s">
-        <x:v>523</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="M152">
         <x:v>100000</x:v>
@@ -8388,24 +8385,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O152" t="s">
-        <x:v>524</x:v>
+        <x:v>523</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="14.25">
       <x:c r="A153" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B153" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="B153" t="s">
+      <x:c r="C153" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="C153" t="s">
-        <x:v>522</x:v>
-      </x:c>
       <x:c r="E153" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F153" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G153">
         <x:v>14</x:v>
@@ -8417,13 +8414,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J153" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K153" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="L153" t="s">
         <x:v>525</x:v>
-      </x:c>
-      <x:c r="L153" t="s">
-        <x:v>526</x:v>
       </x:c>
       <x:c r="M153">
         <x:v>200000</x:v>
@@ -8432,24 +8429,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O153" t="s">
-        <x:v>527</x:v>
+        <x:v>526</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="14.25">
       <x:c r="A154" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B154" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="B154" t="s">
+      <x:c r="C154" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="C154" t="s">
-        <x:v>522</x:v>
-      </x:c>
       <x:c r="E154" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F154" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G154">
         <x:v>14</x:v>
@@ -8461,13 +8458,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J154" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K154" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="L154" t="s">
         <x:v>528</x:v>
-      </x:c>
-      <x:c r="L154" t="s">
-        <x:v>529</x:v>
       </x:c>
       <x:c r="M154">
         <x:v>400000</x:v>
@@ -8476,24 +8473,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O154" t="s">
-        <x:v>530</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="14.25">
       <x:c r="A155" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B155" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="B155" t="s">
+      <x:c r="C155" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="C155" t="s">
-        <x:v>522</x:v>
-      </x:c>
       <x:c r="E155" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F155" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G155">
         <x:v>14</x:v>
@@ -8505,13 +8502,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J155" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K155" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="L155" t="s">
         <x:v>531</x:v>
-      </x:c>
-      <x:c r="L155" t="s">
-        <x:v>532</x:v>
       </x:c>
       <x:c r="M155">
         <x:v>800000</x:v>
@@ -8520,24 +8517,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O155" t="s">
-        <x:v>533</x:v>
+        <x:v>532</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="14.25">
       <x:c r="A156" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B156" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="B156" t="s">
+      <x:c r="C156" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="C156" t="s">
-        <x:v>522</x:v>
-      </x:c>
       <x:c r="E156" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F156" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G156">
         <x:v>14</x:v>
@@ -8549,13 +8546,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J156" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="K156" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="L156" t="s">
         <x:v>534</x:v>
-      </x:c>
-      <x:c r="L156" t="s">
-        <x:v>535</x:v>
       </x:c>
       <x:c r="M156">
         <x:v>1500000</x:v>
@@ -8564,24 +8561,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O156" t="s">
-        <x:v>536</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="14.25">
       <x:c r="A157" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B157" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="B157" t="s">
+      <x:c r="C157" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="C157" t="s">
-        <x:v>522</x:v>
-      </x:c>
       <x:c r="E157" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F157" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G157">
         <x:v>14</x:v>
@@ -8593,13 +8590,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J157" t="s">
-        <x:v>516</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="K157" t="s">
-        <x:v>537</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="L157" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="M157">
         <x:v>3000000</x:v>
@@ -8608,24 +8605,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O157" t="s">
-        <x:v>538</x:v>
+        <x:v>537</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="14.25">
       <x:c r="A158" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B158" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="B158" t="s">
+      <x:c r="C158" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="C158" t="s">
-        <x:v>522</x:v>
-      </x:c>
       <x:c r="E158" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F158" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G158">
         <x:v>14</x:v>
@@ -8637,13 +8634,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J158" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="K158" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="K158" t="s">
+      <x:c r="L158" t="s">
         <x:v>540</x:v>
-      </x:c>
-      <x:c r="L158" t="s">
-        <x:v>541</x:v>
       </x:c>
       <x:c r="M158">
         <x:v>5000000</x:v>
@@ -8652,24 +8649,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O158" t="s">
-        <x:v>542</x:v>
+        <x:v>541</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="14.25">
       <x:c r="A159" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B159" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="B159" t="s">
+      <x:c r="C159" t="s">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="C159" t="s">
-        <x:v>545</x:v>
-      </x:c>
       <x:c r="E159" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F159" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G159">
         <x:v>20</x:v>
@@ -8681,13 +8678,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J159" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K159" t="s">
-        <x:v>544</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="L159" t="s">
-        <x:v>546</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="M159">
         <x:v>100000</x:v>
@@ -8696,24 +8693,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O159" t="s">
-        <x:v>547</x:v>
+        <x:v>546</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="14.25">
       <x:c r="A160" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B160" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="B160" t="s">
+      <x:c r="C160" t="s">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="C160" t="s">
-        <x:v>545</x:v>
-      </x:c>
       <x:c r="E160" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F160" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G160">
         <x:v>20</x:v>
@@ -8725,13 +8722,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J160" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K160" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="L160" t="s">
         <x:v>548</x:v>
-      </x:c>
-      <x:c r="L160" t="s">
-        <x:v>549</x:v>
       </x:c>
       <x:c r="M160">
         <x:v>200000</x:v>
@@ -8740,24 +8737,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O160" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="14.25">
       <x:c r="A161" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B161" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="B161" t="s">
+      <x:c r="C161" t="s">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="C161" t="s">
-        <x:v>545</x:v>
-      </x:c>
       <x:c r="E161" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F161" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G161">
         <x:v>20</x:v>
@@ -8769,13 +8766,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J161" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K161" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="L161" t="s">
         <x:v>551</x:v>
-      </x:c>
-      <x:c r="L161" t="s">
-        <x:v>552</x:v>
       </x:c>
       <x:c r="M161">
         <x:v>400000</x:v>
@@ -8784,24 +8781,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O161" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="14.25">
       <x:c r="A162" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B162" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="B162" t="s">
+      <x:c r="C162" t="s">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="C162" t="s">
-        <x:v>545</x:v>
-      </x:c>
       <x:c r="E162" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F162" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G162">
         <x:v>20</x:v>
@@ -8813,13 +8810,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J162" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="K162" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="L162" t="s">
         <x:v>554</x:v>
-      </x:c>
-      <x:c r="L162" t="s">
-        <x:v>555</x:v>
       </x:c>
       <x:c r="M162">
         <x:v>800000</x:v>
@@ -8828,24 +8825,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O162" t="s">
-        <x:v>556</x:v>
+        <x:v>555</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="14.25">
       <x:c r="A163" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B163" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="B163" t="s">
+      <x:c r="C163" t="s">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="C163" t="s">
-        <x:v>545</x:v>
-      </x:c>
       <x:c r="E163" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F163" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G163">
         <x:v>20</x:v>
@@ -8857,13 +8854,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J163" t="s">
-        <x:v>516</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="K163" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="L163" t="s">
         <x:v>557</x:v>
-      </x:c>
-      <x:c r="L163" t="s">
-        <x:v>558</x:v>
       </x:c>
       <x:c r="M163">
         <x:v>1500000</x:v>
@@ -8872,24 +8869,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O163" t="s">
-        <x:v>559</x:v>
+        <x:v>558</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="14.25">
       <x:c r="A164" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B164" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="B164" t="s">
+      <x:c r="C164" t="s">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="C164" t="s">
-        <x:v>545</x:v>
-      </x:c>
       <x:c r="E164" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F164" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G164">
         <x:v>20</x:v>
@@ -8901,13 +8898,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J164" t="s">
-        <x:v>539</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="K164" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="L164" t="s">
         <x:v>560</x:v>
-      </x:c>
-      <x:c r="L164" t="s">
-        <x:v>561</x:v>
       </x:c>
       <x:c r="M164">
         <x:v>3000000</x:v>
@@ -8916,24 +8913,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O164" t="s">
-        <x:v>562</x:v>
+        <x:v>561</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="14.25">
       <x:c r="A165" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B165" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="B165" t="s">
+      <x:c r="C165" t="s">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="C165" t="s">
-        <x:v>545</x:v>
-      </x:c>
       <x:c r="E165" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F165" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G165">
         <x:v>20</x:v>
@@ -8945,13 +8942,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J165" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="K165" t="s">
         <x:v>563</x:v>
       </x:c>
-      <x:c r="K165" t="s">
+      <x:c r="L165" t="s">
         <x:v>564</x:v>
-      </x:c>
-      <x:c r="L165" t="s">
-        <x:v>565</x:v>
       </x:c>
       <x:c r="M165">
         <x:v>5000000</x:v>
@@ -8960,27 +8957,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O165" t="s">
-        <x:v>566</x:v>
+        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="14.25">
       <x:c r="A166" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B166" t="s">
         <x:v>567</x:v>
       </x:c>
-      <x:c r="B166" t="s">
+      <x:c r="C166" t="s">
         <x:v>568</x:v>
       </x:c>
-      <x:c r="C166" t="s">
+      <x:c r="D166" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="D166" t="s">
+      <x:c r="E166" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F166" t="s">
         <x:v>570</x:v>
-      </x:c>
-      <x:c r="E166" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F166" t="s">
-        <x:v>571</x:v>
       </x:c>
       <x:c r="G166">
         <x:v>18</x:v>
@@ -8992,13 +8989,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J166" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K166" t="s">
-        <x:v>568</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="L166" t="s">
-        <x:v>572</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="M166">
         <x:v>100000</x:v>
@@ -9007,27 +9004,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O166" t="s">
-        <x:v>573</x:v>
+        <x:v>572</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="14.25">
       <x:c r="A167" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B167" t="s">
         <x:v>567</x:v>
       </x:c>
-      <x:c r="B167" t="s">
+      <x:c r="C167" t="s">
         <x:v>568</x:v>
       </x:c>
-      <x:c r="C167" t="s">
+      <x:c r="D167" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="D167" t="s">
+      <x:c r="E167" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F167" t="s">
         <x:v>570</x:v>
-      </x:c>
-      <x:c r="E167" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F167" t="s">
-        <x:v>571</x:v>
       </x:c>
       <x:c r="G167">
         <x:v>18</x:v>
@@ -9039,13 +9036,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J167" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K167" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="L167" t="s">
         <x:v>574</x:v>
-      </x:c>
-      <x:c r="L167" t="s">
-        <x:v>575</x:v>
       </x:c>
       <x:c r="M167">
         <x:v>200000</x:v>
@@ -9054,27 +9051,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O167" t="s">
-        <x:v>576</x:v>
+        <x:v>575</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="14.25">
       <x:c r="A168" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B168" t="s">
         <x:v>567</x:v>
       </x:c>
-      <x:c r="B168" t="s">
+      <x:c r="C168" t="s">
         <x:v>568</x:v>
       </x:c>
-      <x:c r="C168" t="s">
+      <x:c r="D168" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="D168" t="s">
+      <x:c r="E168" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F168" t="s">
         <x:v>570</x:v>
-      </x:c>
-      <x:c r="E168" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F168" t="s">
-        <x:v>571</x:v>
       </x:c>
       <x:c r="G168">
         <x:v>18</x:v>
@@ -9086,13 +9083,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J168" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="K168" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="L168" t="s">
         <x:v>577</x:v>
-      </x:c>
-      <x:c r="L168" t="s">
-        <x:v>578</x:v>
       </x:c>
       <x:c r="M168">
         <x:v>400000</x:v>
@@ -9101,27 +9098,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O168" t="s">
-        <x:v>579</x:v>
+        <x:v>578</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="14.25">
       <x:c r="A169" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B169" t="s">
         <x:v>567</x:v>
       </x:c>
-      <x:c r="B169" t="s">
+      <x:c r="C169" t="s">
         <x:v>568</x:v>
       </x:c>
-      <x:c r="C169" t="s">
+      <x:c r="D169" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="D169" t="s">
+      <x:c r="E169" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F169" t="s">
         <x:v>570</x:v>
-      </x:c>
-      <x:c r="E169" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F169" t="s">
-        <x:v>571</x:v>
       </x:c>
       <x:c r="G169">
         <x:v>18</x:v>
@@ -9133,13 +9130,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J169" t="s">
-        <x:v>516</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="K169" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="L169" t="s">
         <x:v>580</x:v>
-      </x:c>
-      <x:c r="L169" t="s">
-        <x:v>581</x:v>
       </x:c>
       <x:c r="M169">
         <x:v>800000</x:v>
@@ -9148,27 +9145,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O169" t="s">
-        <x:v>582</x:v>
+        <x:v>581</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="14.25">
       <x:c r="A170" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B170" t="s">
         <x:v>567</x:v>
       </x:c>
-      <x:c r="B170" t="s">
+      <x:c r="C170" t="s">
         <x:v>568</x:v>
       </x:c>
-      <x:c r="C170" t="s">
+      <x:c r="D170" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="D170" t="s">
+      <x:c r="E170" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F170" t="s">
         <x:v>570</x:v>
-      </x:c>
-      <x:c r="E170" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F170" t="s">
-        <x:v>571</x:v>
       </x:c>
       <x:c r="G170">
         <x:v>18</x:v>
@@ -9180,13 +9177,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J170" t="s">
-        <x:v>539</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="K170" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="L170" t="s">
         <x:v>583</x:v>
-      </x:c>
-      <x:c r="L170" t="s">
-        <x:v>584</x:v>
       </x:c>
       <x:c r="M170">
         <x:v>1500000</x:v>
@@ -9195,27 +9192,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O170" t="s">
-        <x:v>585</x:v>
+        <x:v>584</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="14.25">
       <x:c r="A171" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B171" t="s">
         <x:v>567</x:v>
       </x:c>
-      <x:c r="B171" t="s">
+      <x:c r="C171" t="s">
         <x:v>568</x:v>
       </x:c>
-      <x:c r="C171" t="s">
+      <x:c r="D171" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="D171" t="s">
+      <x:c r="E171" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F171" t="s">
         <x:v>570</x:v>
-      </x:c>
-      <x:c r="E171" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F171" t="s">
-        <x:v>571</x:v>
       </x:c>
       <x:c r="G171">
         <x:v>18</x:v>
@@ -9227,13 +9224,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J171" t="s">
-        <x:v>563</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="K171" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="L171" t="s">
         <x:v>586</x:v>
-      </x:c>
-      <x:c r="L171" t="s">
-        <x:v>587</x:v>
       </x:c>
       <x:c r="M171">
         <x:v>3000000</x:v>
@@ -9242,27 +9239,27 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O171" t="s">
-        <x:v>588</x:v>
+        <x:v>587</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="14.25">
       <x:c r="A172" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B172" t="s">
         <x:v>567</x:v>
       </x:c>
-      <x:c r="B172" t="s">
+      <x:c r="C172" t="s">
         <x:v>568</x:v>
       </x:c>
-      <x:c r="C172" t="s">
+      <x:c r="D172" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="D172" t="s">
+      <x:c r="E172" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F172" t="s">
         <x:v>570</x:v>
-      </x:c>
-      <x:c r="E172" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F172" t="s">
-        <x:v>571</x:v>
       </x:c>
       <x:c r="G172">
         <x:v>18</x:v>
@@ -9274,13 +9271,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J172" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="K172" t="s">
         <x:v>589</x:v>
       </x:c>
-      <x:c r="K172" t="s">
+      <x:c r="L172" t="s">
         <x:v>590</x:v>
-      </x:c>
-      <x:c r="L172" t="s">
-        <x:v>591</x:v>
       </x:c>
       <x:c r="M172">
         <x:v>5000000</x:v>
@@ -9289,24 +9286,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O172" t="s">
-        <x:v>592</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="14.25">
       <x:c r="A173" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B173" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="B173" t="s">
+      <x:c r="C173" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="C173" t="s">
-        <x:v>595</x:v>
-      </x:c>
       <x:c r="E173" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F173" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G173">
         <x:v>18</x:v>
@@ -9318,13 +9315,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J173" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K173" t="s">
-        <x:v>594</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="L173" t="s">
-        <x:v>596</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="M173">
         <x:v>100000</x:v>
@@ -9333,24 +9330,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O173" t="s">
-        <x:v>597</x:v>
+        <x:v>596</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="14.25">
       <x:c r="A174" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B174" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="B174" t="s">
+      <x:c r="C174" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="C174" t="s">
-        <x:v>595</x:v>
-      </x:c>
       <x:c r="E174" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F174" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G174">
         <x:v>18</x:v>
@@ -9362,13 +9359,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J174" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="K174" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="L174" t="s">
         <x:v>598</x:v>
-      </x:c>
-      <x:c r="L174" t="s">
-        <x:v>599</x:v>
       </x:c>
       <x:c r="M174">
         <x:v>200000</x:v>
@@ -9377,24 +9374,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O174" t="s">
-        <x:v>600</x:v>
+        <x:v>599</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="14.25">
       <x:c r="A175" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B175" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="B175" t="s">
+      <x:c r="C175" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="C175" t="s">
-        <x:v>595</x:v>
-      </x:c>
       <x:c r="E175" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F175" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G175">
         <x:v>18</x:v>
@@ -9406,13 +9403,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J175" t="s">
-        <x:v>516</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="K175" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L175" t="s">
         <x:v>601</x:v>
-      </x:c>
-      <x:c r="L175" t="s">
-        <x:v>602</x:v>
       </x:c>
       <x:c r="M175">
         <x:v>400000</x:v>
@@ -9421,24 +9418,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O175" t="s">
-        <x:v>603</x:v>
+        <x:v>602</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="14.25">
       <x:c r="A176" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B176" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="B176" t="s">
+      <x:c r="C176" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="C176" t="s">
-        <x:v>595</x:v>
-      </x:c>
       <x:c r="E176" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F176" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G176">
         <x:v>18</x:v>
@@ -9450,13 +9447,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J176" t="s">
-        <x:v>539</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="K176" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="L176" t="s">
-        <x:v>604</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="M176">
         <x:v>800000</x:v>
@@ -9465,24 +9462,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O176" t="s">
-        <x:v>605</x:v>
+        <x:v>604</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="14.25">
       <x:c r="A177" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B177" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="B177" t="s">
+      <x:c r="C177" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="C177" t="s">
-        <x:v>595</x:v>
-      </x:c>
       <x:c r="E177" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F177" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G177">
         <x:v>18</x:v>
@@ -9494,13 +9491,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J177" t="s">
-        <x:v>563</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="K177" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="L177" t="s">
         <x:v>606</x:v>
-      </x:c>
-      <x:c r="L177" t="s">
-        <x:v>607</x:v>
       </x:c>
       <x:c r="M177">
         <x:v>1500000</x:v>
@@ -9509,24 +9506,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O177" t="s">
-        <x:v>608</x:v>
+        <x:v>607</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="14.25">
       <x:c r="A178" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B178" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="B178" t="s">
+      <x:c r="C178" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="C178" t="s">
-        <x:v>595</x:v>
-      </x:c>
       <x:c r="E178" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F178" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G178">
         <x:v>18</x:v>
@@ -9538,13 +9535,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J178" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="K178" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="L178" t="s">
         <x:v>609</x:v>
-      </x:c>
-      <x:c r="L178" t="s">
-        <x:v>610</x:v>
       </x:c>
       <x:c r="M178">
         <x:v>3000000</x:v>
@@ -9553,24 +9550,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O178" t="s">
-        <x:v>611</x:v>
+        <x:v>610</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="14.25">
       <x:c r="A179" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B179" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="B179" t="s">
+      <x:c r="C179" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="C179" t="s">
-        <x:v>595</x:v>
-      </x:c>
       <x:c r="E179" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F179" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G179">
         <x:v>18</x:v>
@@ -9582,13 +9579,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J179" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="K179" t="s">
         <x:v>612</x:v>
       </x:c>
-      <x:c r="K179" t="s">
+      <x:c r="L179" t="s">
         <x:v>613</x:v>
-      </x:c>
-      <x:c r="L179" t="s">
-        <x:v>614</x:v>
       </x:c>
       <x:c r="M179">
         <x:v>5000000</x:v>
@@ -9597,24 +9594,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O179" t="s">
-        <x:v>615</x:v>
+        <x:v>614</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="14.25">
       <x:c r="A180" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B180" t="s">
         <x:v>616</x:v>
       </x:c>
-      <x:c r="B180" t="s">
+      <x:c r="C180" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="C180" t="s">
-        <x:v>618</x:v>
-      </x:c>
       <x:c r="E180" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F180" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G180">
         <x:v>24</x:v>
@@ -9626,13 +9623,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J180" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="K180" t="s">
-        <x:v>617</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="L180" t="s">
-        <x:v>619</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="M180">
         <x:v>100000</x:v>
@@ -9641,24 +9638,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O180" t="s">
-        <x:v>620</x:v>
+        <x:v>619</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="14.25">
       <x:c r="A181" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B181" t="s">
         <x:v>616</x:v>
       </x:c>
-      <x:c r="B181" t="s">
+      <x:c r="C181" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="C181" t="s">
-        <x:v>618</x:v>
-      </x:c>
       <x:c r="E181" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F181" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G181">
         <x:v>24</x:v>
@@ -9670,13 +9667,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J181" t="s">
-        <x:v>516</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="K181" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="L181" t="s">
         <x:v>621</x:v>
-      </x:c>
-      <x:c r="L181" t="s">
-        <x:v>622</x:v>
       </x:c>
       <x:c r="M181">
         <x:v>200000</x:v>
@@ -9685,24 +9682,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O181" t="s">
-        <x:v>623</x:v>
+        <x:v>622</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="14.25">
       <x:c r="A182" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B182" t="s">
         <x:v>616</x:v>
       </x:c>
-      <x:c r="B182" t="s">
+      <x:c r="C182" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="C182" t="s">
-        <x:v>618</x:v>
-      </x:c>
       <x:c r="E182" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F182" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G182">
         <x:v>24</x:v>
@@ -9714,13 +9711,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J182" t="s">
-        <x:v>539</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="K182" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="L182" t="s">
         <x:v>624</x:v>
-      </x:c>
-      <x:c r="L182" t="s">
-        <x:v>625</x:v>
       </x:c>
       <x:c r="M182">
         <x:v>400000</x:v>
@@ -9729,24 +9726,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O182" t="s">
-        <x:v>626</x:v>
+        <x:v>625</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="14.25">
       <x:c r="A183" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B183" t="s">
         <x:v>616</x:v>
       </x:c>
-      <x:c r="B183" t="s">
+      <x:c r="C183" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="C183" t="s">
-        <x:v>618</x:v>
-      </x:c>
       <x:c r="E183" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F183" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G183">
         <x:v>24</x:v>
@@ -9758,13 +9755,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J183" t="s">
-        <x:v>563</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="K183" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="L183" t="s">
         <x:v>627</x:v>
-      </x:c>
-      <x:c r="L183" t="s">
-        <x:v>628</x:v>
       </x:c>
       <x:c r="M183">
         <x:v>800000</x:v>
@@ -9773,24 +9770,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O183" t="s">
-        <x:v>629</x:v>
+        <x:v>628</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="14.25">
       <x:c r="A184" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B184" t="s">
         <x:v>616</x:v>
       </x:c>
-      <x:c r="B184" t="s">
+      <x:c r="C184" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="C184" t="s">
-        <x:v>618</x:v>
-      </x:c>
       <x:c r="E184" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F184" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G184">
         <x:v>24</x:v>
@@ -9802,13 +9799,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J184" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="K184" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="L184" t="s">
         <x:v>630</x:v>
-      </x:c>
-      <x:c r="L184" t="s">
-        <x:v>631</x:v>
       </x:c>
       <x:c r="M184">
         <x:v>1500000</x:v>
@@ -9817,24 +9814,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O184" t="s">
-        <x:v>632</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="14.25">
       <x:c r="A185" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B185" t="s">
         <x:v>616</x:v>
       </x:c>
-      <x:c r="B185" t="s">
+      <x:c r="C185" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="C185" t="s">
-        <x:v>618</x:v>
-      </x:c>
       <x:c r="E185" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F185" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G185">
         <x:v>24</x:v>
@@ -9846,13 +9843,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="J185" t="s">
-        <x:v>612</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="K185" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="L185" t="s">
         <x:v>633</x:v>
-      </x:c>
-      <x:c r="L185" t="s">
-        <x:v>634</x:v>
       </x:c>
       <x:c r="M185">
         <x:v>3000000</x:v>
@@ -9861,24 +9858,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O185" t="s">
-        <x:v>635</x:v>
+        <x:v>634</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="14.25">
       <x:c r="A186" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B186" t="s">
         <x:v>616</x:v>
       </x:c>
-      <x:c r="B186" t="s">
+      <x:c r="C186" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="C186" t="s">
-        <x:v>618</x:v>
-      </x:c>
       <x:c r="E186" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F186" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G186">
         <x:v>24</x:v>
@@ -9890,13 +9887,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J186" t="s">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="K186" t="s">
         <x:v>636</x:v>
       </x:c>
-      <x:c r="K186" t="s">
+      <x:c r="L186" t="s">
         <x:v>637</x:v>
-      </x:c>
-      <x:c r="L186" t="s">
-        <x:v>638</x:v>
       </x:c>
       <x:c r="M186">
         <x:v>5000000</x:v>
@@ -9905,7 +9902,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="O186" t="s">
-        <x:v>639</x:v>
+        <x:v>638</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9924,12 +9921,12 @@
     </x:row>
     <x:row r="2" ht="14.25">
       <x:c r="A2" t="s">
-        <x:v>640</x:v>
+        <x:v>639</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="14.25">
       <x:c r="A3" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="14.25"/>
@@ -9940,27 +9937,27 @@
     </x:row>
     <x:row r="6" ht="14.25">
       <x:c r="A6" t="s">
-        <x:v>642</x:v>
+        <x:v>641</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="14.25">
       <x:c r="A7" t="s">
-        <x:v>643</x:v>
+        <x:v>642</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="14.25">
       <x:c r="A8" t="s">
-        <x:v>644</x:v>
+        <x:v>643</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="14.25">
       <x:c r="A9" t="s">
-        <x:v>645</x:v>
+        <x:v>644</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="14.25">
       <x:c r="A10" t="s">
-        <x:v>646</x:v>
+        <x:v>645</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="14.25"/>
@@ -9971,17 +9968,17 @@
     </x:row>
     <x:row r="13" ht="14.25">
       <x:c r="A13" t="s">
-        <x:v>647</x:v>
+        <x:v>646</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="14.25">
       <x:c r="A14" t="s">
-        <x:v>648</x:v>
+        <x:v>647</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="14.25">
       <x:c r="A15" t="s">
-        <x:v>649</x:v>
+        <x:v>648</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="14.25"/>
@@ -9992,64 +9989,64 @@
     </x:row>
     <x:row r="18" ht="14.25">
       <x:c r="A18" t="s">
-        <x:v>650</x:v>
+        <x:v>649</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="14.25">
       <x:c r="A19" t="s">
-        <x:v>651</x:v>
+        <x:v>650</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="14.25">
       <x:c r="A20" t="s">
-        <x:v>652</x:v>
+        <x:v>651</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="14.25"/>
     <x:row r="22" ht="14.25">
       <x:c r="A22" t="s">
-        <x:v>653</x:v>
+        <x:v>652</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="14.25">
       <x:c r="A23" t="s">
-        <x:v>654</x:v>
+        <x:v>653</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="14.25">
       <x:c r="A24" t="s">
-        <x:v>655</x:v>
+        <x:v>654</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="14.25">
       <x:c r="A25" t="s">
-        <x:v>656</x:v>
+        <x:v>655</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="14.25"/>
     <x:row r="27" ht="14.25">
       <x:c r="A27" t="s">
-        <x:v>657</x:v>
+        <x:v>656</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="14.25">
       <x:c r="A28" t="s">
-        <x:v>658</x:v>
+        <x:v>657</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="14.25">
       <x:c r="A29" t="s">
-        <x:v>659</x:v>
+        <x:v>658</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="14.25">
       <x:c r="A30" t="s">
-        <x:v>660</x:v>
+        <x:v>659</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="14.25">
       <x:c r="A31" t="s">
-        <x:v>661</x:v>
+        <x:v>660</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="14.25"/>
@@ -10060,67 +10057,67 @@
     </x:row>
     <x:row r="34" ht="14.25">
       <x:c r="A34" t="s">
-        <x:v>662</x:v>
+        <x:v>661</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="14.25">
       <x:c r="A35" t="s">
-        <x:v>663</x:v>
+        <x:v>662</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="14.25">
       <x:c r="A36" t="s">
-        <x:v>664</x:v>
+        <x:v>663</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="14.25">
       <x:c r="A37" t="s">
-        <x:v>665</x:v>
+        <x:v>664</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="14.25">
       <x:c r="A38" t="s">
-        <x:v>666</x:v>
+        <x:v>665</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="14.25">
       <x:c r="A39" t="s">
-        <x:v>667</x:v>
+        <x:v>666</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="14.25">
       <x:c r="A40" t="s">
-        <x:v>668</x:v>
+        <x:v>667</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="14.25">
       <x:c r="A41" t="s">
-        <x:v>669</x:v>
+        <x:v>668</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="14.25">
       <x:c r="A42" t="s">
-        <x:v>670</x:v>
+        <x:v>669</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="14.25">
       <x:c r="A43" t="s">
-        <x:v>671</x:v>
+        <x:v>670</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="14.25">
       <x:c r="A44" t="s">
-        <x:v>672</x:v>
+        <x:v>671</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="14.25">
       <x:c r="A45" t="s">
-        <x:v>673</x:v>
+        <x:v>672</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="14.25">
       <x:c r="A46" t="s">
-        <x:v>674</x:v>
+        <x:v>673</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="14.25"/>
@@ -10131,28 +10128,28 @@
     </x:row>
     <x:row r="49" ht="14.25">
       <x:c r="A49" t="s">
-        <x:v>675</x:v>
+        <x:v>674</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="14.25">
       <x:c r="A50" t="s">
-        <x:v>676</x:v>
+        <x:v>675</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="14.25">
       <x:c r="A51" t="s">
-        <x:v>677</x:v>
+        <x:v>676</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="14.25"/>
     <x:row r="53" ht="14.25">
       <x:c r="A53" t="s">
-        <x:v>678</x:v>
+        <x:v>677</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="14.25">
       <x:c r="A54" t="s">
-        <x:v>679</x:v>
+        <x:v>678</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="14.25"/>
@@ -10163,7 +10160,7 @@
     </x:row>
     <x:row r="57" ht="14.25">
       <x:c r="A57" t="s">
-        <x:v>680</x:v>
+        <x:v>679</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5550,186 +5550,117 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">岩甲術</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🪨</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">earth</t>
-        </is>
-      </c>
-      <c r="G109">
-        <v>15</v>
+          <t xml:space="preserve">firehunt</t>
+        </is>
       </c>
       <c r="H109">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I109">
-        <v>1</v>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|150</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲術</t>
+          <t xml:space="preserve">烈陽星環</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"sec":10,"castM":30}</t>
+          <t xml:space="preserve">{"count":1,"grow":60,"growSec":4,"spin":30,"pct":50,"pctPer":10}</t>
         </is>
       </c>
       <c r="M109">
-        <v>100000</v>
+        <v>10000000</v>
       </c>
       <c r="N109">
         <v>1.5</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放岩甲強化自身，獲得最大生命值 {pct}% 的岩甲護盾，持續 {sec} 秒</t>
+          <t xml:space="preserve">火狩數量 +{count} 團，體積在 {growSec} 秒內逐漸增大最多 {grow}%，環繞速度 +{spin}%，且造成傷害 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solarRing</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">岩甲術</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🪨</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">earth</t>
-        </is>
-      </c>
-      <c r="G110">
-        <v>15</v>
+          <t xml:space="preserve">firehunt</t>
+        </is>
       </c>
       <c r="H110">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I110">
-        <v>2</v>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|200</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化岩甲</t>
+          <t xml:space="preserve">無限星環</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"count":10,"countPer":1,"m":20}</t>
         </is>
       </c>
       <c r="M110">
-        <v>200000</v>
+        <v>10000000</v>
       </c>
       <c r="N110">
         <v>1.5</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化岩甲，額外獲得最大生命值 {pct}% 的岩甲護盾（與第 1 階累加）</t>
+          <t xml:space="preserve">火狩改為從自身中心呈螺旋狀向外擴散（在 {m} 米處達到最外圈），並於持續時間內不斷放出火狩，最多額外 +{count} 團</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">infiniteRing</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">rockarmor</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">岩甲術</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🪨</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">earth</t>
-        </is>
-      </c>
-      <c r="G111">
-        <v>15</v>
+          <t xml:space="preserve">firehunt</t>
+        </is>
       </c>
       <c r="H111">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I111">
-        <v>3</v>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|250</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲尖刺</t>
+          <t xml:space="preserve">火神降臨</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":5,"pctPer":0.5}</t>
+          <t xml:space="preserve">{"m":6,"gap":0.5,"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3}</t>
         </is>
       </c>
       <c r="M111">
-        <v>400000</v>
+        <v>10000000</v>
       </c>
       <c r="N111">
         <v>1.5</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，攻擊你的敵人會遭受你最大生命值 {pct}% 的地系傷害（獨立於反震，兩者各自結算）</t>
+          <t xml:space="preserve">你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標發射 {orbs} 顆火狩星環</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fireGodDescend</t>
         </is>
       </c>
     </row>
@@ -5766,32 +5697,32 @@
         <v>40</v>
       </c>
       <c r="I112">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|300</t>
+          <t xml:space="preserve">0|150</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">護盾增幅</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"sec":10,"castM":30}</t>
         </is>
       </c>
       <c r="M112">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="N112">
         <v>1.5</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t xml:space="preserve">主動型被動（裝配到技能列即恆時生效）：你獲得的所有護盾效率額外 +{pct}%（乘算）</t>
+          <t xml:space="preserve">施放岩甲強化自身，獲得最大生命值 {pct}% 的岩甲護盾，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -5828,32 +5759,32 @@
         <v>40</v>
       </c>
       <c r="I113">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|350</t>
+          <t xml:space="preserve">0|200</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩之再生</t>
+          <t xml:space="preserve">強化岩甲</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":1,"pctPer":0.1}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M113">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="N113">
         <v>1.5</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 生命值即獲得最大生命 {pct}% 的護盾</t>
+          <t xml:space="preserve">進一步強化岩甲，額外獲得最大生命值 {pct}% 的岩甲護盾（與第 1 階累加）</t>
         </is>
       </c>
     </row>
@@ -5890,32 +5821,32 @@
         <v>40</v>
       </c>
       <c r="I114">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|400</t>
+          <t xml:space="preserve">0|250</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲增幅</t>
+          <t xml:space="preserve">岩甲尖刺</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":0.5,"pctPer":0.05,"max":30,"sec":3}</t>
+          <t xml:space="preserve">{"pct":5,"pctPer":0.5}</t>
         </is>
       </c>
       <c r="M114">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="N114">
         <v>1.5</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 護盾即獲得 {pct}% 傷害增幅（乘算），最多疊 {max} 層，持續 {sec} 秒</t>
+          <t xml:space="preserve">岩甲護盾存在期間，攻擊你的敵人會遭受你最大生命值 {pct}% 的地系傷害（獨立於反震，兩者各自結算）</t>
         </is>
       </c>
     </row>
@@ -5952,54 +5883,49 @@
         <v>40</v>
       </c>
       <c r="I115">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|450</t>
+          <t xml:space="preserve">0|300</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">天地逆返</t>
+          <t xml:space="preserve">護盾增幅</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M115">
-        <v>5000000</v>
+        <v>800000</v>
       </c>
       <c r="N115">
         <v>1.5</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t xml:space="preserve">岩甲護盾存在期間，護盾剩餘量越低則傷害減免越高，護盾歸零時最高額外 +{pct}% 傷害減免（乘算）</t>
+          <t xml:space="preserve">主動型被動（裝配到技能列即恆時生效）：你獲得的所有護盾效率額外 +{pct}%（乘算）</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6019,54 +5945,49 @@
         <v>40</v>
       </c>
       <c r="I116">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|200</t>
+          <t xml:space="preserve">0|350</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩之再生</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.4,"castM":20,"move":30,"aspd":50}</t>
+          <t xml:space="preserve">{"pct":1,"pctPer":0.1}</t>
         </is>
       </c>
       <c r="M116">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="N116">
         <v>1.5</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve">在敵人腳下召喚一片 12×12 米的沼澤（射程 {castM} 米），沼澤中的敵人陷入緩速（移動速度 -{move}%、攻速 -{aspd}%），持續 {sec} 秒</t>
+          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 生命值即獲得最大生命 {pct}% 的護盾</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6086,54 +6007,49 @@
         <v>40</v>
       </c>
       <c r="I117">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|250</t>
+          <t xml:space="preserve">0|400</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛弱</t>
+          <t xml:space="preserve">岩甲增幅</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"pct":0.5,"pctPer":0.05,"max":30,"sec":3}</t>
         </is>
       </c>
       <c r="M117">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="N117">
         <v>1.5</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t xml:space="preserve">受泥沼緩速影響的敵人，受到的傷害提高 {pct}%</t>
+          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 護盾即獲得 {pct}% 傷害增幅（乘算），最多疊 {max} 層，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
+          <t xml:space="preserve">rockarmor</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">泥沼術</t>
+          <t xml:space="preserve">岩甲術</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
+          <t xml:space="preserve">🪨</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6153,233 +6069,149 @@
         <v>40</v>
       </c>
       <c r="I118">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|300</t>
+          <t xml:space="preserve">0|450</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒沼術</t>
+          <t xml:space="preserve">天地逆返</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dotPct":25,"dotPctPer":2.5,"dotGap":0.5}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M118">
-        <v>400000</v>
+        <v>5000000</v>
       </c>
       <c r="N118">
         <v>1.5</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤持續放出毒氣：沼澤中的敵人每 {dotGap} 秒受到魔法攻擊 {dotPct}% 的毒性傷害</t>
+          <t xml:space="preserve">岩甲護盾存在期間，護盾剩餘量越低則傷害減免越高，護盾歸零時最高額外 +{pct}% 傷害減免（乘算）</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">泥沼術</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">earth</t>
-        </is>
-      </c>
-      <c r="G119">
-        <v>15</v>
+          <t xml:space="preserve">rockarmor</t>
+        </is>
       </c>
       <c r="H119">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I119">
-        <v>4</v>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|350</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">毒沼增生</t>
+          <t xml:space="preserve">超重岩之術</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":40}</t>
+          <t xml:space="preserve">{"m":24,"sec":4,"pct":400,"pctPer":40}</t>
         </is>
       </c>
       <c r="M119">
-        <v>800000</v>
+        <v>10000000</v>
       </c>
       <c r="N119">
         <v>1.5</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤結束時傳染給 {m} 米內較近的敵人，最多傳染 {add} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">施放時將巨岩之力壓縮到極致，使 {m} 米內的敵人石化 {sec} 秒：無法行動，且受到的土系傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">superRockArt</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">泥沼術</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">earth</t>
-        </is>
-      </c>
-      <c r="G120">
-        <v>15</v>
+          <t xml:space="preserve">rockarmor</t>
+        </is>
       </c>
       <c r="H120">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I120">
-        <v>5</v>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|400</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤漫延</t>
+          <t xml:space="preserve">金剛不壞</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":6,"pct":40,"pctPer":4,"growSec":4}</t>
+          <t xml:space="preserve">{"red":90,"redPer":0.9,"hp":50,"hpPer":5,"spike":100}</t>
         </is>
       </c>
       <c r="M120">
-        <v>1500000</v>
+        <v>10000000</v>
       </c>
       <c r="N120">
         <v>1.5</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤持續時間提高至 {sec} 秒，且在 {growSec} 秒內逐步擴大，最大擴增 {pct}%</t>
+          <t xml:space="preserve">岩甲護盾存在期間額外獲得 +{red}% 傷害減免（乘算），生命上限與岩甲護盾 +{hp}%，且【岩甲尖刺】的效果額外提高 {spike}%</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">adamantBody</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">mire</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">泥沼術</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🟤</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12*12</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">earth</t>
-        </is>
-      </c>
-      <c r="G121">
-        <v>15</v>
+          <t xml:space="preserve">rockarmor</t>
+        </is>
       </c>
       <c r="H121">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I121">
-        <v>6</v>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|450</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">重力泥沼</t>
+          <t xml:space="preserve">超重力場</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"move":50,"aspd":75,"pct":20,"pctPer":2}</t>
+          <t xml:space="preserve">{"m":24,"pct":300,"pctPer":30,"stiff":65,"stiffSec":5}</t>
         </is>
       </c>
       <c r="M121">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="N121">
         <v>1.5</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t xml:space="preserve">緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%（與第 2 階累加）</t>
+          <t xml:space="preserve">施放岩甲術時同時扭曲 {m} 米內的重力場，使敵人僵化（移動、攻速與傷害 -{stiff}%，持續 {stiffSec} 秒）；岩甲護盾存在期間你的土系傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gravityField</t>
         </is>
       </c>
     </row>
@@ -6421,49 +6253,54 @@
         <v>40</v>
       </c>
       <c r="I122">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|500</t>
+          <t xml:space="preserve">0|200</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">熔岩沼</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":8,"pct":20,"pctPer":2,"dotPct":70,"dotPctPer":7,"dotGap":0.4}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.4,"castM":20,"move":30,"aspd":50}</t>
         </is>
       </c>
       <c r="M122">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N122">
         <v>1.5</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t xml:space="preserve">沼澤轉變為岩漿：持續時間提高至 {sec} 秒、範圍再擴增 {pct}%（與第 5 階累加），其中的目標每 {dotGap} 秒額外受到魔法攻擊 {dotPct}% 的火焰傷害</t>
+          <t xml:space="preserve">在敵人腳下召喚一片 12×12 米的沼澤（射程 {castM} 米），沼澤中的敵人陷入緩速（移動速度 -{move}%、攻速 -{aspd}%），持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6480,10 +6317,10 @@
         <v>15</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6492,40 +6329,45 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">虛弱</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":10,"pctPer":1,"hp":20,"hpPer":2}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M123">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N123">
         <v>1.5</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t xml:space="preserve">主動型被動：自身傷害減免額外 +{pct}%、生命上限額外 +{hp}%（皆為乘算）</t>
+          <t xml:space="preserve">受泥沼緩速影響的敵人，受到的傷害提高 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6542,10 +6384,10 @@
         <v>15</v>
       </c>
       <c r="H124">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6554,40 +6396,45 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地祝福</t>
+          <t xml:space="preserve">毒沼術</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
+          <t xml:space="preserve">{"dotPct":25,"dotPctPer":2.5,"dotGap":0.5}</t>
         </is>
       </c>
       <c r="M124">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N124">
         <v>1.5</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t xml:space="preserve">全屬性傷害額外 +{pct}%（與所有屬性增傷效果為額外的乘法計算）</t>
+          <t xml:space="preserve">沼澤持續放出毒氣：沼澤中的敵人每 {dotGap} 秒受到魔法攻擊 {dotPct}% 的毒性傷害</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6604,10 +6451,10 @@
         <v>15</v>
       </c>
       <c r="H125">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I125">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6616,40 +6463,45 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命再生</t>
+          <t xml:space="preserve">毒沼增生</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":40}</t>
         </is>
       </c>
       <c r="M125">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N125">
         <v>1.5</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命回復額外 +{pct}%、吸血額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
+          <t xml:space="preserve">沼澤結束時傳染給 {m} 米內較近的敵人，最多傳染 {add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6666,10 +6518,10 @@
         <v>15</v>
       </c>
       <c r="H126">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I126">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6678,40 +6530,45 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔力再生</t>
+          <t xml:space="preserve">沼澤漫延</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
+          <t xml:space="preserve">{"sec":6,"pct":40,"pctPer":4,"growSec":4}</t>
         </is>
       </c>
       <c r="M126">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N126">
         <v>1.5</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t xml:space="preserve">法力回復額外 +{pct}%、吸魔額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
+          <t xml:space="preserve">沼澤持續時間提高至 {sec} 秒，且在 {growSec} 秒內逐步擴大，最大擴增 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6728,10 +6585,10 @@
         <v>15</v>
       </c>
       <c r="H127">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I127">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6740,40 +6597,45 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">魔法盾</t>
+          <t xml:space="preserve">重力泥沼</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+          <t xml:space="preserve">{"move":50,"aspd":75,"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M127">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N127">
         <v>1.5</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t xml:space="preserve">你的生命減少時，其中 {pct}% 改由消耗法力承擔（法力不足時只轉換付得起的部分，餘額仍扣生命）</t>
+          <t xml:space="preserve">緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%（與第 2 階累加）</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">earthguard</t>
+          <t xml:space="preserve">mire</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">大地守護</t>
+          <t xml:space="preserve">泥沼術</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌍</t>
+          <t xml:space="preserve">🟤</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12*12</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6790,10 +6652,10 @@
         <v>15</v>
       </c>
       <c r="H128">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I128">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -6802,23 +6664,23 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命反射之盾</t>
+          <t xml:space="preserve">熔岩沼</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":1,"pctPer":0.1,"m":20,"count":1}</t>
+          <t xml:space="preserve">{"sec":8,"pct":20,"pctPer":2,"dotPct":70,"dotPctPer":7,"dotGap":0.4}</t>
         </is>
       </c>
       <c r="M128">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N128">
         <v>1.5</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t xml:space="preserve">你每消耗 1% 生命或護盾，{m} 米內的 {count} 個敵人同步損失 {pct}% 最大生命</t>
+          <t xml:space="preserve">沼澤轉變為岩漿：持續時間提高至 {sec} 秒、範圍再擴增 {pct}%（與第 5 階累加），其中的目標每 {dotGap} 秒額外受到魔法攻擊 {dotPct}% 的火焰傷害</t>
         </is>
       </c>
     </row>
@@ -6852,52 +6714,52 @@
         <v>15</v>
       </c>
       <c r="H129">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I129">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|550</t>
+          <t xml:space="preserve">0|250</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">天地共生</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":8,"sec":5,"cd":60,"cdPer":-3}</t>
+          <t xml:space="preserve">{"pct":10,"pctPer":1,"hp":20,"hpPer":2}</t>
         </is>
       </c>
       <c r="M129">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N129">
         <v>1.5</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t xml:space="preserve">死亡時原地復活並回復 {pct}% 生命，復活後 {sec} 秒無敵；此招自身冷卻 {cd} 秒（顯示於技能格）</t>
+          <t xml:space="preserve">主動型被動：自身傷害減免額外 +{pct}%、生命上限額外 +{hp}%（皆為乘算）</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6907,17 +6769,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G130">
         <v>15</v>
       </c>
       <c r="H130">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6926,40 +6788,40 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地祝福</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":4,"m":30,"castM":30}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5}</t>
         </is>
       </c>
       <c r="M130">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N130">
         <v>1.5</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t xml:space="preserve">丟出一道閃電鏈（射程 {castM} 米），在最多 {count} 個目標間彈射（每段彈射範圍 {m} 米），每擊造成 {pct}% 雷電傷害</t>
+          <t xml:space="preserve">全屬性傷害額外 +{pct}%（與所有屬性增傷效果為額外的乘法計算）</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6969,17 +6831,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G131">
         <v>15</v>
       </c>
       <c r="H131">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6988,40 +6850,40 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化閃電</t>
+          <t xml:space="preserve">生命再生</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
         </is>
       </c>
       <c r="M131">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N131">
         <v>1.5</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化閃電威力，閃電鏈傷害進一步 +{pct}% 雷電傷害</t>
+          <t xml:space="preserve">生命回復額外 +{pct}%、吸血額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7031,17 +6893,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G132">
         <v>15</v>
       </c>
       <c r="H132">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I132">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -7050,40 +6912,40 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷鳴術</t>
+          <t xml:space="preserve">魔力再生</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"drain":50,"drainPer":5}</t>
         </is>
       </c>
       <c r="M132">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N132">
         <v>1.5</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t xml:space="preserve">被閃電鏈擊中的敵人額外再受到 {add} 次雷電傷害（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">法力回復額外 +{pct}%、吸魔額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7093,17 +6955,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G133">
         <v>15</v>
       </c>
       <c r="H133">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -7112,40 +6974,40 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化連鎖</t>
+          <t xml:space="preserve">魔法盾</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M133">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N133">
         <v>1.5</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電鏈的彈射數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">你的生命減少時，其中 {pct}% 改由消耗法力承擔（法力不足時只轉換付得起的部分，餘額仍扣生命）</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7155,17 +7017,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G134">
         <v>15</v>
       </c>
       <c r="H134">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I134">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -7174,40 +7036,40 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">電殛擴散</t>
+          <t xml:space="preserve">生命反射之盾</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":2.5,"count":1,"m":6}</t>
+          <t xml:space="preserve">{"pct":1,"pctPer":0.1,"m":20,"count":1}</t>
         </is>
       </c>
       <c r="M134">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N134">
         <v>1.5</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電鏈每次彈射時，額外對 {m} 米內的 {count} 個敵人造成閃電鏈 {pct}% 的雷電傷害</t>
+          <t xml:space="preserve">你每消耗 1% 生命或護盾，{m} 米內的 {count} 個敵人同步損失 {pct}% 最大生命</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">chainlightning</t>
+          <t xml:space="preserve">earthguard</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">連鎖閃電</t>
+          <t xml:space="preserve">大地守護</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚡</t>
+          <t xml:space="preserve">🌍</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7217,17 +7079,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">lightning</t>
+          <t xml:space="preserve">earth</t>
         </is>
       </c>
       <c r="G135">
         <v>15</v>
       </c>
       <c r="H135">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I135">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -7236,23 +7098,23 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷幻身</t>
+          <t xml:space="preserve">天地共生</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":8,"sec":5,"cd":60,"cdPer":-3}</t>
         </is>
       </c>
       <c r="M135">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N135">
         <v>1.5</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電鏈傷害額外 +{pct}% 雷電傷害；沒有其它彈射目標時可用自身當中繼點繼續彈射（彈到自身不消耗彈射數）</t>
+          <t xml:space="preserve">死亡時原地復活並回復 {pct}% 生命，復活後 {sec} 秒無敵；此招自身冷卻 {cd} 秒（顯示於技能格）</t>
         </is>
       </c>
     </row>
@@ -7289,49 +7151,49 @@
         <v>40</v>
       </c>
       <c r="I136">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|600</t>
+          <t xml:space="preserve">0|300</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電暴風</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":3,"add":1,"addPer":0.1,"pct":100,"pctPer":10,"chance":20}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":4,"m":30,"castM":30}</t>
         </is>
       </c>
       <c r="M136">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N136">
         <v>1.5</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t xml:space="preserve">同時發射 {count} 道閃電鏈，彈射數額外 +{add} 次，且閃電傷害額外 +{pct}%；每次彈射有 {chance}% 機率生成 1 條閃電鏈</t>
+          <t xml:space="preserve">丟出一道閃電鏈（射程 {castM} 米），在最多 {count} 個目標間彈射（每段彈射範圍 {m} 米），每擊造成 {pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7351,7 +7213,7 @@
         <v>40</v>
       </c>
       <c r="I137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -7360,40 +7222,40 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">強化閃電</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"count":2,"gap":0.2,"castM":30}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M137">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N137">
         <v>1.5</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t xml:space="preserve">對 {castM} 米內的 {count} 個目標降下落雷（每道間隔 {gap} 秒），每道造成 {pct}% 雷電傷害</t>
+          <t xml:space="preserve">強化閃電威力，閃電鏈傷害進一步 +{pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7413,7 +7275,7 @@
         <v>40</v>
       </c>
       <c r="I138">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -7422,7 +7284,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷連鎖</t>
+          <t xml:space="preserve">雷鳴術</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -7431,31 +7293,31 @@
         </is>
       </c>
       <c r="M138">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N138">
         <v>1.5</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊目標額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">被閃電鏈擊中的敵人額外再受到 {add} 次雷電傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7475,7 +7337,7 @@
         <v>40</v>
       </c>
       <c r="I139">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -7484,40 +7346,40 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重落雷</t>
+          <t xml:space="preserve">強化連鎖</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
         </is>
       </c>
       <c r="M139">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N139">
         <v>1.5</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t xml:space="preserve">對每個目標的攻擊次數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">閃電鏈的彈射數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7537,7 +7399,7 @@
         <v>40</v>
       </c>
       <c r="I140">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7546,40 +7408,40 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">閃電增幅</t>
+          <t xml:space="preserve">電殛擴散</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5,"count":1,"m":6}</t>
         </is>
       </c>
       <c r="M140">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N140">
         <v>1.5</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化落雷傷害，額外 +{pct}% 雷電傷害</t>
+          <t xml:space="preserve">閃電鏈每次彈射時，額外對 {m} 米內的 {count} 個敵人造成閃電鏈 {pct}% 的雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7599,7 +7461,7 @@
         <v>40</v>
       </c>
       <c r="I141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7608,40 +7470,40 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷電脈衝</t>
+          <t xml:space="preserve">雷幻身</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":1.5,"secPer":0.15,"count":2,"m":6}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M141">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N141">
         <v>1.5</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷落地時產生衝擊波，震暈目標本身與 {m} 米內共 {count} 個敵人 {sec} 秒</t>
+          <t xml:space="preserve">閃電鏈傷害額外 +{pct}% 雷電傷害；沒有其它彈射目標時可用自身當中繼點繼續彈射（彈到自身不消耗彈射數）</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderstrike</t>
+          <t xml:space="preserve">chainlightning</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷術</t>
+          <t xml:space="preserve">連鎖閃電</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌩️</t>
+          <t xml:space="preserve">⚡</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7661,7 +7523,7 @@
         <v>40</v>
       </c>
       <c r="I142">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -7670,23 +7532,23 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">迅雷重生</t>
+          <t xml:space="preserve">雷電暴風</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":20,"chancePer":2,"max":5}</t>
+          <t xml:space="preserve">{"count":3,"add":1,"addPer":0.1,"pct":100,"pctPer":10,"chance":20}</t>
         </is>
       </c>
       <c r="M142">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N142">
         <v>1.5</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t xml:space="preserve">每道落雷結束後有 {chance}% 機率再產生 1 道落雷（同一次施放最多再生 {max} 道）</t>
+          <t xml:space="preserve">同時發射 {count} 道閃電鏈，彈射數額外 +{add} 次，且閃電傷害額外 +{pct}%；每次彈射有 {chance}% 機率生成 1 條閃電鏈</t>
         </is>
       </c>
     </row>
@@ -7723,54 +7585,49 @@
         <v>40</v>
       </c>
       <c r="I143">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|650</t>
+          <t xml:space="preserve">0|350</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">殛道落電</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"mult":2,"pct":50,"pctPer":5,"m":6}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"count":2,"gap":0.2,"castM":30}</t>
         </is>
       </c>
       <c r="M143">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N143">
         <v>1.5</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t xml:space="preserve">落雷擊中時對目標 {m} 米內的所有敵人造成傷害；攻擊次數與目標數量 ×{mult}，且命中暈眩中的敵人時傷害額外 +{pct}%（與原傷害乘算）</t>
+          <t xml:space="preserve">對 {castM} 米內的 {count} 個目標降下落雷（每道間隔 {gap} 秒），每道造成 {pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7790,7 +7647,7 @@
         <v>40</v>
       </c>
       <c r="I144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -7799,45 +7656,40 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷連鎖</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"gap":0.35,"sec":2,"m":3,"speed":6,"castM":30}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M144">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N144">
         <v>1.5</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t xml:space="preserve">召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
+          <t xml:space="preserve">攻擊目標額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7857,7 +7709,7 @@
         <v>40</v>
       </c>
       <c r="I145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7866,45 +7718,40 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">擴增雷球</t>
+          <t xml:space="preserve">雙重落雷</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M145">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N145">
         <v>1.5</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球的體積擴大 {pct}%</t>
+          <t xml:space="preserve">對每個目標的攻擊次數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7924,7 +7771,7 @@
         <v>40</v>
       </c>
       <c r="I146">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7933,45 +7780,40 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">多重雷球</t>
+          <t xml:space="preserve">閃電增幅</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M146">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N146">
         <v>1.5</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球數量額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">進一步強化落雷傷害，額外 +{pct}% 雷電傷害</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7991,7 +7833,7 @@
         <v>40</v>
       </c>
       <c r="I147">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -8000,45 +7842,40 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">環體電球</t>
+          <t xml:space="preserve">雷電脈衝</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":100,"pctPer":10,"sec":6,"m":8,"rps":0.7}</t>
+          <t xml:space="preserve">{"sec":1.5,"secPer":0.15,"count":2,"m":6}</t>
         </is>
       </c>
       <c r="M147">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N147">
         <v>1.5</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 {count} 個電球環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">落雷落地時產生衝擊波，震暈目標本身與 {m} 米內共 {count} 個敵人 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8058,7 +7895,7 @@
         <v>40</v>
       </c>
       <c r="I148">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -8067,45 +7904,40 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化雷球</t>
+          <t xml:space="preserve">迅雷重生</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"max":5}</t>
         </is>
       </c>
       <c r="M148">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N148">
         <v>1.5</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有雷球與電球的雷電傷害額外 +{pct}%</t>
+          <t xml:space="preserve">每道落雷結束後有 {chance}% 機率再產生 1 道落雷（同一次施放最多再生 {max} 道）</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">thunderorb</t>
+          <t xml:space="preserve">thunderstrike</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷球</t>
+          <t xml:space="preserve">落雷術</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔵</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6*6</t>
+          <t xml:space="preserve">🌩️</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8125,7 +7957,7 @@
         <v>40</v>
       </c>
       <c r="I149">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -8134,23 +7966,23 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">伴生雷球</t>
+          <t xml:space="preserve">殛道落電</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"sec":2}</t>
+          <t xml:space="preserve">{"mult":2,"pct":50,"pctPer":5,"m":6}</t>
         </is>
       </c>
       <c r="M149">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N149">
         <v>1.5</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t xml:space="preserve">環體電球命中時有 {chance}% 機率在該處生成一個靜止雷球，持續 {sec} 秒（每次作用只判定一次機率）</t>
+          <t xml:space="preserve">落雷擊中時對目標 {m} 米內的所有敵人造成傷害；攻擊次數與目標數量 ×{mult}，且命中暈眩中的敵人時傷害額外 +{pct}%（與原傷害乘算）</t>
         </is>
       </c>
     </row>
@@ -8192,49 +8024,54 @@
         <v>40</v>
       </c>
       <c r="I150">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|700</t>
+          <t xml:space="preserve">0|400</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷殞天落</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":300,"pctPer":30,"m":15,"sec":3}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"gap":0.35,"sec":2,"m":3,"speed":6,"castM":30}</t>
         </is>
       </c>
       <c r="M150">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N150">
         <v>1.5</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 {count} 個巨大雷球從天而降，各對 {m} 米內的敵人造成 {pct}% 雷電傷害，並以衝擊波擊暈 {sec} 秒</t>
+          <t xml:space="preserve">召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8244,7 +8081,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G151">
@@ -8254,7 +8091,7 @@
         <v>40</v>
       </c>
       <c r="I151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -8263,40 +8100,45 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">擴增雷球</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"deg":15,"castM":30,"speed":45}</t>
+          <t xml:space="preserve">{"pct":15,"pctPer":1.5}</t>
         </is>
       </c>
       <c r="M151">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N151">
         <v>1.5</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">雷球的體積擴大 {pct}%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8306,7 +8148,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G152">
@@ -8316,7 +8158,7 @@
         <v>40</v>
       </c>
       <c r="I152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -8325,40 +8167,45 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜箭</t>
+          <t xml:space="preserve">多重雷球</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"frostPct":50,"frostPctPer":5,"stacks":1}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M152">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N152">
         <v>1.5</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
+          <t xml:space="preserve">雷球數量額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8368,7 +8215,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G153">
@@ -8378,7 +8225,7 @@
         <v>40</v>
       </c>
       <c r="I153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -8387,40 +8234,45 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰系強化</t>
+          <t xml:space="preserve">環體電球</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"count":2,"pct":100,"pctPer":10,"sec":6,"m":8,"rps":0.7}</t>
         </is>
       </c>
       <c r="M153">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N153">
         <v>1.5</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
+          <t xml:space="preserve">額外召喚 {count} 個電球環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8430,7 +8282,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G154">
@@ -8440,7 +8292,7 @@
         <v>40</v>
       </c>
       <c r="I154">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -8449,40 +8301,45 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">貫穿冰箭</t>
+          <t xml:space="preserve">強化雷球</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":10,"mPer":2}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M154">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N154">
         <v>1.5</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
+          <t xml:space="preserve">所有雷球與電球的雷電傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8492,7 +8349,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G155">
@@ -8502,7 +8359,7 @@
         <v>40</v>
       </c>
       <c r="I155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8511,40 +8368,45 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰箭散射</t>
+          <t xml:space="preserve">伴生雷球</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"sec":2}</t>
         </is>
       </c>
       <c r="M155">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N155">
         <v>1.5</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
+          <t xml:space="preserve">環體電球命中時有 {chance}% 機率在該處生成一個靜止雷球，持續 {sec} 秒（每次作用只判定一次機率）</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
+          <t xml:space="preserve">thunderorb</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">雷球</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">❄️</t>
+          <t xml:space="preserve">🔵</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6*6</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8554,7 +8416,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">ice</t>
+          <t xml:space="preserve">lightning</t>
         </is>
       </c>
       <c r="G156">
@@ -8564,7 +8426,7 @@
         <v>40</v>
       </c>
       <c r="I156">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -8573,23 +8435,23 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜凍結</t>
+          <t xml:space="preserve">雷殞天落</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":1,"stacksPer":0.4}</t>
+          <t xml:space="preserve">{"count":2,"pct":300,"pctPer":30,"m":15,"sec":3}</t>
         </is>
       </c>
       <c r="M156">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N156">
         <v>1.5</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
+          <t xml:space="preserve">額外召喚 {count} 個巨大雷球從天而降，各對 {m} 米內的敵人造成 {pct}% 雷電傷害，並以衝擊波擊暈 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -8626,49 +8488,49 @@
         <v>40</v>
       </c>
       <c r="I157">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|750</t>
+          <t xml:space="preserve">0|450</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰爆裂箭</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"m":6,"chaseM":30,"bodyM":1.5,"gap":0.1,"waves":3,"waveGap":0.3}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"deg":15,"castM":30,"speed":45}</t>
         </is>
       </c>
       <c r="M157">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N157">
         <v>1.5</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8688,7 +8550,7 @@
         <v>40</v>
       </c>
       <c r="I158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -8697,40 +8559,40 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒霜箭</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"arcM":8}</t>
+          <t xml:space="preserve">{"frostPct":50,"frostPctPer":5,"stacks":1}</t>
         </is>
       </c>
       <c r="M158">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N158">
         <v>1.5</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -8750,7 +8612,7 @@
         <v>40</v>
       </c>
       <c r="I159">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -8759,40 +8621,40 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰逆轉</t>
+          <t xml:space="preserve">冰系強化</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M159">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N159">
         <v>1.5</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
+          <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8812,7 +8674,7 @@
         <v>40</v>
       </c>
       <c r="I160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -8821,40 +8683,40 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒流彈</t>
+          <t xml:space="preserve">貫穿冰箭</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"frostPct":50,"frostPctPer":20,"stacks":1}</t>
+          <t xml:space="preserve">{"m":10,"mPer":2}</t>
         </is>
       </c>
       <c r="M160">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N160">
         <v>1.5</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
+          <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8874,7 +8736,7 @@
         <v>40</v>
       </c>
       <c r="I161">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -8883,40 +8745,40 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒流爆散</t>
+          <t xml:space="preserve">冰箭散射</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":8,"bounce":2,"bouncePer":0.2}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M161">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N161">
         <v>1.5</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8936,7 +8798,7 @@
         <v>40</v>
       </c>
       <c r="I162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -8945,40 +8807,40 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜擴散</t>
+          <t xml:space="preserve">寒霜凍結</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":10,"count":1}</t>
+          <t xml:space="preserve">{"stacks":1,"stacksPer":0.4}</t>
         </is>
       </c>
       <c r="M162">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N162">
         <v>1.5</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
+          <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8998,7 +8860,7 @@
         <v>40</v>
       </c>
       <c r="I163">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -9007,23 +8869,23 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重流水</t>
+          <t xml:space="preserve">寒冰爆裂箭</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"m":6,"chaseM":30,"bodyM":1.5,"gap":0.1,"waves":3,"waveGap":0.3}</t>
         </is>
       </c>
       <c r="M163">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N163">
         <v>1.5</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
+          <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
@@ -9060,49 +8922,49 @@
         <v>40</v>
       </c>
       <c r="I164">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|800</t>
+          <t xml:space="preserve">0|500</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">水龍捲</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"m":5,"side":10,"frozen":2,"gap":0.35}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"arcM":8}</t>
         </is>
       </c>
       <c r="M164">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N164">
         <v>1.5</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
+          <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9122,7 +8984,7 @@
         <v>40</v>
       </c>
       <c r="I165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -9131,40 +8993,40 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">寒冰逆轉</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":6}</t>
         </is>
       </c>
       <c r="M165">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N165">
         <v>1.5</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
+          <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9184,7 +9046,7 @@
         <v>40</v>
       </c>
       <c r="I166">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -9193,40 +9055,40 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜衝擊</t>
+          <t xml:space="preserve">寒流彈</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"frostPct":50,"frostPctPer":20,"stacks":1}</t>
         </is>
       </c>
       <c r="M166">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N166">
         <v>1.5</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
+          <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9246,7 +9108,7 @@
         <v>40</v>
       </c>
       <c r="I167">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -9255,40 +9117,40 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰體</t>
+          <t xml:space="preserve">寒流爆散</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":1}</t>
+          <t xml:space="preserve">{"m":8,"bounce":2,"bouncePer":0.2}</t>
         </is>
       </c>
       <c r="M167">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N167">
         <v>1.5</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
+          <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9308,7 +9170,7 @@
         <v>40</v>
       </c>
       <c r="I168">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -9317,40 +9179,40 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">極致寒霜</t>
+          <t xml:space="preserve">寒霜擴散</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
+          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":10,"count":1}</t>
         </is>
       </c>
       <c r="M168">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N168">
         <v>1.5</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
+          <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9370,7 +9232,7 @@
         <v>40</v>
       </c>
       <c r="I169">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -9379,40 +9241,40 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重新星</t>
+          <t xml:space="preserve">三重流水</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
         </is>
       </c>
       <c r="M169">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N169">
         <v>1.5</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9432,7 +9294,7 @@
         <v>40</v>
       </c>
       <c r="I170">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -9441,23 +9303,23 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">死亡新星</t>
+          <t xml:space="preserve">水龍捲</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
+          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"m":5,"side":10,"frozen":2,"gap":0.35}</t>
         </is>
       </c>
       <c r="M170">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N170">
         <v>1.5</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
+          <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
         </is>
       </c>
     </row>
@@ -9494,54 +9356,49 @@
         <v>40</v>
       </c>
       <c r="I171">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|850</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風雪</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
         </is>
       </c>
       <c r="M171">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N171">
         <v>1.5</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
+          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9551,7 +9408,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G172">
@@ -9561,7 +9418,7 @@
         <v>40</v>
       </c>
       <c r="I172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -9570,45 +9427,40 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜衝擊</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
+          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M172">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N172">
         <v>1.5</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9618,7 +9470,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G173">
@@ -9628,7 +9480,7 @@
         <v>40</v>
       </c>
       <c r="I173">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -9637,45 +9489,40 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">巨型風刃</t>
+          <t xml:space="preserve">寒冰體</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
+          <t xml:space="preserve">{"stacks":1}</t>
         </is>
       </c>
       <c r="M173">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N173">
         <v>1.5</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
+          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9685,7 +9532,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G174">
@@ -9695,7 +9542,7 @@
         <v>40</v>
       </c>
       <c r="I174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -9704,45 +9551,40 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重風刃</t>
+          <t xml:space="preserve">極致寒霜</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
+          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
         </is>
       </c>
       <c r="M174">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N174">
         <v>1.5</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
+          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -9752,7 +9594,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G175">
@@ -9762,7 +9604,7 @@
         <v>40</v>
       </c>
       <c r="I175">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -9771,45 +9613,40 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂披風</t>
+          <t xml:space="preserve">三重新星</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
         </is>
       </c>
       <c r="M175">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N175">
         <v>1.5</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
+          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -9819,7 +9656,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G176">
@@ -9829,7 +9666,7 @@
         <v>40</v>
       </c>
       <c r="I176">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -9838,45 +9675,40 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">追跡風刃</t>
+          <t xml:space="preserve">死亡新星</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
+          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
         </is>
       </c>
       <c r="M176">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N176">
         <v>1.5</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
+          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -9886,7 +9718,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G177">
@@ -9896,7 +9728,7 @@
         <v>40</v>
       </c>
       <c r="I177">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -9905,23 +9737,23 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂風碎裂</t>
+          <t xml:space="preserve">暴風雪</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
         </is>
       </c>
       <c r="M177">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N177">
         <v>1.5</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
+          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -9963,49 +9795,54 @@
         <v>40</v>
       </c>
       <c r="I178">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|900</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風真空刃</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
         </is>
       </c>
       <c r="M178">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N178">
         <v>1.5</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
+          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10025,7 +9862,7 @@
         <v>40</v>
       </c>
       <c r="I179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -10034,40 +9871,45 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">巨型風刃</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
+          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
         </is>
       </c>
       <c r="M179">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N179">
         <v>1.5</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10087,7 +9929,7 @@
         <v>40</v>
       </c>
       <c r="I180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -10096,40 +9938,45 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空爆震</t>
+          <t xml:space="preserve">雙重風刃</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
         </is>
       </c>
       <c r="M180">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N180">
         <v>1.5</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10149,7 +9996,7 @@
         <v>40</v>
       </c>
       <c r="I181">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -10158,40 +10005,45 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切</t>
+          <t xml:space="preserve">亂披風</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
         </is>
       </c>
       <c r="M181">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N181">
         <v>1.5</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10211,7 +10063,7 @@
         <v>40</v>
       </c>
       <c r="I182">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -10220,40 +10072,45 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋斬</t>
+          <t xml:space="preserve">追跡風刃</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
         </is>
       </c>
       <c r="M182">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N182">
         <v>1.5</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
+          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10273,7 +10130,7 @@
         <v>40</v>
       </c>
       <c r="I183">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -10282,40 +10139,45 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋三重奏</t>
+          <t xml:space="preserve">狂風碎裂</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
+          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
         </is>
       </c>
       <c r="M183">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N183">
         <v>1.5</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10335,7 +10197,7 @@
         <v>40</v>
       </c>
       <c r="I184">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -10344,23 +10206,23 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">無限風切</t>
+          <t xml:space="preserve">暴風真空刃</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
         </is>
       </c>
       <c r="M184">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N184">
         <v>1.5</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
+          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
@@ -10397,49 +10259,49 @@
         <v>40</v>
       </c>
       <c r="I185">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|950</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛空斬</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
         </is>
       </c>
       <c r="M185">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N185">
         <v>1.5</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10459,7 +10321,7 @@
         <v>40</v>
       </c>
       <c r="I186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -10468,40 +10330,40 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空爆震</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
         </is>
       </c>
       <c r="M186">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N186">
         <v>1.5</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10521,7 +10383,7 @@
         <v>40</v>
       </c>
       <c r="I187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -10530,40 +10392,40 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風撕裂</t>
+          <t xml:space="preserve">風切</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
         </is>
       </c>
       <c r="M187">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N187">
         <v>1.5</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10583,7 +10445,7 @@
         <v>40</v>
       </c>
       <c r="I188">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -10592,40 +10454,40 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂風切</t>
+          <t xml:space="preserve">迴旋斬</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
         </is>
       </c>
       <c r="M188">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N188">
         <v>1.5</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -10645,7 +10507,7 @@
         <v>40</v>
       </c>
       <c r="I189">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -10654,40 +10516,40 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風之刃</t>
+          <t xml:space="preserve">迴旋三重奏</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
         </is>
       </c>
       <c r="M189">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N189">
         <v>1.5</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -10707,7 +10569,7 @@
         <v>40</v>
       </c>
       <c r="I190">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -10716,40 +10578,40 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切擴散</t>
+          <t xml:space="preserve">無限風切</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M190">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N190">
         <v>1.5</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -10769,7 +10631,7 @@
         <v>40</v>
       </c>
       <c r="I191">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -10778,23 +10640,23 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">颶風屏障</t>
+          <t xml:space="preserve">虛空斬</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
         </is>
       </c>
       <c r="M191">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N191">
         <v>1.5</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -10831,30 +10693,402 @@
         <v>40</v>
       </c>
       <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|700</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+        </is>
+      </c>
+      <c r="M192">
+        <v>100000</v>
+      </c>
+      <c r="N192">
+        <v>1.5</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G193">
+        <v>15</v>
+      </c>
+      <c r="H193">
+        <v>40</v>
+      </c>
+      <c r="I193">
+        <v>2</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|750</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風撕裂</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+        </is>
+      </c>
+      <c r="M193">
+        <v>200000</v>
+      </c>
+      <c r="N193">
+        <v>1.5</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G194">
+        <v>15</v>
+      </c>
+      <c r="H194">
+        <v>40</v>
+      </c>
+      <c r="I194">
+        <v>3</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|800</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亂風切</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M194">
+        <v>400000</v>
+      </c>
+      <c r="N194">
+        <v>1.5</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G195">
+        <v>15</v>
+      </c>
+      <c r="H195">
+        <v>40</v>
+      </c>
+      <c r="I195">
+        <v>4</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|850</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風之刃</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+        </is>
+      </c>
+      <c r="M195">
+        <v>800000</v>
+      </c>
+      <c r="N195">
+        <v>1.5</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G196">
+        <v>15</v>
+      </c>
+      <c r="H196">
+        <v>40</v>
+      </c>
+      <c r="I196">
+        <v>5</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|900</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切擴散</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+        </is>
+      </c>
+      <c r="M196">
+        <v>1500000</v>
+      </c>
+      <c r="N196">
+        <v>1.5</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G197">
+        <v>15</v>
+      </c>
+      <c r="H197">
+        <v>40</v>
+      </c>
+      <c r="I197">
+        <v>6</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|950</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">颶風屏障</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+        </is>
+      </c>
+      <c r="M197">
+        <v>3000000</v>
+      </c>
+      <c r="N197">
+        <v>1.5</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G198">
+        <v>15</v>
+      </c>
+      <c r="H198">
+        <v>40</v>
+      </c>
+      <c r="I198">
         <v>7</v>
       </c>
-      <c r="J192" t="inlineStr">
+      <c r="J198" t="inlineStr">
         <is>
           <t xml:space="preserve">0|1000</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="K198" t="inlineStr">
         <is>
           <t xml:space="preserve">暴風神體</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">{"red":99,"sec":2,"secPer":0.2,"pct":100,"pctPer":10}</t>
         </is>
       </c>
-      <c r="M192">
+      <c r="M198">
         <v>5000000</v>
       </c>
-      <c r="N192">
-        <v>1.5</v>
-      </c>
-      <c r="O192" t="inlineStr">
+      <c r="N198">
+        <v>1.5</v>
+      </c>
+      <c r="O198" t="inlineStr">
         <is>
           <t xml:space="preserve">施放暴風屏障時同時召喚風暴之神附體：{sec} 秒內傷害減免 +{red}%，且自身的風系傷害額外 ×(1+{pct}%)</t>
         </is>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -5644,7 +5644,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":6,"gap":0.5,"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3,"mps":24}</t>
+          <t xml:space="preserve">{"m":6,"gap":0.5,"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3,"mps":24,"flyM":40}</t>
         </is>
       </c>
       <c r="M111">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve">你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環（{mps} 米／秒）</t>
+          <t xml:space="preserve">你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {mps} 米／秒貫穿飛行 {flyM} 米</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"countPer":0.2,"pct":300,"pctPer":30,"wid":3}</t>
+          <t xml:space="preserve">{"count":2,"countPer":0.2,"pct":300,"pctPer":30,"wid":3,"mps":30}</t>
         </is>
       </c>
       <c r="M159">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放落雷術時同時召喚橫向與直向各 {count} 道落雷橫掃全場（每道寬 {wid} 米），對路徑上的所有敵人造成 {pct}% 雷電傷害</t>
+          <t xml:space="preserve">施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{mps} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8926,186 +8926,117 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">寒冰箭</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">❄️</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ice</t>
-        </is>
-      </c>
-      <c r="G169">
-        <v>15</v>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
       </c>
       <c r="H169">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I169">
-        <v>1</v>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|450</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭</t>
+          <t xml:space="preserve">臨界雷劫</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"deg":15,"castM":30,"speed":45}</t>
+          <t xml:space="preserve">{"count":4,"chanceMult":2,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M169">
-        <v>100000</v>
+        <v>10000000</v>
       </c>
       <c r="N169">
         <v>1.5</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">【伴生雷球】改為一次生成 {count} 顆、觸發機率 ×{chanceMult}，且所有雷球與電球的傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">criticalThunderbolt</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">寒冰箭</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">❄️</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ice</t>
-        </is>
-      </c>
-      <c r="G170">
-        <v>15</v>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
       </c>
       <c r="H170">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I170">
-        <v>2</v>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|500</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜箭</t>
+          <t xml:space="preserve">雷爆</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"frostPct":50,"frostPctPer":5,"stacks":1}</t>
+          <t xml:space="preserve">{"chance":15,"chancePer":0.15,"bounces":4,"m":12,"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M170">
-        <v>200000</v>
+        <v>10000000</v>
       </c>
       <c r="N170">
         <v>1.5</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
+          <t xml:space="preserve">每次被雷球命中的敵人有 {chance}% 機率觸發 1 顆小型雷球，在附近 {m} 米範圍內彈射 {bounces} 次，每次造成 {pct}% 雷電傷害</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderBurst</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">icearrow</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">寒冰箭</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">❄️</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ice</t>
-        </is>
-      </c>
-      <c r="G171">
-        <v>15</v>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
       </c>
       <c r="H171">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I171">
-        <v>3</v>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|550</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰系強化</t>
+          <t xml:space="preserve">雷殞天地碎</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"scale":50,"gap":1,"pct":200,"pctPer":20}</t>
         </is>
       </c>
       <c r="M171">
-        <v>400000</v>
+        <v>10000000</v>
       </c>
       <c r="N171">
         <v>1.5</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
+          <t xml:space="preserve">【雷殞天落】的雷殞石體積增大 {scale}%、傷害額外 +{pct}%，並額外每 {gap} 秒不斷再降下 1 顆</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderfallShatter</t>
         </is>
       </c>
     </row>
@@ -9142,32 +9073,32 @@
         <v>40</v>
       </c>
       <c r="I172">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|600</t>
+          <t xml:space="preserve">0|450</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">貫穿冰箭</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":10,"mPer":2}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"deg":15,"castM":30,"speed":45}</t>
         </is>
       </c>
       <c r="M172">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="N172">
         <v>1.5</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
+          <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
@@ -9204,32 +9135,32 @@
         <v>40</v>
       </c>
       <c r="I173">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|650</t>
+          <t xml:space="preserve">0|500</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰箭散射</t>
+          <t xml:space="preserve">寒霜箭</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
+          <t xml:space="preserve">{"frostPct":50,"frostPctPer":5,"stacks":1}</t>
         </is>
       </c>
       <c r="M173">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="N173">
         <v>1.5</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
+          <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
         </is>
       </c>
     </row>
@@ -9266,32 +9197,32 @@
         <v>40</v>
       </c>
       <c r="I174">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|700</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜凍結</t>
+          <t xml:space="preserve">冰系強化</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":1,"stacksPer":0.4}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M174">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="N174">
         <v>1.5</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
+          <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
         </is>
       </c>
     </row>
@@ -9328,49 +9259,49 @@
         <v>40</v>
       </c>
       <c r="I175">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|750</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰爆裂箭</t>
+          <t xml:space="preserve">貫穿冰箭</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"m":6,"chaseM":30,"bodyM":1.5,"gap":0.1,"waves":3,"waveGap":0.3}</t>
+          <t xml:space="preserve">{"m":10,"mPer":2}</t>
         </is>
       </c>
       <c r="M175">
-        <v>5000000</v>
+        <v>800000</v>
       </c>
       <c r="N175">
         <v>1.5</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -9390,49 +9321,49 @@
         <v>40</v>
       </c>
       <c r="I176">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|500</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">冰箭散射</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"arcM":8}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M176">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="N176">
         <v>1.5</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
+          <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -9452,49 +9383,49 @@
         <v>40</v>
       </c>
       <c r="I177">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|550</t>
+          <t xml:space="preserve">0|700</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰逆轉</t>
+          <t xml:space="preserve">寒霜凍結</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":6}</t>
+          <t xml:space="preserve">{"stacks":1,"stacksPer":0.4}</t>
         </is>
       </c>
       <c r="M177">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="N177">
         <v>1.5</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
+          <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
+          <t xml:space="preserve">icearrow</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈</t>
+          <t xml:space="preserve">寒冰箭</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">💧</t>
+          <t xml:space="preserve">❄️</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9514,218 +9445,149 @@
         <v>40</v>
       </c>
       <c r="I178">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|600</t>
+          <t xml:space="preserve">0|750</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒流彈</t>
+          <t xml:space="preserve">寒冰爆裂箭</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"frostPct":50,"frostPctPer":20,"stacks":1}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"m":6,"chaseM":30,"bodyM":1.5,"gap":0.1,"waves":3,"waveGap":0.3}</t>
         </is>
       </c>
       <c r="M178">
-        <v>400000</v>
+        <v>5000000</v>
       </c>
       <c r="N178">
         <v>1.5</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
+          <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水流彈</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">💧</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ice</t>
-        </is>
-      </c>
-      <c r="G179">
-        <v>15</v>
+          <t xml:space="preserve">icearrow</t>
+        </is>
       </c>
       <c r="H179">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I179">
-        <v>4</v>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|650</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒流爆散</t>
+          <t xml:space="preserve">極寒冰爆</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":8,"bounce":2,"bouncePer":0.2}</t>
+          <t xml:space="preserve">{"waves":10,"waveGap":0.35,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M179">
-        <v>800000</v>
+        <v>10000000</v>
       </c>
       <c r="N179">
         <v>1.5</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">【寒冰爆裂箭】改為每 {waveGap} 秒連射 {waves} 波，且寒冰箭傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absoluteZeroBurst</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水流彈</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">💧</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ice</t>
-        </is>
-      </c>
-      <c r="G180">
-        <v>15</v>
+          <t xml:space="preserve">icearrow</t>
+        </is>
       </c>
       <c r="H180">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I180">
-        <v>5</v>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|700</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜擴散</t>
+          <t xml:space="preserve">無限冰裂</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":10,"count":1}</t>
+          <t xml:space="preserve">{"sec":0.1,"count":4,"countPer":0.4}</t>
         </is>
       </c>
       <c r="M180">
-        <v>1500000</v>
+        <v>10000000</v>
       </c>
       <c r="N180">
         <v>1.5</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
+          <t xml:space="preserve">寒冰箭每造成 1 次傷害就使寒冰箭的冷卻時間 -{sec} 秒，且每次發射的寒冰箭數量額外 +{count} 支（不足 1 支的部分以機率觸發）</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">infiniteIceRift</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">waterball</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">水流彈</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">💧</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ice</t>
-        </is>
-      </c>
-      <c r="G181">
-        <v>15</v>
+          <t xml:space="preserve">icearrow</t>
+        </is>
       </c>
       <c r="H181">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I181">
-        <v>6</v>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|750</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重流水</t>
+          <t xml:space="preserve">冰之淚</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
+          <t xml:space="preserve">{"waves":10,"gap":0.35,"m":30,"pct":200,"pctPer":20}</t>
         </is>
       </c>
       <c r="M181">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="N181">
         <v>1.5</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
+          <t xml:space="preserve">施放寒冰箭時同時召喚 {waves} 波寒冰箭雨從天射下（每波間隔 {gap} 秒），每波對我方 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tearsOfIce</t>
         </is>
       </c>
     </row>
@@ -9762,49 +9624,49 @@
         <v>40</v>
       </c>
       <c r="I182">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|800</t>
+          <t xml:space="preserve">0|500</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">水龍捲</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"m":5,"side":10,"frozen":2,"gap":0.35}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"arcM":8}</t>
         </is>
       </c>
       <c r="M182">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N182">
         <v>1.5</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
+          <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9824,7 +9686,7 @@
         <v>40</v>
       </c>
       <c r="I183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -9833,40 +9695,40 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">寒冰逆轉</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
+          <t xml:space="preserve">{"pct":20,"pctPer":2,"sec":6}</t>
         </is>
       </c>
       <c r="M183">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N183">
         <v>1.5</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
+          <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9886,7 +9748,7 @@
         <v>40</v>
       </c>
       <c r="I184">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -9895,40 +9757,40 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜衝擊</t>
+          <t xml:space="preserve">寒流彈</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"frostPct":50,"frostPctPer":20,"stacks":1}</t>
         </is>
       </c>
       <c r="M184">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N184">
         <v>1.5</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
+          <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9948,7 +9810,7 @@
         <v>40</v>
       </c>
       <c r="I185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -9957,40 +9819,40 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰體</t>
+          <t xml:space="preserve">寒流爆散</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":1}</t>
+          <t xml:space="preserve">{"m":8,"bounce":2,"bouncePer":0.2}</t>
         </is>
       </c>
       <c r="M185">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N185">
         <v>1.5</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
+          <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10010,7 +9872,7 @@
         <v>40</v>
       </c>
       <c r="I186">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -10019,40 +9881,40 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">極致寒霜</t>
+          <t xml:space="preserve">寒霜擴散</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
+          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":10,"count":1}</t>
         </is>
       </c>
       <c r="M186">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N186">
         <v>1.5</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
+          <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10072,7 +9934,7 @@
         <v>40</v>
       </c>
       <c r="I187">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -10081,40 +9943,40 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重新星</t>
+          <t xml:space="preserve">三重流水</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.2}</t>
         </is>
       </c>
       <c r="M187">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N187">
         <v>1.5</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
+          <t xml:space="preserve">waterball</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水流彈</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">🧊</t>
+          <t xml:space="preserve">💧</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10134,7 +9996,7 @@
         <v>40</v>
       </c>
       <c r="I188">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -10143,23 +10005,23 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">死亡新星</t>
+          <t xml:space="preserve">水龍捲</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
+          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"m":5,"side":10,"frozen":2,"gap":0.35}</t>
         </is>
       </c>
       <c r="M188">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N188">
         <v>1.5</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
+          <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
         </is>
       </c>
     </row>
@@ -10196,54 +10058,49 @@
         <v>40</v>
       </c>
       <c r="I189">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|850</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風雪</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
         </is>
       </c>
       <c r="M189">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N189">
         <v>1.5</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
+          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -10253,7 +10110,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G190">
@@ -10263,7 +10120,7 @@
         <v>40</v>
       </c>
       <c r="I190">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -10272,45 +10129,40 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜衝擊</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
+          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M190">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N190">
         <v>1.5</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -10320,7 +10172,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G191">
@@ -10330,7 +10182,7 @@
         <v>40</v>
       </c>
       <c r="I191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -10339,45 +10191,40 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">巨型風刃</t>
+          <t xml:space="preserve">寒冰體</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
+          <t xml:space="preserve">{"stacks":1}</t>
         </is>
       </c>
       <c r="M191">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N191">
         <v>1.5</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
+          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10387,7 +10234,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G192">
@@ -10397,7 +10244,7 @@
         <v>40</v>
       </c>
       <c r="I192">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -10406,45 +10253,40 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重風刃</t>
+          <t xml:space="preserve">極致寒霜</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
+          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
         </is>
       </c>
       <c r="M192">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N192">
         <v>1.5</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
+          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10454,7 +10296,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G193">
@@ -10464,7 +10306,7 @@
         <v>40</v>
       </c>
       <c r="I193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -10473,45 +10315,40 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂披風</t>
+          <t xml:space="preserve">三重新星</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
         </is>
       </c>
       <c r="M193">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N193">
         <v>1.5</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
+          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -10521,7 +10358,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G194">
@@ -10531,7 +10368,7 @@
         <v>40</v>
       </c>
       <c r="I194">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -10540,45 +10377,40 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">追跡風刃</t>
+          <t xml:space="preserve">死亡新星</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
+          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
         </is>
       </c>
       <c r="M194">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N194">
         <v>1.5</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
+          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -10588,7 +10420,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G195">
@@ -10598,7 +10430,7 @@
         <v>40</v>
       </c>
       <c r="I195">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -10607,23 +10439,23 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂風碎裂</t>
+          <t xml:space="preserve">暴風雪</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
         </is>
       </c>
       <c r="M195">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N195">
         <v>1.5</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
+          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -10665,49 +10497,54 @@
         <v>40</v>
       </c>
       <c r="I196">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|900</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風真空刃</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
         </is>
       </c>
       <c r="M196">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N196">
         <v>1.5</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
+          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -10727,7 +10564,7 @@
         <v>40</v>
       </c>
       <c r="I197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -10736,40 +10573,45 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">巨型風刃</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
+          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
         </is>
       </c>
       <c r="M197">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N197">
         <v>1.5</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -10789,7 +10631,7 @@
         <v>40</v>
       </c>
       <c r="I198">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -10798,40 +10640,45 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空爆震</t>
+          <t xml:space="preserve">雙重風刃</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
         </is>
       </c>
       <c r="M198">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N198">
         <v>1.5</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -10851,7 +10698,7 @@
         <v>40</v>
       </c>
       <c r="I199">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -10860,40 +10707,45 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切</t>
+          <t xml:space="preserve">亂披風</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
         </is>
       </c>
       <c r="M199">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N199">
         <v>1.5</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -10913,7 +10765,7 @@
         <v>40</v>
       </c>
       <c r="I200">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -10922,40 +10774,45 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空迴旋</t>
+          <t xml:space="preserve">追跡風刃</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
         </is>
       </c>
       <c r="M200">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N200">
         <v>1.5</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
+          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -10975,7 +10832,7 @@
         <v>40</v>
       </c>
       <c r="I201">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -10984,40 +10841,45 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空三重奏</t>
+          <t xml:space="preserve">狂風碎裂</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
+          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
         </is>
       </c>
       <c r="M201">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N201">
         <v>1.5</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -11037,7 +10899,7 @@
         <v>40</v>
       </c>
       <c r="I202">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -11046,23 +10908,23 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">無限風切</t>
+          <t xml:space="preserve">暴風真空刃</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
         </is>
       </c>
       <c r="M202">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N202">
         <v>1.5</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
+          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
@@ -11099,49 +10961,49 @@
         <v>40</v>
       </c>
       <c r="I203">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|950</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛空斬</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
         </is>
       </c>
       <c r="M203">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N203">
         <v>1.5</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11161,7 +11023,7 @@
         <v>40</v>
       </c>
       <c r="I204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -11170,40 +11032,40 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空爆震</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
         </is>
       </c>
       <c r="M204">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N204">
         <v>1.5</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11223,7 +11085,7 @@
         <v>40</v>
       </c>
       <c r="I205">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -11232,40 +11094,40 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風撕裂</t>
+          <t xml:space="preserve">風切</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
         </is>
       </c>
       <c r="M205">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N205">
         <v>1.5</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11285,7 +11147,7 @@
         <v>40</v>
       </c>
       <c r="I206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -11294,40 +11156,40 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂風切</t>
+          <t xml:space="preserve">真空迴旋</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
         </is>
       </c>
       <c r="M206">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N206">
         <v>1.5</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11347,7 +11209,7 @@
         <v>40</v>
       </c>
       <c r="I207">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -11356,40 +11218,40 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風之刃</t>
+          <t xml:space="preserve">真空三重奏</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
         </is>
       </c>
       <c r="M207">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N207">
         <v>1.5</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11409,7 +11271,7 @@
         <v>40</v>
       </c>
       <c r="I208">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -11418,40 +11280,40 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切擴散</t>
+          <t xml:space="preserve">無限風切</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M208">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N208">
         <v>1.5</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -11471,7 +11333,7 @@
         <v>40</v>
       </c>
       <c r="I209">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -11480,23 +11342,23 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">颶風屏障</t>
+          <t xml:space="preserve">虛空斬</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
         </is>
       </c>
       <c r="M209">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N209">
         <v>1.5</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -11533,30 +11395,402 @@
         <v>40</v>
       </c>
       <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|700</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+        </is>
+      </c>
+      <c r="M210">
+        <v>100000</v>
+      </c>
+      <c r="N210">
+        <v>1.5</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G211">
+        <v>15</v>
+      </c>
+      <c r="H211">
+        <v>40</v>
+      </c>
+      <c r="I211">
+        <v>2</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|750</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風撕裂</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+        </is>
+      </c>
+      <c r="M211">
+        <v>200000</v>
+      </c>
+      <c r="N211">
+        <v>1.5</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G212">
+        <v>15</v>
+      </c>
+      <c r="H212">
+        <v>40</v>
+      </c>
+      <c r="I212">
+        <v>3</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|800</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亂風切</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M212">
+        <v>400000</v>
+      </c>
+      <c r="N212">
+        <v>1.5</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G213">
+        <v>15</v>
+      </c>
+      <c r="H213">
+        <v>40</v>
+      </c>
+      <c r="I213">
+        <v>4</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|850</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風之刃</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+        </is>
+      </c>
+      <c r="M213">
+        <v>800000</v>
+      </c>
+      <c r="N213">
+        <v>1.5</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G214">
+        <v>15</v>
+      </c>
+      <c r="H214">
+        <v>40</v>
+      </c>
+      <c r="I214">
+        <v>5</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|900</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切擴散</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+        </is>
+      </c>
+      <c r="M214">
+        <v>1500000</v>
+      </c>
+      <c r="N214">
+        <v>1.5</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G215">
+        <v>15</v>
+      </c>
+      <c r="H215">
+        <v>40</v>
+      </c>
+      <c r="I215">
+        <v>6</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|950</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">颶風屏障</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+        </is>
+      </c>
+      <c r="M215">
+        <v>3000000</v>
+      </c>
+      <c r="N215">
+        <v>1.5</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G216">
+        <v>15</v>
+      </c>
+      <c r="H216">
+        <v>40</v>
+      </c>
+      <c r="I216">
         <v>7</v>
       </c>
-      <c r="J210" t="inlineStr">
+      <c r="J216" t="inlineStr">
         <is>
           <t xml:space="preserve">0|1000</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="K216" t="inlineStr">
         <is>
           <t xml:space="preserve">暴風神體</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">{"red":99,"sec":2,"secPer":0.2,"pct":100,"pctPer":10}</t>
         </is>
       </c>
-      <c r="M210">
+      <c r="M216">
         <v>5000000</v>
       </c>
-      <c r="N210">
-        <v>1.5</v>
-      </c>
-      <c r="O210" t="inlineStr">
+      <c r="N216">
+        <v>1.5</v>
+      </c>
+      <c r="O216" t="inlineStr">
         <is>
           <t xml:space="preserve">施放暴風屏障時同時召喚風暴之神附體：{sec} 秒內傷害減免 +{red}%，且自身的風系傷害額外 ×(1+{pct}%)</t>
         </is>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -10028,186 +10028,117 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冰霜新星</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🧊</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ice</t>
-        </is>
-      </c>
-      <c r="G189">
-        <v>15</v>
+          <t xml:space="preserve">waterball</t>
+        </is>
       </c>
       <c r="H189">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I189">
-        <v>1</v>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|550</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星</t>
+          <t xml:space="preserve">水牢天瀑</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
+          <t xml:space="preserve">{"m":20,"atkRed":50,"vuln":100,"vulnPer":10,"sec":6}</t>
         </is>
       </c>
       <c r="M189">
-        <v>100000</v>
+        <v>10000000</v>
       </c>
       <c r="N189">
         <v>1.5</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
+          <t xml:space="preserve">施放水流彈時在周圍 {m} 米圍起一圈水牢獄：擋下由圈外射進來的遠程攻擊，圈內的敵人攻擊力 -{atkRed}%、受到的傷害 +{vuln}%，持續 {sec} 秒</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waterPrisonFall</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冰霜新星</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🧊</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ice</t>
-        </is>
-      </c>
-      <c r="G190">
-        <v>15</v>
+          <t xml:space="preserve">waterball</t>
+        </is>
       </c>
       <c r="H190">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I190">
-        <v>2</v>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|600</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜衝擊</t>
+          <t xml:space="preserve">怒海狂濤</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"need":10,"m":20,"hits":20,"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M190">
-        <v>200000</v>
+        <v>10000000</v>
       </c>
       <c r="N190">
         <v>1.5</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
+          <t xml:space="preserve">場上同時有 {need} 道水龍捲時，在它們的中央再生成 1 道巨大水龍捲，對 {m} 米內的所有敵人造成連續 {hits} 段 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ragingTide</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">frostnova</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">冰霜新星</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🧊</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ice</t>
-        </is>
-      </c>
-      <c r="G191">
-        <v>15</v>
+          <t xml:space="preserve">waterball</t>
+        </is>
       </c>
       <c r="H191">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I191">
-        <v>3</v>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|650</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">寒冰體</t>
+          <t xml:space="preserve">海淵葬界</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":1}</t>
+          <t xml:space="preserve">{"m":30,"gap":0.35,"stacks":10,"stacksPer":1}</t>
         </is>
       </c>
       <c r="M191">
-        <v>400000</v>
+        <v>10000000</v>
       </c>
       <c r="N191">
         <v>1.5</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
+          <t xml:space="preserve">在周圍 {m} 米展開一道永久的水之領域：每 {gap} 秒對領域內的敵人施加寒霜狀態，且領域內的敵人可額外再疊 {stacks} 層寒霜</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abyssBurial</t>
         </is>
       </c>
     </row>
@@ -10244,32 +10175,32 @@
         <v>40</v>
       </c>
       <c r="I192">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|700</t>
+          <t xml:space="preserve">0|550</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">極致寒霜</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
         </is>
       </c>
       <c r="M192">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="N192">
         <v>1.5</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
+          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
         </is>
       </c>
     </row>
@@ -10306,32 +10237,32 @@
         <v>40</v>
       </c>
       <c r="I193">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|750</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">三重新星</t>
+          <t xml:space="preserve">冰霜衝擊</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
+          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M193">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="N193">
         <v>1.5</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
@@ -10368,32 +10299,32 @@
         <v>40</v>
       </c>
       <c r="I194">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|800</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">死亡新星</t>
+          <t xml:space="preserve">寒冰體</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
+          <t xml:space="preserve">{"stacks":1}</t>
         </is>
       </c>
       <c r="M194">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="N194">
         <v>1.5</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
+          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
         </is>
       </c>
     </row>
@@ -10430,54 +10361,49 @@
         <v>40</v>
       </c>
       <c r="I195">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|850</t>
+          <t xml:space="preserve">0|700</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風雪</t>
+          <t xml:space="preserve">極致寒霜</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
+          <t xml:space="preserve">{"dmgPct":40,"dmgPctPer":4,"durPct":40,"durPctPer":4}</t>
         </is>
       </c>
       <c r="M195">
-        <v>5000000</v>
+        <v>800000</v>
       </c>
       <c r="N195">
         <v>1.5</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
+          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -10487,7 +10413,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G196">
@@ -10497,54 +10423,49 @@
         <v>40</v>
       </c>
       <c r="I196">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|600</t>
+          <t xml:space="preserve">0|750</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">三重新星</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
         </is>
       </c>
       <c r="M196">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="N196">
         <v>1.5</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -10554,7 +10475,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G197">
@@ -10564,54 +10485,49 @@
         <v>40</v>
       </c>
       <c r="I197">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|650</t>
+          <t xml:space="preserve">0|800</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">巨型風刃</t>
+          <t xml:space="preserve">死亡新星</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
+          <t xml:space="preserve">{"chance":35,"chancePer":6.5}</t>
         </is>
       </c>
       <c r="M197">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="N197">
         <v>1.5</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
+          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
+          <t xml:space="preserve">frostnova</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃</t>
+          <t xml:space="preserve">冰霜新星</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
+          <t xml:space="preserve">🧊</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -10621,7 +10537,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">wind</t>
+          <t xml:space="preserve">ice</t>
         </is>
       </c>
       <c r="G198">
@@ -10631,233 +10547,149 @@
         <v>40</v>
       </c>
       <c r="I198">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|700</t>
+          <t xml:space="preserve">0|850</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">雙重風刃</t>
+          <t xml:space="preserve">暴風雪</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
         </is>
       </c>
       <c r="M198">
-        <v>400000</v>
+        <v>5000000</v>
       </c>
       <c r="N198">
         <v>1.5</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
+          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">風刃</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wind</t>
-        </is>
-      </c>
-      <c r="G199">
-        <v>15</v>
+          <t xml:space="preserve">frostnova</t>
+        </is>
       </c>
       <c r="H199">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I199">
-        <v>4</v>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|750</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂披風</t>
+          <t xml:space="preserve">無限新星</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
+          <t xml:space="preserve">{"gap":1,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M199">
-        <v>800000</v>
+        <v>10000000</v>
       </c>
       <c r="N199">
         <v>1.5</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
+          <t xml:space="preserve">每隔 {gap} 秒自動施放 1 次冰霜新星（不扣法力、不進冷卻），且冰霜新星傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">infiniteNova</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">風刃</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wind</t>
-        </is>
-      </c>
-      <c r="G200">
-        <v>15</v>
+          <t xml:space="preserve">frostnova</t>
+        </is>
       </c>
       <c r="H200">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I200">
-        <v>5</v>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|800</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">追跡風刃</t>
+          <t xml:space="preserve">極致之冰</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
+          <t xml:space="preserve">{"m":8,"gap":0.4,"pct":200,"pctPer":20}</t>
         </is>
       </c>
       <c r="M200">
-        <v>1500000</v>
+        <v>10000000</v>
       </c>
       <c r="N200">
         <v>1.5</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
+          <t xml:space="preserve">凍結中的敵人形成冰晶共鳴：每 {gap} 秒對相距 {m} 米內的其他凍結敵人造成 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crystalResonance</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">windblade</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">風刃</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🍃</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4*8</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wind</t>
-        </is>
-      </c>
-      <c r="G201">
-        <v>15</v>
+          <t xml:space="preserve">frostnova</t>
+        </is>
       </c>
       <c r="H201">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I201">
-        <v>6</v>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|850</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂風碎裂</t>
+          <t xml:space="preserve">冰皇領域</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
+          <t xml:space="preserve">{"scale":50,"gap":1,"min":2,"max":8,"hits":4,"pct":200,"pctPer":20,"m":8}</t>
         </is>
       </c>
       <c r="M201">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="N201">
         <v>1.5</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
+          <t xml:space="preserve">暴風雪的範圍擴大 {scale}%，且每 {gap} 秒在範圍內隨機 {min}～{max} 個目標的地面昇起冰錐，每根冰錐對周圍 {m} 米內的敵人造成連續 {hits} 段 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iceKingDomain</t>
         </is>
       </c>
     </row>
@@ -10899,49 +10731,54 @@
         <v>40</v>
       </c>
       <c r="I202">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|900</t>
+          <t xml:space="preserve">0|600</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風真空刃</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
         </is>
       </c>
       <c r="M202">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N202">
         <v>1.5</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
+          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10961,7 +10798,7 @@
         <v>40</v>
       </c>
       <c r="I203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -10970,40 +10807,45 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">巨型風刃</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
+          <t xml:space="preserve">{"size":30,"sizePer":3}</t>
         </is>
       </c>
       <c r="M203">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N203">
         <v>1.5</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11023,7 +10865,7 @@
         <v>40</v>
       </c>
       <c r="I204">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -11032,40 +10874,45 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空爆震</t>
+          <t xml:space="preserve">雙重風刃</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":30}</t>
         </is>
       </c>
       <c r="M204">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N204">
         <v>1.5</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11085,7 +10932,7 @@
         <v>40</v>
       </c>
       <c r="I205">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -11094,40 +10941,45 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切</t>
+          <t xml:space="preserve">亂披風</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
         </is>
       </c>
       <c r="M205">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N205">
         <v>1.5</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11147,7 +10999,7 @@
         <v>40</v>
       </c>
       <c r="I206">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -11156,40 +11008,45 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空迴旋</t>
+          <t xml:space="preserve">追跡風刃</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
         </is>
       </c>
       <c r="M206">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N206">
         <v>1.5</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
+          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11209,7 +11066,7 @@
         <v>40</v>
       </c>
       <c r="I207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -11218,40 +11075,45 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空三重奏</t>
+          <t xml:space="preserve">狂風碎裂</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
+          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
         </is>
       </c>
       <c r="M207">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N207">
         <v>1.5</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
+          <t xml:space="preserve">windblade</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">風刃</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌀</t>
+          <t xml:space="preserve">🍃</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4*8</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11271,7 +11133,7 @@
         <v>40</v>
       </c>
       <c r="I208">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -11280,23 +11142,23 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">無限風切</t>
+          <t xml:space="preserve">暴風真空刃</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
         </is>
       </c>
       <c r="M208">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N208">
         <v>1.5</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
+          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
@@ -11333,49 +11195,49 @@
         <v>40</v>
       </c>
       <c r="I209">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|950</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛空斬</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
         </is>
       </c>
       <c r="M209">
-        <v>5000000</v>
+        <v>100000</v>
       </c>
       <c r="N209">
         <v>1.5</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -11395,7 +11257,7 @@
         <v>40</v>
       </c>
       <c r="I210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -11404,40 +11266,40 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空爆震</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
         </is>
       </c>
       <c r="M210">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="N210">
         <v>1.5</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11457,7 +11319,7 @@
         <v>40</v>
       </c>
       <c r="I211">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -11466,40 +11328,40 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風撕裂</t>
+          <t xml:space="preserve">風切</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
         </is>
       </c>
       <c r="M211">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="N211">
         <v>1.5</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -11519,7 +11381,7 @@
         <v>40</v>
       </c>
       <c r="I212">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -11528,40 +11390,40 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂風切</t>
+          <t xml:space="preserve">真空迴旋</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
         </is>
       </c>
       <c r="M212">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="N212">
         <v>1.5</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -11581,7 +11443,7 @@
         <v>40</v>
       </c>
       <c r="I213">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -11590,40 +11452,40 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風之刃</t>
+          <t xml:space="preserve">真空三重奏</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
         </is>
       </c>
       <c r="M213">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="N213">
         <v>1.5</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -11643,7 +11505,7 @@
         <v>40</v>
       </c>
       <c r="I214">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -11652,40 +11514,40 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切擴散</t>
+          <t xml:space="preserve">無限風切</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M214">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
       <c r="N214">
         <v>1.5</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -11705,7 +11567,7 @@
         <v>40</v>
       </c>
       <c r="I215">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -11714,23 +11576,23 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">颶風屏障</t>
+          <t xml:space="preserve">虛空斬</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
         </is>
       </c>
       <c r="M215">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="N215">
         <v>1.5</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -11767,30 +11629,402 @@
         <v>40</v>
       </c>
       <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|700</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+        </is>
+      </c>
+      <c r="M216">
+        <v>100000</v>
+      </c>
+      <c r="N216">
+        <v>1.5</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G217">
+        <v>15</v>
+      </c>
+      <c r="H217">
+        <v>40</v>
+      </c>
+      <c r="I217">
+        <v>2</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|750</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風撕裂</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+        </is>
+      </c>
+      <c r="M217">
+        <v>200000</v>
+      </c>
+      <c r="N217">
+        <v>1.5</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G218">
+        <v>15</v>
+      </c>
+      <c r="H218">
+        <v>40</v>
+      </c>
+      <c r="I218">
+        <v>3</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|800</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亂風切</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M218">
+        <v>400000</v>
+      </c>
+      <c r="N218">
+        <v>1.5</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G219">
+        <v>15</v>
+      </c>
+      <c r="H219">
+        <v>40</v>
+      </c>
+      <c r="I219">
+        <v>4</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|850</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風之刃</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+        </is>
+      </c>
+      <c r="M219">
+        <v>800000</v>
+      </c>
+      <c r="N219">
+        <v>1.5</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G220">
+        <v>15</v>
+      </c>
+      <c r="H220">
+        <v>40</v>
+      </c>
+      <c r="I220">
+        <v>5</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|900</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切擴散</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+        </is>
+      </c>
+      <c r="M220">
+        <v>1500000</v>
+      </c>
+      <c r="N220">
+        <v>1.5</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G221">
+        <v>15</v>
+      </c>
+      <c r="H221">
+        <v>40</v>
+      </c>
+      <c r="I221">
+        <v>6</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|950</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">颶風屏障</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+        </is>
+      </c>
+      <c r="M221">
+        <v>3000000</v>
+      </c>
+      <c r="N221">
+        <v>1.5</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G222">
+        <v>15</v>
+      </c>
+      <c r="H222">
+        <v>40</v>
+      </c>
+      <c r="I222">
         <v>7</v>
       </c>
-      <c r="J216" t="inlineStr">
+      <c r="J222" t="inlineStr">
         <is>
           <t xml:space="preserve">0|1000</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="K222" t="inlineStr">
         <is>
           <t xml:space="preserve">暴風神體</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="L222" t="inlineStr">
         <is>
           <t xml:space="preserve">{"red":99,"sec":2,"secPer":0.2,"pct":100,"pctPer":10}</t>
         </is>
       </c>
-      <c r="M216">
+      <c r="M222">
         <v>5000000</v>
       </c>
-      <c r="N216">
-        <v>1.5</v>
-      </c>
-      <c r="O216" t="inlineStr">
+      <c r="N222">
+        <v>1.5</v>
+      </c>
+      <c r="O222" t="inlineStr">
         <is>
           <t xml:space="preserve">施放暴風屏障時同時召喚風暴之神附體：{sec} 秒內傷害減免 +{red}%，且自身的風系傷害額外 ×(1+{pct}%)</t>
         </is>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -10957,7 +10957,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t xml:space="preserve">風刃射出時同時朝其兩側各 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），每道造成原風刃 {pct}% 的傷害</t>
+          <t xml:space="preserve">風刃射出時同時朝其一側 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），造成原風刃 {pct}% 的傷害</t>
         </is>
       </c>
     </row>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":3,"directions":4,"gap":0.2}</t>
+          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":2,"directions":4,"gap":0.2}</t>
         </is>
       </c>
       <c r="M208">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -11165,186 +11165,117 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">真空斬</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wind</t>
-        </is>
-      </c>
-      <c r="G209">
-        <v>15</v>
+          <t xml:space="preserve">windblade</t>
+        </is>
       </c>
       <c r="H209">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I209">
-        <v>1</v>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|650</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬</t>
+          <t xml:space="preserve">暴風萬刃</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"add":1,"chaseM":60,"sec":4}</t>
         </is>
       </c>
       <c r="M209">
-        <v>100000</v>
+        <v>10000000</v>
       </c>
       <c r="N209">
         <v>1.5</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">大型風刃改為在 {chaseM} 米內持續追擊敵人 {sec} 秒，【暴風真空刃】每個方向再多射出 {add} 道風刃，且風刃傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormMyriad</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">真空斬</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wind</t>
-        </is>
-      </c>
-      <c r="G210">
-        <v>15</v>
+          <t xml:space="preserve">windblade</t>
+        </is>
       </c>
       <c r="H210">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I210">
-        <v>2</v>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|700</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空爆震</t>
+          <t xml:space="preserve">嵐之山</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"directions":4,"scale":100}</t>
         </is>
       </c>
       <c r="M210">
-        <v>200000</v>
+        <v>10000000</v>
       </c>
       <c r="N210">
         <v>1.5</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">【暴風真空刃】改為把該次所有大型與小型風刃融合，朝 {directions} 個方向各射出 1 道體積 +{scale}% 的巨型風刃，每道傷害為所融合風刃總和的 {pct}%</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormMountain</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">vacuumslash</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">真空斬</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🌀</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wind</t>
-        </is>
-      </c>
-      <c r="G211">
-        <v>15</v>
+          <t xml:space="preserve">windblade</t>
+        </is>
       </c>
       <c r="H211">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I211">
-        <v>3</v>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|750</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切</t>
+          <t xml:space="preserve">天穹崩裂</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
+          <t xml:space="preserve">{"chance":20,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M211">
-        <v>400000</v>
+        <v>10000000</v>
       </c>
       <c r="N211">
         <v>1.5</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">風刃改為被動技能：受到攻擊時有 {chance}% 機率朝攻擊者射出一道風刃，且其傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skyCollapse</t>
         </is>
       </c>
     </row>
@@ -11381,32 +11312,32 @@
         <v>40</v>
       </c>
       <c r="I212">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|800</t>
+          <t xml:space="preserve">0|650</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空迴旋</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
         </is>
       </c>
       <c r="M212">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="N212">
         <v>1.5</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
+          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
         </is>
       </c>
     </row>
@@ -11443,32 +11374,32 @@
         <v>40</v>
       </c>
       <c r="I213">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|850</t>
+          <t xml:space="preserve">0|700</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">真空三重奏</t>
+          <t xml:space="preserve">真空爆震</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
+          <t xml:space="preserve">{"hits":1,"hitsPer":0.1}</t>
         </is>
       </c>
       <c r="M213">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="N213">
         <v>1.5</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
+          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
@@ -11505,32 +11436,32 @@
         <v>40</v>
       </c>
       <c r="I214">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|900</t>
+          <t xml:space="preserve">0|750</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">無限風切</t>
+          <t xml:space="preserve">風切</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
         </is>
       </c>
       <c r="M214">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="N214">
         <v>1.5</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
+          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
@@ -11567,49 +11498,49 @@
         <v>40</v>
       </c>
       <c r="I215">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|950</t>
+          <t xml:space="preserve">0|800</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">虛空斬</t>
+          <t xml:space="preserve">真空迴旋</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
         </is>
       </c>
       <c r="M215">
-        <v>5000000</v>
+        <v>800000</v>
       </c>
       <c r="N215">
         <v>1.5</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
+          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -11629,49 +11560,49 @@
         <v>40</v>
       </c>
       <c r="I216">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|700</t>
+          <t xml:space="preserve">0|850</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空三重奏</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
         </is>
       </c>
       <c r="M216">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="N216">
         <v>1.5</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -11691,49 +11622,49 @@
         <v>40</v>
       </c>
       <c r="I217">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|750</t>
+          <t xml:space="preserve">0|900</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風撕裂</t>
+          <t xml:space="preserve">無限風切</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+          <t xml:space="preserve">{"stacks":3,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M217">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="N217">
         <v>1.5</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
+          <t xml:space="preserve">vacuumslash</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障</t>
+          <t xml:space="preserve">真空斬</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌪️</t>
+          <t xml:space="preserve">🌀</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -11753,218 +11684,149 @@
         <v>40</v>
       </c>
       <c r="I218">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t xml:space="preserve">0|800</t>
+          <t xml:space="preserve">0|950</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">亂風切</t>
+          <t xml:space="preserve">虛空斬</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
         </is>
       </c>
       <c r="M218">
-        <v>400000</v>
+        <v>5000000</v>
       </c>
       <c r="N218">
         <v>1.5</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">暴風屏障</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🌪️</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wind</t>
-        </is>
-      </c>
-      <c r="G219">
-        <v>15</v>
+          <t xml:space="preserve">vacuumslash</t>
+        </is>
       </c>
       <c r="H219">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I219">
-        <v>4</v>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|850</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風之刃</t>
+          <t xml:space="preserve">萬象風劫</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"pct":100,"sec":3,"gap":0.25,"grow":2}</t>
         </is>
       </c>
       <c r="M219">
-        <v>800000</v>
+        <v>10000000</v>
       </c>
       <c r="N219">
         <v>1.5</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+          <t xml:space="preserve">真空斬命中時有 {chance}% 機率在該處留下一道靜止的真空斬：持續 {sec} 秒、半徑隨時間擴大為 {grow} 倍，對碰到的敵人造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vacuumOmen</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">暴風屏障</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🌪️</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wind</t>
-        </is>
-      </c>
-      <c r="G220">
-        <v>15</v>
+          <t xml:space="preserve">vacuumslash</t>
+        </is>
       </c>
       <c r="H220">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I220">
-        <v>5</v>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|900</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切擴散</t>
+          <t xml:space="preserve">虛空滅界</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+          <t xml:space="preserve">{"gap":2,"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M220">
-        <v>1500000</v>
+        <v>10000000</v>
       </c>
       <c r="N220">
         <v>1.5</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+          <t xml:space="preserve">每 {gap} 秒自動斬出 1 道【虛空斬】，且虛空斬傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voidAnnihilation</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">stormbarrier</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">暴風屏障</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🌪️</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magic</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wind</t>
-        </is>
-      </c>
-      <c r="G221">
-        <v>15</v>
+          <t xml:space="preserve">vacuumslash</t>
+        </is>
       </c>
       <c r="H221">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="I221">
-        <v>6</v>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0|950</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">颶風屏障</t>
+          <t xml:space="preserve">時空崩解</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+          <t xml:space="preserve">{"m":12,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M221">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="N221">
         <v>1.5</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+          <t xml:space="preserve">【虛空斬】不再向外擴展，改為全部固定在你周圍 {m} 米環繞，且持續時間額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spacetimeCollapse</t>
         </is>
       </c>
     </row>
@@ -12001,30 +11863,402 @@
         <v>40</v>
       </c>
       <c r="I222">
+        <v>1</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|700</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+        </is>
+      </c>
+      <c r="M222">
+        <v>100000</v>
+      </c>
+      <c r="N222">
+        <v>1.5</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G223">
+        <v>15</v>
+      </c>
+      <c r="H223">
+        <v>40</v>
+      </c>
+      <c r="I223">
+        <v>2</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|750</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風撕裂</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+        </is>
+      </c>
+      <c r="M223">
+        <v>200000</v>
+      </c>
+      <c r="N223">
+        <v>1.5</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G224">
+        <v>15</v>
+      </c>
+      <c r="H224">
+        <v>40</v>
+      </c>
+      <c r="I224">
+        <v>3</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|800</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亂風切</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
+        </is>
+      </c>
+      <c r="M224">
+        <v>400000</v>
+      </c>
+      <c r="N224">
+        <v>1.5</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G225">
+        <v>15</v>
+      </c>
+      <c r="H225">
+        <v>40</v>
+      </c>
+      <c r="I225">
+        <v>4</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|850</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風之刃</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5}</t>
+        </is>
+      </c>
+      <c r="M225">
+        <v>800000</v>
+      </c>
+      <c r="N225">
+        <v>1.5</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G226">
+        <v>15</v>
+      </c>
+      <c r="H226">
+        <v>40</v>
+      </c>
+      <c r="I226">
+        <v>5</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|900</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切擴散</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+        </is>
+      </c>
+      <c r="M226">
+        <v>1500000</v>
+      </c>
+      <c r="N226">
+        <v>1.5</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G227">
+        <v>15</v>
+      </c>
+      <c r="H227">
+        <v>40</v>
+      </c>
+      <c r="I227">
+        <v>6</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0|950</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">颶風屏障</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"shield":2,"shieldPer":0.2}</t>
+        </is>
+      </c>
+      <c r="M227">
+        <v>3000000</v>
+      </c>
+      <c r="N227">
+        <v>1.5</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌪️</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magic</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="G228">
+        <v>15</v>
+      </c>
+      <c r="H228">
+        <v>40</v>
+      </c>
+      <c r="I228">
         <v>7</v>
       </c>
-      <c r="J222" t="inlineStr">
+      <c r="J228" t="inlineStr">
         <is>
           <t xml:space="preserve">0|1000</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="K228" t="inlineStr">
         <is>
           <t xml:space="preserve">暴風神體</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t xml:space="preserve">{"red":99,"sec":2,"secPer":0.2,"pct":100,"pctPer":10}</t>
         </is>
       </c>
-      <c r="M222">
+      <c r="M228">
         <v>5000000</v>
       </c>
-      <c r="N222">
-        <v>1.5</v>
-      </c>
-      <c r="O222" t="inlineStr">
+      <c r="N228">
+        <v>1.5</v>
+      </c>
+      <c r="O228" t="inlineStr">
         <is>
           <t xml:space="preserve">施放暴風屏障時同時召喚風暴之神附體：{sec} 秒內傷害減免 +{red}%，且自身的風系傷害額外 ×(1+{pct}%)</t>
         </is>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -12264,6 +12264,123 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="H229">
+        <v>300</v>
+      </c>
+      <c r="I229">
+        <v>8</v>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓦爾格之力</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"sec":50,"secPer":5,"red":0.1,"redPer":0.1,"pct":50,"pctPer":5}</t>
+        </is>
+      </c>
+      <c r="M229">
+        <v>10000000</v>
+      </c>
+      <c r="N229">
+        <v>1.5</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">召喚風之神祇降臨：【暴風神體】的持續時間 +{sec}%、傷害減免再 +{red}%，且自身風系傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valgrForce</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="H230">
+        <v>300</v>
+      </c>
+      <c r="I230">
+        <v>9</v>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天穹崩裂</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"gap":2,"min":1,"max":3,"maxPer":0.3,"pct":400,"pctPer":40,"m":8}</t>
+        </is>
+      </c>
+      <c r="M230">
+        <v>10000000</v>
+      </c>
+      <c r="N230">
+        <v>1.5</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每 {gap} 秒從天上落下 {min}～{max} 個召喚星體（巨大風刃／雷殞石／火殞石隨機，不足 1 個的部分以機率觸發），每個對落點 {m} 米內的敵人造成 {pct}% 傷害</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skyfallStars</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="H231">
+        <v>300</v>
+      </c>
+      <c r="I231">
+        <v>10</v>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">森羅萬象</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
+        </is>
+      </c>
+      <c r="M231">
+        <v>10000000</v>
+      </c>
+      <c r="N231">
+        <v>1.5</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放暴風屏障時同時打出【暴風真空刃】與【虛空斬】，且這兩者的傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">myriadPhenomena</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -89,6 +89,31 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t xml:space="preserve">施放特效</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊特效</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">飛行子彈</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受擊特效</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地板特效</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t xml:space="preserve">超神ID</t>
         </is>
       </c>
@@ -525,7 +550,7 @@
           <t xml:space="preserve">突刺命中時，傷害同時擴散至該敵人周圍 {m} 米內的所有敵人；施放突刺後 {sec} 秒內，你有 {dodge}% 機率絕對閃避敵方攻擊</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t xml:space="preserve">phantomOcta</t>
         </is>
@@ -564,7 +589,7 @@
           <t xml:space="preserve">突刺命中時堆疊【靈魂撕裂】：每層使該敵人受到的傷害提高 {perStack}%，最多 {maxStacks} 層（疊滿＝+{pct}%）</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t xml:space="preserve">shadowExecutioner</t>
         </is>
@@ -603,7 +628,7 @@
           <t xml:space="preserve">【八方連刺】改為朝前方的 1 道突刺，但傷害改為 {mult} 倍，且可以立即殺死普通敵人</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t xml:space="preserve">oneStrikeKill</t>
         </is>
@@ -1006,7 +1031,7 @@
           <t xml:space="preserve">【迴身四方斬】的攻擊次數 +{times} 次，且物理傷害再額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t xml:space="preserve">voidShatter</t>
         </is>
@@ -1045,7 +1070,7 @@
           <t xml:space="preserve">迴旋斬每命中 1 次，就在該敵人所在位置生成一道龍捲風：對半徑 {m} 米內的敵人造成 {hits} 段、每段 {pct}% 風系傷害</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t xml:space="preserve">windChaser</t>
         </is>
@@ -1084,7 +1109,7 @@
           <t xml:space="preserve">迴旋斬範圍擴大 {range}%，並改為被動技能：不再主動施放，改為每 {sec} 秒自動施放 1 次（每級施放間隔 -0.5 秒，仍需裝配在技能列才生效）</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t xml:space="preserve">stormGodSlash</t>
         </is>
@@ -1487,7 +1512,7 @@
           <t xml:space="preserve">每把飛刀（含彈射）都會對飛行路徑上的所有敵人造成 {pct}% 技能傷害</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t xml:space="preserve">petalStorm</t>
         </is>
@@ -1526,7 +1551,7 @@
           <t xml:space="preserve">飛刀殺死敵人時堆疊【死亡收割】：每層使你造成的傷害提高 {pct}%，最多 {maxStacks} 層，持續 {dur} 秒</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t xml:space="preserve">deathReaper</t>
         </is>
@@ -1565,7 +1590,7 @@
           <t xml:space="preserve">每次施放飛刀時額外射出 1 支無限飛刀，追擊周圍 {m} 米內的任意敵人：傷害提高 {pct}%，彈射次數不受限制；只有一個目標時會貫穿後繞回再次攻擊，不會停留原地重複傷害</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t xml:space="preserve">soulhunterBlade</t>
         </is>
@@ -1968,7 +1993,7 @@
           <t xml:space="preserve">疾風斬的最後一斬會對你周圍 {m} 米內的敵人造成「單段傷害 × 連擊數 × {mult}」的傷害</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t xml:space="preserve">thunderFlash</t>
         </is>
@@ -2007,7 +2032,7 @@
           <t xml:space="preserve">疾風斬附加雷電：每次斬擊命中時降下 1 道落雷，對命中處周圍 {m} 米內的敵人造成 {pct}% 閃電傷害</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t xml:space="preserve">thunderGodSlash</t>
         </is>
@@ -2046,7 +2071,7 @@
           <t xml:space="preserve">【月牙斬】不再由範圍內的敵人均分傷害，改為每個敵人都受到完整傷害，且傷害再額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t xml:space="preserve">chidori</t>
         </is>
@@ -2449,7 +2474,7 @@
           <t xml:space="preserve">永久展開 {m} 米的殺神領域：領域內的敵人死亡時堆疊【殺神】，每層使你造成的傷害 +{pct}%，同時回復 {healPct}% 最大生命；最多 {maxStacks} 層，持續 {dur} 秒</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t xml:space="preserve">slayerDomain</t>
         </is>
@@ -2488,7 +2513,7 @@
           <t xml:space="preserve">永久展開 {m} 米的萬毒領域：領域內的敵人每 {gap} 秒受到 {pct}% 中毒傷害，該中毒持續 {dur} 秒且可堆疊至 {maxStacks} 層</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t xml:space="preserve">venomDomain</t>
         </is>
@@ -2527,7 +2552,7 @@
           <t xml:space="preserve">中毒與流血不再有持續時間，塗上的當下就結算完整傷害；結算後爆炸，對周圍 {m} 米內的敵人造成該效果 {pct}% 的傷害</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t xml:space="preserve">disintegrate</t>
         </is>
@@ -2930,7 +2955,7 @@
           <t xml:space="preserve">每施放 1 次雙刀亂舞就失去當下 {hpPct}% 生命值（不會致死），但雙刀亂舞的傷害提高 {pct}%</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t xml:space="preserve">doomDance</t>
         </is>
@@ -2969,7 +2994,7 @@
           <t xml:space="preserve">雙刀亂舞附加火焰：每次命中堆疊 1 層【神樂灼焰】，每層每 {gap} 秒造成 {pct}% 火屬性傷害，最多 {maxStacks} 層，持續 {dur} 秒</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t xml:space="preserve">flameKagura</t>
         </is>
@@ -3008,7 +3033,7 @@
           <t xml:space="preserve">讓你可以同時裝備兩把雙手武器（主手與副手各一把），且雙手武器的詞條效果提升 {pct}%</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t xml:space="preserve">asuraDance</t>
         </is>
@@ -3411,7 +3436,7 @@
           <t xml:space="preserve">每 {count} 次反擊後朝目標射出一顆光彈，對其周圍 {m} 米內的敵人造成 {pct}% 神聖傷害</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t xml:space="preserve">holyBody</t>
         </is>
@@ -3450,7 +3475,7 @@
           <t xml:space="preserve">死亡時對 {m} 米內的所有敵人造成 {pct}% 地系傷害，並在 {sec} 秒後原地復活繼續戰鬥（不算戰鬥失敗）；冷卻 {cd} 秒</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t xml:space="preserve">indomitable</t>
         </is>
@@ -3489,7 +3514,7 @@
           <t xml:space="preserve">你在 {sec} 秒內損失的生命百分比，會在接下來 {sec} 秒內的反擊中一併附加到敵人身上</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t xml:space="preserve">warGodBody</t>
         </is>
@@ -3892,7 +3917,7 @@
           <t xml:space="preserve">狂怒期間普攻傷害 +{pct}%，且同時對目標周圍 {m} 米內的所有敵人造成傷害</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t xml:space="preserve">slayerAdvent</t>
         </is>
@@ -3931,7 +3956,7 @@
           <t xml:space="preserve">狂怒期間你無法獲得護盾，但每殺死 1 個敵人使你造成的所有傷害 +{pct}%，最多 {maxStacks} 層，持續到你死亡為止</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t xml:space="preserve">warGodRoll</t>
         </is>
@@ -3970,7 +3995,7 @@
           <t xml:space="preserve">每 {gap} 秒，你造成的所有傷害 +{pct}%，持續 {sec} 秒</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t xml:space="preserve">asuraFist</t>
         </is>
@@ -4443,7 +4468,7 @@
           <t xml:space="preserve">殞石的體積 +{size}%、造成的傷害 +{pct}%，且每次施放額外連續落下 {count} 顆巨大殞石</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t xml:space="preserve">meteorFall</t>
         </is>
@@ -4482,7 +4507,7 @@
           <t xml:space="preserve">每 {gap} 秒，天空落下一顆超巨型殞石：普通敵人 -{normal}% 生命、菁英 -{elite}% 生命、BOSS -{boss}% 生命</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t xml:space="preserve">starfallCataclysm</t>
         </is>
@@ -4521,7 +4546,7 @@
           <t xml:space="preserve">殞石數量 +{count} 顆，且每顆殞石落下時伴隨 {balls} 顆火球一同落下；火球與殞石造成的傷害 +{pct}%</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t xml:space="preserve">phoenixPrairie</t>
         </is>
@@ -4994,7 +5019,7 @@
           <t xml:space="preserve">每次施放的火龍捲（火牆）數量變為 {mult} 倍（小數部分依機率補 1 道）</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="U99" t="inlineStr">
         <is>
           <t xml:space="preserve">infernoTempest</t>
         </is>
@@ -5033,7 +5058,7 @@
           <t xml:space="preserve">火龍捲會在附近 {m} 米內隨機游走，並在移動軌跡上留下火池：每 {gap} 秒造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t xml:space="preserve">eternalInferno</t>
         </is>
@@ -5072,7 +5097,7 @@
           <t xml:space="preserve">所有火龍捲改為聚攏在你身邊，並持續將 {m} 米內的敵人拉向你，且火龍捲的傷害段數 +{hits} 段</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="U101" t="inlineStr">
         <is>
           <t xml:space="preserve">dragonDevour</t>
         </is>
@@ -5580,7 +5605,7 @@
           <t xml:space="preserve">火狩數量 +{count} 團，體積在 {growSec} 秒內逐漸增大最多 {grow}%，環繞速度 +{spin}%，且造成傷害 +{pct}%</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
+      <c r="U109" t="inlineStr">
         <is>
           <t xml:space="preserve">solarRing</t>
         </is>
@@ -5619,7 +5644,7 @@
           <t xml:space="preserve">火狩改為從自身中心呈螺旋狀向外擴散（在 {m} 米處達到最外圈），並於持續時間內不斷放出火狩，最多額外 +{count} 團</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="U110" t="inlineStr">
         <is>
           <t xml:space="preserve">infiniteRing</t>
         </is>
@@ -5658,7 +5683,7 @@
           <t xml:space="preserve">你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {mps} 米／秒貫穿飛行 {flyM} 米</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
+      <c r="U111" t="inlineStr">
         <is>
           <t xml:space="preserve">fireGodDescend</t>
         </is>
@@ -6131,7 +6156,7 @@
           <t xml:space="preserve">施放時將巨岩之力壓縮到極致，使 {m} 米內的敵人石化 {sec} 秒：無法行動，且受到的土系傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
+      <c r="U119" t="inlineStr">
         <is>
           <t xml:space="preserve">superRockArt</t>
         </is>
@@ -6170,7 +6195,7 @@
           <t xml:space="preserve">岩甲護盾存在期間額外獲得 +{red}% 傷害減免（乘算），生命上限與岩甲護盾 +{hp}%，且【岩甲尖刺】的效果額外提高 {spike}%</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
+      <c r="U120" t="inlineStr">
         <is>
           <t xml:space="preserve">adamantBody</t>
         </is>
@@ -6209,7 +6234,7 @@
           <t xml:space="preserve">施放岩甲術時同時扭曲 {m} 米內的重力場，使敵人僵化（移動、攻速與傷害 -{stiff}%，持續 {stiffSec} 秒）；岩甲護盾存在期間你的土系傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
+      <c r="U121" t="inlineStr">
         <is>
           <t xml:space="preserve">gravityField</t>
         </is>
@@ -6717,7 +6742,7 @@
           <t xml:space="preserve">沼澤範圍內的敵人染上【瘟疫】：每 {gap} 秒受到魔法攻擊 {pct}% 的毒性傷害，且受到的毒性傷害額外 +{amp}%；離開沼澤後仍持續 {sec} 秒</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr">
+      <c r="U129" t="inlineStr">
         <is>
           <t xml:space="preserve">plagueMire</t>
         </is>
@@ -6756,7 +6781,7 @@
           <t xml:space="preserve">熔岩沼每 {gap} 秒對範圍內的敵人噴出 1 道火龍捲（半徑 {m} 米、{hits} 段、每段 {pct}% 火焰傷害），並將命中的敵人屬性改變為火屬性，持續 {sec} 秒</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr">
+      <c r="U130" t="inlineStr">
         <is>
           <t xml:space="preserve">abyssInferno</t>
         </is>
@@ -6795,7 +6820,7 @@
           <t xml:space="preserve">沼澤範圍內生命值 {hpPct}% 以下的敵人，每次受到傷害有 {chance}% 機率直接被斬殺，且該機率每次受傷再累加 {add}%</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr">
+      <c r="U131" t="inlineStr">
         <is>
           <t xml:space="preserve">netherMire</t>
         </is>
@@ -7268,7 +7293,7 @@
           <t xml:space="preserve">生命與法力回復額外 +{pct}%（乘算），且溢出的生命與法力以 {conv}% 轉為你的生命護盾</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr">
+      <c r="U139" t="inlineStr">
         <is>
           <t xml:space="preserve">hallOfRadiance</t>
         </is>
@@ -7307,7 +7332,7 @@
           <t xml:space="preserve">被你殺死的普通與菁英敵人有 {chance}% 機率（上限 100%）以 {hp}% 生命重生（同一個敵人只會重生一次）</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr">
+      <c r="U140" t="inlineStr">
         <is>
           <t xml:space="preserve">worldRebirth</t>
         </is>
@@ -7346,7 +7371,7 @@
           <t xml:space="preserve">【天地共生】的冷卻結束後可累積復活次數，最多累積 {max} 次（小數四捨五入取整）</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr">
+      <c r="U141" t="inlineStr">
         <is>
           <t xml:space="preserve">fateReversal</t>
         </is>
@@ -7819,7 +7844,7 @@
           <t xml:space="preserve">施放連鎖閃電後每 {gap} 秒自動再施放 1 次，持續 {sec} 秒（自動施放不扣法力、不進冷卻）</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr">
+      <c r="U149" t="inlineStr">
         <is>
           <t xml:space="preserve">skyThunderArray</t>
         </is>
@@ -7858,7 +7883,7 @@
           <t xml:space="preserve">額外射出 1 道無限彈射的閃電鏈：在自身與 {m} 米內的任意敵人之間往返彈射，每經過自身 1 次使你的雷電傷害 +{pct}%，最多 {maxStacks} 層（持續到你死亡為止）</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr">
+      <c r="U150" t="inlineStr">
         <is>
           <t xml:space="preserve">eternalSuperconductor</t>
         </is>
@@ -7897,7 +7922,7 @@
           <t xml:space="preserve">施放後每 {gap} 秒放出 {count} 道閃電，分別打向 {m} 米內最遠的 {count} 個敵人，各對命中處 {r} 米內的所有敵人造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr">
+      <c r="U151" t="inlineStr">
         <is>
           <t xml:space="preserve">flyingThunderGod</t>
         </is>
@@ -8370,7 +8395,7 @@
           <t xml:space="preserve">施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{mps} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr">
+      <c r="U159" t="inlineStr">
         <is>
           <t xml:space="preserve">thunderMatrix</t>
         </is>
@@ -8409,7 +8434,7 @@
           <t xml:space="preserve">額外召喚 1 道永久持續的天劫雷電：每 {gap} 秒追擊 {m} 米內生命值最低的敵人，造成 {pct}% 雷電傷害</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr">
+      <c r="U160" t="inlineStr">
         <is>
           <t xml:space="preserve">heavenTribulation</t>
         </is>
@@ -8448,7 +8473,7 @@
           <t xml:space="preserve">施放落雷術後每 {gap} 秒自動再施放 1 次，持續 {sec} 秒（自動施放不扣法力、不進冷卻）</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr">
+      <c r="U161" t="inlineStr">
         <is>
           <t xml:space="preserve">eternalThunderPrison</t>
         </is>
@@ -8956,7 +8981,7 @@
           <t xml:space="preserve">【伴生雷球】改為一次生成 {count} 顆、觸發機率 ×{chanceMult}，且所有雷球與電球的傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P169" t="inlineStr">
+      <c r="U169" t="inlineStr">
         <is>
           <t xml:space="preserve">criticalThunderbolt</t>
         </is>
@@ -8995,7 +9020,7 @@
           <t xml:space="preserve">每次被雷球命中的敵人有 {chance}% 機率觸發 1 顆小型雷球，在附近 {m} 米範圍內彈射 {bounces} 次，每次造成 {pct}% 雷電傷害</t>
         </is>
       </c>
-      <c r="P170" t="inlineStr">
+      <c r="U170" t="inlineStr">
         <is>
           <t xml:space="preserve">thunderBurst</t>
         </is>
@@ -9034,7 +9059,7 @@
           <t xml:space="preserve">【雷殞天落】的雷殞石體積增大 {scale}%、傷害額外 +{pct}%，並額外每 {gap} 秒不斷再降下 1 顆</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr">
+      <c r="U171" t="inlineStr">
         <is>
           <t xml:space="preserve">thunderfallShatter</t>
         </is>
@@ -9507,7 +9532,7 @@
           <t xml:space="preserve">【寒冰爆裂箭】改為每 {waveGap} 秒連射 {waves} 波，且寒冰箭傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P179" t="inlineStr">
+      <c r="U179" t="inlineStr">
         <is>
           <t xml:space="preserve">absoluteZeroBurst</t>
         </is>
@@ -9546,7 +9571,7 @@
           <t xml:space="preserve">寒冰箭每造成 1 次傷害就使寒冰箭的冷卻時間 -{sec} 秒，且每次發射的寒冰箭數量額外 +{count} 支（不足 1 支的部分以機率觸發）</t>
         </is>
       </c>
-      <c r="P180" t="inlineStr">
+      <c r="U180" t="inlineStr">
         <is>
           <t xml:space="preserve">infiniteIceRift</t>
         </is>
@@ -9585,7 +9610,7 @@
           <t xml:space="preserve">施放寒冰箭時同時召喚 {waves} 波寒冰箭雨從天射下（每波間隔 {gap} 秒），每波對我方 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
-      <c r="P181" t="inlineStr">
+      <c r="U181" t="inlineStr">
         <is>
           <t xml:space="preserve">tearsOfIce</t>
         </is>
@@ -10058,7 +10083,7 @@
           <t xml:space="preserve">施放水流彈時在周圍 {m} 米圍起一圈水牢獄：擋下由圈外射進來的遠程攻擊，圈內的敵人攻擊力 -{atkRed}%、受到的傷害 +{vuln}%，持續 {sec} 秒</t>
         </is>
       </c>
-      <c r="P189" t="inlineStr">
+      <c r="U189" t="inlineStr">
         <is>
           <t xml:space="preserve">waterPrisonFall</t>
         </is>
@@ -10097,7 +10122,7 @@
           <t xml:space="preserve">場上同時有 {need} 道水龍捲時，在它們的中央再生成 1 道巨大水龍捲，對 {m} 米內的所有敵人造成連續 {hits} 段 {pct}% 寒冰傷害</t>
         </is>
       </c>
-      <c r="P190" t="inlineStr">
+      <c r="U190" t="inlineStr">
         <is>
           <t xml:space="preserve">ragingTide</t>
         </is>
@@ -10136,7 +10161,7 @@
           <t xml:space="preserve">在周圍 {m} 米展開一道永久的水之領域：每 {gap} 秒對領域內的敵人施加寒霜狀態，且領域內的敵人可額外再疊 {stacks} 層寒霜</t>
         </is>
       </c>
-      <c r="P191" t="inlineStr">
+      <c r="U191" t="inlineStr">
         <is>
           <t xml:space="preserve">abyssBurial</t>
         </is>
@@ -10609,7 +10634,7 @@
           <t xml:space="preserve">每隔 {gap} 秒自動施放 1 次冰霜新星（不扣法力、不進冷卻），且冰霜新星傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P199" t="inlineStr">
+      <c r="U199" t="inlineStr">
         <is>
           <t xml:space="preserve">infiniteNova</t>
         </is>
@@ -10648,7 +10673,7 @@
           <t xml:space="preserve">凍結中的敵人形成冰晶共鳴：每 {gap} 秒對相距 {m} 米內的其他凍結敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
-      <c r="P200" t="inlineStr">
+      <c r="U200" t="inlineStr">
         <is>
           <t xml:space="preserve">crystalResonance</t>
         </is>
@@ -10687,7 +10712,7 @@
           <t xml:space="preserve">暴風雪的範圍擴大 {scale}%，且每 {gap} 秒在範圍內隨機 {min}～{max} 個目標的地面昇起冰錐，每根冰錐對周圍 {m} 米內的敵人造成連續 {hits} 段 {pct}% 寒冰傷害</t>
         </is>
       </c>
-      <c r="P201" t="inlineStr">
+      <c r="U201" t="inlineStr">
         <is>
           <t xml:space="preserve">iceKingDomain</t>
         </is>
@@ -11195,7 +11220,7 @@
           <t xml:space="preserve">大型風刃改為在 {chaseM} 米內持續追擊敵人 {sec} 秒，【暴風真空刃】每個方向再多射出 {add} 道風刃，且風刃傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P209" t="inlineStr">
+      <c r="U209" t="inlineStr">
         <is>
           <t xml:space="preserve">stormMyriad</t>
         </is>
@@ -11234,7 +11259,7 @@
           <t xml:space="preserve">【暴風真空刃】改為把該次所有大型與小型風刃融合，朝 {directions} 個方向各射出 1 道體積 +{scale}% 的巨型風刃，每道傷害為所融合風刃總和的 {pct}%</t>
         </is>
       </c>
-      <c r="P210" t="inlineStr">
+      <c r="U210" t="inlineStr">
         <is>
           <t xml:space="preserve">stormMountain</t>
         </is>
@@ -11273,7 +11298,7 @@
           <t xml:space="preserve">風刃改為被動技能：受到攻擊時有 {chance}% 機率朝攻擊者射出一道風刃，且其傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P211" t="inlineStr">
+      <c r="U211" t="inlineStr">
         <is>
           <t xml:space="preserve">skyCollapse</t>
         </is>
@@ -11746,7 +11771,7 @@
           <t xml:space="preserve">真空斬命中時有 {chance}% 機率在該處留下一道靜止的真空斬：持續 {sec} 秒、半徑隨時間擴大為 {grow} 倍，對碰到的敵人造成 {pct}% 風系傷害</t>
         </is>
       </c>
-      <c r="P219" t="inlineStr">
+      <c r="U219" t="inlineStr">
         <is>
           <t xml:space="preserve">vacuumOmen</t>
         </is>
@@ -11785,7 +11810,7 @@
           <t xml:space="preserve">每 {gap} 秒自動斬出 1 道【虛空斬】，且虛空斬傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P220" t="inlineStr">
+      <c r="U220" t="inlineStr">
         <is>
           <t xml:space="preserve">voidAnnihilation</t>
         </is>
@@ -11824,7 +11849,7 @@
           <t xml:space="preserve">【虛空斬】不再向外擴展，改為全部固定在你周圍 {m} 米環繞，且持續時間額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P221" t="inlineStr">
+      <c r="U221" t="inlineStr">
         <is>
           <t xml:space="preserve">spacetimeCollapse</t>
         </is>
@@ -12297,7 +12322,7 @@
           <t xml:space="preserve">召喚風之神祇降臨：【暴風神體】的持續時間 +{sec}%、傷害減免再 +{red}%，且自身風系傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P229" t="inlineStr">
+      <c r="U229" t="inlineStr">
         <is>
           <t xml:space="preserve">valgrForce</t>
         </is>
@@ -12336,7 +12361,7 @@
           <t xml:space="preserve">每 {gap} 秒從天上落下 {min}～{max} 個召喚星體（巨大風刃／雷殞石／火殞石隨機，不足 1 個的部分以機率觸發），每個對落點 {m} 米內的敵人造成 {pct}% 傷害</t>
         </is>
       </c>
-      <c r="P230" t="inlineStr">
+      <c r="U230" t="inlineStr">
         <is>
           <t xml:space="preserve">skyfallStars</t>
         </is>
@@ -12375,7 +12400,7 @@
           <t xml:space="preserve">施放暴風屏障時同時打出【暴風真空刃】與【虛空斬】，且這兩者的傷害額外 +{pct}%</t>
         </is>
       </c>
-      <c r="P231" t="inlineStr">
+      <c r="U231" t="inlineStr">
         <is>
           <t xml:space="preserve">myriadPhenomena</t>
         </is>
@@ -12733,6 +12758,63 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放特效 / 攻擊特效 / 飛行子彈 / 受擊特效 / 地板特效（2026-09-03 VFX Preset 化）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每一格填 VFX 編輯器存出來的 Preset 檔名（vfx/presets/&lt;檔名&gt;.json，不含 .json；含 .json 也接受）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每一列＝該階（或該超神選項）「引入」的特效：第 1 階那一列是技能本體，後面各階只填那一階新增的畫面</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　（例：火球術第 1 階＝火球＋受擊、第 3 階火球爆裂＝小火球＋大爆炸、第 7 階殞石術＝隕石＋落點預警）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">程式在送出特效時會標明「這一發屬於第幾階」，然後讀那一列的格子；同一階沒填的角色就沒有那一段畫面；</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放特效＝角色身上；攻擊特效＝攻擊本體（斬弧／爆發／光束／雷柱／護罩）；飛行子彈＝會移動的東西（含環繞體）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受擊特效＝命中爆點；地板特效＝持續場域（泥沼、火牆、軌道環、預警圈），依實際判定範圍自動縮放（Preset 以半徑 100px、矩形 200×100px 繪製）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">整列留白＝該階沿用舊版程式畫法（退回機制）；想換特效就在 VFX 編輯器另存新檔名再填進來，不必改程式。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -174,6 +174,16 @@
           <t xml:space="preserve">對前方敵人造成 {count} 次 {pct}% 物理傷害</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-thrust-lance</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -345,6 +355,16 @@
           <t xml:space="preserve">每次能進行 {count} 道平行貫穿突刺，且突刺範圍提升 {range}%</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-thrust-lance</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -402,6 +422,11 @@
           <t xml:space="preserve">突刺造成的傷害有 {pct}% 會擴散至周圍的 {count} 個敵人</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -459,6 +484,16 @@
           <t xml:space="preserve">突刺會造成一直線的傷害，貫穿路徑上所有敵人，貫穿長度在原本長度上再增加 {m} 米</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-thrust-lance</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -516,6 +551,16 @@
           <t xml:space="preserve">向八個方向同時進行 {count} 次突刺，且造成傷害額外 +{pct}%</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-thrust-lance</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -685,6 +730,16 @@
           <t xml:space="preserve">對範圍內的所有敵人造成 1 次 {pct}% 物理傷害</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-cleave-arc</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -945,6 +1000,16 @@
           <t xml:space="preserve">斬擊會向前飛出 {m} 米距離，命中路徑上的敵人</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-cleave-arc</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -997,6 +1062,16 @@
           <t xml:space="preserve">同時朝前後左右四個方向各使出 {times} 次斬擊，且傷害額外 +{pct}%（每級 +5% 傷害；與原有傷害乘法計算）</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-cleave-sector</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1070,6 +1145,11 @@
           <t xml:space="preserve">迴旋斬每命中 1 次，就在該敵人所在位置生成一道龍捲風：對半徑 {m} 米內的敵人造成 {hits} 段、每段 {pct}% 風系傷害</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-tornado-wind</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t xml:space="preserve">windChaser</t>
@@ -1166,6 +1246,16 @@
           <t xml:space="preserve">朝前方 {deg} 度扇形內丟出 {count} 把飛刀，每把造成 {pct}% 物理傷害</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-knife</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1270,6 +1360,16 @@
           <t xml:space="preserve">每把飛刀會在範圍20米內的 {count} 個敵人間彈跳，每次彈射造成 {pct}% 技能傷害</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-knife</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1590,6 +1690,16 @@
           <t xml:space="preserve">每次施放飛刀時額外射出 1 支無限飛刀，追擊周圍 {m} 米內的任意敵人：傷害提高 {pct}%，彈射次數不受限制；只有一個目標時會貫穿後繞回再次攻擊，不會停留原地重複傷害</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-knife-gold</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t xml:space="preserve">soulhunterBlade</t>
@@ -1647,6 +1757,16 @@
           <t xml:space="preserve">對敵人造成連續 {hits} 次 {pct}% 物理傷害（同一目標）</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-gale-sector</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1993,6 +2113,11 @@
           <t xml:space="preserve">疾風斬的最後一斬會對你周圍 {m} 米內的敵人造成「單段傷害 × 連擊數 × {mult}」的傷害</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t xml:space="preserve">thunderFlash</t>
@@ -2032,6 +2157,16 @@
           <t xml:space="preserve">疾風斬附加雷電：每次斬擊命中時降下 1 道落雷，對命中處周圍 {m} 米內的敵人造成 {pct}% 閃電傷害</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bolt-sky-purple</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-thunder-purple</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t xml:space="preserve">thunderGodSlash</t>
@@ -2128,6 +2263,16 @@
           <t xml:space="preserve">對敵人造成 1 次 {pct}% 物理傷害，並附加流血：每 {dotGap} 秒造成技能傷害 {dotPct}% 的傷害，持續 {dotSec} 秒</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-bloodblade</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-bleed</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2180,6 +2325,16 @@
           <t xml:space="preserve">流血持續時間 +{sec} 秒，且流血作用間隔縮短 {gapPct}%（跳得更快、總傷更高）</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curse-bleed</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-bleed</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2284,6 +2439,16 @@
           <t xml:space="preserve">敵人流血的同時也會中毒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的毒屬性傷害，持續 {dotSec} 秒</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curse-poison</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-poison</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2336,6 +2501,16 @@
           <t xml:space="preserve">血毒刃的毒在每次作用時，有 {chance}% 機率傳染給附近的 {count} 個敵人</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-poison-drop</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-poison</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2388,6 +2563,16 @@
           <t xml:space="preserve">流血或中毒狀態的敵人死亡時爆炸，對附近 {count} 個敵人造成 {pct}% 技能傷害並傳染中毒</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-blood</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-bleed</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2440,6 +2625,16 @@
           <t xml:space="preserve">流血或中毒狀態在每次作用時有 {chance}% 機率立即造成剩餘的持續傷害；作用結束後將流血及中毒傳染給 {m} 米內的隨機 {count} 個敵人，且流血與中毒傷害 +{pct}%</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-zero-infection</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-poison</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2474,6 +2669,11 @@
           <t xml:space="preserve">永久展開 {m} 米的殺神領域：領域內的敵人死亡時堆疊【殺神】，每層使你造成的傷害 +{pct}%，同時回復 {healPct}% 最大生命；最多 {maxStacks} 層，持續 {dur} 秒</t>
         </is>
       </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-mire</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t xml:space="preserve">slayerDomain</t>
@@ -2513,6 +2713,21 @@
           <t xml:space="preserve">永久展開 {m} 米的萬毒領域：領域內的敵人每 {gap} 秒受到 {pct}% 中毒傷害，該中毒持續 {dur} 秒且可堆疊至 {maxStacks} 層</t>
         </is>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">curse-poison</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-poison</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-mire-poison</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t xml:space="preserve">venomDomain</t>
@@ -2552,6 +2767,16 @@
           <t xml:space="preserve">中毒與流血不再有持續時間，塗上的當下就結算完整傷害；結算後爆炸，對周圍 {m} 米內的敵人造成該效果 {pct}% 的傷害</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-blood</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-bleed</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t xml:space="preserve">disintegrate</t>
@@ -2609,6 +2834,16 @@
           <t xml:space="preserve">對附近 {count} 個敵人各造成 1 次 {pct}% 物理傷害（只有 1 個敵人時全部打向同一目標）</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-dual</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2921,6 +3156,21 @@
           <t xml:space="preserve">化身暴風在敵人間穿梭 {sec} 秒：每 {gap} 秒自動施放 1 次雙刀亂舞；期間無法普攻但可施放技能</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-dual</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-cyclone-avatar</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3090,6 +3340,16 @@
           <t xml:space="preserve">被動：受到傷害時有 {chance}% 機率對攻擊者反擊，造成 {pct}% 普攻傷害</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-phys</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3298,6 +3558,11 @@
           <t xml:space="preserve">格擋時有 {chance}% 機率造成破甲：防禦 -{def}%，持續 {sec} 秒，最多疊 {max} 層（疊層時重置時間）</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-earth</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3436,6 +3701,16 @@
           <t xml:space="preserve">每 {count} 次反擊後朝目標射出一顆光彈，對其周圍 {m} 米內的敵人造成 {pct}% 神聖傷害</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-holy</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-light</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t xml:space="preserve">holyBody</t>
@@ -3475,6 +3750,21 @@
           <t xml:space="preserve">死亡時對 {m} 米內的所有敵人造成 {pct}% 地系傷害，並在 {sec} 秒後原地復活繼續戰鬥（不算戰鬥失敗）；冷卻 {cd} 秒</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-earth</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-earth</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aura-rock-armor</t>
+        </is>
+      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t xml:space="preserve">indomitable</t>
@@ -3571,6 +3861,11 @@
           <t xml:space="preserve">攻速額外 +{pct}%（乘算，不受攻速上限限制），持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aura-bloodrage</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3995,6 +4290,11 @@
           <t xml:space="preserve">每 {gap} 秒，你造成的所有傷害 +{pct}%，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aura-bloodrage</t>
+        </is>
+      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t xml:space="preserve">asuraFist</t>
@@ -4062,6 +4362,26 @@
           <t xml:space="preserve">射出一顆火球（射程 {castM} 米），命中時爆炸，對目標及 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast-magic</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-fire</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-fireball</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4124,6 +4444,11 @@
           <t xml:space="preserve">被火球擊中的敵人陷入燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st-tick-fire</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4186,6 +4511,21 @@
           <t xml:space="preserve">火球爆炸後分裂出 {count} 個小火球，射向目標 {m} 米內的敵人，每個造成原始火球 {pct}% 的傷害</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-fire</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-fireball</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire-explosion</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4310,6 +4650,16 @@
           <t xml:space="preserve">燃燒結束或敵人死亡時爆炸，對我方 {m} 米內的 {count} 個敵人造成該敵人整段燃燒累積傷害 {pct}% 的傷害</t>
         </is>
       </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-fire</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4434,6 +4784,26 @@
           <t xml:space="preserve">改為召喚 {count} 顆巨大火殞石從天而降（射程 {castM} 米），每顆對目標 {m} 米內的敵人造成 {pct}% 火焰傷害，且殞石造成的燃燒傷害為 2 倍（第 2~6 階效果仍然生效）</t>
         </is>
       </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-fire-shockwave</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-meteor</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire-explosion</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mark-red</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4507,6 +4877,26 @@
           <t xml:space="preserve">每 {gap} 秒，天空落下一顆超巨型殞石：普通敵人 -{normal}% 生命、菁英 -{elite}% 生命、BOSS -{boss}% 生命</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-fire-shockwave</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-starfall</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-starfall-shadow</t>
+        </is>
+      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t xml:space="preserve">starfallCataclysm</t>
@@ -4546,6 +4936,16 @@
           <t xml:space="preserve">殞石數量 +{count} 顆，且每顆殞石落下時伴隨 {balls} 顆火球一同落下；火球與殞石造成的傷害 +{pct}%</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-fireball</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire-explosion</t>
+        </is>
+      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t xml:space="preserve">phoenixPrairie</t>
@@ -4613,6 +5013,16 @@
           <t xml:space="preserve">在敵人腳下召喚一道火柱（射程 {castM} 米），對目標 {m} 米內的敵人連續造成 {hits} 段傷害，每段 {pct}% 火焰傷害（全程約 {sec} 秒）</t>
         </is>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-tornado-fire</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4861,6 +5271,16 @@
           <t xml:space="preserve">火龍捲或火牆消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
         </is>
       </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-fire-shockwave</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4985,6 +5405,16 @@
           <t xml:space="preserve">改為施放 {count} 道火牆（橫向 {len}×{wid} 米），每道造成 {hits} 段 {pct}% 火焰傷害；每道火牆消失後再召喚 1 道（僅能再觸發一次；第 2~6 階效果仍然生效）</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-firewall</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5058,6 +5488,11 @@
           <t xml:space="preserve">火龍捲會在附近 {m} 米內隨機游走，並在移動軌跡上留下火池：每 {gap} 秒造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-mire-lava</t>
+        </is>
+      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t xml:space="preserve">eternalInferno</t>
@@ -5169,6 +5604,26 @@
           <t xml:space="preserve">召喚 {count} 團火狩環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-fire</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb-firehunt</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire-explosion</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-orbit-ring-fire</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5683,6 +6138,21 @@
           <t xml:space="preserve">你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {mps} 米／秒貫穿飛行 {flyM} 米</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-firehunt-ring</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-domain-fire</t>
+        </is>
+      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t xml:space="preserve">fireGodDescend</t>
@@ -5750,6 +6220,11 @@
           <t xml:space="preserve">施放岩甲強化自身，獲得最大生命值 {pct}% 的岩甲護盾，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aura-rock-armor</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5874,6 +6349,11 @@
           <t xml:space="preserve">岩甲護盾存在期間，攻擊你的敵人會遭受你最大生命值 {pct}% 的地系傷害（獨立於反震，兩者各自結算）</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-earth</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6156,6 +6636,21 @@
           <t xml:space="preserve">施放時將巨岩之力壓縮到極致，使 {m} 米內的敵人石化 {sec} 秒：無法行動，且受到的土系傷害額外 +{pct}%</t>
         </is>
       </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-rock-petrify</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-earth</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-domain-earth</t>
+        </is>
+      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t xml:space="preserve">superRockArt</t>
@@ -6234,6 +6729,21 @@
           <t xml:space="preserve">施放岩甲術時同時扭曲 {m} 米內的重力場，使敵人僵化（移動、攻速與傷害 -{stiff}%，持續 {stiffSec} 秒）；岩甲護盾存在期間你的土系傷害額外 +{pct}%</t>
         </is>
       </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-gravity</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-earth</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-domain-earth</t>
+        </is>
+      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t xml:space="preserve">gravityField</t>
@@ -6306,6 +6816,11 @@
           <t xml:space="preserve">在敵人腳下召喚一片 12×12 米的沼澤（射程 {castM} 米），沼澤中的敵人陷入緩速（移動速度 -{move}%、攻速 -{aspd}%），持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-mire</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6440,6 +6955,11 @@
           <t xml:space="preserve">沼澤持續放出毒氣：沼澤中的敵人每 {dotGap} 秒受到魔法攻擊 {dotPct}% 的毒性傷害</t>
         </is>
       </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-mire-poison</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6708,6 +7228,11 @@
           <t xml:space="preserve">沼澤轉變為岩漿：持續時間提高至 {sec} 秒、範圍再擴增 {pct}%（與第 5 階累加），其中的目標每 {dotGap} 秒額外受到魔法攻擊 {dotPct}% 的火焰傷害</t>
         </is>
       </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-mire-lava</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6781,6 +7306,16 @@
           <t xml:space="preserve">熔岩沼每 {gap} 秒對範圍內的敵人噴出 1 道火龍捲（半徑 {m} 米、{hits} 段、每段 {pct}% 火焰傷害），並將命中的敵人屬性改變為火屬性，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-tornado-fire</t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t xml:space="preserve">abyssInferno</t>
@@ -7197,6 +7732,16 @@
           <t xml:space="preserve">你每消耗 1% 生命或護盾，{m} 米內的 {count} 個敵人同步損失 {pct}% 最大生命</t>
         </is>
       </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beam-light</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-light</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7259,6 +7804,16 @@
           <t xml:space="preserve">死亡時原地復活並回復 {pct}% 生命，復活後 {sec} 秒無敵；此招自身冷卻 {cd} 秒（顯示於技能格）</t>
         </is>
       </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pillar-light</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-light</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7332,6 +7887,16 @@
           <t xml:space="preserve">被你殺死的普通與菁英敵人有 {chance}% 機率（上限 100%）以 {hp}% 生命重生（同一個敵人只會重生一次）</t>
         </is>
       </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pillar-earth</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-earth</t>
+        </is>
+      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t xml:space="preserve">worldRebirth</t>
@@ -7438,6 +8003,21 @@
           <t xml:space="preserve">丟出一道閃電鏈（射程 {castM} 米），在最多 {count} 個目標間彈射（每段彈射範圍 {m} 米），每擊造成 {pct}% 雷電傷害</t>
         </is>
       </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast-magic</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bolt-chain-lightning</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7686,6 +8266,11 @@
           <t xml:space="preserve">閃電鏈每次彈射時，額外對 {m} 米內的 {count} 個敵人造成閃電鏈 {pct}% 的雷電傷害</t>
         </is>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7748,6 +8333,11 @@
           <t xml:space="preserve">閃電鏈傷害額外 +{pct}% 雷電傷害；沒有其它彈射目標時可用自身當中繼點繼續彈射（彈到自身不消耗彈射數）</t>
         </is>
       </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aura-lightning-relay</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7883,6 +8473,21 @@
           <t xml:space="preserve">額外射出 1 道無限彈射的閃電鏈：在自身與 {m} 米內的任意敵人之間往返彈射，每經過自身 1 次使你的雷電傷害 +{pct}%，最多 {maxStacks} 層（持續到你死亡為止）</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bolt-chain-lightning</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aura-lightning-relay</t>
+        </is>
+      </c>
       <c r="U150" t="inlineStr">
         <is>
           <t xml:space="preserve">eternalSuperconductor</t>
@@ -7922,6 +8527,16 @@
           <t xml:space="preserve">施放後每 {gap} 秒放出 {count} 道閃電，分別打向 {m} 米內最遠的 {count} 個敵人，各對命中處 {r} 米內的所有敵人造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bolt-chain-lightning</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t xml:space="preserve">flyingThunderGod</t>
@@ -7989,6 +8604,21 @@
           <t xml:space="preserve">對 {castM} 米內的 {count} 個目標降下落雷（每道間隔 {gap} 秒），每道造成 {pct}% 雷電傷害</t>
         </is>
       </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast-magic</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bolt-sky-purple</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-thunder-purple</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8395,6 +9025,16 @@
           <t xml:space="preserve">施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{mps} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
         </is>
       </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bolt-curtain-lightning</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-thunder-curtain</t>
+        </is>
+      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t xml:space="preserve">thunderMatrix</t>
@@ -8434,6 +9074,16 @@
           <t xml:space="preserve">額外召喚 1 道永久持續的天劫雷電：每 {gap} 秒追擊 {m} 米內生命值最低的敵人，造成 {pct}% 雷電傷害</t>
         </is>
       </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bolt-sky-purple</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-thunder-purple</t>
+        </is>
+      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t xml:space="preserve">heavenTribulation</t>
@@ -8545,6 +9195,21 @@
           <t xml:space="preserve">召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
         </is>
       </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast-magic</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-thunder-orb</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8746,6 +9411,21 @@
           <t xml:space="preserve">額外召喚 {count} 個電球環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb-thunder</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-orbit-ring-lightning</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8880,6 +9560,16 @@
           <t xml:space="preserve">環體電球命中時有 {chance}% 機率在該處生成一個靜止雷球，持續 {sec} 秒（每次作用只判定一次機率）</t>
         </is>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-thunder-orb</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8947,6 +9637,26 @@
           <t xml:space="preserve">額外召喚 {count} 個巨大雷球從天而降，各對 {m} 米內的敵人造成 {pct}% 雷電傷害，並以衝擊波擊暈 {sec} 秒</t>
         </is>
       </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-fire-shockwave</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-thunder-orb-fall</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mark-blue</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9020,6 +9730,11 @@
           <t xml:space="preserve">每次被雷球命中的敵人有 {chance}% 機率觸發 1 顆小型雷球，在附近 {m} 米範圍內彈射 {bounces} 次，每次造成 {pct}% 雷電傷害</t>
         </is>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-lightning</t>
+        </is>
+      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t xml:space="preserve">thunderBurst</t>
@@ -9126,6 +9841,21 @@
           <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast-magic</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-ice-shard</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9188,6 +9918,11 @@
           <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
         </is>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st-tick-ice</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9312,6 +10047,16 @@
           <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
         </is>
       </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-ice-shard</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9374,6 +10119,11 @@
           <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-homing-ice-shard</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9498,6 +10248,16 @@
           <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-ice-blast</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9610,6 +10370,16 @@
           <t xml:space="preserve">施放寒冰箭時同時召喚 {waves} 波寒冰箭雨從天射下（每波間隔 {gap} 秒），每波對我方 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-ice-shard</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t xml:space="preserve">tearsOfIce</t>
@@ -9677,6 +10447,21 @@
           <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast-magic</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-waterball</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9863,6 +10648,21 @@
           <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-frost-nova</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-waterball</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9925,6 +10725,16 @@
           <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
         </is>
       </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-ice-shard</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10049,6 +10859,11 @@
           <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
         </is>
       </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-tornado-water</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10083,6 +10898,11 @@
           <t xml:space="preserve">施放水流彈時在周圍 {m} 米圍起一圈水牢獄：擋下由圈外射進來的遠程攻擊，圈內的敵人攻擊力 -{atkRed}%、受到的傷害 +{vuln}%，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-domain-ice</t>
+        </is>
+      </c>
       <c r="U189" t="inlineStr">
         <is>
           <t xml:space="preserve">waterPrisonFall</t>
@@ -10122,6 +10942,11 @@
           <t xml:space="preserve">場上同時有 {need} 道水龍捲時，在它們的中央再生成 1 道巨大水龍捲，對 {m} 米內的所有敵人造成連續 {hits} 段 {pct}% 寒冰傷害</t>
         </is>
       </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-tornado-water</t>
+        </is>
+      </c>
       <c r="U190" t="inlineStr">
         <is>
           <t xml:space="preserve">ragingTide</t>
@@ -10161,6 +10986,16 @@
           <t xml:space="preserve">在周圍 {m} 米展開一道永久的水之領域：每 {gap} 秒對領域內的敵人施加寒霜狀態，且領域內的敵人可額外再疊 {stacks} 層寒霜</t>
         </is>
       </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st-tick-ice</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-domain-ice</t>
+        </is>
+      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t xml:space="preserve">abyssBurial</t>
@@ -10228,6 +11063,21 @@
           <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
         </is>
       </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast-magic</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-frost-nova</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10352,6 +11202,11 @@
           <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
         </is>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10414,6 +11269,16 @@
           <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
         </is>
       </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-frost-freeze</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10600,6 +11465,11 @@
           <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-blizzard</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10673,6 +11543,16 @@
           <t xml:space="preserve">凍結中的敵人形成冰晶共鳴：每 {gap} 秒對相距 {m} 米內的其他凍結敵人造成 {pct}% 寒冰傷害</t>
         </is>
       </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-ice-shard</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-ice</t>
+        </is>
+      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t xml:space="preserve">crystalResonance</t>
@@ -10712,6 +11592,11 @@
           <t xml:space="preserve">暴風雪的範圍擴大 {scale}%，且每 {gap} 秒在範圍內隨機 {min}～{max} 個目標的地面昇起冰錐，每根冰錐對周圍 {m} 米內的敵人造成連續 {hits} 段 {pct}% 寒冰傷害</t>
         </is>
       </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-tornado-water</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t xml:space="preserve">iceKingDomain</t>
@@ -10784,6 +11669,21 @@
           <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
         </is>
       </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast-magic</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-wind-crescent</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10985,6 +11885,16 @@
           <t xml:space="preserve">風刃射出時同時朝其一側 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），造成原風刃 {pct}% 的傷害</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-wind-crescent</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11052,6 +11962,16 @@
           <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
         </is>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-homing-wind-crescent</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11119,6 +12039,16 @@
           <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
         </is>
       </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-wind</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11220,6 +12150,16 @@
           <t xml:space="preserve">大型風刃改為在 {chaseM} 米內持續追擊敵人 {sec} 秒，【暴風真空刃】每個方向再多射出 {add} 道風刃，且風刃傷害額外 +{pct}%</t>
         </is>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-homing-wind-crescent</t>
+        </is>
+      </c>
       <c r="U209" t="inlineStr">
         <is>
           <t xml:space="preserve">stormMyriad</t>
@@ -11259,6 +12199,16 @@
           <t xml:space="preserve">【暴風真空刃】改為把該次所有大型與小型風刃融合，朝 {directions} 個方向各射出 1 道體積 +{scale}% 的巨型風刃，每道傷害為所融合風刃總和的 {pct}%</t>
         </is>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-wind-crescent</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
       <c r="U210" t="inlineStr">
         <is>
           <t xml:space="preserve">stormMountain</t>
@@ -11365,6 +12315,21 @@
           <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
         </is>
       </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast-magic</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-wind-crescent</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11551,6 +12516,16 @@
           <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
         </is>
       </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-wind-spin</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11737,6 +12712,26 @@
           <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-wind</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb-void-disc</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-orbit-ring-wind</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11771,6 +12766,16 @@
           <t xml:space="preserve">真空斬命中時有 {chance}% 機率在該處留下一道靜止的真空斬：持續 {sec} 秒、半徑隨時間擴大為 {grow} 倍，對碰到的敵人造成 {pct}% 風系傷害</t>
         </is>
       </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-homing-wind-crescent</t>
+        </is>
+      </c>
       <c r="U219" t="inlineStr">
         <is>
           <t xml:space="preserve">vacuumOmen</t>
@@ -11916,6 +12921,11 @@
           <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-storm-barrier</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11978,6 +12988,16 @@
           <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
         </is>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-storm-rip</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12040,6 +13060,11 @@
           <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12102,6 +13127,16 @@
           <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
         </is>
       </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-wind-crescent</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12164,6 +13199,16 @@
           <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-wind-crescent</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12288,6 +13333,11 @@
           <t xml:space="preserve">施放暴風屏障時同時召喚風暴之神附體：{sec} 秒內傷害減免 +{red}%，且自身的風系傷害額外 ×(1+{pct}%)</t>
         </is>
       </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-storm-god</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12361,6 +13411,26 @@
           <t xml:space="preserve">每 {gap} 秒從天上落下 {min}～{max} 個召喚星體（巨大風刃／雷殞石／火殞石隨機，不足 1 個的部分以機率觸發），每個對落點 {m} 米內的敵人造成 {pct}% 傷害</t>
         </is>
       </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-fire-shockwave</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proj-meteor</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-fire-explosion</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mark-red</t>
+        </is>
+      </c>
       <c r="U230" t="inlineStr">
         <is>
           <t xml:space="preserve">skyfallStars</t>
@@ -12398,6 +13468,21 @@
       <c r="O231" t="inlineStr">
         <is>
           <t xml:space="preserve">施放暴風屏障時同時打出【暴風真空刃】與【虛空斬】，且這兩者的傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb-void-disc</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-wind</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground-orbit-ring-wind</t>
         </is>
       </c>
       <c r="U231" t="inlineStr">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -298,6 +298,16 @@
           <t xml:space="preserve">進一步強化突刺傷害，額外 +{pct}% 物理傷害（與第 1 階累加）</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-thrust-empowered</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hit-phys</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -357,7 +367,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">slash-thrust-lance</t>
+          <t xml:space="preserve">slash-thrust-empowered</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -422,6 +432,11 @@
           <t xml:space="preserve">突刺造成的傷害有 {pct}% 會擴散至周圍的 {count} 個敵人</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-thrust-scatter</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t xml:space="preserve">hit-phys</t>
@@ -486,7 +501,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">slash-thrust-lance</t>
+          <t xml:space="preserve">slash-thrust-scatter</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -553,7 +568,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">slash-thrust-lance</t>
+          <t xml:space="preserve">slash-thrust-scatter</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -13468,6 +13483,11 @@
       <c r="O231" t="inlineStr">
         <is>
           <t xml:space="preserve">施放暴風屏障時同時打出【暴風真空刃】與【虛空斬】，且這兩者的傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burst-wind</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -963,6 +963,11 @@
           <t xml:space="preserve">斬擊時有 {chance}% 機率擊暈敵人 {sec} 秒</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-cleave-stun</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1017,7 +1022,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">slash-cleave-arc</t>
+          <t xml:space="preserve">slash-cleave-stun</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1079,7 +1084,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">slash-cleave-sector</t>
+          <t xml:space="preserve">slash-cleave-stun</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">slash-gale-sector</t>
+          <t xml:space="preserve">hit-gale-burst</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -2097,6 +2097,11 @@
       <c r="O38" t="inlineStr">
         <is>
           <t xml:space="preserve">疾風斬的傷害由目標周圍 {m} 米內的所有敵人均分，且傷害額外 +{pct}%</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slash-gale-moon</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -1763,7 +1763,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":20,"hits":3}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":20,"hits":3,"castM":5,"gap":0.2}</t>
         </is>
       </c>
       <c r="M32">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":300,"pctPer":30,"m":5}</t>
+          <t xml:space="preserve">{"pct":300,"pctPer":30,"m":5,"castM":5}</t>
         </is>
       </c>
       <c r="M38">
@@ -13814,47 +13814,53 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">疾風斬調整：第 1 階 castM＝起手施放距離（米），gap＝每段攻擊間隔（秒，傷害／特效同步）；</t>
+        </is>
+      </c>
+    </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">解鎖轉生/等級</t>
+          <t xml:space="preserve">　　　　　　第 4 階 m＝以主目標為中心的擴散搜尋半徑（米）；第 7 階 m＝月牙傷害半徑（米），特效同步等比縮放；</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">用途：這一階要達到什麼進度才能投資；格式「轉生次數|等級」，例如 0|100 ＝ 0 轉 100 級解鎖；</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注意：留白＝無門檻；未解鎖的階一律視為 Lv.0（含第 1 階的預設開啟），已投入的等級留在存檔裡，</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">　　　　　　月牙使用第 7 階 castM，可與第 1 階獨立調整。range 欄不控制疾風斬／月牙斬；</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　達到門檻就原樣回來；</t>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
+          <t xml:space="preserve">解鎖轉生/等級</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用途：這一階要達到什麼進度才能投資；格式「轉生次數|等級」，例如 0|100 ＝ 0 轉 100 級解鎖；</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">升級金幣基數 / 升級金幣倍率</t>
+          <t xml:space="preserve">注意：留白＝無門檻；未解鎖的階一律視為 Lv.0（含第 1 階的預設開啟），已投入的等級留在存檔裡，</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">升到下一級費用＝基數 × 倍率^目前等級（取整）；</t>
+          <t xml:space="preserve">　　　達到門檻就原樣回來；</t>
         </is>
       </c>
     </row>
@@ -13862,14 +13868,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果說明模板</t>
+          <t xml:space="preserve">升級金幣基數 / 升級金幣倍率</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">遊戲內顯示的說明文字；{鍵} 會代入目前等級的計算值（鍵名同「效果參數(JSON)」）。</t>
+          <t xml:space="preserve">升到下一級費用＝基數 × 倍率^目前等級（取整）；</t>
         </is>
       </c>
     </row>
@@ -13877,54 +13883,69 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放特效 / 攻擊特效 / 飛行子彈 / 受擊特效 / 地板特效（2026-09-03 VFX Preset 化）</t>
+          <t xml:space="preserve">效果說明模板</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">每一格填 VFX 編輯器存出來的 Preset 檔名（vfx/presets/&lt;檔名&gt;.json，不含 .json；含 .json 也接受）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">每一列＝該階（或該超神選項）「引入」的特效：第 1 階那一列是技能本體，後面各階只填那一階新增的畫面</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">遊戲內顯示的說明文字；{鍵} 會代入目前等級的計算值（鍵名同「效果參數(JSON)」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　（例：火球術第 1 階＝火球＋受擊、第 3 階火球爆裂＝小火球＋大爆炸、第 7 階殞石術＝隕石＋落點預警）；</t>
+          <t xml:space="preserve">施放特效 / 攻擊特效 / 飛行子彈 / 受擊特效 / 地板特效（2026-09-03 VFX Preset 化）</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">程式在送出特效時會標明「這一發屬於第幾階」，然後讀那一列的格子；同一階沒填的角色就沒有那一段畫面；</t>
+          <t xml:space="preserve">每一格填 VFX 編輯器存出來的 Preset 檔名（vfx/presets/&lt;檔名&gt;.json，不含 .json；含 .json 也接受）；</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">施放特效＝角色身上；攻擊特效＝攻擊本體（斬弧／爆發／光束／雷柱／護罩）；飛行子彈＝會移動的東西（含環繞體）；</t>
+          <t xml:space="preserve">每一列＝該階（或該超神選項）「引入」的特效：第 1 階那一列是技能本體，後面各階只填那一階新增的畫面</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">受擊特效＝命中爆點；地板特效＝持續場域（泥沼、火牆、軌道環、預警圈），依實際判定範圍自動縮放（Preset 以半徑 100px、矩形 200×100px 繪製）；</t>
+          <t xml:space="preserve">　　（例：火球術第 1 階＝火球＋受擊、第 3 階火球爆裂＝小火球＋大爆炸、第 7 階殞石術＝隕石＋落點預警）；</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">程式在送出特效時會標明「這一發屬於第幾階」，然後讀那一列的格子；同一階沒填的角色就沒有那一段畫面；</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放特效＝角色身上；攻擊特效＝攻擊本體（斬弧／爆發／光束／雷柱／護罩）；飛行子彈＝會移動的東西（含環繞體）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受擊特效＝命中爆點；地板特效＝持續場域（泥沼、火牆、軌道環、預警圈），依實際判定範圍自動縮放（Preset 以半徑 100px、矩形 200×100px 繪製）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t xml:space="preserve">整列留白＝該階沿用舊版程式畫法（退回機制）；想換特效就在 VFX 編輯器另存新檔名再填進來，不必改程式。</t>
         </is>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -10,6 +10,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="55" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="55" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="20" max="20" width="15" customWidth="1"/>
+    <col min="21" max="21" width="15" customWidth="1"/>
+    <col min="22" max="22" width="34" customWidth="1"/>
+    <col min="23" max="23" width="34" customWidth="1"/>
+    <col min="24" max="24" width="34" customWidth="1"/>
+    <col min="25" max="25" width="34" customWidth="1"/>
+    <col min="26" max="26" width="34" customWidth="1"/>
+    <col min="27" max="27" width="34" customWidth="1"/>
+    <col min="28" max="28" width="34" customWidth="1"/>
+    <col min="29" max="29" width="34" customWidth="1"/>
+    <col min="30" max="30" width="34" customWidth="1"/>
+    <col min="31" max="31" width="34" customWidth="1"/>
+    <col min="32" max="32" width="34" customWidth="1"/>
+    <col min="33" max="33" width="34" customWidth="1"/>
+    <col min="34" max="34" width="90" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -117,6 +153,71 @@
           <t xml:space="preserve">超神ID</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放距離（米）</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放距離每級增加（米）</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作用距離（米；用途見說明）</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作用距離每級增加（米）</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每段或每跳間隔（秒）</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">間隔每級增減（秒）</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矩形長度（米）</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矩形長度每級增加（米）</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矩形寬度（米）</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矩形寬度每級增加（米）</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">扇形角度（度）</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">角度每級增減（度）</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作用方式與距離用途（唯讀說明）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -184,6 +285,11 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對前方敵人造成 {count} 次 {pct}% 物理傷害</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -241,6 +347,11 @@
           <t xml:space="preserve">有 {chance}% 的機率再次進行 {count} 次突刺</t>
         </is>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有 {chance}% 的機率再次進行 {count} 次突刺</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -308,6 +419,11 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進一步強化突刺傷害，額外 +{pct}% 物理傷害（與第 1 階累加）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -375,6 +491,11 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次能進行 {count} 道平行貫穿突刺，且突刺範圍提升 {range}%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -442,6 +563,11 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">突刺造成的傷害有 {pct}% 會擴散至周圍的 {count} 個敵人</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -485,7 +611,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":5,"mPer":0.5}</t>
+          <t xml:space="preserve">{}</t>
         </is>
       </c>
       <c r="M7">
@@ -509,6 +635,17 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="X7">
+        <v>5</v>
+      </c>
+      <c r="Y7">
+        <v>0.5</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">突刺會造成一直線的傷害，貫穿路徑上所有敵人，貫穿長度在原本長度上再增加 {m} 米</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -576,6 +713,11 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">向八個方向同時進行 {count} 次突刺，且造成傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -596,7 +738,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":6,"mPer":0.6,"dodge":30,"sec":2}</t>
+          <t xml:space="preserve">{"dodge":30,"sec":2}</t>
         </is>
       </c>
       <c r="M9">
@@ -615,6 +757,17 @@
           <t xml:space="preserve">phantomOcta</t>
         </is>
       </c>
+      <c r="X9">
+        <v>6</v>
+      </c>
+      <c r="Y9">
+        <v>0.6</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">突刺命中時，傷害同時擴散至該敵人周圍 {m} 米內的所有敵人；施放突刺後 {sec} 秒內，你有 {dodge}% 機率絕對閃避敵方攻擊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -654,6 +807,11 @@
           <t xml:space="preserve">shadowExecutioner</t>
         </is>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">突刺命中時堆疊【靈魂撕裂】：每層使該敵人受到的傷害提高 {perStack}%，最多 {maxStacks} 層（疊滿＝+{pct}%）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -693,6 +851,11 @@
           <t xml:space="preserve">oneStrikeKill</t>
         </is>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【八方連刺】改為朝前方的 1 道突刺，但傷害改為 {mult} 倍，且可以立即殺死普通敵人</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -755,6 +918,11 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對範圍內的所有敵人造成 1 次 {pct}% 物理傷害</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -807,6 +975,11 @@
           <t xml:space="preserve">斬擊範圍擴大 {range}%（每級 +1.5% 範圍）</t>
         </is>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">斬擊範圍擴大 {range}%（每級 +1.5% 範圍）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -859,6 +1032,11 @@
           <t xml:space="preserve">進一步強化斬擊傷害，額外 +{pct}% 物理傷害</t>
         </is>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進一步強化斬擊傷害，額外 +{pct}% 物理傷害</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -911,6 +1089,11 @@
           <t xml:space="preserve">斬擊時有 {chance}% 機率連續劈出共 {times} 次斬擊（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">斬擊時有 {chance}% 機率連續劈出共 {times} 次斬擊（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -968,6 +1151,11 @@
           <t xml:space="preserve">slash-cleave-stun</t>
         </is>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">斬擊時有 {chance}% 機率擊暈敵人 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1006,7 +1194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":12,"mPer":0.5}</t>
+          <t xml:space="preserve">{}</t>
         </is>
       </c>
       <c r="M17">
@@ -1030,6 +1218,17 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="X17">
+        <v>12</v>
+      </c>
+      <c r="Y17">
+        <v>0.5</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">斬擊會向前飛出 {m} 米距離，命中路徑上的敵人</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1092,6 +1291,11 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同時朝前後左右四個方向各使出 {times} 次斬擊，且傷害額外 +{pct}%（每級 +5% 傷害；與原有傷害乘法計算）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1131,6 +1335,11 @@
           <t xml:space="preserve">voidShatter</t>
         </is>
       </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【迴身四方斬】的攻擊次數 +{times} 次，且物理傷害再額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1151,7 +1360,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"hits":4,"hitsPer":0.4,"pct":100,"pctPer":10,"m":4,"gap":0.4}</t>
+          <t xml:space="preserve">{"hits":4,"hitsPer":0.4,"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M20">
@@ -1175,6 +1384,17 @@
           <t xml:space="preserve">windChaser</t>
         </is>
       </c>
+      <c r="X20">
+        <v>4</v>
+      </c>
+      <c r="Z20">
+        <v>0.4</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迴旋斬每命中 1 次，就在該敵人所在位置生成一道龍捲風：對半徑 {m} 米內的敵人造成 {hits} 段、每段 {pct}% 風系傷害</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1214,6 +1434,11 @@
           <t xml:space="preserve">stormGodSlash</t>
         </is>
       </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迴旋斬範圍擴大 {range}%，並改為被動技能：不再主動施放，改為每 {sec} 秒自動施放 1 次（每級施放間隔 -0.5 秒，仍需裝配在技能列才生效）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1252,7 +1477,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":3,"deg":60}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":3}</t>
         </is>
       </c>
       <c r="M22">
@@ -1276,6 +1501,14 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AF22">
+        <v>60</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">朝前方 {deg} 度扇形內丟出 {count} 把飛刀，每把造成 {pct}% 物理傷害</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1328,6 +1561,11 @@
           <t xml:space="preserve">飛刀傷害進一步提升，額外 +{pct}% 物理傷害</t>
         </is>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">飛刀傷害進一步提升，額外 +{pct}% 物理傷害</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1366,7 +1604,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":5,"count":1,"m":20}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":5,"count":1}</t>
         </is>
       </c>
       <c r="M24">
@@ -1390,6 +1628,14 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="X24">
+        <v>20</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每把飛刀會在範圍20米內的 {count} 個敵人間彈跳，每次彈射造成 {pct}% 技能傷害</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1442,6 +1688,11 @@
           <t xml:space="preserve">飛刀彈射的敵人數量額外 +{add}（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">飛刀彈射的敵人數量額外 +{add}（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1494,6 +1745,11 @@
           <t xml:space="preserve">改為向周圍的 {count} 個敵人丟出飛刀（全圓形範圍鎖敵；不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改為向周圍的 {count} 個敵人丟出飛刀（全圓形範圍鎖敵；不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1546,6 +1802,11 @@
           <t xml:space="preserve">飛刀彈射後有 {chance}% 機率再次彈射，最多連續 {max} 次</t>
         </is>
       </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">飛刀彈射後有 {chance}% 機率再次彈射，最多連續 {max} 次</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1598,6 +1859,11 @@
           <t xml:space="preserve">每把飛刀（含彈射）爆擊時，使飛刀技能冷卻時間 -{sec} 秒</t>
         </is>
       </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每把飛刀（含彈射）爆擊時，使飛刀技能冷卻時間 -{sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1637,6 +1903,11 @@
           <t xml:space="preserve">petalStorm</t>
         </is>
       </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每把飛刀（含彈射）都會對飛行路徑上的所有敵人造成 {pct}% 技能傷害</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1676,6 +1947,11 @@
           <t xml:space="preserve">deathReaper</t>
         </is>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">飛刀殺死敵人時堆疊【死亡收割】：每層使你造成的傷害提高 {pct}%，最多 {maxStacks} 層，持續 {dur} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1696,7 +1972,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":45}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M31">
@@ -1725,6 +2001,14 @@
           <t xml:space="preserve">soulhunterBlade</t>
         </is>
       </c>
+      <c r="X31">
+        <v>45</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次施放飛刀時額外射出 1 支無限飛刀，追擊周圍 {m} 米內的任意敵人：傷害提高 {pct}%，彈射次數不受限制；只有一個目標時會貫穿後繞回再次攻擊，不會停留原地重複傷害</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1763,7 +2047,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":20,"hits":3,"castM":5,"gap":0.2}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":20,"hits":3}</t>
         </is>
       </c>
       <c r="M32">
@@ -1787,6 +2071,17 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="V32">
+        <v>5</v>
+      </c>
+      <c r="Z32">
+        <v>0.2</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對敵人造成連續 {hits} 次 {pct}% 物理傷害（同一目標）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1839,6 +2134,11 @@
           <t xml:space="preserve">斬擊次數額外 +{add}（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">斬擊次數額外 +{add}（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1891,6 +2191,11 @@
           <t xml:space="preserve">進一步強化斬擊傷害，額外 +{pct}% 物理傷害</t>
         </is>
       </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進一步強化斬擊傷害，額外 +{pct}% 物理傷害</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1929,7 +2234,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":10}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M35">
@@ -1943,6 +2248,14 @@
           <t xml:space="preserve">每次斬擊額外對 {m} 米內最近的 1 個敵人造成 {pct}% 技能傷害；附近沒有敵人時改對原目標造成</t>
         </is>
       </c>
+      <c r="X35">
+        <v>10</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次斬擊額外對 {m} 米內最近的 1 個敵人造成 {pct}% 技能傷害；附近沒有敵人時改對原目標造成</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1995,6 +2308,11 @@
           <t xml:space="preserve">施放疾風斬使你的攻速額外提高 {pct}%，持續 {sec} 秒（突破攻速上限，與自身攻速相乘）</t>
         </is>
       </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放疾風斬使你的攻速額外提高 {pct}%，持續 {sec} 秒（突破攻速上限，與自身攻速相乘）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2047,6 +2365,11 @@
           <t xml:space="preserve">疾風斬的冷卻時間 -{sec} 秒</t>
         </is>
       </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">疾風斬的冷卻時間 -{sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2085,7 +2408,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":300,"pctPer":30,"m":5,"castM":5}</t>
+          <t xml:space="preserve">{"pct":300,"pctPer":30}</t>
         </is>
       </c>
       <c r="M38">
@@ -2104,6 +2427,17 @@
           <t xml:space="preserve">slash-gale-moon</t>
         </is>
       </c>
+      <c r="V38">
+        <v>5</v>
+      </c>
+      <c r="X38">
+        <v>5</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">疾風斬的傷害由目標周圍 {m} 米內的所有敵人均分，且傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2124,7 +2458,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"mult":5,"multPer":0.5,"m":6}</t>
+          <t xml:space="preserve">{"mult":5,"multPer":0.5}</t>
         </is>
       </c>
       <c r="M39">
@@ -2148,6 +2482,14 @@
           <t xml:space="preserve">thunderFlash</t>
         </is>
       </c>
+      <c r="X39">
+        <v>6</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">疾風斬的最後一斬會對你周圍 {m} 米內的敵人造成「單段傷害 × 連擊數 × {mult}」的傷害</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2168,7 +2510,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"m":8}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20}</t>
         </is>
       </c>
       <c r="M40">
@@ -2197,6 +2539,14 @@
           <t xml:space="preserve">thunderGodSlash</t>
         </is>
       </c>
+      <c r="X40">
+        <v>8</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">疾風斬附加雷電：每次斬擊命中時降下 1 道落雷，對命中處周圍 {m} 米內的敵人造成 {pct}% 閃電傷害</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2236,6 +2586,11 @@
           <t xml:space="preserve">chidori</t>
         </is>
       </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【月牙斬】不再由範圍內的敵人均分傷害，改為每個敵人都受到完整傷害，且傷害再額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2298,6 +2653,11 @@
           <t xml:space="preserve">hit-bleed</t>
         </is>
       </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對敵人造成 1 次 {pct}% 物理傷害，並附加流血：每 {dotGap} 秒造成技能傷害 {dotPct}% 的傷害，持續 {dotSec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2360,6 +2720,11 @@
           <t xml:space="preserve">hit-bleed</t>
         </is>
       </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">流血持續時間 +{sec} 秒，且流血作用間隔縮短 {gapPct}%（跳得更快、總傷更高）</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2412,6 +2777,11 @@
           <t xml:space="preserve">流血中的敵人受到的傷害提高 {pct}%</t>
         </is>
       </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">流血中的敵人受到的傷害提高 {pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2474,6 +2844,11 @@
           <t xml:space="preserve">hit-poison</t>
         </is>
       </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">敵人流血的同時也會中毒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的毒屬性傷害，持續 {dotSec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2536,6 +2911,11 @@
           <t xml:space="preserve">hit-poison</t>
         </is>
       </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">血毒刃的毒在每次作用時，有 {chance}% 機率傳染給附近的 {count} 個敵人</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2598,6 +2978,11 @@
           <t xml:space="preserve">hit-bleed</t>
         </is>
       </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">流血或中毒狀態的敵人死亡時爆炸，對附近 {count} 個敵人造成 {pct}% 技能傷害並傳染中毒</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2636,7 +3021,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":20,"chancePer":2,"pct":40,"pctPer":4,"m":20,"count":1}</t>
+          <t xml:space="preserve">{"chance":20,"chancePer":2,"pct":40,"pctPer":4,"count":1}</t>
         </is>
       </c>
       <c r="M48">
@@ -2660,6 +3045,14 @@
           <t xml:space="preserve">hit-poison</t>
         </is>
       </c>
+      <c r="X48">
+        <v>20</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">流血或中毒狀態在每次作用時有 {chance}% 機率立即造成剩餘的持續傷害；作用結束後將流血及中毒傳染給 {m} 米內的隨機 {count} 個敵人，且流血與中毒傷害 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2680,7 +3073,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":2,"pctPer":0.2,"healPct":2,"healPctPer":0.2,"m":24,"dur":6,"maxStacks":100}</t>
+          <t xml:space="preserve">{"pct":2,"pctPer":0.2,"healPct":2,"healPctPer":0.2,"dur":6,"maxStacks":100}</t>
         </is>
       </c>
       <c r="M49">
@@ -2704,6 +3097,14 @@
           <t xml:space="preserve">slayerDomain</t>
         </is>
       </c>
+      <c r="X49">
+        <v>24</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">永久展開 {m} 米的殺神領域：領域內的敵人死亡時堆疊【殺神】，每層使你造成的傷害 +{pct}%，同時回復 {healPct}% 最大生命；最多 {maxStacks} 層，持續 {dur} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2724,7 +3125,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"m":24,"gap":0.5,"dur":6,"maxStacks":10}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"dur":6,"maxStacks":10}</t>
         </is>
       </c>
       <c r="M50">
@@ -2758,6 +3159,17 @@
           <t xml:space="preserve">venomDomain</t>
         </is>
       </c>
+      <c r="X50">
+        <v>24</v>
+      </c>
+      <c r="Z50">
+        <v>0.5</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">永久展開 {m} 米的萬毒領域：領域內的敵人每 {gap} 秒受到 {pct}% 中毒傷害，該中毒持續 {dur} 秒且可堆疊至 {maxStacks} 層</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2778,7 +3190,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":6}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M51">
@@ -2807,6 +3219,14 @@
           <t xml:space="preserve">disintegrate</t>
         </is>
       </c>
+      <c r="X51">
+        <v>6</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中毒與流血不再有持續時間，塗上的當下就結算完整傷害；結算後爆炸，對周圍 {m} 米內的敵人造成該效果 {pct}% 的傷害</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2869,6 +3289,11 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對附近 {count} 個敵人各造成 1 次 {pct}% 物理傷害（只有 1 個敵人時全部打向同一目標）</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2921,6 +3346,11 @@
           <t xml:space="preserve">額外攻擊附近 {add} 個敵人（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外攻擊附近 {add} 個敵人（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2973,6 +3403,11 @@
           <t xml:space="preserve">進一步強化雙刀傷害，額外 +{pct}% 物理傷害</t>
         </is>
       </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進一步強化雙刀傷害，額外 +{pct}% 物理傷害</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3025,6 +3460,11 @@
           <t xml:space="preserve">讓你的暴擊率 +{cr}%、連擊數 +{add}，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">讓你的暴擊率 +{cr}%、連擊數 +{add}，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3063,7 +3503,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":3.5,"pctPer":0.35,"sec":3,"gap":0.35,"m":5}</t>
+          <t xml:space="preserve">{"pct":3.5,"pctPer":0.35,"sec":3}</t>
         </is>
       </c>
       <c r="M56">
@@ -3077,6 +3517,17 @@
           <t xml:space="preserve">施放雙刀亂舞時使你以及附近 {m} 米內的所有敵人流血：每 {gap} 秒造成最大生命值 {pct}% 傷害，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="X56">
+        <v>5</v>
+      </c>
+      <c r="Z56">
+        <v>0.35</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放雙刀亂舞時使你以及附近 {m} 米內的所有敵人流血：每 {gap} 秒造成最大生命值 {pct}% 傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3129,6 +3580,11 @@
           <t xml:space="preserve">施放雙刀亂舞後 {sec} 秒內，生命值或護盾每減少 1%，獲得 {pct}% 技能傷害提升</t>
         </is>
       </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放雙刀亂舞後 {sec} 秒內，生命值或護盾每減少 1%，獲得 {pct}% 技能傷害提升</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3167,7 +3623,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":3,"secPer":0.3,"gap":0.35}</t>
+          <t xml:space="preserve">{"sec":3,"secPer":0.3}</t>
         </is>
       </c>
       <c r="M58">
@@ -3196,6 +3652,14 @@
           <t xml:space="preserve">ground-cyclone-avatar</t>
         </is>
       </c>
+      <c r="Z58">
+        <v>0.35</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">化身暴風在敵人間穿梭 {sec} 秒：每 {gap} 秒自動施放 1 次雙刀亂舞；期間無法普攻但可施放技能</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3235,6 +3699,11 @@
           <t xml:space="preserve">doomDance</t>
         </is>
       </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每施放 1 次雙刀亂舞就失去當下 {hpPct}% 生命值（不會致死），但雙刀亂舞的傷害提高 {pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3255,7 +3724,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":10,"pctPer":1,"gap":0.5,"dur":6,"maxStacks":20}</t>
+          <t xml:space="preserve">{"pct":10,"pctPer":1,"dur":6,"maxStacks":20}</t>
         </is>
       </c>
       <c r="M60">
@@ -3274,6 +3743,14 @@
           <t xml:space="preserve">flameKagura</t>
         </is>
       </c>
+      <c r="Z60">
+        <v>0.5</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雙刀亂舞附加火焰：每次命中堆疊 1 層【神樂灼焰】，每層每 {gap} 秒造成 {pct}% 火屬性傷害，最多 {maxStacks} 層，持續 {dur} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3313,6 +3790,11 @@
           <t xml:space="preserve">asuraDance</t>
         </is>
       </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">讓你可以同時裝備兩把雙手武器（主手與副手各一把），且雙手武器的詞條效果提升 {pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3375,6 +3857,11 @@
           <t xml:space="preserve">hit-phys</t>
         </is>
       </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被動：受到傷害時有 {chance}% 機率對攻擊者反擊，造成 {pct}% 普攻傷害</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3427,6 +3914,11 @@
           <t xml:space="preserve">格擋時必定對敵人反擊，造成「格擋減傷值 × {mult}%」的普攻傷害</t>
         </is>
       </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">格擋時必定對敵人反擊，造成「格擋減傷值 × {mult}%」的普攻傷害</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3479,6 +3971,11 @@
           <t xml:space="preserve">進一步提升反擊傷害，額外 +{pct}% 反擊普攻傷害</t>
         </is>
       </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進一步提升反擊傷害，額外 +{pct}% 反擊普攻傷害</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3531,6 +4028,11 @@
           <t xml:space="preserve">觸發反擊時，回復自身最大生命 {pct}% 的護盾</t>
         </is>
       </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">觸發反擊時，回復自身最大生命 {pct}% 的護盾</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3588,6 +4090,11 @@
           <t xml:space="preserve">hit-earth</t>
         </is>
       </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">格擋時有 {chance}% 機率造成破甲：防禦 -{def}%，持續 {sec} 秒，最多疊 {max} 層（疊層時重置時間）</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3640,6 +4147,11 @@
           <t xml:space="preserve">反擊時有 {chance}% 機率再追加 {count} 次反擊（追加反擊不會再觸發反擊）</t>
         </is>
       </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">反擊時有 {chance}% 機率再追加 {count} 次反擊（追加反擊不會再觸發反擊）</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3678,7 +4190,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"m":80}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2}</t>
         </is>
       </c>
       <c r="M68">
@@ -3692,6 +4204,14 @@
           <t xml:space="preserve">每次反擊時，額外對 {m} 米內隨機 {count} 個敵人反擊，造成 {pct}% 普攻傷害（不會再觸發反擊）</t>
         </is>
       </c>
+      <c r="X68">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次反擊時，額外對 {m} 米內隨機 {count} 個敵人反擊，造成 {pct}% 普攻傷害（不會再觸發反擊）</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3712,7 +4232,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":10,"pct":400,"pctPer":40,"m":8}</t>
+          <t xml:space="preserve">{"count":10,"pct":400,"pctPer":40}</t>
         </is>
       </c>
       <c r="M69">
@@ -3741,6 +4261,14 @@
           <t xml:space="preserve">holyBody</t>
         </is>
       </c>
+      <c r="X69">
+        <v>8</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每 {count} 次反擊後朝目標射出一顆光彈，對其周圍 {m} 米內的敵人造成 {pct}% 神聖傷害</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3761,7 +4289,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":2000,"pctPer":200,"m":30,"sec":5,"cd":60}</t>
+          <t xml:space="preserve">{"pct":2000,"pctPer":200,"sec":5,"cd":60}</t>
         </is>
       </c>
       <c r="M70">
@@ -3795,6 +4323,14 @@
           <t xml:space="preserve">indomitable</t>
         </is>
       </c>
+      <c r="X70">
+        <v>30</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">死亡時對 {m} 米內的所有敵人造成 {pct}% 地系傷害，並在 {sec} 秒後原地復活繼續戰鬥（不算戰鬥失敗）；冷卻 {cd} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3834,6 +4370,11 @@
           <t xml:space="preserve">warGodBody</t>
         </is>
       </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你在 {sec} 秒內損失的生命百分比，會在接下來 {sec} 秒內的反擊中一併附加到敵人身上</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3891,6 +4432,11 @@
           <t xml:space="preserve">aura-bloodrage</t>
         </is>
       </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻速額外 +{pct}%（乘算，不受攻速上限限制），持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3943,6 +4489,11 @@
           <t xml:space="preserve">狂怒期間爆擊傷害額外 +{pct}%（乘算）</t>
         </is>
       </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂怒期間爆擊傷害額外 +{pct}%（乘算）</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3995,6 +4546,11 @@
           <t xml:space="preserve">狂怒期間總傷害額外 +{pct}%（乘算）</t>
         </is>
       </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂怒期間總傷害額外 +{pct}%（乘算）</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4047,6 +4603,11 @@
           <t xml:space="preserve">狂怒期間基礎連擊數 +{add}，且每擊殺 1 個敵人再 +{kill}（累計上限 +{killMax}；不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂怒期間基礎連擊數 +{add}，且每擊殺 1 個敵人再 +{kill}（累計上限 +{killMax}；不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4099,6 +4660,11 @@
           <t xml:space="preserve">狂怒期間反震傷害提高 {pct}%（乘算，可與其它反震加成疊加）</t>
         </is>
       </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂怒期間反震傷害提高 {pct}%（乘算，可與其它反震加成疊加）</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4137,7 +4703,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"self":1,"m":80}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"self":1}</t>
         </is>
       </c>
       <c r="M77">
@@ -4151,6 +4717,14 @@
           <t xml:space="preserve">狂怒期間傷害額外提高 {pct}%（乘算），但 {m} 米內的敵人每次受傷都會使你損失最大生命 {self}%（直接扣血，無法被護盾吸收）</t>
         </is>
       </c>
+      <c r="X77">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂怒期間傷害額外提高 {pct}%（乘算），但 {m} 米內的敵人每次受傷都會使你損失最大生命 {self}%（直接扣血，無法被護盾吸收）</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4203,6 +4777,11 @@
           <t xml:space="preserve">狂怒期間每擊殺 1 個敵人，持續時間延長 {sec} 秒；且生命值每減少 1%，傷害額外 +{pct}%（乘算，無限疊加），每 1 連擊數使普攻可同時攻擊 1 個敵人（無限疊加）</t>
         </is>
       </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂怒期間每擊殺 1 個敵人，持續時間延長 {sec} 秒；且生命值每減少 1%，傷害額外 +{pct}%（乘算，無限疊加），每 1 連擊數使普攻可同時攻擊 1 個敵人（無限疊加）</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4223,7 +4802,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"m":8}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M79">
@@ -4242,6 +4821,14 @@
           <t xml:space="preserve">slayerAdvent</t>
         </is>
       </c>
+      <c r="X79">
+        <v>8</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂怒期間普攻傷害 +{pct}%，且同時對目標周圍 {m} 米內的所有敵人造成傷害</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4281,6 +4868,11 @@
           <t xml:space="preserve">warGodRoll</t>
         </is>
       </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂怒期間你無法獲得護盾，但每殺死 1 個敵人使你造成的所有傷害 +{pct}%，最多 {maxStacks} 層，持續到你死亡為止</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4301,7 +4893,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":500,"pctPer":50,"sec":1,"secPer":0.1,"gap":10}</t>
+          <t xml:space="preserve">{"pct":500,"pctPer":50,"sec":1,"secPer":0.1}</t>
         </is>
       </c>
       <c r="M81">
@@ -4325,6 +4917,14 @@
           <t xml:space="preserve">asuraFist</t>
         </is>
       </c>
+      <c r="Z81">
+        <v>10</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每 {gap} 秒，你造成的所有傷害 +{pct}%，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4373,7 +4973,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":15,"m":6,"castM":30}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":15}</t>
         </is>
       </c>
       <c r="M82">
@@ -4407,6 +5007,17 @@
           <t xml:space="preserve">hit-fire</t>
         </is>
       </c>
+      <c r="V82">
+        <v>30</v>
+      </c>
+      <c r="X82">
+        <v>6</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">射出一顆火球（射程 {castM} 米），命中時爆炸，對目標及 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4474,6 +5085,11 @@
           <t xml:space="preserve">st-tick-fire</t>
         </is>
       </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被火球擊中的敵人陷入燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4522,7 +5138,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"count":3,"m":20}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"count":3}</t>
         </is>
       </c>
       <c r="M84">
@@ -4551,6 +5167,14 @@
           <t xml:space="preserve">hit-fire-explosion</t>
         </is>
       </c>
+      <c r="X84">
+        <v>20</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火球爆炸後分裂出 {count} 個小火球，射向目標 {m} 米內的敵人，每個造成原始火球 {pct}% 的傷害</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4599,7 +5223,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":0.4,"gapPer":-0.015}</t>
+          <t xml:space="preserve">{}</t>
         </is>
       </c>
       <c r="M85">
@@ -4613,6 +5237,17 @@
           <t xml:space="preserve">燃燒的作用間隔縮短至 {gap} 秒（跳得更快＝總傷更高）</t>
         </is>
       </c>
+      <c r="Z85">
+        <v>0.4</v>
+      </c>
+      <c r="AA85">
+        <v>-0.015</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燃燒的作用間隔縮短至 {gap} 秒（跳得更快＝總傷更高）</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4661,7 +5296,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"m":12}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2}</t>
         </is>
       </c>
       <c r="M86">
@@ -4685,6 +5320,14 @@
           <t xml:space="preserve">hit-fire</t>
         </is>
       </c>
+      <c r="X86">
+        <v>12</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燃燒結束或敵人死亡時爆炸，對我方 {m} 米內的 {count} 個敵人造成該敵人整段燃燒累積傷害 {pct}% 的傷害</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4733,7 +5376,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":0.25,"pctPer":0.025,"sec":4,"m":20}</t>
+          <t xml:space="preserve">{"pct":0.25,"pctPer":0.025,"sec":4}</t>
         </is>
       </c>
       <c r="M87">
@@ -4747,6 +5390,14 @@
           <t xml:space="preserve">我方 {m} 米內每有 1 次燃燒作用，你的火焰傷害 +{pct}%，持續 {sec} 秒（無限疊加，每次疊加時重置時間）</t>
         </is>
       </c>
+      <c r="X87">
+        <v>20</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我方 {m} 米內每有 1 次燃燒作用，你的火焰傷害 +{pct}%，持續 {sec} 秒（無限疊加，每次疊加時重置時間）</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4795,7 +5446,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":15,"castM":20}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3}</t>
         </is>
       </c>
       <c r="M88">
@@ -4829,6 +5480,17 @@
           <t xml:space="preserve">mark-red</t>
         </is>
       </c>
+      <c r="V88">
+        <v>20</v>
+      </c>
+      <c r="X88">
+        <v>15</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改為召喚 {count} 顆巨大火殞石從天而降（射程 {castM} 米），每顆對目標 {m} 米內的敵人造成 {pct}% 火焰傷害，且殞石造成的燃燒傷害為 2 倍（第 2~6 階效果仍然生效）</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4868,6 +5530,11 @@
           <t xml:space="preserve">meteorFall</t>
         </is>
       </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">殞石的體積 +{size}%、造成的傷害 +{pct}%，且每次施放額外連續落下 {count} 顆巨大殞石</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4888,7 +5555,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":60,"gapPer":-3,"normal":90,"elite":40,"boss":20}</t>
+          <t xml:space="preserve">{"normal":90,"elite":40,"boss":20}</t>
         </is>
       </c>
       <c r="M90">
@@ -4927,6 +5594,17 @@
           <t xml:space="preserve">starfallCataclysm</t>
         </is>
       </c>
+      <c r="Z90">
+        <v>60</v>
+      </c>
+      <c r="AA90">
+        <v>-3</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每 {gap} 秒，天空落下一顆超巨型殞石：普通敵人 -{normal}% 生命、菁英 -{elite}% 生命、BOSS -{boss}% 生命</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4976,6 +5654,11 @@
           <t xml:space="preserve">phoenixPrairie</t>
         </is>
       </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">殞石數量 +{count} 顆，且每顆殞石落下時伴隨 {balls} 顆火球一同落下；火球與殞石造成的傷害 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5024,7 +5707,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":60,"pctPer":6,"hits":5,"m":3,"castM":30,"sec":2.5}</t>
+          <t xml:space="preserve">{"pct":60,"pctPer":6,"hits":5,"sec":2.5}</t>
         </is>
       </c>
       <c r="M92">
@@ -5048,6 +5731,17 @@
           <t xml:space="preserve">ground-tornado-fire</t>
         </is>
       </c>
+      <c r="V92">
+        <v>30</v>
+      </c>
+      <c r="X92">
+        <v>3</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在敵人腳下召喚一道火柱（射程 {castM} 米），對目標 {m} 米內的敵人連續造成 {hits} 段傷害，每段 {pct}% 火焰傷害（全程約 {sec} 秒）</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5110,6 +5804,11 @@
           <t xml:space="preserve">火柱的傷害範圍擴大 {pct}%</t>
         </is>
       </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火柱的傷害範圍擴大 {pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5158,7 +5857,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":20,"pctPer":2,"m":20}</t>
+          <t xml:space="preserve">{"count":2,"pct":20,"pctPer":2}</t>
         </is>
       </c>
       <c r="M94">
@@ -5172,6 +5871,14 @@
           <t xml:space="preserve">可同時對 {m} 米內的 {count} 個目標施放火柱，且火焰傷害額外 +{pct}%</t>
         </is>
       </c>
+      <c r="X94">
+        <v>20</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可同時對 {m} 米內的 {count} 個目標施放火柱，且火焰傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5234,6 +5941,11 @@
           <t xml:space="preserve">火柱每次作用時有 {chance}% 機率使敵人燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
         </is>
       </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火柱每次作用時有 {chance}% 機率使敵人燃燒：每 {dotGap} 秒造成技能傷害 {dotPct}% 的火焰傷害，持續 {dotSec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5282,7 +5994,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"m":6}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M96">
@@ -5306,6 +6018,14 @@
           <t xml:space="preserve">hit-fire</t>
         </is>
       </c>
+      <c r="X96">
+        <v>6</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火龍捲或火牆消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5354,7 +6074,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":20}</t>
+          <t xml:space="preserve">{"chance":25,"chancePer":2.5}</t>
         </is>
       </c>
       <c r="M97">
@@ -5368,6 +6088,14 @@
           <t xml:space="preserve">火柱消失後有 {chance}% 機率在我方 {m} 米內的敵人身上重生</t>
         </is>
       </c>
+      <c r="X97">
+        <v>20</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火柱消失後有 {chance}% 機率在我方 {m} 米內的敵人身上重生</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5416,7 +6144,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":3,"hits":8,"pct":100,"pctPer":10,"len":18,"wid":6,"respawn":1}</t>
+          <t xml:space="preserve">{"count":3,"hits":8,"pct":100,"pctPer":10,"respawn":1}</t>
         </is>
       </c>
       <c r="M98">
@@ -5440,6 +6168,17 @@
           <t xml:space="preserve">ground-firewall</t>
         </is>
       </c>
+      <c r="AB98">
+        <v>18</v>
+      </c>
+      <c r="AD98">
+        <v>6</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改為施放 {count} 道火牆（橫向 {len}×{wid} 米），每道造成 {hits} 段 {pct}% 火焰傷害；每道火牆消失後再召喚 1 道（僅能再觸發一次；第 2~6 階效果仍然生效）</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5479,6 +6218,11 @@
           <t xml:space="preserve">infernoTempest</t>
         </is>
       </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次施放的火龍捲（火牆）數量變為 {mult} 倍（小數部分依機率補 1 道）</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5499,7 +6243,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":20,"pct":200,"pctPer":20,"gap":0.5,"sec":6}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"sec":6}</t>
         </is>
       </c>
       <c r="M100">
@@ -5523,6 +6267,17 @@
           <t xml:space="preserve">eternalInferno</t>
         </is>
       </c>
+      <c r="X100">
+        <v>20</v>
+      </c>
+      <c r="Z100">
+        <v>0.5</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火龍捲會在附近 {m} 米內隨機游走，並在移動軌跡上留下火池：每 {gap} 秒造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5543,7 +6298,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":30,"hits":3,"hitsPer":0.3}</t>
+          <t xml:space="preserve">{"hits":3,"hitsPer":0.3}</t>
         </is>
       </c>
       <c r="M101">
@@ -5562,6 +6317,14 @@
           <t xml:space="preserve">dragonDevour</t>
         </is>
       </c>
+      <c r="X101">
+        <v>30</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所有火龍捲改為聚攏在你身邊，並持續將 {m} 米內的敵人拉向你，且火龍捲的傷害段數 +{hits} 段</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5615,7 +6378,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"count":2,"sec":4,"m":8,"rps":0.455,"castM":8}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"count":2,"sec":4,"rps":0.455}</t>
         </is>
       </c>
       <c r="M102">
@@ -5649,6 +6412,17 @@
           <t xml:space="preserve">ground-orbit-ring-fire</t>
         </is>
       </c>
+      <c r="V102">
+        <v>8</v>
+      </c>
+      <c r="X102">
+        <v>8</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">召喚 {count} 團火狩環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5716,6 +6490,11 @@
           <t xml:space="preserve">火狩的體積與環繞範圍同步擴大 {pct}%</t>
         </is>
       </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩的體積與環繞範圍同步擴大 {pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5769,7 +6548,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":20,"chancePer":2,"m":1}</t>
+          <t xml:space="preserve">{"chance":20,"chancePer":2}</t>
         </is>
       </c>
       <c r="M104">
@@ -5783,6 +6562,14 @@
           <t xml:space="preserve">火狩命中時有 {chance}% 機率在其後方 {m} 米處伴生一團火狩（每團只能伴生一次，伴生出的不再伴生）</t>
         </is>
       </c>
+      <c r="X104">
+        <v>1</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩命中時有 {chance}% 機率在其後方 {m} 米處伴生一團火狩（每團只能伴生一次，伴生出的不再伴生）</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5850,6 +6637,11 @@
           <t xml:space="preserve">改為召喚 {count} 團火狩，每團造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改為召喚 {count} 團火狩，每團造成 {pct}% 火焰傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5917,6 +6709,11 @@
           <t xml:space="preserve">火狩的旋轉速度 +{pct}%</t>
         </is>
       </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩的旋轉速度 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5984,6 +6781,11 @@
           <t xml:space="preserve">火狩每擊殺 1 個敵人，全部火狩的持續時間延長 {sec} 秒</t>
         </is>
       </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩每擊殺 1 個敵人，全部火狩的持續時間延長 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6037,7 +6839,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"rings":2,"pct":150,"pctPer":15,"sec":6,"m":6}</t>
+          <t xml:space="preserve">{"rings":2,"pct":150,"pctPer":15,"sec":6}</t>
         </is>
       </c>
       <c r="M108">
@@ -6051,6 +6853,14 @@
           <t xml:space="preserve">改為一次施放 {rings} 道火狩（外圈距內圈 {m} 米、兩道旋轉方向相反），每團造成 {pct}% 火焰傷害、出現時自帶伴生，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="X108">
+        <v>6</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改為一次施放 {rings} 道火狩（外圈距內圈 {m} 米、兩道旋轉方向相反），每團造成 {pct}% 火焰傷害、出現時自帶伴生，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6090,6 +6900,11 @@
           <t xml:space="preserve">solarRing</t>
         </is>
       </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩數量 +{count} 團，體積在 {growSec} 秒內逐漸增大最多 {grow}%，環繞速度 +{spin}%，且造成傷害 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6110,7 +6925,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":10,"countPer":1,"m":40}</t>
+          <t xml:space="preserve">{"count":10,"countPer":1}</t>
         </is>
       </c>
       <c r="M110">
@@ -6129,6 +6944,14 @@
           <t xml:space="preserve">infiniteRing</t>
         </is>
       </c>
+      <c r="X110">
+        <v>40</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火狩改為從自身中心呈螺旋狀向外擴散（在 {m} 米處達到最外圈），並於持續時間內不斷放出火狩，最多額外 +{count} 團</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6149,7 +6972,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":6,"gap":0.5,"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3,"mps":24,"flyM":40}</t>
+          <t xml:space="preserve">{"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3,"mps":24,"flyM":40}</t>
         </is>
       </c>
       <c r="M111">
@@ -6183,6 +7006,17 @@
           <t xml:space="preserve">fireGodDescend</t>
         </is>
       </c>
+      <c r="X111">
+        <v>6</v>
+      </c>
+      <c r="Z111">
+        <v>0.5</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {mps} 米／秒貫穿飛行 {flyM} 米</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6231,7 +7065,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"sec":10,"castM":30}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"sec":10}</t>
         </is>
       </c>
       <c r="M112">
@@ -6250,6 +7084,14 @@
           <t xml:space="preserve">aura-rock-armor</t>
         </is>
       </c>
+      <c r="V112">
+        <v>30</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放岩甲強化自身，獲得最大生命值 {pct}% 的岩甲護盾，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6312,6 +7154,11 @@
           <t xml:space="preserve">進一步強化岩甲，額外獲得最大生命值 {pct}% 的岩甲護盾（與第 1 階累加）</t>
         </is>
       </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進一步強化岩甲，額外獲得最大生命值 {pct}% 的岩甲護盾（與第 1 階累加）</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6379,6 +7226,11 @@
           <t xml:space="preserve">hit-earth</t>
         </is>
       </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">岩甲護盾存在期間，攻擊你的敵人會遭受你最大生命值 {pct}% 的地系傷害（獨立於反震，兩者各自結算）</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6441,6 +7293,11 @@
           <t xml:space="preserve">主動型被動（裝配到技能列即恆時生效）：你獲得的所有護盾效率額外 +{pct}%（乘算）</t>
         </is>
       </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主動型被動（裝配到技能列即恆時生效）：你獲得的所有護盾效率額外 +{pct}%（乘算）</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6503,6 +7360,11 @@
           <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 生命值即獲得最大生命 {pct}% 的護盾</t>
         </is>
       </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 生命值即獲得最大生命 {pct}% 的護盾</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6565,6 +7427,11 @@
           <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 護盾即獲得 {pct}% 傷害增幅（乘算），最多疊 {max} 層，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">岩甲護盾存在期間，你每減少 1% 護盾即獲得 {pct}% 傷害增幅（乘算），最多疊 {max} 層，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6627,6 +7494,11 @@
           <t xml:space="preserve">岩甲護盾存在期間，護盾剩餘量越低則傷害減免越高，護盾歸零時最高額外 +{pct}% 傷害減免（乘算）</t>
         </is>
       </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">岩甲護盾存在期間，護盾剩餘量越低則傷害減免越高，護盾歸零時最高額外 +{pct}% 傷害減免（乘算）</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6647,7 +7519,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":24,"sec":4,"pct":400,"pctPer":40}</t>
+          <t xml:space="preserve">{"sec":4,"pct":400,"pctPer":40}</t>
         </is>
       </c>
       <c r="M119">
@@ -6681,6 +7553,14 @@
           <t xml:space="preserve">superRockArt</t>
         </is>
       </c>
+      <c r="X119">
+        <v>24</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放時將巨岩之力壓縮到極致，使 {m} 米內的敵人石化 {sec} 秒：無法行動，且受到的土系傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6720,6 +7600,11 @@
           <t xml:space="preserve">adamantBody</t>
         </is>
       </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">岩甲護盾存在期間額外獲得 +{red}% 傷害減免（乘算），生命上限與岩甲護盾 +{hp}%，且【岩甲尖刺】的效果額外提高 {spike}%</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6740,7 +7625,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":24,"pct":300,"pctPer":30,"stiff":65,"stiffSec":5}</t>
+          <t xml:space="preserve">{"pct":300,"pctPer":30,"stiff":65,"stiffSec":5}</t>
         </is>
       </c>
       <c r="M121">
@@ -6774,6 +7659,14 @@
           <t xml:space="preserve">gravityField</t>
         </is>
       </c>
+      <c r="X121">
+        <v>24</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放岩甲術時同時扭曲 {m} 米內的重力場，使敵人僵化（移動、攻速與傷害 -{stiff}%，持續 {stiffSec} 秒）；岩甲護盾存在期間你的土系傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6827,7 +7720,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.4,"castM":20,"move":30,"aspd":50}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.4,"move":30,"aspd":50}</t>
         </is>
       </c>
       <c r="M122">
@@ -6846,6 +7739,14 @@
           <t xml:space="preserve">ground-mire</t>
         </is>
       </c>
+      <c r="V122">
+        <v>20</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在敵人腳下召喚一片 12×12 米的沼澤（射程 {castM} 米），沼澤中的敵人陷入緩速（移動速度 -{move}%、攻速 -{aspd}%），持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6913,6 +7814,11 @@
           <t xml:space="preserve">受泥沼緩速影響的敵人，受到的傷害提高 {pct}%</t>
         </is>
       </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受泥沼緩速影響的敵人，受到的傷害提高 {pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6985,6 +7891,11 @@
           <t xml:space="preserve">ground-mire-poison</t>
         </is>
       </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沼澤持續放出毒氣：沼澤中的敵人每 {dotGap} 秒受到魔法攻擊 {dotPct}% 的毒性傷害</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7038,7 +7949,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":40}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M125">
@@ -7052,6 +7963,14 @@
           <t xml:space="preserve">沼澤結束時傳染給 {m} 米內較近的敵人，最多傳染 {add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="X125">
+        <v>40</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沼澤結束時傳染給 {m} 米內較近的敵人，最多傳染 {add} 次（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7119,6 +8038,11 @@
           <t xml:space="preserve">沼澤持續時間提高至 {sec} 秒，且在 {growSec} 秒內逐步擴大，最大擴增 {pct}%</t>
         </is>
       </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沼澤持續時間提高至 {sec} 秒，且在 {growSec} 秒內逐步擴大，最大擴增 {pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7186,6 +8110,11 @@
           <t xml:space="preserve">緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%（與第 2 階累加）</t>
         </is>
       </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">緩速強化為移動速度 -{move}%、攻速 -{aspd}%，且受影響目標受到的傷害再提高 {pct}%（與第 2 階累加）</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7258,6 +8187,11 @@
           <t xml:space="preserve">ground-mire-lava</t>
         </is>
       </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沼澤轉變為岩漿：持續時間提高至 {sec} 秒、範圍再擴增 {pct}%（與第 5 階累加），其中的目標每 {dotGap} 秒額外受到魔法攻擊 {dotPct}% 的火焰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7278,7 +8212,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":0.35,"pct":200,"pctPer":20,"amp":100,"ampPer":10,"sec":8}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"amp":100,"ampPer":10,"sec":8}</t>
         </is>
       </c>
       <c r="M129">
@@ -7297,6 +8231,14 @@
           <t xml:space="preserve">plagueMire</t>
         </is>
       </c>
+      <c r="Z129">
+        <v>0.35</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沼澤範圍內的敵人染上【瘟疫】：每 {gap} 秒受到魔法攻擊 {pct}% 的毒性傷害，且受到的毒性傷害額外 +{amp}%；離開沼澤後仍持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7317,7 +8259,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":2,"hits":8,"pct":100,"pctPer":10,"sec":8,"m":6}</t>
+          <t xml:space="preserve">{"hits":8,"pct":100,"pctPer":10,"sec":8}</t>
         </is>
       </c>
       <c r="M130">
@@ -7346,6 +8288,17 @@
           <t xml:space="preserve">abyssInferno</t>
         </is>
       </c>
+      <c r="X130">
+        <v>6</v>
+      </c>
+      <c r="Z130">
+        <v>2</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">熔岩沼每 {gap} 秒對範圍內的敵人噴出 1 道火龍捲（半徑 {m} 米、{hits} 段、每段 {pct}% 火焰傷害），並將命中的敵人屬性改變為火屬性，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7385,6 +8338,11 @@
           <t xml:space="preserve">netherMire</t>
         </is>
       </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沼澤範圍內生命值 {hpPct}% 以下的敵人，每次受到傷害有 {chance}% 機率直接被斬殺，且該機率每次受傷再累加 {add}%</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7447,6 +8405,11 @@
           <t xml:space="preserve">主動型被動：自身傷害減免額外 +{pct}%、生命上限額外 +{hp}%（皆為乘算）</t>
         </is>
       </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主動型被動：自身傷害減免額外 +{pct}%、生命上限額外 +{hp}%（皆為乘算）</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7509,6 +8472,11 @@
           <t xml:space="preserve">全屬性傷害額外 +{pct}%（與所有屬性增傷效果為額外的乘法計算）</t>
         </is>
       </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">全屬性傷害額外 +{pct}%（與所有屬性增傷效果為額外的乘法計算）</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7571,6 +8539,11 @@
           <t xml:space="preserve">生命回復額外 +{pct}%、吸血額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
         </is>
       </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生命回復額外 +{pct}%、吸血額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7633,6 +8606,11 @@
           <t xml:space="preserve">法力回復額外 +{pct}%、吸魔額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
         </is>
       </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">法力回復額外 +{pct}%、吸魔額外 +{drain}%（皆與原屬性為額外的乘法計算）</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7695,6 +8673,11 @@
           <t xml:space="preserve">你的生命減少時，其中 {pct}% 改由消耗法力承擔，承擔的法力降低 {manaRed}%（法力不足時只轉換付得起的部分，餘額仍扣生命）</t>
         </is>
       </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你的生命減少時，其中 {pct}% 改由消耗法力承擔，承擔的法力降低 {manaRed}%（法力不足時只轉換付得起的部分，餘額仍扣生命）</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7743,7 +8726,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":1,"pctPer":0.1,"m":20,"count":1}</t>
+          <t xml:space="preserve">{"pct":1,"pctPer":0.1,"count":1}</t>
         </is>
       </c>
       <c r="M137">
@@ -7767,6 +8750,14 @@
           <t xml:space="preserve">hit-light</t>
         </is>
       </c>
+      <c r="X137">
+        <v>20</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你每消耗 1% 生命或護盾，{m} 米內的 {count} 個敵人同步損失 {pct}% 最大生命</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7839,6 +8830,11 @@
           <t xml:space="preserve">hit-light</t>
         </is>
       </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">死亡時原地復活並回復 {pct}% 生命，復活後 {sec} 秒無敵；此招自身冷卻 {cd} 秒（顯示於技能格）</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7878,6 +8874,11 @@
           <t xml:space="preserve">hallOfRadiance</t>
         </is>
       </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生命與法力回復額外 +{pct}%（乘算），且溢出的生命與法力以 {conv}% 轉為你的生命護盾</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7927,6 +8928,11 @@
           <t xml:space="preserve">worldRebirth</t>
         </is>
       </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被你殺死的普通與菁英敵人有 {chance}% 機率（上限 100%）以 {hp}% 生命重生（同一個敵人只會重生一次）</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7966,6 +8972,11 @@
           <t xml:space="preserve">fateReversal</t>
         </is>
       </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【天地共生】的冷卻結束後可累積復活次數，最多累積 {max} 次（小數四捨五入取整）</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8014,7 +9025,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":4,"m":30,"castM":30}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":15,"count":4}</t>
         </is>
       </c>
       <c r="M142">
@@ -8043,6 +9054,17 @@
           <t xml:space="preserve">hit-lightning</t>
         </is>
       </c>
+      <c r="V142">
+        <v>30</v>
+      </c>
+      <c r="X142">
+        <v>30</v>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">丟出一道閃電鏈（射程 {castM} 米），在最多 {count} 個目標間彈射（每段彈射範圍 {m} 米），每擊造成 {pct}% 雷電傷害</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8105,6 +9127,11 @@
           <t xml:space="preserve">強化閃電威力，閃電鏈傷害進一步 +{pct}% 雷電傷害</t>
         </is>
       </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">強化閃電威力，閃電鏈傷害進一步 +{pct}% 雷電傷害</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8167,6 +9194,11 @@
           <t xml:space="preserve">被閃電鏈擊中的敵人額外再受到 {add} 次雷電傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被閃電鏈擊中的敵人額外再受到 {add} 次雷電傷害（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8229,6 +9261,11 @@
           <t xml:space="preserve">閃電鏈的彈射數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">閃電鏈的彈射數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8277,7 +9314,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":25,"pctPer":2.5,"count":1,"m":6}</t>
+          <t xml:space="preserve">{"pct":25,"pctPer":2.5,"count":1}</t>
         </is>
       </c>
       <c r="M146">
@@ -8296,6 +9333,14 @@
           <t xml:space="preserve">hit-lightning</t>
         </is>
       </c>
+      <c r="X146">
+        <v>6</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">閃電鏈每次彈射時，額外對 {m} 米內的 {count} 個敵人造成閃電鏈 {pct}% 的雷電傷害</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8363,6 +9408,11 @@
           <t xml:space="preserve">aura-lightning-relay</t>
         </is>
       </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">閃電鏈傷害額外 +{pct}% 雷電傷害；沒有其它彈射目標時可用自身當中繼點繼續彈射（彈到自身不消耗彈射數）</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8425,6 +9475,11 @@
           <t xml:space="preserve">同時發射 {count} 道閃電鏈，彈射數額外 +{add} 次，且閃電傷害額外 +{pct}%；每次彈射有 {chance}% 機率生成 1 條閃電鏈</t>
         </is>
       </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同時發射 {count} 道閃電鏈，彈射數額外 +{add} 次，且閃電傷害額外 +{pct}%；每次彈射有 {chance}% 機率生成 1 條閃電鏈</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8445,7 +9500,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":1,"gapPer":-0.05,"sec":3,"secPer":0.3}</t>
+          <t xml:space="preserve">{"sec":3,"secPer":0.3}</t>
         </is>
       </c>
       <c r="M149">
@@ -8464,6 +9519,17 @@
           <t xml:space="preserve">skyThunderArray</t>
         </is>
       </c>
+      <c r="Z149">
+        <v>1</v>
+      </c>
+      <c r="AA149">
+        <v>-0.05</v>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放連鎖閃電後每 {gap} 秒自動再施放 1 次，持續 {sec} 秒（自動施放不扣法力、不進冷卻）</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8484,7 +9550,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":30,"pct":2,"pctPer":0.2,"maxStacks":100}</t>
+          <t xml:space="preserve">{"pct":2,"pctPer":0.2,"maxStacks":100}</t>
         </is>
       </c>
       <c r="M150">
@@ -8518,6 +9584,14 @@
           <t xml:space="preserve">eternalSuperconductor</t>
         </is>
       </c>
+      <c r="X150">
+        <v>30</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外射出 1 道無限彈射的閃電鏈：在自身與 {m} 米內的任意敵人之間往返彈射，每經過自身 1 次使你的雷電傷害 +{pct}%，最多 {maxStacks} 層（持續到你死亡為止）</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8538,7 +9612,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":0.35,"count":3,"m":30,"r":12,"pct":200,"pctPer":20,"sec":6}</t>
+          <t xml:space="preserve">{"count":3,"r":12,"pct":200,"pctPer":20,"sec":6}</t>
         </is>
       </c>
       <c r="M151">
@@ -8567,6 +9641,17 @@
           <t xml:space="preserve">flyingThunderGod</t>
         </is>
       </c>
+      <c r="X151">
+        <v>30</v>
+      </c>
+      <c r="Z151">
+        <v>0.35</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放後每 {gap} 秒放出 {count} 道閃電，分別打向 {m} 米內最遠的 {count} 個敵人，各對命中處 {r} 米內的所有敵人造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8615,7 +9700,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"count":2,"gap":0.2,"castM":30}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"count":2}</t>
         </is>
       </c>
       <c r="M152">
@@ -8644,6 +9729,17 @@
           <t xml:space="preserve">hit-thunder-purple</t>
         </is>
       </c>
+      <c r="V152">
+        <v>30</v>
+      </c>
+      <c r="Z152">
+        <v>0.2</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對 {castM} 米內的 {count} 個目標降下落雷（每道間隔 {gap} 秒），每道造成 {pct}% 雷電傷害</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8706,6 +9802,11 @@
           <t xml:space="preserve">攻擊目標額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊目標額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8768,6 +9869,11 @@
           <t xml:space="preserve">對每個目標的攻擊次數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對每個目標的攻擊次數額外 +{add} 次（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8830,6 +9936,11 @@
           <t xml:space="preserve">進一步強化落雷傷害，額外 +{pct}% 雷電傷害</t>
         </is>
       </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進一步強化落雷傷害，額外 +{pct}% 雷電傷害</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8878,7 +9989,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":1.5,"secPer":0.15,"count":2,"m":6}</t>
+          <t xml:space="preserve">{"sec":1.5,"secPer":0.15,"count":2}</t>
         </is>
       </c>
       <c r="M156">
@@ -8892,6 +10003,14 @@
           <t xml:space="preserve">落雷落地時產生衝擊波，震暈目標本身與 {m} 米內共 {count} 個敵人 {sec} 秒</t>
         </is>
       </c>
+      <c r="X156">
+        <v>6</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷落地時產生衝擊波，震暈目標本身與 {m} 米內共 {count} 個敵人 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8954,6 +10073,11 @@
           <t xml:space="preserve">每道落雷結束後有 {chance}% 機率再產生 1 道落雷（同一次施放最多再生 {max} 道）</t>
         </is>
       </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每道落雷結束後有 {chance}% 機率再產生 1 道落雷（同一次施放最多再生 {max} 道）</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9002,7 +10126,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"mult":2,"pct":50,"pctPer":5,"m":6}</t>
+          <t xml:space="preserve">{"mult":2,"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M158">
@@ -9016,6 +10140,14 @@
           <t xml:space="preserve">落雷擊中時對目標 {m} 米內的所有敵人造成傷害；攻擊次數與目標數量 ×{mult}，且命中暈眩中的敵人時傷害額外 +{pct}%（與原傷害乘算）</t>
         </is>
       </c>
+      <c r="X158">
+        <v>6</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">落雷擊中時對目標 {m} 米內的所有敵人造成傷害；攻擊次數與目標數量 ×{mult}，且命中暈眩中的敵人時傷害額外 +{pct}%（與原傷害乘算）</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9036,7 +10168,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"countPer":0.2,"pct":300,"pctPer":30,"wid":3,"mps":30}</t>
+          <t xml:space="preserve">{"count":2,"countPer":0.2,"pct":300,"pctPer":30,"mps":30}</t>
         </is>
       </c>
       <c r="M159">
@@ -9065,6 +10197,14 @@
           <t xml:space="preserve">thunderMatrix</t>
         </is>
       </c>
+      <c r="AD159">
+        <v>3</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{mps} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9085,7 +10225,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":30,"gap":0.35,"pct":400,"pctPer":40}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40}</t>
         </is>
       </c>
       <c r="M160">
@@ -9114,6 +10254,17 @@
           <t xml:space="preserve">heavenTribulation</t>
         </is>
       </c>
+      <c r="X160">
+        <v>30</v>
+      </c>
+      <c r="Z160">
+        <v>0.35</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外召喚 1 道永久持續的天劫雷電：每 {gap} 秒追擊 {m} 米內生命值最低的敵人，造成 {pct}% 雷電傷害</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9134,7 +10285,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":1,"gapPer":-0.05,"sec":3,"secPer":0.3}</t>
+          <t xml:space="preserve">{"sec":3,"secPer":0.3}</t>
         </is>
       </c>
       <c r="M161">
@@ -9153,6 +10304,17 @@
           <t xml:space="preserve">eternalThunderPrison</t>
         </is>
       </c>
+      <c r="Z161">
+        <v>1</v>
+      </c>
+      <c r="AA161">
+        <v>-0.05</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放落雷術後每 {gap} 秒自動再施放 1 次，持續 {sec} 秒（自動施放不扣法力、不進冷卻）</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9206,7 +10368,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"gap":0.35,"sec":2,"m":3,"speed":6,"castM":30}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5,"count":2,"sec":2,"speed":6}</t>
         </is>
       </c>
       <c r="M162">
@@ -9235,6 +10397,20 @@
           <t xml:space="preserve">ground-thunder-orb</t>
         </is>
       </c>
+      <c r="V162">
+        <v>30</v>
+      </c>
+      <c r="X162">
+        <v>3</v>
+      </c>
+      <c r="Z162">
+        <v>0.35</v>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">召喚 {count} 個雷球緩慢飛向目標（射程 {castM} 米、飛行速度 {speed} 米/秒），途中每 {gap} 秒對半徑 {m} 米內的所有敵人造成 {pct}% 雷電傷害，抵達後停留 {sec} 秒才消散</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9302,6 +10478,11 @@
           <t xml:space="preserve">雷球的體積擴大 {pct}%</t>
         </is>
       </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球的體積擴大 {pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9369,6 +10550,11 @@
           <t xml:space="preserve">雷球數量額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷球數量額外 +{add} 個（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9422,7 +10608,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":100,"pctPer":10,"sec":6,"m":8,"rps":0.7}</t>
+          <t xml:space="preserve">{"count":2,"pct":100,"pctPer":10,"sec":6,"rps":0.7}</t>
         </is>
       </c>
       <c r="M165">
@@ -9451,6 +10637,14 @@
           <t xml:space="preserve">ground-orbit-ring-lightning</t>
         </is>
       </c>
+      <c r="X165">
+        <v>8</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外召喚 {count} 個電球環繞自身（環繞半徑 {m} 米、每秒 {rps} 圈），碰到敵人即命中一次，每次造成 {pct}% 雷電傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9518,6 +10712,11 @@
           <t xml:space="preserve">所有雷球與電球的雷電傷害額外 +{pct}%</t>
         </is>
       </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所有雷球與電球的雷電傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9595,6 +10794,11 @@
           <t xml:space="preserve">ground-thunder-orb</t>
         </is>
       </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環體電球命中時有 {chance}% 機率在該處生成一個靜止雷球，持續 {sec} 秒（每次作用只判定一次機率）</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9648,7 +10852,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":2,"pct":300,"pctPer":30,"m":15,"sec":3}</t>
+          <t xml:space="preserve">{"count":2,"pct":300,"pctPer":30,"sec":3}</t>
         </is>
       </c>
       <c r="M168">
@@ -9682,6 +10886,14 @@
           <t xml:space="preserve">mark-blue</t>
         </is>
       </c>
+      <c r="X168">
+        <v>15</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外召喚 {count} 個巨大雷球從天而降，各對 {m} 米內的敵人造成 {pct}% 雷電傷害，並以衝擊波擊暈 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9721,6 +10933,11 @@
           <t xml:space="preserve">criticalThunderbolt</t>
         </is>
       </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【伴生雷球】改為一次生成 {count} 顆、觸發機率 ×{chanceMult}，且所有雷球與電球的傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9741,7 +10958,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":0.15,"bounces":4,"m":12,"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"chance":15,"chancePer":0.15,"bounces":4,"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M170">
@@ -9765,6 +10982,14 @@
           <t xml:space="preserve">thunderBurst</t>
         </is>
       </c>
+      <c r="X170">
+        <v>12</v>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次被雷球命中的敵人有 {chance}% 機率觸發 1 顆小型雷球，在附近 {m} 米範圍內彈射 {bounces} 次，每次造成 {pct}% 雷電傷害</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9785,7 +11010,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"scale":50,"gap":1,"pct":200,"pctPer":20}</t>
+          <t xml:space="preserve">{"scale":50,"pct":200,"pctPer":20}</t>
         </is>
       </c>
       <c r="M171">
@@ -9804,6 +11029,14 @@
           <t xml:space="preserve">thunderfallShatter</t>
         </is>
       </c>
+      <c r="Z171">
+        <v>1</v>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【雷殞天落】的雷殞石體積增大 {scale}%、傷害額外 +{pct}%，並額外每 {gap} 秒不斷再降下 1 顆</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9852,7 +11085,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"deg":15,"castM":30,"speed":45}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":2,"speed":45}</t>
         </is>
       </c>
       <c r="M172">
@@ -9881,6 +11114,17 @@
           <t xml:space="preserve">hit-ice</t>
         </is>
       </c>
+      <c r="V172">
+        <v>30</v>
+      </c>
+      <c r="AF172">
+        <v>15</v>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">朝前方射出 {count} 支寒冰箭，每支箭夾角 {deg} 度（射程 {castM} 米、飛行速度 {speed} 米／秒），每支對 1 個敵人造成 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9948,6 +11192,11 @@
           <t xml:space="preserve">st-tick-ice</t>
         </is>
       </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被寒冰箭擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成寒冰箭傷害 {frostPct}% 的寒冰傷害，每層使移動與攻速下降，疊滿層數時凍結</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10010,6 +11259,11 @@
           <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
         </is>
       </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進一步強化寒冰箭，額外 +{pct}% 寒冰傷害（與第 1 階累加）</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10058,7 +11312,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":10,"mPer":2}</t>
+          <t xml:space="preserve">{}</t>
         </is>
       </c>
       <c r="M175">
@@ -10082,6 +11336,17 @@
           <t xml:space="preserve">hit-ice</t>
         </is>
       </c>
+      <c r="X175">
+        <v>10</v>
+      </c>
+      <c r="Y175">
+        <v>2</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒冰箭改為貫穿攻擊，貫穿路徑上的所有敵人，貫穿長度 {m} 米（不足以打到主目標時自動延長到主目標）</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10149,6 +11414,11 @@
           <t xml:space="preserve">ground-homing-ice-shard</t>
         </is>
       </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">射出的寒冰箭數量額外 +{add} 支（不足 1 支的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10211,6 +11481,11 @@
           <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒冰箭射中帶寒霜狀態的敵人時，立即再疊 {stacks} 層寒霜，並造成該敵人寒霜剩餘的全部寒冰傷害（不足 1 層的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10259,7 +11534,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"m":6,"chaseM":30,"bodyM":1.5,"gap":0.1,"waves":3,"waveGap":0.3}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"sec":6,"chaseM":30,"bodyM":1.5,"waves":3,"waveGap":0.3}</t>
         </is>
       </c>
       <c r="M178">
@@ -10283,6 +11558,17 @@
           <t xml:space="preserve">hit-ice</t>
         </is>
       </c>
+      <c r="X178">
+        <v>6</v>
+      </c>
+      <c r="Z178">
+        <v>0.1</v>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒冰爆裂箭連射 {waves} 波，每波間隔 {waveGap} 秒；寒冰箭變為追蹤冰箭，在 {chaseM} 米內來回穿梭追擊敵人 {sec} 秒（碰到才算一次命中）；敵人的凍結結束時產生冰爆，對其周圍 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10322,6 +11608,11 @@
           <t xml:space="preserve">absoluteZeroBurst</t>
         </is>
       </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【寒冰爆裂箭】改為每 {waveGap} 秒連射 {waves} 波，且寒冰箭傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10361,6 +11652,11 @@
           <t xml:space="preserve">infiniteIceRift</t>
         </is>
       </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒冰箭每造成 1 次傷害就使寒冰箭的冷卻時間 -{sec} 秒，且每次發射的寒冰箭數量額外 +{count} 支（不足 1 支的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10381,7 +11677,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"waves":10,"gap":0.35,"m":30,"pct":200,"pctPer":20}</t>
+          <t xml:space="preserve">{"waves":10,"pct":200,"pctPer":20}</t>
         </is>
       </c>
       <c r="M181">
@@ -10410,6 +11706,17 @@
           <t xml:space="preserve">tearsOfIce</t>
         </is>
       </c>
+      <c r="X181">
+        <v>30</v>
+      </c>
+      <c r="Z181">
+        <v>0.35</v>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放寒冰箭時同時召喚 {waves} 波寒冰箭雨從天射下（每波間隔 {gap} 秒），每波對我方 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10458,7 +11765,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"arcM":8}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"arcM":8}</t>
         </is>
       </c>
       <c r="M182">
@@ -10487,6 +11794,14 @@
           <t xml:space="preserve">hit-ice</t>
         </is>
       </c>
+      <c r="V182">
+        <v>30</v>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">丟出一顆水彈砸向敵人（射程 {castM} 米、拋物線離地最高 {arcM} 米），造成 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10549,6 +11864,11 @@
           <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被水流彈擊中的敵人強制轉變為寒冰屬性，且受到的寒冰傷害 +{pct}%，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10611,6 +11931,11 @@
           <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
         </is>
       </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被水流彈擊中的敵人附加 {stacks} 層寒霜狀態：每跳造成水流彈傷害 {frostPct}% 的寒冰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10659,7 +11984,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":8,"bounce":2,"bouncePer":0.2}</t>
+          <t xml:space="preserve">{"bounce":2,"bouncePer":0.2}</t>
         </is>
       </c>
       <c r="M185">
@@ -10688,6 +12013,14 @@
           <t xml:space="preserve">hit-ice</t>
         </is>
       </c>
+      <c r="X185">
+        <v>8</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水流彈改為範圍攻擊，對目標 {m} 米內的所有敵人造成傷害，並再彈射 {bounce} 次（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10736,7 +12069,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"m":10,"count":1}</t>
+          <t xml:space="preserve">{"chance":25,"chancePer":2.5,"count":1}</t>
         </is>
       </c>
       <c r="M186">
@@ -10760,6 +12093,14 @@
           <t xml:space="preserve">hit-ice</t>
         </is>
       </c>
+      <c r="X186">
+        <v>10</v>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒霜狀態每次作用時有 {chance}% 機率擴散至目標 {m} 米內的 {count} 個敵人</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10822,6 +12163,11 @@
           <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">朝隨機目標額外丟出 {add} 顆水流彈（不足 1 顆的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10870,7 +12216,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"m":5,"side":10,"frozen":2,"gap":0.35}</t>
+          <t xml:space="preserve">{"count":4,"hits":6,"pct":100,"pctPer":10,"side":10,"frozen":2}</t>
         </is>
       </c>
       <c r="M188">
@@ -10889,6 +12235,17 @@
           <t xml:space="preserve">ground-tornado-water</t>
         </is>
       </c>
+      <c r="X188">
+        <v>5</v>
+      </c>
+      <c r="Z188">
+        <v>0.35</v>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外在我方 {side}×{side} 米正方形的四個頂點召喚 {count} 道水龍捲（傷害半徑 {m} 米），每道造成連續 {hits} 段 {pct}% 寒冰傷害，且對凍結中的敵人傷害為 {frozen} 倍</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10909,7 +12266,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":20,"atkRed":50,"vuln":100,"vulnPer":10,"sec":6}</t>
+          <t xml:space="preserve">{"atkRed":50,"vuln":100,"vulnPer":10,"sec":6}</t>
         </is>
       </c>
       <c r="M189">
@@ -10933,6 +12290,14 @@
           <t xml:space="preserve">waterPrisonFall</t>
         </is>
       </c>
+      <c r="X189">
+        <v>20</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放水流彈時在周圍 {m} 米圍起一圈水牢獄：擋下由圈外射進來的遠程攻擊，圈內的敵人攻擊力 -{atkRed}%、受到的傷害 +{vuln}%，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10953,7 +12318,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"need":10,"m":20,"hits":20,"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"need":10,"hits":20,"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M190">
@@ -10977,6 +12342,14 @@
           <t xml:space="preserve">ragingTide</t>
         </is>
       </c>
+      <c r="X190">
+        <v>20</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">場上同時有 {need} 道水龍捲時，在它們的中央再生成 1 道巨大水龍捲，對 {m} 米內的所有敵人造成連續 {hits} 段 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10997,7 +12370,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":30,"gap":0.35,"stacks":10,"stacksPer":1}</t>
+          <t xml:space="preserve">{"stacks":10,"stacksPer":1}</t>
         </is>
       </c>
       <c r="M191">
@@ -11026,6 +12399,17 @@
           <t xml:space="preserve">abyssBurial</t>
         </is>
       </c>
+      <c r="X191">
+        <v>30</v>
+      </c>
+      <c r="Z191">
+        <v>0.35</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在周圍 {m} 米展開一道永久的水之領域：每 {gap} 秒對領域內的敵人施加寒霜狀態，且領域內的敵人可額外再疊 {stacks} 層寒霜</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11074,7 +12458,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":150,"pctPer":5,"m":12,"castM":12,"stacks":2,"frostPct":50}</t>
+          <t xml:space="preserve">{"pct":150,"pctPer":5,"stacks":2,"frostPct":50}</t>
         </is>
       </c>
       <c r="M192">
@@ -11103,6 +12487,17 @@
           <t xml:space="preserve">hit-ice</t>
         </is>
       </c>
+      <c r="V192">
+        <v>12</v>
+      </c>
+      <c r="X192">
+        <v>12</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對周圍 {m} 米內的敵人釋放冰霜新星，造成 {pct}% 寒冰傷害並附加 {stacks} 層寒霜狀態（寒霜每跳造成新星傷害 {frostPct}% 的寒冰傷害）</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11151,7 +12546,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":13,"mPer":0.6,"castM":13,"castMPer":0.6,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M193">
@@ -11165,6 +12560,23 @@
           <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
         </is>
       </c>
+      <c r="V193">
+        <v>13</v>
+      </c>
+      <c r="W193">
+        <v>0.6</v>
+      </c>
+      <c r="X193">
+        <v>13</v>
+      </c>
+      <c r="Y193">
+        <v>0.6</v>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冰霜新星的範圍擴展至 {m} 米，且寒冰傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11232,6 +12644,11 @@
           <t xml:space="preserve">hit-ice</t>
         </is>
       </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放冰霜新星後的 6 秒內，攻擊你的敵人有 25% 機率被附加 {stacks} 層寒霜狀態</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11304,6 +12721,11 @@
           <t xml:space="preserve">hit-ice</t>
         </is>
       </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所有來源的寒霜狀態傷害提高 {dmgPct}%，且持續時間增加 {durPct}%</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11352,7 +12774,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":1,"addPer":0.1,"m":3}</t>
+          <t xml:space="preserve">{"add":1,"addPer":0.1}</t>
         </is>
       </c>
       <c r="M196">
@@ -11366,6 +12788,14 @@
           <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="X196">
+        <v>3</v>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冰霜新星的施放次數額外 +{add} 次，且每次釋放的範圍再 +{m} 米（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11428,6 +12858,11 @@
           <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
         </is>
       </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">帶寒霜狀態的敵人死亡時有 {chance}% 機率再釋放 1 次冰霜新星</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11476,7 +12911,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":100,"pctPer":10,"gap":0.4,"sec":8,"side":24}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10,"sec":8,"side":24}</t>
         </is>
       </c>
       <c r="M198">
@@ -11495,6 +12930,14 @@
           <t xml:space="preserve">ground-blizzard</t>
         </is>
       </c>
+      <c r="Z198">
+        <v>0.4</v>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外召喚 1 道暴風雪籠罩天空，對 {side}×{side} 米範圍內的敵人每 {gap} 秒造成 {pct}% 寒冰傷害，暴風雪跟隨我方移動，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11515,7 +12958,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":1,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M199">
@@ -11534,6 +12977,14 @@
           <t xml:space="preserve">infiniteNova</t>
         </is>
       </c>
+      <c r="Z199">
+        <v>1</v>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每隔 {gap} 秒自動施放 1 次冰霜新星（不扣法力、不進冷卻），且冰霜新星傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11554,7 +13005,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":8,"gap":0.4,"pct":200,"pctPer":20}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20}</t>
         </is>
       </c>
       <c r="M200">
@@ -11583,6 +13034,17 @@
           <t xml:space="preserve">crystalResonance</t>
         </is>
       </c>
+      <c r="X200">
+        <v>8</v>
+      </c>
+      <c r="Z200">
+        <v>0.4</v>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">凍結中的敵人形成冰晶共鳴：每 {gap} 秒對相距 {m} 米內的其他凍結敵人造成 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11603,7 +13065,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"scale":50,"gap":1,"min":2,"max":8,"hits":4,"pct":200,"pctPer":20,"m":8}</t>
+          <t xml:space="preserve">{"scale":50,"min":2,"max":8,"hits":4,"pct":200,"pctPer":20}</t>
         </is>
       </c>
       <c r="M201">
@@ -11627,6 +13089,17 @@
           <t xml:space="preserve">iceKingDomain</t>
         </is>
       </c>
+      <c r="X201">
+        <v>8</v>
+      </c>
+      <c r="Z201">
+        <v>1</v>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風雪的範圍擴大 {scale}%，且每 {gap} 秒在範圍內隨機 {min}～{max} 個目標的地面昇起冰錐，每根冰錐對周圍 {m} 米內的敵人造成連續 {hits} 段 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11680,7 +13153,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":200,"pctPer":20,"castM":30,"m":80,"speed":18}</t>
+          <t xml:space="preserve">{"pct":200,"pctPer":20,"speed":18}</t>
         </is>
       </c>
       <c r="M202">
@@ -11709,6 +13182,17 @@
           <t xml:space="preserve">hit-wind</t>
         </is>
       </c>
+      <c r="V202">
+        <v>30</v>
+      </c>
+      <c r="X202">
+        <v>80</v>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">朝前方射出一道弧形風刃（射程 {castM} 米、飛行速度 {speed} 米/秒），貫穿飛行路徑 {m} 米上的所有敵人，各造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11776,6 +13260,11 @@
           <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
         </is>
       </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風刃的體積 +{size}%（判定範圍與特效同步放大）</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11843,6 +13332,11 @@
           <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
         </is>
       </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同時向前方與後方各射出一道風刃，且風刃傷害額外 +{pct}%（與第 1 階累加）</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11896,7 +13390,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"deg":30,"lenM":3,"widthM":6}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3,"lenM":3,"widthM":6}</t>
         </is>
       </c>
       <c r="M205">
@@ -11920,6 +13414,14 @@
           <t xml:space="preserve">hit-wind</t>
         </is>
       </c>
+      <c r="AF205">
+        <v>30</v>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風刃射出時同時朝其一側 {deg} 度發射 1 道小型風刃（體積 {lenM}×{widthM} 米、同樣貫穿全場），造成原風刃 {pct}% 的傷害</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11973,7 +13475,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30,"gap":0.1}</t>
+          <t xml:space="preserve">{"sec":4,"secPer":0.3,"chaseM":30}</t>
         </is>
       </c>
       <c r="M206">
@@ -11997,6 +13499,14 @@
           <t xml:space="preserve">ground-homing-wind-crescent</t>
         </is>
       </c>
+      <c r="Z206">
+        <v>0.1</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小型風刃不再向前射出，改為在 {chaseM} 米內隨機追擊敵人 {sec} 秒，對路徑上的所有敵人造成傷害（碰到才算一次命中）</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12050,7 +13560,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"move":60,"gap":0.6,"gapPer":-0.03,"pct":50,"m":6}</t>
+          <t xml:space="preserve">{"move":60,"pct":50}</t>
         </is>
       </c>
       <c r="M207">
@@ -12074,6 +13584,20 @@
           <t xml:space="preserve">hit-wind</t>
         </is>
       </c>
+      <c r="X207">
+        <v>6</v>
+      </c>
+      <c r="Z207">
+        <v>0.6</v>
+      </c>
+      <c r="AA207">
+        <v>-0.03</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風刃命中的敵人移動速度 -{move}%；風刃並在飛行途中每 {gap} 秒對半徑 {m} 米內的敵人造成風刃 {pct}% 的傷害（不含小型風刃）</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12127,7 +13651,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":2,"directions":4,"gap":0.2}</t>
+          <t xml:space="preserve">{"pct":40,"pctPer":40,"count":2,"directions":4}</t>
         </is>
       </c>
       <c r="M208">
@@ -12141,6 +13665,14 @@
           <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
         </is>
       </c>
+      <c r="Z208">
+        <v>0.2</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改為朝前後左右 {directions} 個方向各連續射出 {count} 道風刃（每道間隔 {gap} 秒，小型風刃同步發射），且風刃傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12190,6 +13722,11 @@
           <t xml:space="preserve">stormMyriad</t>
         </is>
       </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大型風刃改為在 {chaseM} 米內持續追擊敵人 {sec} 秒，【暴風真空刃】每個方向再多射出 {add} 道風刃，且風刃傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12239,6 +13776,11 @@
           <t xml:space="preserve">stormMountain</t>
         </is>
       </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【暴風真空刃】改為把該次所有大型與小型風刃融合，朝 {directions} 個方向各射出 1 道體積 +{scale}% 的巨型風刃，每道傷害為所融合風刃總和的 {pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12278,6 +13820,11 @@
           <t xml:space="preserve">skyCollapse</t>
         </is>
       </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風刃改為被動技能：受到攻擊時有 {chance}% 機率朝攻擊者射出一道風刃，且其傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12326,7 +13873,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3,"m":6,"castM":6}</t>
+          <t xml:space="preserve">{"pct":250,"pctPer":25,"count":3}</t>
         </is>
       </c>
       <c r="M212">
@@ -12355,6 +13902,17 @@
           <t xml:space="preserve">hit-wind</t>
         </is>
       </c>
+      <c r="V212">
+        <v>6</v>
+      </c>
+      <c r="X212">
+        <v>6</v>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">朝前方 {m} 米範圍內的 {count} 名敵人揮出一道真空斬擊，造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12417,6 +13975,11 @@
           <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">真空斬會爆發出震波，額外造成 {hits} 次傷害（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12465,7 +14028,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4,"gap":0.5}</t>
+          <t xml:space="preserve">{"cutPct":50,"cutPctPer":5,"move":80,"hit":50,"sec":4}</t>
         </is>
       </c>
       <c r="M214">
@@ -12479,6 +14042,14 @@
           <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
         </is>
       </c>
+      <c r="Z214">
+        <v>0.5</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被真空斬擊中的敵人附加風切狀態：移動速度 -{move}%、命中率 -{hit}%，且每 {gap} 秒受到真空斬傷害 {cutPct}% 的風系傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12527,7 +14098,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":30,"pctPer":3,"m":6}</t>
+          <t xml:space="preserve">{"pct":30,"pctPer":3}</t>
         </is>
       </c>
       <c r="M215">
@@ -12551,6 +14122,14 @@
           <t xml:space="preserve">hit-wind</t>
         </is>
       </c>
+      <c r="X215">
+        <v>6</v>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">真空斬改為對自身周圍 {m} 米內的所有敵人造成傷害，且造成的傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12599,7 +14178,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"add":2,"addPer":0.2,"m":6}</t>
+          <t xml:space="preserve">{"add":2,"addPer":0.2}</t>
         </is>
       </c>
       <c r="M216">
@@ -12613,6 +14192,14 @@
           <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
         </is>
       </c>
+      <c r="X216">
+        <v>6</v>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迴旋斬額外連續施展 {add} 次，每次的範圍再擴大 {m} 米（不足 1 次的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12675,6 +14262,11 @@
           <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
         </is>
       </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切狀態可堆疊至 {stacks} 層，每多 1 層使風切每跳額外造成 {pct}% 的風系傷害</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12723,7 +14315,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"m":6,"growM":4,"bodyM":6,"rps":1}</t>
+          <t xml:space="preserve">{"pct":400,"pctPer":40,"count":4,"sec":6,"growM":4,"bodyM":6,"rps":1}</t>
         </is>
       </c>
       <c r="M218">
@@ -12757,6 +14349,14 @@
           <t xml:space="preserve">ground-orbit-ring-wind</t>
         </is>
       </c>
+      <c r="X218">
+        <v>6</v>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">額外斬出 {count} 道虛空斬擊：以自身為中心從半徑 {m} 米起每秒擴大 {growM} 米、{count} 道皆順時針繞行 {rps} 圈，對碰到的敵人造成 {pct}% 風系傷害，持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12777,7 +14377,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"pct":100,"sec":3,"gap":0.25,"grow":2}</t>
+          <t xml:space="preserve">{"chance":15,"chancePer":1.5,"pct":100,"sec":3,"grow":2}</t>
         </is>
       </c>
       <c r="M219">
@@ -12806,6 +14406,14 @@
           <t xml:space="preserve">vacuumOmen</t>
         </is>
       </c>
+      <c r="Z219">
+        <v>0.25</v>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">真空斬命中時有 {chance}% 機率在該處留下一道靜止的真空斬：持續 {sec} 秒、半徑隨時間擴大為 {grow} 倍，對碰到的敵人造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12826,7 +14434,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":2,"pct":100,"pctPer":10}</t>
+          <t xml:space="preserve">{"pct":100,"pctPer":10}</t>
         </is>
       </c>
       <c r="M220">
@@ -12845,6 +14453,14 @@
           <t xml:space="preserve">voidAnnihilation</t>
         </is>
       </c>
+      <c r="Z220">
+        <v>2</v>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每 {gap} 秒自動斬出 1 道【虛空斬】，且虛空斬傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12865,7 +14481,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"m":12,"pct":50,"pctPer":5}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M221">
@@ -12884,6 +14500,14 @@
           <t xml:space="preserve">spacetimeCollapse</t>
         </is>
       </c>
+      <c r="X221">
+        <v>12</v>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【虛空斬】不再向外擴展，改為全部固定在你周圍 {m} 米環繞，且持續時間額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12932,7 +14556,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8,"gap":0.5,"castM":30}</t>
+          <t xml:space="preserve">{"shield":1,"shieldPer":1,"red":10,"redPer":1,"sec":8}</t>
         </is>
       </c>
       <c r="M222">
@@ -12951,6 +14575,17 @@
           <t xml:space="preserve">ground-storm-barrier</t>
         </is>
       </c>
+      <c r="V222">
+        <v>30</v>
+      </c>
+      <c r="Z222">
+        <v>0.5</v>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對自身施加暴風屏障：每 {gap} 秒獲得最大生命 {shield}% 的護盾，且傷害減免 +{red}%（乘算，只與風系類型的減免相加總），持續 {sec} 秒</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12999,7 +14634,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"pct":50,"pctPer":5,"m":8}</t>
+          <t xml:space="preserve">{"pct":50,"pctPer":5}</t>
         </is>
       </c>
       <c r="M223">
@@ -13023,6 +14658,14 @@
           <t xml:space="preserve">ground-storm-rip</t>
         </is>
       </c>
+      <c r="X223">
+        <v>8</v>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對自身半徑 {m} 米內的敵人造成 {pct}% 風系傷害</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13090,6 +14733,11 @@
           <t xml:space="preserve">hit-wind</t>
         </is>
       </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時，對周圍的 {count} 個敵人附加風切狀態（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13162,6 +14810,11 @@
           <t xml:space="preserve">hit-wind</t>
         </is>
       </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障作用中受到傷害時，有 {chance}% 機率射出 1 道貫穿風刃（【風刃】第 1 階的效果，不含其後續進化）</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13210,7 +14863,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"count":1,"countPer":0.1,"m":10}</t>
+          <t xml:space="preserve">{"count":1,"countPer":0.1}</t>
         </is>
       </c>
       <c r="M226">
@@ -13234,6 +14887,14 @@
           <t xml:space="preserve">hit-wind</t>
         </is>
       </c>
+      <c r="X226">
+        <v>10</v>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">風切狀態結束後擴散至 {m} 米內的 {count} 個敵人（不足 1 個的部分以機率觸發）</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13296,6 +14957,11 @@
           <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
         </is>
       </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴風屏障每次作用時額外獲得最大生命 {shield}% 的護盾（與第 1 階相加）</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13363,6 +15029,11 @@
           <t xml:space="preserve">ground-storm-god</t>
         </is>
       </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放暴風屏障時同時召喚風暴之神附體：{sec} 秒內傷害減免 +{red}%，且自身的風系傷害額外 ×(1+{pct}%)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13402,6 +15073,11 @@
           <t xml:space="preserve">valgrForce</t>
         </is>
       </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">召喚風之神祇降臨：【暴風神體】的持續時間 +{sec}%、傷害減免再 +{red}%，且自身風系傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13422,7 +15098,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"gap":2,"min":1,"max":3,"maxPer":0.3,"pct":400,"pctPer":40,"m":8}</t>
+          <t xml:space="preserve">{"min":1,"max":3,"maxPer":0.3,"pct":400,"pctPer":40}</t>
         </is>
       </c>
       <c r="M230">
@@ -13461,6 +15137,17 @@
           <t xml:space="preserve">skyfallStars</t>
         </is>
       </c>
+      <c r="X230">
+        <v>8</v>
+      </c>
+      <c r="Z230">
+        <v>2</v>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每 {gap} 秒從天上落下 {min}～{max} 個召喚星體（巨大風刃／雷殞石／火殞石隨機，不足 1 個的部分以機率觸發），每個對落點 {m} 米內的敵人造成 {pct}% 傷害</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13520,8 +15207,14 @@
           <t xml:space="preserve">myriadPhenomena</t>
         </is>
       </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放暴風屏障時同時打出【暴風真空刃】與【虛空斬】，且這兩者的傷害額外 +{pct}%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AH231"/>
 </worksheet>
 </file>
 
@@ -13726,7 +15419,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">各階的數值參數。命名慣例：&lt;鍵&gt;＝不含升級效果的底值、&lt;鍵&gt;Per＝每級增量，值＝底值＋增量×等級；</t>
+          <t xml:space="preserve">其餘未拆成獨立欄的數值參數；距離、間隔、長寬與角度請改右側中文欄。命名慣例：&lt;鍵&gt;＝不含升級效果的底值、&lt;鍵&gt;Per＝每級增量，值＝底值＋增量×等級；</t>
         </is>
       </c>
     </row>
@@ -13890,7 +15583,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">遊戲內顯示的說明文字；{鍵} 會代入目前等級的計算值（鍵名同「效果參數(JSON)」）。</t>
+          <t xml:space="preserve">遊戲內顯示的說明文字；{鍵} 會代入目前等級的計算值（鍵名同各獨立數值欄對應的 fx 鍵或「效果參數(JSON)」）。</t>
         </is>
       </c>
     </row>
@@ -13951,6 +15644,146 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">獨立距離與間隔欄（優先於舊 JSON 同名鍵）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只改有值的欄位；留白代表本階未設定此參數，不代表 0 米或 0 秒。未接線技能勿自行填入新參數。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放距離：玩家離主目標多遠可開始施放。高階明列時覆寫低階；一般技能未設時沿用近戰距離。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作用距離：對應 m；可能是傷害半徑、彈射搜尋距離或額外延伸長度，請搭配右側「作用方式與距離用途」閱讀，不能一概視為半徑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">疾風斬：第一階施放距離及間隔控制前六階；第四階作用距離是以主目標為中心的擴散搜尋半徑；第七階為月牙傷害半徑及獨立施放距離，仍共用第一階間隔。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每段或每跳間隔：對應 gap，具體是連斬、持續傷害或週期觸發，依本階作用說明；不是技能冷卻。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每級增減可填負數，例如間隔每級減少；所有數值為底值，實際值＝底值＋每級增量×等級。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">獨立欄位會回寫原 fx 鍵；效果參數(JSON)不再重複存這些鍵。舊版沒有新欄的 CSV 仍可讀取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放距離（米） → fx.castM</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施放距離每級增加（米） → fx.castMPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作用距離（米；用途見說明） → fx.m</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作用距離每級增加（米） → fx.mPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每段或每跳間隔（秒） → fx.gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">間隔每級增減（秒） → fx.gapPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矩形長度（米） → fx.len</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矩形長度每級增加（米） → fx.lenPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矩形寬度（米） → fx.wid</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">矩形寬度每級增加（米） → fx.widPer</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">扇形角度（度） → fx.deg</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">角度每級增減（度） → fx.degPer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -6737,8 +6737,10 @@
       <c r="X62" s="1">
         <v>5</v>
       </c>
-      <c r="Z62" t="s">
-        <v>274</v>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>proj-counter-ripple</t>
+        </is>
       </c>
       <c r="AB62" t="s">
         <v>40</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -12689,8 +12689,11 @@
       <c r="X188" s="1">
         <v>40</v>
       </c>
-      <c r="AC188" t="s">
-        <v>739</v>
+      <c r="AC188"/>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>field-water-tornado</t>
+        </is>
       </c>
       <c r="AE188" t="s">
         <v>740</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -7568,14 +7568,20 @@
       <c r="Y82" t="s">
         <v>352</v>
       </c>
-      <c r="Z82" t="s">
-        <v>353</v>
-      </c>
-      <c r="AA82" t="s">
-        <v>354</v>
-      </c>
-      <c r="AB82" t="s">
-        <v>355</v>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>hit-fireball-rupture</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>proj-fireball-ember</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AE82" t="s">
         <v>356</v>
@@ -7677,14 +7683,20 @@
       <c r="X84" s="1">
         <v>80</v>
       </c>
-      <c r="Z84" t="s">
-        <v>353</v>
-      </c>
-      <c r="AA84" t="s">
-        <v>354</v>
-      </c>
-      <c r="AB84" t="s">
-        <v>363</v>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>hit-fireball-rupture</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>proj-fireball-ember</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>hit-fireball-rupture</t>
+        </is>
       </c>
       <c r="AE84" t="s">
         <v>364</v>
@@ -7898,14 +7910,20 @@
       <c r="X88" s="1">
         <v>320</v>
       </c>
-      <c r="Z88" t="s">
-        <v>374</v>
-      </c>
-      <c r="AA88" t="s">
-        <v>375</v>
-      </c>
-      <c r="AB88" t="s">
-        <v>363</v>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>burst-meteor-inferno</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>proj-meteor-inferno</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>burst-meteor-inferno</t>
+        </is>
       </c>
       <c r="AC88" t="s">
         <v>376</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -9069,8 +9069,10 @@
       <c r="X112" s="1">
         <v>40</v>
       </c>
-      <c r="AC112" t="s">
-        <v>305</v>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>aura-rockarmor-stone</t>
+        </is>
       </c>
       <c r="AE112" t="s">
         <v>472</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8702,6 +8702,11 @@
       <c r="X104" s="1">
         <v>80</v>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>orb-firehunt-companion</t>
+        </is>
+      </c>
       <c r="AE104" t="s">
         <v>440</v>
       </c>
@@ -8711,11 +8716,15 @@
       <c r="AG104">
         <v>1.5</v>
       </c>
-      <c r="AH104" t="s">
-        <v>441</v>
-      </c>
-      <c r="AI104" t="s">
-        <v>441</v>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>火狩命中時有 {chance}% 機率在母體外緣後方留 {m} 米間隙伴生一團火狩（每團只能伴生一次，伴生出的不再伴生）</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>火狩命中時有 {chance}% 機率在母體外緣後方留 {m} 米間隙伴生一團火狩（每團只能伴生一次，伴生出的不再伴生）</t>
+        </is>
       </c>
     </row>
     <row r="105" spans="1:35" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -9368,6 +9368,11 @@
       <c r="X118" s="1">
         <v>40</v>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>aura-earth-reversal</t>
+        </is>
+      </c>
       <c r="AE118" t="s">
         <v>487</v>
       </c>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -9546,8 +9546,10 @@
       <c r="X122" s="1">
         <v>40</v>
       </c>
-      <c r="AC122" t="s">
-        <v>224</v>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>ground-mire-earth</t>
+        </is>
       </c>
       <c r="AE122" t="s">
         <v>508</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -9651,8 +9651,10 @@
       <c r="X124" s="1">
         <v>40</v>
       </c>
-      <c r="AC124" t="s">
-        <v>229</v>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>ground-mire-venom</t>
+        </is>
       </c>
       <c r="AE124" t="s">
         <v>512</v>
@@ -9857,8 +9859,10 @@
       <c r="X128" s="1">
         <v>40</v>
       </c>
-      <c r="AC128" t="s">
-        <v>421</v>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>ground-mire-magma</t>
+        </is>
       </c>
       <c r="AE128" t="s">
         <v>524</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -10037,6 +10037,11 @@
       <c r="AI132" t="s">
         <v>542</v>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>aura-earthguard-hexagram</t>
+        </is>
+      </c>
     </row>
     <row r="133" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
@@ -10131,6 +10136,11 @@
       <c r="AI134" t="s">
         <v>547</v>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>aura-earthguard-life</t>
+        </is>
+      </c>
     </row>
     <row r="135" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
@@ -10178,6 +10188,11 @@
       <c r="AI135" t="s">
         <v>549</v>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>aura-earthguard-mana</t>
+        </is>
+      </c>
     </row>
     <row r="136" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
@@ -10333,6 +10348,11 @@
       </c>
       <c r="AI138" t="s">
         <v>560</v>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>aura-earthguard-symbiosis</t>
+        </is>
       </c>
     </row>
     <row r="139" spans="1:35" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -10497,8 +10497,10 @@
       <c r="Y142" t="s">
         <v>352</v>
       </c>
-      <c r="AA142" t="s">
-        <v>578</v>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AB142" t="s">
         <v>153</v>
@@ -10517,6 +10519,11 @@
       </c>
       <c r="AI142" t="s">
         <v>580</v>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>bolt-chain-bluewhite</t>
+        </is>
       </c>
     </row>
     <row r="143" spans="1:35" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -10522,7 +10522,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>bolt-chain-bluewhite</t>
+          <t>bolt-chain-travel-bluewhite</t>
         </is>
       </c>
     </row>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -10763,11 +10763,15 @@
       <c r="AG147">
         <v>1.5</v>
       </c>
-      <c r="AH147" t="s">
-        <v>592</v>
-      </c>
-      <c r="AI147" t="s">
-        <v>592</v>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>閃電鏈傷害額外 +{pct}% 雷電傷害；沒有可彈射的敵人時立即終止</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>閃電鏈傷害額外 +{pct}% 雷電傷害；沒有可彈射的敵人時立即終止</t>
+        </is>
       </c>
     </row>
     <row r="148" spans="1:35" x14ac:dyDescent="0.25">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -11008,11 +11008,15 @@
       <c r="Y152" t="s">
         <v>350</v>
       </c>
-      <c r="Z152" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB152" t="s">
-        <v>184</v>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>bolt-thunderstrike-bluewhite</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>hit-thunderstrike-bluewhite</t>
+        </is>
       </c>
       <c r="AE152" t="s">
         <v>606</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -11818,14 +11818,20 @@
       <c r="X168" s="1">
         <v>40</v>
       </c>
-      <c r="Z168" t="s">
-        <v>372</v>
-      </c>
-      <c r="AA168" t="s">
-        <v>657</v>
-      </c>
-      <c r="AB168" t="s">
-        <v>153</v>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>hit-thunderfall-impact</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>proj-thunderfall-sky</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>hit-thunderfall-impact</t>
+        </is>
       </c>
       <c r="AC168" t="s">
         <v>658</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -4111,7 +4111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI231"/>
+  <dimension ref="A1:AJ231"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="2" customWidth="1"/>
@@ -4130,6 +4130,7 @@
     <col min="32" max="33" width="15" customWidth="1"/>
     <col min="34" max="34" width="55" customWidth="1"/>
     <col min="35" max="35" width="90" customWidth="1"/>
+    <col min="36" max="36" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -4238,6 +4239,11 @@
       <c r="AI1" t="s">
         <v>33</v>
       </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>飛行子彈速度（米／秒）</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -4288,6 +4294,9 @@
       <c r="AI2" t="s">
         <v>42</v>
       </c>
+      <c r="AJ2">
+        <v>48</v>
+      </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -4737,6 +4746,9 @@
       <c r="AI12" t="s">
         <v>85</v>
       </c>
+      <c r="AJ12">
+        <v>24</v>
+      </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -5159,6 +5171,9 @@
       <c r="AI22" t="s">
         <v>121</v>
       </c>
+      <c r="AJ22">
+        <v>50.4</v>
+      </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
@@ -7682,6 +7697,9 @@
       <c r="AI82" t="s">
         <v>355</v>
       </c>
+      <c r="AJ82" s="1">
+        <v>65.52</v>
+      </c>
     </row>
     <row r="83" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
@@ -8015,6 +8033,9 @@
       <c r="AI88" t="s">
         <v>376</v>
       </c>
+      <c r="AJ88" s="1">
+        <v>36</v>
+      </c>
     </row>
     <row r="89" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
@@ -9090,8 +9111,10 @@
       <c r="AC111" t="s">
         <v>462</v>
       </c>
-      <c r="AE111" t="s">
-        <v>463</v>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>{"pct":300,"pctPer":30,"orbs":3,"orbsPer":0.3,"flyM":40}</t>
+        </is>
       </c>
       <c r="AF111">
         <v>10000000</v>
@@ -9099,11 +9122,18 @@
       <c r="AG111">
         <v>1.5</v>
       </c>
-      <c r="AH111" t="s">
-        <v>464</v>
-      </c>
-      <c r="AI111" t="s">
-        <v>464</v>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {speed} 米／秒貫穿飛行 {flyM} 米</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>你的身體被火焰包裹：每 {gap} 秒對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害；普攻同時朝目標射出 {orbs} 顆火狩星環，以 {speed} 米／秒貫穿飛行 {flyM} 米</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>24</v>
       </c>
     </row>
     <row r="112" spans="1:35" x14ac:dyDescent="0.3">
@@ -11347,8 +11377,10 @@
       <c r="AC159" t="s">
         <v>626</v>
       </c>
-      <c r="AE159" t="s">
-        <v>627</v>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>{"count":2,"countPer":0.2,"pct":300,"pctPer":30}</t>
+        </is>
       </c>
       <c r="AF159">
         <v>10000000</v>
@@ -11356,11 +11388,18 @@
       <c r="AG159">
         <v>1.5</v>
       </c>
-      <c r="AH159" t="s">
-        <v>628</v>
-      </c>
-      <c r="AI159" t="s">
-        <v>628</v>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{speed} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>施放落雷術時同時召喚橫向與直向各 {count} 道雷幕橫掃全場（每道寬 {wid} 米、{speed} 米／秒，相鄰兩道由反方向交錯掃過），對掃過的所有敵人各造成 1 次 {pct}% 雷電傷害</t>
+        </is>
+      </c>
+      <c r="AJ159">
+        <v>30</v>
       </c>
     </row>
     <row r="160" spans="1:35" x14ac:dyDescent="0.3">
@@ -11497,8 +11536,10 @@
       <c r="AD162" t="s">
         <v>971</v>
       </c>
-      <c r="AE162" t="s">
-        <v>640</v>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>{"pct":50,"pctPer":5,"count":2,"sec":2}</t>
+        </is>
       </c>
       <c r="AF162">
         <v>100000</v>
@@ -11511,6 +11552,9 @@
       </c>
       <c r="AI162" t="s">
         <v>641</v>
+      </c>
+      <c r="AJ162" s="1">
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:35" x14ac:dyDescent="0.3">
@@ -12003,8 +12047,10 @@
       <c r="AB172" t="s">
         <v>678</v>
       </c>
-      <c r="AE172" t="s">
-        <v>679</v>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>{"pct":250,"pctPer":25,"count":2}</t>
+        </is>
       </c>
       <c r="AF172">
         <v>100000</v>
@@ -12017,6 +12063,9 @@
       </c>
       <c r="AI172" t="s">
         <v>680</v>
+      </c>
+      <c r="AJ172" s="1">
+        <v>58.5</v>
       </c>
     </row>
     <row r="173" spans="1:35" x14ac:dyDescent="0.3">
@@ -12497,6 +12546,9 @@
       <c r="AI182" t="s">
         <v>717</v>
       </c>
+      <c r="AJ182" s="1">
+        <v>50.4</v>
+      </c>
     </row>
     <row r="183" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
@@ -13473,8 +13525,10 @@
       <c r="AB202" t="s">
         <v>791</v>
       </c>
-      <c r="AE202" t="s">
-        <v>792</v>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>{"pct":200,"pctPer":20}</t>
+        </is>
       </c>
       <c r="AF202">
         <v>100000</v>
@@ -13487,6 +13541,9 @@
       </c>
       <c r="AI202" t="s">
         <v>793</v>
+      </c>
+      <c r="AJ202" s="1">
+        <v>18</v>
       </c>
     </row>
     <row r="203" spans="1:35" x14ac:dyDescent="0.3">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -12041,11 +12041,15 @@
       <c r="Y172" t="s">
         <v>350</v>
       </c>
-      <c r="AA172" t="s">
-        <v>677</v>
-      </c>
-      <c r="AB172" t="s">
-        <v>678</v>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>proj-icearrow-frost</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>hit-icearrow-shatter</t>
+        </is>
       </c>
       <c r="AE172" t="inlineStr">
         <is>
@@ -12202,11 +12206,15 @@
       <c r="X175" s="1">
         <v>40</v>
       </c>
-      <c r="AA175" t="s">
-        <v>677</v>
-      </c>
-      <c r="AB175" t="s">
-        <v>678</v>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>proj-icearrow-frost</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>hit-icearrow-shatter</t>
+        </is>
       </c>
       <c r="AE175" t="s">
         <v>62</v>
@@ -12255,8 +12263,10 @@
       <c r="X176" s="1">
         <v>40</v>
       </c>
-      <c r="AC176" t="s">
-        <v>690</v>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>ground-icearrow-frost</t>
+        </is>
       </c>
       <c r="AE176" t="s">
         <v>512</v>
@@ -12466,11 +12476,15 @@
       <c r="X181" s="1">
         <v>300</v>
       </c>
-      <c r="AA181" t="s">
-        <v>677</v>
-      </c>
-      <c r="AB181" t="s">
-        <v>678</v>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>proj-icearrow-frost</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>hit-icearrow-shatter</t>
+        </is>
       </c>
       <c r="AE181" t="s">
         <v>710</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -12368,8 +12368,10 @@
       <c r="X178" s="1">
         <v>40</v>
       </c>
-      <c r="Z178" t="s">
-        <v>697</v>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>burst-icearrow-crystal</t>
+        </is>
       </c>
       <c r="AB178" t="s">
         <v>678</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -12541,11 +12541,15 @@
       <c r="Y182" t="s">
         <v>350</v>
       </c>
-      <c r="AA182" t="s">
-        <v>715</v>
-      </c>
-      <c r="AB182" t="s">
-        <v>678</v>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>proj-waterball-flow</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>hit-waterball-splash</t>
+        </is>
       </c>
       <c r="AE182" t="s">
         <v>716</v>
@@ -12562,8 +12566,8 @@
       <c r="AI182" t="s">
         <v>717</v>
       </c>
-      <c r="AJ182" s="1">
-        <v>50.4</v>
+      <c r="AJ182" s="1" t="n">
+        <v>57.96</v>
       </c>
     </row>
     <row r="183" spans="1:35" x14ac:dyDescent="0.3">
@@ -12697,11 +12701,15 @@
       <c r="Z185" t="s">
         <v>725</v>
       </c>
-      <c r="AA185" t="s">
-        <v>715</v>
-      </c>
-      <c r="AB185" t="s">
-        <v>678</v>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>proj-waterball-flow</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>hit-waterball-splash</t>
+        </is>
       </c>
       <c r="AE185" t="s">
         <v>726</v>

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -12526,6 +12526,9 @@
       <c r="I182" s="1">
         <v>30</v>
       </c>
+      <c r="K182" t="n">
+        <v>6</v>
+      </c>
       <c r="U182" s="1" t="s">
         <v>348</v>
       </c>
@@ -12560,11 +12563,15 @@
       <c r="AG182">
         <v>1.5</v>
       </c>
-      <c r="AH182" t="s">
-        <v>717</v>
-      </c>
-      <c r="AI182" t="s">
-        <v>717</v>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>朝敵人起飛時的座標拋出水彈（射程 {castM} 米、弧高 {arcM} 米），途中不追蹤；落地時對落點半徑 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>朝敵人起飛時的座標拋出水彈（射程 {castM} 米、弧高 {arcM} 米），途中不追蹤；落地時對落點半徑 {m} 米內的所有敵人造成 {pct}% 寒冰傷害</t>
+        </is>
       </c>
       <c r="AJ182" s="1" t="n">
         <v>57.96</v>
@@ -12683,8 +12690,8 @@
       <c r="F185" t="s">
         <v>326</v>
       </c>
-      <c r="K185" s="1">
-        <v>8</v>
+      <c r="K185" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="U185" s="1" t="s">
         <v>348</v>
@@ -12720,11 +12727,15 @@
       <c r="AG185">
         <v>1.5</v>
       </c>
-      <c r="AH185" t="s">
-        <v>727</v>
-      </c>
-      <c r="AI185" t="s">
-        <v>727</v>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>水流彈落地後再彈射 {bounce} 次（不足 1 次以機率觸發）；每次起飛重新鎖定敵人當下座標，途中不追蹤，落地造成半徑 {m} 米範圍傷害</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>水流彈落地後再彈射 {bounce} 次（不足 1 次以機率觸發）；每次起飛重新鎖定敵人當下座標，途中不追蹤，落地造成半徑 {m} 米範圍傷害</t>
+        </is>
       </c>
     </row>
     <row r="186" spans="1:35" x14ac:dyDescent="0.3">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8412,11 +8412,15 @@
       <c r="AG96">
         <v>1.5</v>
       </c>
-      <c r="AH96" t="s">
-        <v>405</v>
-      </c>
-      <c r="AI96" t="s">
-        <v>405</v>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火龍捲消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火龍捲消失時，對周圍 {m} 米內的敵人造成 {pct}% 火焰傷害</t>
+        </is>
       </c>
     </row>
     <row r="97" spans="1:35" x14ac:dyDescent="0.3">
@@ -8476,8 +8480,10 @@
       <c r="B98" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>409</v>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無限火龍</t>
+        </is>
       </c>
       <c r="D98" s="1" t="s">
         <v>393</v>
@@ -8488,12 +8494,8 @@
       <c r="F98" t="s">
         <v>139</v>
       </c>
-      <c r="O98" s="1">
-        <v>18</v>
-      </c>
-      <c r="Q98" s="1">
-        <v>6</v>
-      </c>
+      <c r="O98" s="1"/>
+      <c r="Q98" s="1"/>
       <c r="U98" s="1" t="s">
         <v>348</v>
       </c>
@@ -8509,11 +8511,16 @@
       <c r="AB98" t="s">
         <v>353</v>
       </c>
-      <c r="AC98" t="s">
-        <v>410</v>
-      </c>
-      <c r="AE98" t="s">
-        <v>411</v>
+      <c r="AC98"/>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire-tornado-infinite</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"hitsAdd":5,"pct":100,"pctPer":10,"respawn":1}</t>
+        </is>
       </c>
       <c r="AF98">
         <v>5000000</v>
@@ -8521,11 +8528,18 @@
       <c r="AG98">
         <v>1.5</v>
       </c>
-      <c r="AH98" t="s">
-        <v>412</v>
-      </c>
-      <c r="AI98" t="s">
-        <v>412</v>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火龍捲傷害段數 +{hitsAdd} 段，每段 {pct}% 火焰傷害；以每秒 {speed} 米持續隨機追敵，單一敵人時在其附近移動；消散後再召喚 {respawn} 次（再召喚不可連鎖），火焰轉為暗紅色</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火龍捲傷害段數 +{hitsAdd} 段，每段 {pct}% 火焰傷害；以每秒 {speed} 米持續隨機追敵，單一敵人時在其附近移動；消散後再召喚 {respawn} 次（再召喚不可連鎖），火焰轉為暗紅色</t>
+        </is>
+      </c>
+      <c r="AJ98">
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:35" x14ac:dyDescent="0.3">
@@ -8553,11 +8567,15 @@
       <c r="AG99">
         <v>1.5</v>
       </c>
-      <c r="AH99" t="s">
-        <v>416</v>
-      </c>
-      <c r="AI99" t="s">
-        <v>416</v>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次施放的火龍捲數量變為 {mult} 倍（小數部分依機率補 1 道）</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每次施放的火龍捲數量變為 {mult} 倍（小數部分依機率補 1 道）</t>
+        </is>
       </c>
     </row>
     <row r="100" spans="1:35" x14ac:dyDescent="0.3">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -8203,8 +8203,10 @@
       <c r="AD92" t="s">
         <v>980</v>
       </c>
-      <c r="AE92" t="s">
-        <v>395</v>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"pct":60,"pctPer":6,"hits":6,"sec":3}</t>
+        </is>
       </c>
       <c r="AF92">
         <v>100000</v>
@@ -8519,7 +8521,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"hitsAdd":5,"pct":100,"pctPer":10,"respawn":1}</t>
+          <t xml:space="preserve">{"hitsAdd":6,"pct":100,"pctPer":10,"respawn":1,"sec":6}</t>
         </is>
       </c>
       <c r="AF98">
@@ -8530,12 +8532,12 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲傷害段數 +{hitsAdd} 段，每段 {pct}% 火焰傷害；以每秒 {speed} 米持續隨機追敵，單一敵人時在其附近移動；消散後再召喚 {respawn} 次（再召喚不可連鎖），火焰轉為暗紅色</t>
+          <t xml:space="preserve">火龍捲持續 {sec} 秒，傷害段數 +{hitsAdd} 段，每段 {pct}% 火焰傷害；以每秒 {speed} 米持續隨機追敵，單一敵人時在其附近移動；消散後再召喚 {respawn} 次（再召喚不可連鎖），火焰轉為暗紅色</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t xml:space="preserve">火龍捲傷害段數 +{hitsAdd} 段，每段 {pct}% 火焰傷害；以每秒 {speed} 米持續隨機追敵，單一敵人時在其附近移動；消散後再召喚 {respawn} 次（再召喚不可連鎖），火焰轉為暗紅色</t>
+          <t xml:space="preserve">火龍捲持續 {sec} 秒，傷害段數 +{hitsAdd} 段，每段 {pct}% 火焰傷害；以每秒 {speed} 米持續隨機追敵，單一敵人時在其附近移動；消散後再召喚 {respawn} 次（再召喚不可連鎖），火焰轉為暗紅色</t>
         </is>
       </c>
       <c r="AJ98">

--- a/config/Excel/Skills2.xlsx
+++ b/config/Excel/Skills2.xlsx
@@ -4110,7 +4110,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ231"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14138,6 +14138,11 @@
       <c r="X213" s="1">
         <v>40</v>
       </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>burst-vacuum-shockwave</t>
+        </is>
+      </c>
       <c r="AE213" t="s">
         <v>833</v>
       </c>
